--- a/data/monthly_report_2026-03.xlsx
+++ b/data/monthly_report_2026-03.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2개 받았는데 300% 개꿀딱[7] / 돈 될만한 종목은 개미한테 매수 기회조차 ...[2] / 미친 한국주식시장..이런거나 고쳐라 / 미국1조3천억+중국5천억. 총 1조8천억 기술이...</t>
+          <t>2개 받았는데 300% 개꿀딱[7] / 미친 한국주식시장..이런거나 고쳐라 / 알지노믹 공모가 22,500원.최고가23만.....[1] / 조단위 기술수출+96.5%보호예수.품절주됨...[1]</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>상한가, 300%, 유통물량</t>
+          <t>상한가, ..., 유통물량</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -569,7 +569,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'title': '미친 한국주식시장..이런거나 고쳐라', 'date': '2026.03.20 11:46', 'views': '142', 'likes': '20', 'dislikes': '2', 'link': '/item/board_read.naver?code=493280&amp;nid=415473520&amp;page=5', 'score': 742}, {'title': '2개 받았는데 300% 개꿀딱[7]', 'date': '2026.03.20 09:22', 'views': '1203', 'likes': '18', 'dislikes': '5', 'link': '/item/board_read.naver?code=493280&amp;nid=415443396&amp;page=8', 'score': 1743}, {'title': '월욜 상한가 135200원이 종가', 'date': '2026.03.20 15:15', 'views': '127', 'likes': '15', 'dislikes': '4', 'link': '/item/board_read.naver?code=493280&amp;nid=415505509&amp;page=2', 'score': 577}, {'title': '조단위 기술수출+96.5%보호예수.품절주됨...[1]', 'date': '2026.03.20 12:22', 'views': '227', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=493280&amp;nid=415478934&amp;page=5', 'score': 617}, {'title': '■■■따따블매수■■■[1]', 'date': '2026.03.20 09:28', 'views': '152', 'likes': '12', 'dislikes': '3', 'link': '/item/board_read.naver?code=493280&amp;nid=415445066&amp;page=8', 'score': 512}, {'title': '조단위 기술수출+96.5%보호예수.품절주됨.....', 'date': '2026.03.20 17:00', 'views': '136', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=493280&amp;nid=415516332&amp;page=1', 'score': 466}, {'title': '매년적자 펩트론은 수출도없이 40만원 갔다....[2]', 'date': '2026.03.20 13:18', 'views': '226', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=493280&amp;nid=415487110&amp;page=4', 'score': 556}, {'title': '돈 될만한 종목은 개미한테 매수 기회조차 ...[2]', 'date': '2026.03.20 11:47', 'views': '758', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=493280&amp;nid=415473753&amp;page=5', 'score': 1088}, {'title': '미국1조3천억+중국5천억. 총 1조8천억 기술이...', 'date': '2026.03.20 10:16', 'views': '298', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=493280&amp;nid=415456611&amp;page=7', 'score': 628}, {'title': '알지노믹 공모가 22,500원.최고가23만.....[1]', 'date': '2026.03.20 17:02', 'views': '284', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=493280&amp;nid=415516486&amp;page=1', 'score': 584}]</t>
+          <t>[{'title': '미친 한국주식시장..이런거나 고쳐라', 'date': '2026.03.20 11:46', 'views': '143', 'likes': '20', 'dislikes': '2', 'link': '/item/board_read.naver?code=493280&amp;nid=415473520&amp;page=5', 'score': 743}, {'title': '2개 받았는데 300% 개꿀딱[7]', 'date': '2026.03.20 09:22', 'views': '1208', 'likes': '18', 'dislikes': '5', 'link': '/item/board_read.naver?code=493280&amp;nid=415443396&amp;page=9', 'score': 1748}, {'title': '월욜 상한가 135200원이 종가', 'date': '2026.03.20 15:15', 'views': '128', 'likes': '15', 'dislikes': '4', 'link': '/item/board_read.naver?code=493280&amp;nid=415505509&amp;page=3', 'score': 578}, {'title': '조단위 기술수출+96.5%보호예수.품절주됨...[1]', 'date': '2026.03.20 12:22', 'views': '228', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=493280&amp;nid=415478934&amp;page=5', 'score': 618}, {'title': '■■■따따블매수■■■[1]', 'date': '2026.03.20 09:28', 'views': '153', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=493280&amp;nid=415445066&amp;page=8', 'score': 513}, {'title': '알지노믹 공모가 22,500원.최고가23만.....[1]', 'date': '2026.03.20 17:02', 'views': '290', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=493280&amp;nid=415516486&amp;page=1', 'score': 620}, {'title': '조단위 기술수출+96.5%보호예수.품절주됨.....', 'date': '2026.03.20 17:00', 'views': '139', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=493280&amp;nid=415516332&amp;page=1', 'score': 469}, {'title': '연기금 보험이', 'date': '2026.03.20 16:13', 'views': '133', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=493280&amp;nid=415512981&amp;page=2', 'score': 463}, {'title': '유통물량 14% 기관 확약률 96.5% 점상 몇방이...[1]', 'date': '2026.03.20 15:39', 'views': '231', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=493280&amp;nid=415509202&amp;page=2', 'score': 561}, {'title': '매년적자 펩트론은 수출도없이 40만원 갔다....[2]', 'date': '2026.03.20 13:18', 'views': '226', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=493280&amp;nid=415487110&amp;page=4', 'score': 556}]</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>국내외 광트랜시버 제조사에 채택 가능성- ...[2] / 대한광통신VS우리로광통신~~~[3] / 우리로광통신! / 털렸네 ㅋㅋ</t>
+          <t>국내외 광트랜시버 제조사에 채택 가능성- 제미나...[2] / 대한광통신VS우리로광통신~~~[3] / 우리로광통신! / 털렸네 ㅋㅋ</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>[{'title': '일단 1조 가자', 'date': '2026.03.20 14:05', 'views': '93', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=046970&amp;nid=415494439&amp;page=1', 'score': 483}, {'title': '쩜상10방200Gbps광검출기없어서못판다...', 'date': '2026.03.20 11:12', 'views': '159', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415467252&amp;page=2', 'score': 549}, {'title': '우리로광통신!', 'date': '2026.03.20 13:18', 'views': '229', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415487096&amp;page=2', 'score': 589}, {'title': '응아가 10연발 간다고 어제 분명히 말했...', 'date': '2026.03.20 11:12', 'views': '78', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415467305&amp;page=2', 'score': 438}, {'title': '지금 없어서 못판다고 합니다!!', 'date': '2026.03.20 10:57', 'views': '192', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415464594&amp;page=2', 'score': 552}, {'title': '대한광통신VS우리로광통신~~~[3]', 'date': '2026.03.20 10:22', 'views': '264', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415457884&amp;page=3', 'score': 624}, {'title': '국내외 광트랜시버 제조사에 채택 가능성- ...[2]', 'date': '2026.03.20 16:12', 'views': '520', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415512943&amp;page=1', 'score': 850}, {'title': '털렸네 ㅋㅋ', 'date': '2026.03.20 11:05', 'views': '237', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415466133&amp;page=2', 'score': 567}, {'title': '개인의 그릇이 정확히 드러나는 시점이내[2]', 'date': '2026.03.20 10:16', 'views': '227', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415456527&amp;page=3', 'score': 557}, {'title': '오늘 감사보고서 받아 적정판결', 'date': '2026.03.20 14:16', 'views': '165', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415496290&amp;page=1', 'score': 465}]</t>
+          <t>[{'title': '일단 1조 가자', 'date': '2026.03.20 14:05', 'views': '95', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=046970&amp;nid=415494439&amp;page=1', 'score': 485}, {'title': '쩜상10방200Gbps광검출기없어서못판다...', 'date': '2026.03.20 11:12', 'views': '159', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415467252&amp;page=2', 'score': 549}, {'title': '우리로광통신!', 'date': '2026.03.20 13:18', 'views': '230', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415487096&amp;page=2', 'score': 590}, {'title': '응아가 10연발 간다고 어제 분명히 말했...', 'date': '2026.03.20 11:12', 'views': '78', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415467305&amp;page=2', 'score': 438}, {'title': '지금 없어서 못판다고 합니다!!', 'date': '2026.03.20 10:57', 'views': '192', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415464594&amp;page=3', 'score': 552}, {'title': '대한광통신VS우리로광통신~~~[3]', 'date': '2026.03.20 10:22', 'views': '264', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415457884&amp;page=3', 'score': 624}, {'title': '국내외 광트랜시버 제조사에 채택 가능성- 제미나...[2]', 'date': '2026.03.20 16:12', 'views': '531', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415512943&amp;page=1', 'score': 861}, {'title': '털렸네 ㅋㅋ', 'date': '2026.03.20 11:05', 'views': '237', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415466133&amp;page=2', 'score': 567}, {'title': '개인의 그릇이 정확히 드러나는 시점이내[2]', 'date': '2026.03.20 10:16', 'views': '227', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415456527&amp;page=3', 'score': 557}, {'title': '오늘 감사보고서 받아 적정판결', 'date': '2026.03.20 14:16', 'views': '166', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415496290&amp;page=1', 'score': 466}]</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>[{'title': '진짜 설마 설마 했는데[5]', 'date': '2026.03.20 15:23', 'views': '573', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=375500&amp;nid=415506745&amp;page=4', 'score': 963}, {'title': '미국 원전주..이란 전쟁 재건주[4]', 'date': '2026.03.20 18:08', 'views': '354', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=375500&amp;nid=415520425&amp;page=1', 'score': 654}, {'title': '축하드립니다.[2]', 'date': '2026.03.20 15:09', 'views': '152', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415504578&amp;page=5', 'score': 422}, {'title': '이란 전쟁재건 대장주는 DL이앤씨다. 왜냐하', 'date': '2026.03.20 14:22', 'views': '293', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=375500&amp;nid=415497229&amp;page=6', 'score': 563}, {'title': '5년을 기다렸다[2]', 'date': '2026.03.20 10:21', 'views': '241', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415457629&amp;page=10', 'score': 511}, {'title': '소형모듈원전 SMR 건설 분야 국내  1...', 'date': '2026.03.20 10:02', 'views': '186', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415453423&amp;page=10', 'score': 456}, {'title': '미-이란 전쟁이 끝나면 대박', 'date': '2026.03.20 16:46', 'views': '119', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415515306&amp;page=2', 'score': 359}, {'title': 'Gs건설 더 간다', 'date': '2026.03.20 09:25', 'views': '55', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415444110&amp;page=11', 'score': 295}, {'title': '앞으로 5년', 'date': '2026.03.20 18:29', 'views': '51', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415521565&amp;page=1', 'score': 261}, {'title': '월요일 10퍼이상 상승출발예측[1]', 'date': '2026.03.20 16:50', 'views': '217', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=375500&amp;nid=415515620&amp;page=2', 'score': 427}]</t>
+          <t>[{'title': '진짜 설마 설마 했는데[5]', 'date': '2026.03.20 15:23', 'views': '589', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=375500&amp;nid=415506745&amp;page=4', 'score': 979}, {'title': '미국 원전주..이란 전쟁 재건주[4]', 'date': '2026.03.20 18:08', 'views': '366', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=375500&amp;nid=415520425&amp;page=1', 'score': 666}, {'title': '축하드립니다.[2]', 'date': '2026.03.20 15:09', 'views': '152', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415504578&amp;page=5', 'score': 422}, {'title': '이란 전쟁재건 대장주는 DL이앤씨다. 왜냐하', 'date': '2026.03.20 14:22', 'views': '293', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=375500&amp;nid=415497229&amp;page=6', 'score': 563}, {'title': '5년을 기다렸다[2]', 'date': '2026.03.20 10:21', 'views': '241', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415457629&amp;page=10', 'score': 511}, {'title': '소형모듈원전 SMR 건설 분야 국내  1...', 'date': '2026.03.20 10:02', 'views': '186', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415453423&amp;page=10', 'score': 456}, {'title': '미-이란 전쟁이 끝나면 대박', 'date': '2026.03.20 16:46', 'views': '119', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415515306&amp;page=2', 'score': 359}, {'title': 'Gs건설 더 간다', 'date': '2026.03.20 09:25', 'views': '55', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415444110&amp;page=11', 'score': 295}, {'title': '앞으로 5년', 'date': '2026.03.20 18:29', 'views': '54', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=375500&amp;nid=415521565&amp;page=1', 'score': 264}, {'title': '월요일 10퍼이상 상승출발예측[1]', 'date': '2026.03.20 16:50', 'views': '218', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=375500&amp;nid=415515620&amp;page=2', 'score': 428}]</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>석유·가스 플랜트에 들어가는 공랭식 열교환기(...[1] / EB로 풀린 45만주 오늘 정리?[5] / 목표가 10만 기도 54일차[3] / 이놈이 대장이었네..</t>
+          <t>석유·가스 플랜트에 들어가는 공랭식 열교환기(A...[1] / EB로 풀린 45만주 오늘 정리?[5] / 목표가 10만 기도 54일차[3] / 이놈이 대장이었네..</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>[{'title': '석유·가스 플랜트에 들어가는 공랭식 열교환기(...[1]', 'date': '2026.03.20 12:10', 'views': '435', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415477187&amp;page=5', 'score': 975}, {'title': 'EB로 풀린 45만주 오늘 정리?[5]', 'date': '2026.03.20 15:36', 'views': '154', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415508766&amp;page=3', 'score': 454}, {'title': '목표가 10만 기도 54일차[3]', 'date': '2026.03.20 12:46', 'views': '118', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415482256&amp;page=5', 'score': 388}, {'title': '이놈이 대장이었네..', 'date': '2026.03.20 09:56', 'views': '73', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415451935&amp;page=8', 'score': 343}, {'title': '지주사가 50%이상 가지고 있는데', 'date': '2026.03.20 18:04', 'views': '58', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415520229&amp;page=1', 'score': 268}, {'title': '운전실력.예술![2]', 'date': '2026.03.20 15:21', 'views': '116', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=100840&amp;nid=415506519&amp;page=3', 'score': 326}, {'title': 'IMM 제발 오늘 다 털고 꺼지시길[1]', 'date': '2026.03.20 15:07', 'views': '63', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=100840&amp;nid=415504219&amp;page=3', 'score': 273}, {'title': '차트', 'date': '2026.03.20 14:33', 'views': '33', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415498879&amp;page=4', 'score': 243}, {'title': '사우디 아람코와 아랍에미레이트 석유국은 완전 갑...[1]', 'date': '2026.03.20 10:04', 'views': '131', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415454003&amp;page=8', 'score': 341}, {'title': '주식이 이런거지...[1]', 'date': '2026.03.20 09:43', 'views': '73', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415449004&amp;page=8', 'score': 283}]</t>
+          <t>[{'title': '석유·가스 플랜트에 들어가는 공랭식 열교환기(A...[1]', 'date': '2026.03.20 12:10', 'views': '441', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415477187&amp;page=5', 'score': 981}, {'title': 'EB로 풀린 45만주 오늘 정리?[5]', 'date': '2026.03.20 15:36', 'views': '157', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415508766&amp;page=2', 'score': 457}, {'title': '목표가 10만 기도 54일차[3]', 'date': '2026.03.20 12:46', 'views': '118', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415482256&amp;page=5', 'score': 388}, {'title': '이놈이 대장이었네..', 'date': '2026.03.20 09:56', 'views': '73', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415451935&amp;page=8', 'score': 343}, {'title': '지주사가 50%이상 가지고 있는데', 'date': '2026.03.20 18:04', 'views': '62', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415520229&amp;page=1', 'score': 272}, {'title': '운전실력.예술![2]', 'date': '2026.03.20 15:21', 'views': '116', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=100840&amp;nid=415506519&amp;page=3', 'score': 326}, {'title': 'IMM 제발 오늘 다 털고 꺼지시길[1]', 'date': '2026.03.20 15:07', 'views': '63', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=100840&amp;nid=415504219&amp;page=3', 'score': 273}, {'title': '차트', 'date': '2026.03.20 14:33', 'views': '33', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415498879&amp;page=4', 'score': 243}, {'title': '사우디 아람코와 아랍에미레이트 석유국은 완전 ...[1]', 'date': '2026.03.20 10:04', 'views': '131', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415454003&amp;page=8', 'score': 341}, {'title': '주식이 이런거지...[1]', 'date': '2026.03.20 09:43', 'views': '73', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415449004&amp;page=8', 'score': 283}]</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>[{'title': '테마 엮기 좋고 가벼워서 세력붙으면 정신없이 ...', 'date': '2026.03.20 08:25', 'views': '59', 'likes': '8', 'dislikes': '4', 'link': '/item/board_read.naver?code=044490&amp;nid=415433094&amp;page=7', 'score': 299}, {'title': '이런 월요일[1]', 'date': '2026.03.20 17:08', 'views': '191', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=044490&amp;nid=415516846&amp;page=1', 'score': 401}, {'title': '아 짜증나서 던졌음..', 'date': '2026.03.20 17:00', 'views': '42', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415516322&amp;page=1', 'score': 222}, {'title': '이제 매물이 없어요..🤗', 'date': '2026.03.20 16:07', 'views': '56', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=044490&amp;nid=415512465&amp;page=2', 'score': 236}, {'title': '문어발', 'date': '2026.03.20 12:29', 'views': '51', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=044490&amp;nid=415479929&amp;page=3', 'score': 231}, {'title': '상한가에 전량 매도~ 감사감사[2]', 'date': '2026.03.20 12:03', 'views': '90', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415476158&amp;page=3', 'score': 270}, {'title': '오늘 상이네 ㅎㅎ', 'date': '2026.03.20 09:34', 'views': '27', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415446673&amp;page=6', 'score': 207}, {'title': '태웅', 'date': '2026.03.20 08:44', 'views': '32', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415435563&amp;page=7', 'score': 212}, {'title': '요상하다[1]', 'date': '2026.03.20 18:16', 'views': '85', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=044490&amp;nid=415520871&amp;page=1', 'score': 235}, {'title': '축하 축하 드립니다  상입니다!', 'date': '2026.03.20 18:28', 'views': '21', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=044490&amp;nid=415521465&amp;page=1', 'score': 141}]</t>
+          <t>[{'title': '테마 엮기 좋고 가벼워서 세력붙으면 정신없이 ...', 'date': '2026.03.20 08:25', 'views': '59', 'likes': '8', 'dislikes': '4', 'link': '/item/board_read.naver?code=044490&amp;nid=415433094&amp;page=7', 'score': 299}, {'title': '이런 월요일[1]', 'date': '2026.03.20 17:08', 'views': '192', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=044490&amp;nid=415516846&amp;page=1', 'score': 402}, {'title': '아 짜증나서 던졌음..', 'date': '2026.03.20 17:00', 'views': '43', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415516322&amp;page=1', 'score': 223}, {'title': '이제 매물이 없어요..🤗', 'date': '2026.03.20 16:07', 'views': '57', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=044490&amp;nid=415512465&amp;page=2', 'score': 237}, {'title': '문어발', 'date': '2026.03.20 12:29', 'views': '51', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=044490&amp;nid=415479929&amp;page=3', 'score': 231}, {'title': '상한가에 전량 매도~ 감사감사[2]', 'date': '2026.03.20 12:03', 'views': '90', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415476158&amp;page=3', 'score': 270}, {'title': '오늘 상이네 ㅎㅎ', 'date': '2026.03.20 09:34', 'views': '27', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415446673&amp;page=6', 'score': 207}, {'title': '태웅', 'date': '2026.03.20 08:44', 'views': '32', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415435563&amp;page=7', 'score': 212}, {'title': '요상하다[1]', 'date': '2026.03.20 18:16', 'views': '87', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=044490&amp;nid=415520871&amp;page=1', 'score': 237}, {'title': '축하 축하 드립니다  상입니다!', 'date': '2026.03.20 18:28', 'views': '21', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=044490&amp;nid=415521465&amp;page=1', 'score': 141}]</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>[{'title': '원전 해체 세계 최초 상용화 뭐가 두렵노[1]', 'date': '2026.03.20 15:43', 'views': '241', 'likes': '20', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415509812&amp;page=2', 'score': 841}, {'title': '눈물 나네요.[2]', 'date': '2026.03.20 13:54', 'views': '298', 'likes': '19', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415492815&amp;page=4', 'score': 868}, {'title': '오르비텍', 'date': '2026.03.20 13:16', 'views': '189', 'likes': '18', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415486662&amp;page=4', 'score': 729}, {'title': '답답하다 투경이고뭐고[2]', 'date': '2026.03.20 16:42', 'views': '577', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=046120&amp;nid=415515087&amp;page=1', 'score': 997}, {'title': '100주 샀음요', 'date': '2026.03.20 16:10', 'views': '100', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=046120&amp;nid=415512779&amp;page=1', 'score': 520}, {'title': '3만원은 넘길듯...[2]', 'date': '2026.03.20 13:09', 'views': '345', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=046120&amp;nid=415485691&amp;page=4', 'score': 765}, {'title': '여기 주포는', 'date': '2026.03.20 16:40', 'views': '416', 'likes': '13', 'dislikes': '2', 'link': '/item/board_read.naver?code=046120&amp;nid=415514954&amp;page=1', 'score': 806}, {'title': '시간 외 상 박아 주고 담주 20% 갭으로 가자...', 'date': '2026.03.20 15:28', 'views': '130', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415507583&amp;page=2', 'score': 520}, {'title': '오늘 13568 밑에서 끝나면[3]', 'date': '2026.03.20 14:46', 'views': '497', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=046120&amp;nid=415500943&amp;page=3', 'score': 857}, {'title': '신고가 축하드립니다.', 'date': '2026.03.20 14:26', 'views': '149', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=046120&amp;nid=415497809&amp;page=3', 'score': 509}]</t>
+          <t>[{'title': '원전 해체 세계 최초 상용화 뭐가 두렵노[1]', 'date': '2026.03.20 15:43', 'views': '245', 'likes': '20', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415509812&amp;page=2', 'score': 845}, {'title': '눈물 나네요.[2]', 'date': '2026.03.20 13:54', 'views': '299', 'likes': '19', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415492815&amp;page=4', 'score': 869}, {'title': '오르비텍', 'date': '2026.03.20 13:16', 'views': '189', 'likes': '18', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415486662&amp;page=4', 'score': 729}, {'title': '답답하다 투경이고뭐고[2]', 'date': '2026.03.20 16:42', 'views': '581', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=046120&amp;nid=415515087&amp;page=1', 'score': 1001}, {'title': '100주 샀음요', 'date': '2026.03.20 16:10', 'views': '101', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=046120&amp;nid=415512779&amp;page=1', 'score': 521}, {'title': '3만원은 넘길듯...[2]', 'date': '2026.03.20 13:09', 'views': '345', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=046120&amp;nid=415485691&amp;page=4', 'score': 765}, {'title': '여기 주포는', 'date': '2026.03.20 16:40', 'views': '418', 'likes': '13', 'dislikes': '2', 'link': '/item/board_read.naver?code=046120&amp;nid=415514954&amp;page=1', 'score': 808}, {'title': '시간 외 상 박아 주고 담주 20% 갭으로 가자...', 'date': '2026.03.20 15:28', 'views': '131', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415507583&amp;page=2', 'score': 521}, {'title': '오늘 13568 밑에서 끝나면[3]', 'date': '2026.03.20 14:46', 'views': '497', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=046120&amp;nid=415500943&amp;page=3', 'score': 857}, {'title': '신고가 축하드립니다.', 'date': '2026.03.20 14:26', 'views': '149', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=046120&amp;nid=415497809&amp;page=3', 'score': 509}]</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Positive (82%)</t>
+          <t>Positive (81%)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>상한가, 원전, 이제</t>
+          <t>상한가, 이제, 원전</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>[{'title': '매물소화중이라니까 계속들 파시네', 'date': '2026.03.20 15:27', 'views': '196', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415507418&amp;page=6', 'score': 646}, {'title': '건설 우량주 Gs건설 상한가 한방 묵자', 'date': '2026.03.20 12:50', 'views': '105', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415482959&amp;page=11', 'score': 465}, {'title': '뉴스케일파워 믿고 투자하세요.', 'date': '2026.03.20 18:25', 'views': '69', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=006360&amp;nid=415521311&amp;page=3', 'score': 369}, {'title': 's넥장[1]', 'date': '2026.03.20 15:47', 'views': '155', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415510318&amp;page=6', 'score': 455}, {'title': 'Gs건설이 원전으로만 올라가는걸로 보...', 'date': '2026.03.20 11:30', 'views': '523', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=006360&amp;nid=415470730&amp;page=12', 'score': 823}, {'title': '누가 원전주  아니라더니', 'date': '2026.03.20 16:06', 'views': '102', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=006360&amp;nid=415512357&amp;page=5', 'score': 372}, {'title': '상한가 가도', 'date': '2026.03.20 13:06', 'views': '74', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=006360&amp;nid=415485164&amp;page=11', 'score': 344}, {'title': '미국에서 SMR건설 누가하겠냐 GS건설[1]', 'date': '2026.03.20 17:27', 'views': '295', 'likes': '8', 'dislikes': '3', 'link': '/item/board_read.naver?code=006360&amp;nid=415518090&amp;page=4', 'score': 535}, {'title': '상 안쳐도 되는이유[3]', 'date': '2026.03.20 16:05', 'views': '175', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=006360&amp;nid=415512280&amp;page=5', 'score': 415}, {'title': '지건인 에너지 회사임[1]', 'date': '2026.03.20 15:57', 'views': '104', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=006360&amp;nid=415511460&amp;page=5', 'score': 344}]</t>
+          <t>[{'title': '매물소화중이라니까 계속들 파시네', 'date': '2026.03.20 15:27', 'views': '196', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415507418&amp;page=7', 'score': 646}, {'title': '건설 우량주 Gs건설 상한가 한방 묵자', 'date': '2026.03.20 12:50', 'views': '105', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415482959&amp;page=11', 'score': 465}, {'title': '뉴스케일파워 믿고 투자하세요.', 'date': '2026.03.20 18:25', 'views': '69', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=006360&amp;nid=415521311&amp;page=4', 'score': 369}, {'title': 's넥장[1]', 'date': '2026.03.20 15:47', 'views': '155', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415510318&amp;page=6', 'score': 455}, {'title': 'Gs건설이 원전으로만 올라가는걸로 보...', 'date': '2026.03.20 11:30', 'views': '523', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=006360&amp;nid=415470730&amp;page=12', 'score': 823}, {'title': '누가 원전주  아니라더니', 'date': '2026.03.20 16:06', 'views': '102', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=006360&amp;nid=415512357&amp;page=6', 'score': 372}, {'title': '상한가 가도', 'date': '2026.03.20 13:06', 'views': '74', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=006360&amp;nid=415485164&amp;page=11', 'score': 344}, {'title': '미국에서 SMR건설 누가하겠냐 GS건설[1]', 'date': '2026.03.20 17:27', 'views': '295', 'likes': '8', 'dislikes': '3', 'link': '/item/board_read.naver?code=006360&amp;nid=415518090&amp;page=5', 'score': 535}, {'title': '상 안쳐도 되는이유[3]', 'date': '2026.03.20 16:05', 'views': '175', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=006360&amp;nid=415512280&amp;page=6', 'score': 415}, {'title': '지건인 에너지 회사임[1]', 'date': '2026.03.20 15:57', 'views': '104', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=006360&amp;nid=415511460&amp;page=6', 'score': 344}]</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>답지 준다. 이거만 외워라.[4] / 총 칠천만주에 거래량 3800만주  터... / 1차 목표가 만원 2차 목표가 5만원[2] / 3,000원대 까지는 ~~~[5]</t>
+          <t>답지 준다. 이거만 외워라.[4] / 총 칠천만주에 거래량 3800만주  터... / 3,000원대 까지는 ~~~[5] / 1차 목표가 만원 2차 목표가 5만원[2]</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>[{'title': '총 칠천만주에 거래량 3800만주  터...', 'date': '2026.03.20 15:38', 'views': '277', 'likes': '21', 'dislikes': '1', 'link': '/item/board_read.naver?code=018000&amp;nid=415509095&amp;page=2', 'score': 907}, {'title': '1차 목표가 만원 2차 목표가 5만원[2]', 'date': '2026.03.20 11:35', 'views': '292', 'likes': '20', 'dislikes': '2', 'link': '/item/board_read.naver?code=018000&amp;nid=415471508&amp;page=4', 'score': 892}, {'title': '신재생에너지 기업 주가가', 'date': '2026.03.20 15:49', 'views': '247', 'likes': '19', 'dislikes': '1', 'link': '/item/board_read.naver?code=018000&amp;nid=415510489&amp;page=2', 'score': 817}, {'title': '유니슨 오늘 외인 매수  및 프로그램 대량 매수중[1]', 'date': '2026.03.20 11:51', 'views': '179', 'likes': '19', 'dislikes': '0', 'link': '/item/board_read.naver?code=018000&amp;nid=415474322&amp;page=4', 'score': 749}, {'title': '3,000원대 까지는 ~~~[5]', 'date': '2026.03.20 16:19', 'views': '362', 'likes': '17', 'dislikes': '2', 'link': '/item/board_read.naver?code=018000&amp;nid=415513488&amp;page=1', 'score': 872}, {'title': '답지 준다. 이거만 외워라.[4]', 'date': '2026.03.20 10:24', 'views': '644', 'likes': '17', 'dislikes': '5', 'link': '/item/board_read.naver?code=018000&amp;nid=415458177&amp;page=4', 'score': 1154}, {'title': '오후에 .. 일단 상[1]', 'date': '2026.03.20 12:26', 'views': '258', 'likes': '16', 'dislikes': '5', 'link': '/item/board_read.naver?code=018000&amp;nid=415479527&amp;page=3', 'score': 738}, {'title': '지금까지[1]', 'date': '2026.03.20 11:01', 'views': '204', 'likes': '16', 'dislikes': '1', 'link': '/item/board_read.naver?code=018000&amp;nid=415465465&amp;page=4', 'score': 684}, {'title': '소머리국밥 먹으러 갑니다.[1]', 'date': '2026.03.20 17:48', 'views': '165', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=018000&amp;nid=415519355&amp;page=1', 'score': 555}, {'title': '십수년동안 요즘이 거의 저점이다...', 'date': '2026.03.20 16:42', 'views': '132', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=018000&amp;nid=415515055&amp;page=1', 'score': 522}]</t>
+          <t>[{'title': '총 칠천만주에 거래량 3800만주  터...', 'date': '2026.03.20 15:38', 'views': '278', 'likes': '21', 'dislikes': '1', 'link': '/item/board_read.naver?code=018000&amp;nid=415509095&amp;page=2', 'score': 908}, {'title': '1차 목표가 만원 2차 목표가 5만원[2]', 'date': '2026.03.20 11:35', 'views': '292', 'likes': '20', 'dislikes': '2', 'link': '/item/board_read.naver?code=018000&amp;nid=415471508&amp;page=4', 'score': 892}, {'title': '신재생에너지 기업 주가가', 'date': '2026.03.20 15:49', 'views': '250', 'likes': '19', 'dislikes': '1', 'link': '/item/board_read.naver?code=018000&amp;nid=415510489&amp;page=2', 'score': 820}, {'title': '유니슨 오늘 외인 매수  및 프로그램 대량 매수중[1]', 'date': '2026.03.20 11:51', 'views': '179', 'likes': '19', 'dislikes': '0', 'link': '/item/board_read.naver?code=018000&amp;nid=415474322&amp;page=4', 'score': 749}, {'title': '3,000원대 까지는 ~~~[5]', 'date': '2026.03.20 16:19', 'views': '367', 'likes': '18', 'dislikes': '2', 'link': '/item/board_read.naver?code=018000&amp;nid=415513488&amp;page=1', 'score': 907}, {'title': '답지 준다. 이거만 외워라.[4]', 'date': '2026.03.20 10:24', 'views': '644', 'likes': '17', 'dislikes': '5', 'link': '/item/board_read.naver?code=018000&amp;nid=415458177&amp;page=4', 'score': 1154}, {'title': '오후에 .. 일단 상[1]', 'date': '2026.03.20 12:26', 'views': '258', 'likes': '16', 'dislikes': '5', 'link': '/item/board_read.naver?code=018000&amp;nid=415479527&amp;page=3', 'score': 738}, {'title': '지금까지[1]', 'date': '2026.03.20 11:01', 'views': '204', 'likes': '16', 'dislikes': '1', 'link': '/item/board_read.naver?code=018000&amp;nid=415465465&amp;page=4', 'score': 684}, {'title': '십수년동안 요즘이 거의 저점이다...', 'date': '2026.03.20 16:42', 'views': '134', 'likes': '14', 'dislikes': '0', 'link': '/item/board_read.naver?code=018000&amp;nid=415515055&amp;page=1', 'score': 554}, {'title': '소머리국밥 먹으러 갑니다.[1]', 'date': '2026.03.20 17:48', 'views': '170', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=018000&amp;nid=415519355&amp;page=1', 'score': 560}]</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Positive (64%)</t>
+          <t>Positive (54%)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>[{'title': '22200원 입성', 'date': '2026.03.20 13:16', 'views': '35', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=217590&amp;nid=415486668&amp;page=5', 'score': 215}, {'title': '24050 추매', 'date': '2026.03.20 17:00', 'views': '21', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415516296&amp;page=3', 'score': 171}, {'title': 'TMC 선박케이블 세계1위, 원전케이블도 장...', 'date': '2026.03.20 12:16', 'views': '250', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415478084&amp;page=6', 'score': 400}, {'title': '25050 전량매도[1]', 'date': '2026.03.20 18:15', 'views': '82', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=217590&amp;nid=415520806&amp;page=2', 'score': 202}, {'title': '22층에 3개월 물려잇었는데[5]', 'date': '2026.03.20 18:02', 'views': '145', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=217590&amp;nid=415520147&amp;page=2', 'score': 265}, {'title': '성호전자 엔비디아 뉴스로 시총 3조 됐다', 'date': '2026.03.20 17:19', 'views': '50', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=217590&amp;nid=415517635&amp;page=3', 'score': 170}, {'title': '주린인데..투경예고? 아닌가요?[3]', 'date': '2026.03.20 16:26', 'views': '683', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=217590&amp;nid=415513982&amp;page=3', 'score': 803}, {'title': '오늘 연기금 81779주 떡 매수로', 'date': '2026.03.20 16:07', 'views': '63', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415512408&amp;page=4', 'score': 183}, {'title': '상이가', 'date': '2026.03.20 16:02', 'views': '36', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415511962&amp;page=4', 'score': 156}, {'title': '신고가에 수급좋고 상 가나요?', 'date': '2026.03.20 15:58', 'views': '33', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=217590&amp;nid=415511584&amp;page=4', 'score': 153}]</t>
+          <t>[{'title': '22200원 입성', 'date': '2026.03.20 13:16', 'views': '35', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=217590&amp;nid=415486668&amp;page=5', 'score': 215}, {'title': '24050 추매', 'date': '2026.03.20 17:00', 'views': '21', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415516296&amp;page=3', 'score': 171}, {'title': 'TMC 선박케이블 세계1위, 원전케이블도 장...', 'date': '2026.03.20 12:16', 'views': '250', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415478084&amp;page=6', 'score': 400}, {'title': '25050 전량매도[1]', 'date': '2026.03.20 18:15', 'views': '84', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=217590&amp;nid=415520806&amp;page=2', 'score': 204}, {'title': '22층에 3개월 물려잇었는데[5]', 'date': '2026.03.20 18:02', 'views': '146', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=217590&amp;nid=415520147&amp;page=2', 'score': 266}, {'title': '성호전자 엔비디아 뉴스로 시총 3조 됐다', 'date': '2026.03.20 17:19', 'views': '50', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=217590&amp;nid=415517635&amp;page=3', 'score': 170}, {'title': '주린인데..투경예고? 아닌가요?[3]', 'date': '2026.03.20 16:26', 'views': '697', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=217590&amp;nid=415513982&amp;page=3', 'score': 817}, {'title': '오늘 연기금 81779주 떡 매수로', 'date': '2026.03.20 16:07', 'views': '63', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415512408&amp;page=4', 'score': 183}, {'title': '상이가', 'date': '2026.03.20 16:02', 'views': '36', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415511962&amp;page=4', 'score': 156}, {'title': '신고가에 수급좋고 상 가나요?', 'date': '2026.03.20 15:58', 'views': '33', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=217590&amp;nid=415511584&amp;page=4', 'score': 153}]</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>불안하신 분은 필독) / 월요일도...15~20% 내외 상승 예상[4] / 뉴스 보셨죠? -  삼전의 M&amp;A 가능성 대두...[9] / 이 정도면 쩜상 가야지[1]</t>
+          <t>불안하신 분은 필독) / 뉴스 보셨죠? -  삼전의 M&amp;A 가능성 대두....[9] / 월요일도...15~20% 내외 상승 예상[4] / +소부장 Top Pickup 1으로 찜~1년 가...[3]</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>오늘, 상한가, ...</t>
+          <t>오늘, ..., 상한가</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>[{'title': '불안하신 분은 필독)', 'date': '2026.03.20 16:17', 'views': '317', 'likes': '12', 'dislikes': '5', 'link': '/item/board_read.naver?code=036930&amp;nid=415513340&amp;page=2', 'score': 677}, {'title': '+소부장 Top Pickup 1으로 찜~1년 ...[3]', 'date': '2026.03.20 16:49', 'views': '182', 'likes': '10', 'dislikes': '4', 'link': '/item/board_read.naver?code=036930&amp;nid=415515572&amp;page=1', 'score': 482}, {'title': '월요일도...15~20% 내외 상승 예상[4]', 'date': '2026.03.20 15:20', 'views': '246', 'likes': '10', 'dislikes': '7', 'link': '/item/board_read.naver?code=036930&amp;nid=415506370&amp;page=3', 'score': 546}, {'title': '외국인 역대급 매수', 'date': '2026.03.20 16:13', 'views': '216', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=036930&amp;nid=415512980&amp;page=2', 'score': 486}, {'title': '한미반도체가 본딩장비로 재평가 받았듯이[2]', 'date': '2026.03.20 14:31', 'views': '205', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=036930&amp;nid=415498603&amp;page=4', 'score': 475}, {'title': '이 정도면 쩜상 가야지[1]', 'date': '2026.03.20 12:09', 'views': '221', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=036930&amp;nid=415477137&amp;page=6', 'score': 491}, {'title': '뉴스 보셨죠? -  삼전의 M&amp;A 가능성 대두...[9]', 'date': '2026.03.20 18:43', 'views': '306', 'likes': '8', 'dislikes': '6', 'link': '/item/board_read.naver?code=036930&amp;nid=415522176&amp;page=1', 'score': 546}, {'title': '고맙다 시외에서 싸게 던져줘서', 'date': '2026.03.20 18:07', 'views': '84', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=036930&amp;nid=415520385&amp;page=1', 'score': 294}, {'title': '공매도는 숏커버 안할까?[2]', 'date': '2026.03.20 16:04', 'views': '190', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=036930&amp;nid=415512174&amp;page=2', 'score': 400}, {'title': '본드로 시가 총액 30조---- 신노광장비...', 'date': '2026.03.20 10:21', 'views': '143', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=036930&amp;nid=415457543&amp;page=8', 'score': 353}]</t>
+          <t>[{'title': '불안하신 분은 필독)', 'date': '2026.03.20 16:17', 'views': '320', 'likes': '13', 'dislikes': '5', 'link': '/item/board_read.naver?code=036930&amp;nid=415513340&amp;page=2', 'score': 710}, {'title': '+소부장 Top Pickup 1으로 찜~1년 가...[3]', 'date': '2026.03.20 16:49', 'views': '183', 'likes': '11', 'dislikes': '4', 'link': '/item/board_read.naver?code=036930&amp;nid=415515572&amp;page=1', 'score': 513}, {'title': '월요일도...15~20% 내외 상승 예상[4]', 'date': '2026.03.20 15:20', 'views': '249', 'likes': '10', 'dislikes': '7', 'link': '/item/board_read.naver?code=036930&amp;nid=415506370&amp;page=3', 'score': 549}, {'title': '외국인 역대급 매수', 'date': '2026.03.20 16:13', 'views': '221', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=036930&amp;nid=415512980&amp;page=2', 'score': 491}, {'title': '한미반도체가 본딩장비로 재평가 받았듯이[2]', 'date': '2026.03.20 14:31', 'views': '205', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=036930&amp;nid=415498603&amp;page=4', 'score': 475}, {'title': '이 정도면 쩜상 가야지[1]', 'date': '2026.03.20 12:09', 'views': '221', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=036930&amp;nid=415477137&amp;page=6', 'score': 491}, {'title': '뉴스 보셨죠? -  삼전의 M&amp;A 가능성 대두....[9]', 'date': '2026.03.20 18:43', 'views': '322', 'likes': '8', 'dislikes': '6', 'link': '/item/board_read.naver?code=036930&amp;nid=415522176&amp;page=1', 'score': 562}, {'title': '고맙다 시외에서 싸게 던져줘서[1]', 'date': '2026.03.20 18:07', 'views': '93', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=036930&amp;nid=415520385&amp;page=1', 'score': 303}, {'title': '공매도는 숏커버 안할까?[2]', 'date': '2026.03.20 16:04', 'views': '193', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=036930&amp;nid=415512174&amp;page=2', 'score': 403}, {'title': '본드로 시가 총액 30조---- 신노광장비...', 'date': '2026.03.20 10:21', 'views': '143', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=036930&amp;nid=415457543&amp;page=8', 'score': 353}]</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>원전해체1위[1] / [AI 요약] 우진의 단일판매ㆍ공급계약 ...[1] / ■우리기술 &gt; 우진으로 순환매 첫 도입이네요!... / 시간외 5시 30분후에 만주 몰빵[1]</t>
+          <t>원전해체1위[1] / [AI 요약] 우진의 단일판매ㆍ공급계약 ...[1] / 시간외 5시 30분후에 만주 몰빵[1] / ■우리기술 &gt; 우진으로 순환매 첫 도입이네요!...</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>[{'title': '원전해체1위[1]', 'date': '2026.03.20 10:17', 'views': '328', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415456769&amp;page=6', 'score': 658}, {'title': '■우리기술 &gt; 우진으로 순환매 첫 도입이네요!...', 'date': '2026.03.20 15:33', 'views': '64', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415508292&amp;page=2', 'score': 334}, {'title': '님들 시총 2조 가능하다고 보심????', 'date': '2026.03.20 15:23', 'views': '46', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=105840&amp;nid=415506832&amp;page=2', 'score': 226}, {'title': '종가 풀매수[1]', 'date': '2026.03.20 15:55', 'views': '102', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=105840&amp;nid=415511288&amp;page=1', 'score': 252}, {'title': '어디가 찐일까?', 'date': '2026.03.20 15:15', 'views': '48', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415505510&amp;page=2', 'score': 198}, {'title': '상가자[1]', 'date': '2026.03.20 14:37', 'views': '89', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415499569&amp;page=3', 'score': 239}, {'title': '[AI 요약] 우진의 단일판매ㆍ공급계약 ...[1]', 'date': '2026.03.20 13:55', 'views': '244', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415492926&amp;page=4', 'score': 394}, {'title': '시간외 5시 30분후에 만주 몰빵[1]', 'date': '2026.03.20 15:44', 'views': '214', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=105840&amp;nid=415509911&amp;page=1', 'score': 334}, {'title': '물린 주주들도 없고[1]', 'date': '2026.03.20 15:42', 'views': '108', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=105840&amp;nid=415509703&amp;page=1', 'score': 228}, {'title': '개미 50만주 매도 외인기관50만주 매수[1]', 'date': '2026.03.20 15:39', 'views': '93', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=105840&amp;nid=415509272&amp;page=1', 'score': 213}]</t>
+          <t>[{'title': '원전해체1위[1]', 'date': '2026.03.20 10:17', 'views': '330', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415456769&amp;page=6', 'score': 660}, {'title': '■우리기술 &gt; 우진으로 순환매 첫 도입이네요!...', 'date': '2026.03.20 15:33', 'views': '64', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415508292&amp;page=2', 'score': 334}, {'title': '님들 시총 2조 가능하다고 보심????', 'date': '2026.03.20 15:23', 'views': '46', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=105840&amp;nid=415506832&amp;page=2', 'score': 226}, {'title': '종가 풀매수[1]', 'date': '2026.03.20 15:55', 'views': '104', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=105840&amp;nid=415511288&amp;page=1', 'score': 254}, {'title': '어디가 찐일까?', 'date': '2026.03.20 15:15', 'views': '48', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415505510&amp;page=2', 'score': 198}, {'title': '상가자[1]', 'date': '2026.03.20 14:37', 'views': '89', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415499569&amp;page=3', 'score': 239}, {'title': '[AI 요약] 우진의 단일판매ㆍ공급계약 ...[1]', 'date': '2026.03.20 13:55', 'views': '244', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415492926&amp;page=4', 'score': 394}, {'title': '시간외 5시 30분후에 만주 몰빵[1]', 'date': '2026.03.20 15:44', 'views': '215', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=105840&amp;nid=415509911&amp;page=1', 'score': 335}, {'title': '물린 주주들도 없고[1]', 'date': '2026.03.20 15:42', 'views': '109', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=105840&amp;nid=415509703&amp;page=1', 'score': 229}, {'title': '개미 50만주 매도 외인기관50만주 매수[1]', 'date': '2026.03.20 15:39', 'views': '93', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=105840&amp;nid=415509272&amp;page=1', 'score': 213}]</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>봐라 또 개미들만 팔았제 ?[2] / ㅎ ㅎ ㅎ / 개인만 열라게[2] / 솔직히 형들</t>
+          <t>봐라 또 개미들만 팔았제 ?[2] / ㅎ ㅎ ㅎ / 오늘의 시황//그리고 액면병합 모멘텀은 계속 유...[1] / 개인만 열라게[2]</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Positive (63%)</t>
+          <t>Positive (62%)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>[{'title': '개인만 열라게[2]', 'date': '2026.03.20 15:42', 'views': '216', 'likes': '16', 'dislikes': '2', 'link': '/item/board_read.naver?code=001510&amp;nid=415509682&amp;page=4', 'score': 696}, {'title': '봐라 또 개미들만 팔았제 ?[2]', 'date': '2026.03.20 15:36', 'views': '491', 'likes': '16', 'dislikes': '1', 'link': '/item/board_read.naver?code=001510&amp;nid=415508782&amp;page=4', 'score': 971}, {'title': '솔직히 형들', 'date': '2026.03.20 17:50', 'views': '292', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=001510&amp;nid=415519424&amp;page=2', 'score': 682}, {'title': '증권주 비교하면 적정가 5~6천이상은 가야...[2]', 'date': '2026.03.20 15:59', 'views': '290', 'likes': '13', 'dislikes': '2', 'link': '/item/board_read.naver?code=001510&amp;nid=415511679&amp;page=3', 'score': 680}, {'title': '오늘의 시황과 액면병합 모멘텀은 계속유효하다[1]', 'date': '2026.03.20 18:59', 'views': '312', 'likes': '12', 'dislikes': '2', 'link': '/item/board_read.naver?code=001510&amp;nid=415522976&amp;page=1', 'score': 672}, {'title': 'ㅎ ㅎ ㅎ', 'date': '2026.03.20 18:09', 'views': '523', 'likes': '11', 'dislikes': '3', 'link': '/item/board_read.naver?code=001510&amp;nid=415520530&amp;page=1', 'score': 853}, {'title': '개미 짜였네 짜였어ㅋㅋㅋ[1]', 'date': '2026.03.20 15:38', 'views': '200', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=001510&amp;nid=415509133&amp;page=4', 'score': 530}, {'title': '또 개미만 털림', 'date': '2026.03.20 15:36', 'views': '274', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=001510&amp;nid=415508740&amp;page=4', 'score': 604}, {'title': '길게 보세요 거래량은 못 속입니다 1차 300...', 'date': '2026.03.20 15:32', 'views': '238', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=001510&amp;nid=415508198&amp;page=5', 'score': 568}, {'title': '진짜 왜팔지??', 'date': '2026.03.20 15:25', 'views': '116', 'likes': '11', 'dislikes': '4', 'link': '/item/board_read.naver?code=001510&amp;nid=415507155&amp;page=5', 'score': 446}]</t>
+          <t>[{'title': '개인만 열라게[2]', 'date': '2026.03.20 15:42', 'views': '216', 'likes': '16', 'dislikes': '2', 'link': '/item/board_read.naver?code=001510&amp;nid=415509682&amp;page=4', 'score': 696}, {'title': '봐라 또 개미들만 팔았제 ?[2]', 'date': '2026.03.20 15:36', 'views': '491', 'likes': '16', 'dislikes': '1', 'link': '/item/board_read.naver?code=001510&amp;nid=415508782&amp;page=4', 'score': 971}, {'title': '오늘의 시황//그리고 액면병합 모멘텀은 계속 유...[1]', 'date': '2026.03.20 18:59', 'views': '352', 'likes': '14', 'dislikes': '3', 'link': '/item/board_read.naver?code=001510&amp;nid=415522976&amp;page=1', 'score': 772}, {'title': '솔직히 형들', 'date': '2026.03.20 17:50', 'views': '293', 'likes': '13', 'dislikes': '4', 'link': '/item/board_read.naver?code=001510&amp;nid=415519424&amp;page=2', 'score': 683}, {'title': '증권주 비교하면 적정가 5~6천이상은 가야...[2]', 'date': '2026.03.20 15:59', 'views': '290', 'likes': '13', 'dislikes': '2', 'link': '/item/board_read.naver?code=001510&amp;nid=415511679&amp;page=4', 'score': 680}, {'title': 'ㅎ ㅎ ㅎ', 'date': '2026.03.20 18:09', 'views': '541', 'likes': '12', 'dislikes': '3', 'link': '/item/board_read.naver?code=001510&amp;nid=415520530&amp;page=1', 'score': 901}, {'title': '아직 저평가 야', 'date': '2026.03.20 18:41', 'views': '166', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=001510&amp;nid=415522092&amp;page=1', 'score': 496}, {'title': '개미 짜였네 짜였어ㅋㅋㅋ[1]', 'date': '2026.03.20 15:38', 'views': '200', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=001510&amp;nid=415509133&amp;page=4', 'score': 530}, {'title': '또 개미만 털림', 'date': '2026.03.20 15:36', 'views': '274', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=001510&amp;nid=415508740&amp;page=4', 'score': 604}, {'title': '길게 보세요 거래량은 못 속입니다 1차 300...', 'date': '2026.03.20 15:32', 'views': '238', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=001510&amp;nid=415508198&amp;page=5', 'score': 568}]</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Positive (62%)</t>
+          <t>Positive (61%)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>[{'title': '시간외  단가~~~~[4]', 'date': '2026.03.20 18:01', 'views': '970', 'likes': '38', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415520059&amp;page=1', 'score': 2110}, {'title': "투자 경보는 시총 100위내에는 해당안됨 '중복...[1]", 'date': '2026.03.20 18:31', 'views': '584', 'likes': '36', 'dislikes': '1', 'link': '/item/board_read.naver?code=047040&amp;nid=415521635&amp;page=1', 'score': 1664}, {'title': '대우야 니가 삼전 하닉 현기차보다 효자다......', 'date': '2026.03.20 15:55', 'views': '194', 'likes': '35', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415511194&amp;page=4', 'score': 1244}, {'title': '금일 상한가 21,000원[1]', 'date': '2026.03.20 11:13', 'views': '146', 'likes': '33', 'dislikes': '5', 'link': '/item/board_read.naver?code=047040&amp;nid=415467547&amp;page=30', 'score': 1136}, {'title': '월요일엄청쏠듯[2]', 'date': '2026.03.20 17:15', 'views': '595', 'likes': '32', 'dislikes': '3', 'link': '/item/board_read.naver?code=047040&amp;nid=415517331&amp;page=2', 'score': 1555}, {'title': '상한가  한방없이 여지껏  이리 말아올린  주...[2]', 'date': '2026.03.20 15:51', 'views': '468', 'likes': '32', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415510710&amp;page=4', 'score': 1428}, {'title': '2만원 가면 호가 50원씩~~', 'date': '2026.03.20 15:52', 'views': '185', 'likes': '27', 'dislikes': '1', 'link': '/item/board_read.naver?code=047040&amp;nid=415510815&amp;page=4', 'score': 995}, {'title': '5년 기다린 보람있네요.[3]', 'date': '2026.03.20 16:04', 'views': '545', 'likes': '26', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415512192&amp;page=3', 'score': 1325}, {'title': '10만원  직행......[1]', 'date': '2026.03.20 16:24', 'views': '285', 'likes': '23', 'dislikes': '2', 'link': '/item/board_read.naver?code=047040&amp;nid=415513878&amp;page=3', 'score': 975}, {'title': '세력분들 감사합니다', 'date': '2026.03.20 15:55', 'views': '102', 'likes': '23', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415511164&amp;page=4', 'score': 792}]</t>
+          <t>[{'title': '시간외  단가~~~~[4]', 'date': '2026.03.20 18:01', 'views': '991', 'likes': '39', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415520059&amp;page=1', 'score': 2161}, {'title': "투자 경보는 시총 100위내에는 해당안됨 '중복...[1]", 'date': '2026.03.20 18:31', 'views': '614', 'likes': '38', 'dislikes': '1', 'link': '/item/board_read.naver?code=047040&amp;nid=415521635&amp;page=1', 'score': 1754}, {'title': '대우야 니가 삼전 하닉 현기차보다 효자다......', 'date': '2026.03.20 15:55', 'views': '194', 'likes': '35', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415511194&amp;page=4', 'score': 1244}, {'title': '월요일엄청쏠듯[2]', 'date': '2026.03.20 17:15', 'views': '601', 'likes': '33', 'dislikes': '3', 'link': '/item/board_read.naver?code=047040&amp;nid=415517331&amp;page=2', 'score': 1591}, {'title': '금일 상한가 21,000원[1]', 'date': '2026.03.20 11:13', 'views': '146', 'likes': '33', 'dislikes': '5', 'link': '/item/board_read.naver?code=047040&amp;nid=415467547&amp;page=30', 'score': 1136}, {'title': '상한가  한방없이 여지껏  이리 말아올린  주...[2]', 'date': '2026.03.20 15:51', 'views': '468', 'likes': '32', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415510710&amp;page=4', 'score': 1428}, {'title': '2만원 가면 호가 50원씩~~', 'date': '2026.03.20 15:52', 'views': '185', 'likes': '27', 'dislikes': '1', 'link': '/item/board_read.naver?code=047040&amp;nid=415510815&amp;page=4', 'score': 995}, {'title': '5년 기다린 보람있네요.[3]', 'date': '2026.03.20 16:04', 'views': '547', 'likes': '26', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415512192&amp;page=4', 'score': 1327}, {'title': '월요일에 갭 뜰 것 같은데', 'date': '2026.03.20 17:53', 'views': '110', 'likes': '23', 'dislikes': '1', 'link': '/item/board_read.naver?code=047040&amp;nid=415519631&amp;page=1', 'score': 800}, {'title': '10만원  직행......[1]', 'date': '2026.03.20 16:24', 'views': '287', 'likes': '23', 'dislikes': '2', 'link': '/item/board_read.naver?code=047040&amp;nid=415513878&amp;page=3', 'score': 977}]</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>[{'title': '양재동 상법', 'date': '2026.03.20 14:59', 'views': '242', 'likes': '21', 'dislikes': '2', 'link': '/item/board_read.naver?code=003380&amp;nid=415502969&amp;page=2', 'score': 872}, {'title': '매집중[3]', 'date': '2026.03.20 11:18', 'views': '385', 'likes': '21', 'dislikes': '4', 'link': '/item/board_read.naver?code=003380&amp;nid=415468347&amp;page=6', 'score': 1015}, {'title': '[하림지주 공유][3]', 'date': '2026.03.20 10:37', 'views': '226', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=003380&amp;nid=415460583&amp;page=7', 'score': 766}, {'title': '안녕하세요 차티스트입니다.', 'date': '2026.03.20 16:20', 'views': '389', 'likes': '17', 'dislikes': '3', 'link': '/item/board_read.naver?code=003380&amp;nid=415513578&amp;page=1', 'score': 899}, {'title': '묻어 두면  몇배 ![1]', 'date': '2026.03.20 15:44', 'views': '542', 'likes': '16', 'dislikes': '2', 'link': '/item/board_read.naver?code=003380&amp;nid=415509939&amp;page=2', 'score': 1022}, {'title': '차트충은 아니지만...[4]', 'date': '2026.03.20 15:32', 'views': '459', 'likes': '16', 'dislikes': '0', 'link': '/item/board_read.naver?code=003380&amp;nid=415508104&amp;page=2', 'score': 939}, {'title': '갈 수 밖에 없는 이유', 'date': '2026.03.20 14:41', 'views': '166', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=003380&amp;nid=415500156&amp;page=3', 'score': 616}, {'title': '월요일 20000원 찍고 화요일 발표하자[1]', 'date': '2026.03.20 13:41', 'views': '201', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=003380&amp;nid=415490894&amp;page=4', 'score': 651}, {'title': '팩트 공유~ 3/17일 2시 양재동 부지 건...[1]', 'date': '2026.03.20 12:08', 'views': '362', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=003380&amp;nid=415476901&amp;page=6', 'score': 812}, {'title': '오늘은 지주사들 날이구만', 'date': '2026.03.20 11:35', 'views': '110', 'likes': '13', 'dislikes': '2', 'link': '/item/board_read.naver?code=003380&amp;nid=415471552&amp;page=6', 'score': 500}]</t>
+          <t>[{'title': '양재동 상법', 'date': '2026.03.20 14:59', 'views': '244', 'likes': '21', 'dislikes': '2', 'link': '/item/board_read.naver?code=003380&amp;nid=415502969&amp;page=2', 'score': 874}, {'title': '매집중[3]', 'date': '2026.03.20 11:18', 'views': '385', 'likes': '21', 'dislikes': '4', 'link': '/item/board_read.naver?code=003380&amp;nid=415468347&amp;page=6', 'score': 1015}, {'title': '[하림지주 공유][3]', 'date': '2026.03.20 10:37', 'views': '227', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=003380&amp;nid=415460583&amp;page=8', 'score': 767}, {'title': '안녕하세요 차티스트입니다.', 'date': '2026.03.20 16:20', 'views': '394', 'likes': '17', 'dislikes': '3', 'link': '/item/board_read.naver?code=003380&amp;nid=415513578&amp;page=1', 'score': 904}, {'title': '묻어 두면  몇배 ![1]', 'date': '2026.03.20 15:44', 'views': '549', 'likes': '16', 'dislikes': '2', 'link': '/item/board_read.naver?code=003380&amp;nid=415509939&amp;page=2', 'score': 1029}, {'title': '차트충은 아니지만...[4]', 'date': '2026.03.20 15:32', 'views': '461', 'likes': '16', 'dislikes': '0', 'link': '/item/board_read.naver?code=003380&amp;nid=415508104&amp;page=2', 'score': 941}, {'title': '갈 수 밖에 없는 이유', 'date': '2026.03.20 14:41', 'views': '167', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=003380&amp;nid=415500156&amp;page=3', 'score': 617}, {'title': '월요일 20000원 찍고 화요일 발표하자[1]', 'date': '2026.03.20 13:41', 'views': '201', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=003380&amp;nid=415490894&amp;page=4', 'score': 651}, {'title': '팩트 공유~ 3/17일 2시 양재동 부지 건...[1]', 'date': '2026.03.20 12:08', 'views': '362', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=003380&amp;nid=415476901&amp;page=6', 'score': 812}, {'title': '오늘은 지주사들 날이구만', 'date': '2026.03.20 11:35', 'views': '110', 'likes': '13', 'dislikes': '2', 'link': '/item/board_read.naver?code=003380&amp;nid=415471552&amp;page=6', 'score': 500}]</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>[{'title': '오랜만에 글써봅니다.[3]', 'date': '2026.03.20 13:40', 'views': '288', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=388050&amp;nid=415490676&amp;page=3', 'score': 468}, {'title': '3년의 저항 뚫음', 'date': '2026.03.20 16:28', 'views': '90', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=388050&amp;nid=415514142&amp;page=1', 'score': 210}, {'title': '다음주 대장 이겠네', 'date': '2026.03.20 15:21', 'views': '43', 'likes': '3', 'dislikes': '1', 'link': '/item/board_read.naver?code=388050&amp;nid=415506512&amp;page=1', 'score': 133}, {'title': '신고가 영역이라', 'date': '2026.03.20 13:36', 'views': '72', 'likes': '3', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415490070&amp;page=3', 'score': 162}, {'title': '&lt;진짜 한결같다 너도.', 'date': '2026.03.20 11:01', 'views': '36', 'likes': '3', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415465467&amp;page=4', 'score': 126}, {'title': '여기 주포 개양이라 윗꼬리 조심하소', 'date': '2026.03.20 11:01', 'views': '26', 'likes': '3', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415465361&amp;page=4', 'score': 116}, {'title': '▣ 1.4만 터치하는 순간...', 'date': '2026.03.20 11:32', 'views': '74', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415471054&amp;page=3', 'score': 134}, {'title': '윗꼬리 전문 상한가 없는 종목임[1]', 'date': '2026.03.20 10:49', 'views': '31', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415462920&amp;page=4', 'score': 91}, {'title': '이게', 'date': '2026.03.20 10:35', 'views': '22', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415460191&amp;page=4', 'score': 82}, {'title': '장중조정시 쓸어 담으시길~~~~[2]', 'date': '2026.03.20 09:46', 'views': '61', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415449742&amp;page=5', 'score': 121}]</t>
+          <t>[{'title': '오랜만에 글써봅니다.[3]', 'date': '2026.03.20 13:40', 'views': '291', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=388050&amp;nid=415490676&amp;page=3', 'score': 471}, {'title': '3년의 저항 뚫음', 'date': '2026.03.20 16:28', 'views': '90', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=388050&amp;nid=415514142&amp;page=1', 'score': 210}, {'title': '다음주 대장 이겠네', 'date': '2026.03.20 15:21', 'views': '43', 'likes': '3', 'dislikes': '1', 'link': '/item/board_read.naver?code=388050&amp;nid=415506512&amp;page=1', 'score': 133}, {'title': '신고가 영역이라', 'date': '2026.03.20 13:36', 'views': '72', 'likes': '3', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415490070&amp;page=3', 'score': 162}, {'title': '&lt;진짜 한결같다 너도.', 'date': '2026.03.20 11:01', 'views': '36', 'likes': '3', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415465467&amp;page=4', 'score': 126}, {'title': '여기 주포 개양이라 윗꼬리 조심하소', 'date': '2026.03.20 11:01', 'views': '26', 'likes': '3', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415465361&amp;page=4', 'score': 116}, {'title': '4만 이상은 가이지♡', 'date': '2026.03.20 19:03', 'views': '16', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415523174&amp;page=1', 'score': 76}, {'title': '▣ 1.4만 터치하는 순간...', 'date': '2026.03.20 11:32', 'views': '74', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415471054&amp;page=3', 'score': 134}, {'title': '윗꼬리 전문 상한가 없는 종목임[1]', 'date': '2026.03.20 10:49', 'views': '31', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415462920&amp;page=4', 'score': 91}, {'title': '이게', 'date': '2026.03.20 10:35', 'views': '22', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415460191&amp;page=4', 'score': 82}]</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>[{'title': '목표가 10만원 갑시다.[2]', 'date': '2026.03.20 15:55', 'views': '248', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415511206&amp;page=3', 'score': 548}, {'title': '시외상이가?[2]', 'date': '2026.03.20 15:46', 'views': '134', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415510141&amp;page=3', 'score': 374}, {'title': '면역항암제[1]', 'date': '2026.03.20 14:48', 'views': '55', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415501211&amp;page=7', 'score': 265}, {'title': '참 이상해.. 3분기 기준 아이엠바이오로직스 ...', 'date': '2026.03.20 09:16', 'views': '116', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415441602&amp;page=14', 'score': 326}, {'title': '매동! 외인/기관 양끌이 매수~[1]', 'date': '2026.03.20 15:36', 'views': '80', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415508796&amp;page=3', 'score': 260}, {'title': '또 속았수다', 'date': '2026.03.20 12:36', 'views': '25', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415480879&amp;page=9', 'score': 205}, {'title': '단일가로 상승할 확률이 높아보이네요[1]', 'date': '2026.03.20 15:42', 'views': '168', 'likes': '5', 'dislikes': '3', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415509687&amp;page=3', 'score': 318}, {'title': '어짜피[1]', 'date': '2026.03.20 14:09', 'views': '51', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415495129&amp;page=8', 'score': 201}, {'title': '재미없네', 'date': '2026.03.20 12:57', 'views': '16', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415483933&amp;page=9', 'score': 166}, {'title': '어제 기도가 통했네[2]', 'date': '2026.03.20 11:58', 'views': '38', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415475444&amp;page=10', 'score': 188}]</t>
+          <t>[{'title': '목표가 10만원 갑시다.[2]', 'date': '2026.03.20 15:55', 'views': '249', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415511206&amp;page=3', 'score': 549}, {'title': '시외상이가?[2]', 'date': '2026.03.20 15:46', 'views': '134', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415510141&amp;page=3', 'score': 374}, {'title': '면역항암제[1]', 'date': '2026.03.20 14:48', 'views': '55', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415501211&amp;page=7', 'score': 265}, {'title': '참 이상해.. 3분기 기준 아이엠바이오로직스 ...', 'date': '2026.03.20 09:16', 'views': '116', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415441602&amp;page=14', 'score': 326}, {'title': '매동! 외인/기관 양끌이 매수~[1]', 'date': '2026.03.20 15:36', 'views': '80', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415508796&amp;page=3', 'score': 260}, {'title': '또 속았수다', 'date': '2026.03.20 12:36', 'views': '25', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415480879&amp;page=9', 'score': 205}, {'title': '단일가로 상승할 확률이 높아보이네요[1]', 'date': '2026.03.20 15:42', 'views': '168', 'likes': '5', 'dislikes': '3', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415509687&amp;page=3', 'score': 318}, {'title': '어짜피[1]', 'date': '2026.03.20 14:09', 'views': '51', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415495129&amp;page=8', 'score': 201}, {'title': '재미없네', 'date': '2026.03.20 12:57', 'views': '16', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415483933&amp;page=9', 'score': 166}, {'title': '어제 기도가 통했네[2]', 'date': '2026.03.20 11:58', 'views': '39', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415475444&amp;page=10', 'score': 189}]</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>[{'title': '이회사는 진짜[1]', 'date': '2026.03.20 10:56', 'views': '72', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415464456&amp;page=3', 'score': 282}, {'title': '20연상 가야지[1]', 'date': '2026.03.20 09:30', 'views': '80', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=007460&amp;nid=415445608&amp;page=5', 'score': 260}, {'title': '기술적 반등일 뿐,,,ㅎㅎ[2]', 'date': '2026.03.20 16:55', 'views': '74', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415515936&amp;page=1', 'score': 224}, {'title': '오늘360원 안착[1]', 'date': '2026.03.20 14:58', 'views': '90', 'likes': '5', 'dislikes': '3', 'link': '/item/board_read.naver?code=007460&amp;nid=415502818&amp;page=1', 'score': 240}, {'title': '장 끝나고', 'date': '2026.03.20 14:57', 'views': '52', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415502648&amp;page=1', 'score': 202}, {'title': '감사보고서 장종료 하고 나올거임.담주450원 넘으...[2]', 'date': '2026.03.20 14:42', 'views': '241', 'likes': '5', 'dislikes': '10', 'link': '/item/board_read.naver?code=007460&amp;nid=415500219&amp;page=1', 'score': 391}, {'title': '또 이러네... 재섭고 정줄논 넘드라[1]', 'date': '2026.03.20 11:45', 'views': '48', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415473398&amp;page=3', 'score': 198}, {'title': '불쌍한 개미들....[1]', 'date': '2026.03.20 16:04', 'views': '129', 'likes': '4', 'dislikes': '4', 'link': '/item/board_read.naver?code=007460&amp;nid=415512154&amp;page=1', 'score': 249}, {'title': '느낌에...[1]', 'date': '2026.03.20 13:26', 'views': '160', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415488389&amp;page=2', 'score': 280}, {'title': '원전주', 'date': '2026.03.20 11:44', 'views': '74', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=007460&amp;nid=415473151&amp;page=3', 'score': 194}]</t>
+          <t>[{'title': '이회사는 진짜[1]', 'date': '2026.03.20 10:56', 'views': '72', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415464456&amp;page=3', 'score': 282}, {'title': '20연상 가야지[1]', 'date': '2026.03.20 09:30', 'views': '80', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=007460&amp;nid=415445608&amp;page=5', 'score': 260}, {'title': '기술적 반등일 뿐,,,ㅎㅎ[2]', 'date': '2026.03.20 16:55', 'views': '76', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415515936&amp;page=1', 'score': 226}, {'title': '오늘360원 안착[1]', 'date': '2026.03.20 14:58', 'views': '90', 'likes': '5', 'dislikes': '3', 'link': '/item/board_read.naver?code=007460&amp;nid=415502818&amp;page=1', 'score': 240}, {'title': '장 끝나고', 'date': '2026.03.20 14:57', 'views': '52', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415502648&amp;page=1', 'score': 202}, {'title': '감사보고서 장종료 하고 나올거임.담주450원 넘으...[2]', 'date': '2026.03.20 14:42', 'views': '243', 'likes': '5', 'dislikes': '10', 'link': '/item/board_read.naver?code=007460&amp;nid=415500219&amp;page=1', 'score': 393}, {'title': '또 이러네... 재섭고 정줄논 넘드라[1]', 'date': '2026.03.20 11:45', 'views': '48', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415473398&amp;page=3', 'score': 198}, {'title': '불쌍한 개미들....[1]', 'date': '2026.03.20 16:04', 'views': '130', 'likes': '4', 'dislikes': '4', 'link': '/item/board_read.naver?code=007460&amp;nid=415512154&amp;page=1', 'score': 250}, {'title': '느낌에...[1]', 'date': '2026.03.20 13:26', 'views': '160', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415488389&amp;page=2', 'score': 280}, {'title': '원전주', 'date': '2026.03.20 11:44', 'views': '74', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=007460&amp;nid=415473151&amp;page=3', 'score': 194}]</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>[[[삼천당꿈(시즌2)]]] - 삼천당의 자신...[18] / [[[삼천당꿈(시즌2)]]]  -경구인슐린 10...[26] / 터제파타이드 경구용 daily &amp; weekly[9] / 공매와 안티야, 형이야[11]</t>
+          <t>[[[삼천당꿈(시즌2)]]] - 삼천당의 자신...[18] / [[[삼천당꿈(시즌2)]]]  -경구인슐린 100...[26] / 공매와 안티야, 형이야[11] / 3월 주총과 4월 20일 IR에서 듣고 싶...[5]</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>[{'title': '[[[삼천당꿈(시즌2)]]] - 삼천당의 자신...[18]', 'date': '2026.03.20 09:05', 'views': '1316', 'likes': '145', 'dislikes': '2', 'link': '/item/board_read.naver?code=000250&amp;nid=415438916&amp;page=31', 'score': 5666}, {'title': '[[[삼천당꿈(시즌2)]]]  -경구인슐린 10...[26]', 'date': '2026.03.20 12:05', 'views': '614', 'likes': '141', 'dislikes': '1', 'link': '/item/board_read.naver?code=000250&amp;nid=415476519&amp;page=15', 'score': 4844}, {'title': '공매와 안티야, 형이야[11]', 'date': '2026.03.20 16:41', 'views': '447', 'likes': '90', 'dislikes': '1', 'link': '/item/board_read.naver?code=000250&amp;nid=415515012&amp;page=4', 'score': 3147}, {'title': '나의 10대 소원[8]', 'date': '2026.03.20 15:53', 'views': '419', 'likes': '90', 'dislikes': '1', 'link': '/item/board_read.naver?code=000250&amp;nid=415510993&amp;page=5', 'score': 3119}, {'title': '터제파타이드 경구용 daily &amp; weekly[9]', 'date': '2026.03.20 15:40', 'views': '554', 'likes': '87', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415509385&amp;page=5', 'score': 3164}, {'title': '가슴이 또[5]', 'date': '2026.03.20 16:10', 'views': '564', 'likes': '82', 'dislikes': '2', 'link': '/item/board_read.naver?code=000250&amp;nid=415512731&amp;page=4', 'score': 3024}, {'title': '3월 주총과 4월 20일 IR에서 듣고 싶...[5]', 'date': '2026.03.20 16:56', 'views': '742', 'likes': '80', 'dislikes': '5', 'link': '/item/board_read.naver?code=000250&amp;nid=415515999&amp;page=4', 'score': 3142}, {'title': 'PeternAnne님 감사합니다^^[7]', 'date': '2026.03.20 15:57', 'views': '376', 'likes': '79', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415511422&amp;page=5', 'score': 2746}, {'title': '주주분들, 코스닥 1위 달성을 축하드립니다[5]', 'date': '2026.03.20 18:01', 'views': '407', 'likes': '75', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415520063&amp;page=2', 'score': 2657}, {'title': '대한민국에 위해주 애널리스트 말고 전부 외면하...[3]', 'date': '2026.03.20 18:31', 'views': '445', 'likes': '69', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415521650&amp;page=1', 'score': 2515}]</t>
+          <t>[{'title': '[[[삼천당꿈(시즌2)]]] - 삼천당의 자신...[18]', 'date': '2026.03.20 09:05', 'views': '1321', 'likes': '145', 'dislikes': '2', 'link': '/item/board_read.naver?code=000250&amp;nid=415438916&amp;page=31', 'score': 5671}, {'title': '[[[삼천당꿈(시즌2)]]]  -경구인슐린 100...[26]', 'date': '2026.03.20 12:05', 'views': '615', 'likes': '141', 'dislikes': '1', 'link': '/item/board_read.naver?code=000250&amp;nid=415476519&amp;page=15', 'score': 4845}, {'title': '공매와 안티야, 형이야[11]', 'date': '2026.03.20 16:41', 'views': '454', 'likes': '92', 'dislikes': '1', 'link': '/item/board_read.naver?code=000250&amp;nid=415515012&amp;page=4', 'score': 3214}, {'title': '나의 10대 소원[8]', 'date': '2026.03.20 15:53', 'views': '420', 'likes': '90', 'dislikes': '1', 'link': '/item/board_read.naver?code=000250&amp;nid=415510993&amp;page=5', 'score': 3120}, {'title': '터제파타이드 경구용 daily &amp; weekly...[9]', 'date': '2026.03.20 15:40', 'views': '554', 'likes': '88', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415509385&amp;page=6', 'score': 3194}, {'title': '가슴이 또[5]', 'date': '2026.03.20 16:10', 'views': '566', 'likes': '84', 'dislikes': '2', 'link': '/item/board_read.naver?code=000250&amp;nid=415512731&amp;page=4', 'score': 3086}, {'title': '3월 주총과 4월 20일 IR에서 듣고 싶...[5]', 'date': '2026.03.20 16:56', 'views': '751', 'likes': '82', 'dislikes': '5', 'link': '/item/board_read.naver?code=000250&amp;nid=415515999&amp;page=4', 'score': 3211}, {'title': 'PeternAnne님 감사합니다^^[7]', 'date': '2026.03.20 15:57', 'views': '377', 'likes': '79', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415511422&amp;page=5', 'score': 2747}, {'title': '주주분들, 코스닥 1위 달성을 축하드립니다[5]', 'date': '2026.03.20 18:01', 'views': '422', 'likes': '78', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415520063&amp;page=2', 'score': 2762}, {'title': '대한민국에 위해주 애널리스트 말고 전부 외...[3]', 'date': '2026.03.20 18:31', 'views': '464', 'likes': '73', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415521650&amp;page=2', 'score': 2654}]</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>[{'title': '9년 만에 주총참여[1]', 'date': '2026.03.20 11:40', 'views': '421', 'likes': '25', 'dislikes': '0', 'link': '/item/board_read.naver?code=008700&amp;nid=415472484&amp;page=3', 'score': 1171}, {'title': '3연상간다[2]', 'date': '2026.03.20 09:11', 'views': '175', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=008700&amp;nid=415440381&amp;page=5', 'score': 385}, {'title': '전체주식 33%나 매수+소각은.증시역사 최초.....[1]', 'date': '2026.03.20 16:36', 'views': '235', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=008700&amp;nid=415514670&amp;page=1', 'score': 415}, {'title': '욕심없이 잘 먹고갑니다', 'date': '2026.03.20 09:06', 'views': '176', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=008700&amp;nid=415439116&amp;page=5', 'score': 356}, {'title': '매수가 1560원보다 올라가면', 'date': '2026.03.20 08:21', 'views': '85', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=008700&amp;nid=415432634&amp;page=6', 'score': 265}, {'title': '유통주식 반을. 소각 5연상', 'date': '2026.03.20 11:27', 'views': '104', 'likes': '5', 'dislikes': '4', 'link': '/item/board_read.naver?code=008700&amp;nid=415470137&amp;page=3', 'score': 254}, {'title': '매각 포지션 보다 엠엔에이 인것같다[3]', 'date': '2026.03.20 10:43', 'views': '168', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=008700&amp;nid=415461642&amp;page=3', 'score': 318}, {'title': '공개매수 소각 한다는건', 'date': '2026.03.20 09:01', 'views': '66', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=008700&amp;nid=415437807&amp;page=5', 'score': 216}, {'title': '36층 주민입니다.', 'date': '2026.03.20 15:56', 'views': '90', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=008700&amp;nid=415511332&amp;page=1', 'score': 210}, {'title': '시작 동시호가 끝나는 동시호가[1]', 'date': '2026.03.20 15:31', 'views': '110', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=008700&amp;nid=415507932&amp;page=1', 'score': 230}]</t>
+          <t>[{'title': '9년 만에 주총참여[1]', 'date': '2026.03.20 11:40', 'views': '421', 'likes': '25', 'dislikes': '0', 'link': '/item/board_read.naver?code=008700&amp;nid=415472484&amp;page=3', 'score': 1171}, {'title': '3연상간다[2]', 'date': '2026.03.20 09:11', 'views': '175', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=008700&amp;nid=415440381&amp;page=5', 'score': 385}, {'title': '전체주식 33%나 매수+소각은.증시역사 최초.....[1]', 'date': '2026.03.20 16:36', 'views': '241', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=008700&amp;nid=415514670&amp;page=1', 'score': 421}, {'title': '욕심없이 잘 먹고갑니다', 'date': '2026.03.20 09:06', 'views': '176', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=008700&amp;nid=415439116&amp;page=5', 'score': 356}, {'title': '매수가 1560원보다 올라가면', 'date': '2026.03.20 08:21', 'views': '85', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=008700&amp;nid=415432634&amp;page=6', 'score': 265}, {'title': '유통주식 반을. 소각 5연상', 'date': '2026.03.20 11:27', 'views': '104', 'likes': '5', 'dislikes': '4', 'link': '/item/board_read.naver?code=008700&amp;nid=415470137&amp;page=3', 'score': 254}, {'title': '매각 포지션 보다 엠엔에이 인것같다[3]', 'date': '2026.03.20 10:43', 'views': '168', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=008700&amp;nid=415461642&amp;page=3', 'score': 318}, {'title': '공개매수 소각 한다는건', 'date': '2026.03.20 09:01', 'views': '66', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=008700&amp;nid=415437807&amp;page=5', 'score': 216}, {'title': '36층 주민입니다.', 'date': '2026.03.20 15:56', 'views': '92', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=008700&amp;nid=415511332&amp;page=1', 'score': 212}, {'title': '시작 동시호가 끝나는 동시호가[1]', 'date': '2026.03.20 15:31', 'views': '111', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=008700&amp;nid=415507932&amp;page=1', 'score': 231}]</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>휴림로봇과 키맞춤 할거야[3] / ■제2의 우리기술주다[1] / 텐버거 종목 같다[1] / 상철아 ㅡ</t>
+          <t>휴림로봇과 키맞춤 할거야[3] / ■제2의 우리기술주다[1] / 텐버거 종목 같다[1] / 헤헤헤헤[1]</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>[{'title': '상철아 ㅡ', 'date': '2026.03.20 13:55', 'views': '27', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=078590&amp;nid=415492834&amp;page=4', 'score': 267}, {'title': '공포에사라', 'date': '2026.03.20 14:38', 'views': '28', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415499587&amp;page=2', 'score': 238}, {'title': '헤헤헤헤[1]', 'date': '2026.03.20 16:50', 'views': '56', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415515630&amp;page=1', 'score': 236}, {'title': '텐버거 종목 같다[1]', 'date': '2026.03.20 15:33', 'views': '136', 'likes': '6', 'dislikes': '2', 'link': '/item/board_read.naver?code=078590&amp;nid=415508262&amp;page=1', 'score': 316}, {'title': '신바거!', 'date': '2026.03.20 14:37', 'views': '22', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415499557&amp;page=2', 'score': 202}, {'title': '대차게 들어올려라~~~~~', 'date': '2026.03.20 14:24', 'views': '26', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415497582&amp;page=3', 'score': 206}, {'title': '상 상 상', 'date': '2026.03.20 13:51', 'views': '29', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415492355&amp;page=4', 'score': 209}, {'title': '천원 뚫기[1]', 'date': '2026.03.20 13:26', 'views': '80', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415488372&amp;page=5', 'score': 260}, {'title': '■제2의 우리기술주다[1]', 'date': '2026.03.20 12:39', 'views': '192', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=078590&amp;nid=415481237&amp;page=5', 'score': 372}, {'title': '휴림로봇과 키맞춤 할거야[3]', 'date': '2026.03.20 12:07', 'views': '558', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=078590&amp;nid=415476887&amp;page=5', 'score': 738}]</t>
+          <t>[{'title': '상철아 ㅡ', 'date': '2026.03.20 13:55', 'views': '27', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=078590&amp;nid=415492834&amp;page=4', 'score': 267}, {'title': '헤헤헤헤[1]', 'date': '2026.03.20 16:50', 'views': '63', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415515630&amp;page=1', 'score': 273}, {'title': '공포에사라', 'date': '2026.03.20 14:38', 'views': '28', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415499587&amp;page=2', 'score': 238}, {'title': '텐버거 종목 같다[1]', 'date': '2026.03.20 15:33', 'views': '138', 'likes': '6', 'dislikes': '2', 'link': '/item/board_read.naver?code=078590&amp;nid=415508262&amp;page=1', 'score': 318}, {'title': '신바거!', 'date': '2026.03.20 14:37', 'views': '22', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415499557&amp;page=2', 'score': 202}, {'title': '대차게 들어올려라~~~~~', 'date': '2026.03.20 14:24', 'views': '26', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415497582&amp;page=3', 'score': 206}, {'title': '상 상 상', 'date': '2026.03.20 13:51', 'views': '29', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415492355&amp;page=4', 'score': 209}, {'title': '천원 뚫기[1]', 'date': '2026.03.20 13:26', 'views': '81', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415488372&amp;page=5', 'score': 261}, {'title': '■제2의 우리기술주다[1]', 'date': '2026.03.20 12:39', 'views': '192', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=078590&amp;nid=415481237&amp;page=5', 'score': 372}, {'title': '휴림로봇과 키맞춤 할거야[3]', 'date': '2026.03.20 12:07', 'views': '559', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=078590&amp;nid=415476887&amp;page=5', 'score': 739}]</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Negative (67%)</t>
+          <t>Negative (66%)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>[{'title': '60층 이상에서 마음고생 중인 주주분들을 위해[4]', 'date': '2026.03.20 18:03', 'views': '486', 'likes': '21', 'dislikes': '2', 'link': '/item/board_read.naver?code=475150&amp;nid=415520191&amp;page=3', 'score': 1116}, {'title': 'SK다[1]', 'date': '2026.03.20 18:56', 'views': '140', 'likes': '15', 'dislikes': '6', 'link': '/item/board_read.naver?code=475150&amp;nid=415522858&amp;page=2', 'score': 590}, {'title': '다음주엔 앞자리7?[1]', 'date': '2026.03.20 14:30', 'views': '332', 'likes': '15', 'dislikes': '4', 'link': '/item/board_read.naver?code=475150&amp;nid=415498430&amp;page=14', 'score': 782}, {'title': '[매동] 실시간 매매추이 5차', 'date': '2026.03.20 14:25', 'views': '227', 'likes': '14', 'dislikes': '3', 'link': '/item/board_read.naver?code=475150&amp;nid=415497771&amp;page=14', 'score': 647}, {'title': '물렸으면 지금 넥장에서 판매할거 아니...[1]', 'date': '2026.03.20 17:30', 'views': '183', 'likes': '13', 'dislikes': '5', 'link': '/item/board_read.naver?code=475150&amp;nid=415518308&amp;page=4', 'score': 573}, {'title': '상한가ㄱㄱ', 'date': '2026.03.20 16:10', 'views': '64', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=475150&amp;nid=415512777&amp;page=7', 'score': 454}, {'title': '66500에 풀신용 지른 1인입니다[3]', 'date': '2026.03.20 15:01', 'views': '262', 'likes': '13', 'dislikes': '5', 'link': '/item/board_read.naver?code=475150&amp;nid=415503210&amp;page=12', 'score': 652}, {'title': '간단히 얘기한다 시총 20조 넘는다', 'date': '2026.03.20 19:18', 'views': '208', 'likes': '12', 'dislikes': '2', 'link': '/item/board_read.naver?code=475150&amp;nid=415523855&amp;page=1', 'score': 568}, {'title': '차라리', 'date': '2026.03.20 16:10', 'views': '109', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=475150&amp;nid=415512730&amp;page=7', 'score': 469}, {'title': '66500원에 신용으로 산거 손절하고 간다[5]', 'date': '2026.03.20 16:18', 'views': '529', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=475150&amp;nid=415513374&amp;page=7', 'score': 859}]</t>
+          <t>[{'title': '60층 이상에서 마음고생 중인 주주분들을 위해[4]', 'date': '2026.03.20 18:03', 'views': '489', 'likes': '21', 'dislikes': '2', 'link': '/item/board_read.naver?code=475150&amp;nid=415520191&amp;page=3', 'score': 1119}, {'title': 'SK다[1]', 'date': '2026.03.20 18:56', 'views': '144', 'likes': '15', 'dislikes': '6', 'link': '/item/board_read.naver?code=475150&amp;nid=415522858&amp;page=2', 'score': 594}, {'title': '다음주엔 앞자리7?[1]', 'date': '2026.03.20 14:30', 'views': '332', 'likes': '15', 'dislikes': '4', 'link': '/item/board_read.naver?code=475150&amp;nid=415498430&amp;page=14', 'score': 782}, {'title': '[매동] 실시간 매매추이 5차', 'date': '2026.03.20 14:25', 'views': '227', 'likes': '14', 'dislikes': '3', 'link': '/item/board_read.naver?code=475150&amp;nid=415497771&amp;page=14', 'score': 647}, {'title': '물렸으면 지금 넥장에서 판매할거 아니면 그냥...[1]', 'date': '2026.03.20 17:30', 'views': '185', 'likes': '13', 'dislikes': '5', 'link': '/item/board_read.naver?code=475150&amp;nid=415518308&amp;page=5', 'score': 575}, {'title': '상한가ㄱㄱ', 'date': '2026.03.20 16:10', 'views': '64', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=475150&amp;nid=415512777&amp;page=7', 'score': 454}, {'title': '66500에 풀신용 지른 1인입니다[3]', 'date': '2026.03.20 15:01', 'views': '262', 'likes': '13', 'dislikes': '5', 'link': '/item/board_read.naver?code=475150&amp;nid=415503210&amp;page=12', 'score': 652}, {'title': '간단히 얘기한다 시총 20조 넘는다', 'date': '2026.03.20 19:18', 'views': '229', 'likes': '12', 'dislikes': '2', 'link': '/item/board_read.naver?code=475150&amp;nid=415523855&amp;page=2', 'score': 589}, {'title': '차라리', 'date': '2026.03.20 16:10', 'views': '109', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=475150&amp;nid=415512730&amp;page=7', 'score': 469}, {'title': '66500원에 신용으로 산거 손절하고 간다[5]', 'date': '2026.03.20 16:18', 'views': '530', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=475150&amp;nid=415513374&amp;page=7', 'score': 860}]</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>[{'title': '간판부터 바꾸면 안되나?', 'date': '2026.03.20 16:08', 'views': '102', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=002780&amp;nid=415512538&amp;page=1', 'score': 552}, {'title': '오늘 외국인 120만주 나감', 'date': '2026.03.20 14:46', 'views': '93', 'likes': '13', 'dislikes': '5', 'link': '/item/board_read.naver?code=002780&amp;nid=415500919&amp;page=2', 'score': 483}, {'title': '화가..많이 나시죠~[1]', 'date': '2026.03.20 15:10', 'views': '199', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=002780&amp;nid=415504779&amp;page=2', 'score': 499}, {'title': '난진흥이가 효성하고 잘하길 빌어', 'date': '2026.03.20 14:46', 'views': '56', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=002780&amp;nid=415500896&amp;page=2', 'score': 326}, {'title': '27프로[2]', 'date': '2026.03.20 14:36', 'views': '123', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=002780&amp;nid=415499375&amp;page=2', 'score': 393}, {'title': '날마다[5]', 'date': '2026.03.20 12:12', 'views': '71', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=002780&amp;nid=415477539&amp;page=6', 'score': 341}, {'title': '호재가 넘사라 내가봤을땐 삼표처럼 1만 찍는다[3]', 'date': '2026.03.20 13:36', 'views': '127', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=002780&amp;nid=415490049&amp;page=3', 'score': 367}, {'title': '3000 올까요 몇년전 오세훈 출마할때 물렸...', 'date': '2026.03.20 13:20', 'views': '47', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=002780&amp;nid=415487402&amp;page=4', 'score': 287}, {'title': '전력설비', 'date': '2026.03.20 08:03', 'views': '54', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=002780&amp;nid=415430271&amp;page=9', 'score': 294}, {'title': '이제1파 상승했다[2]', 'date': '2026.03.20 16:25', 'views': '218', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=002780&amp;nid=415513930&amp;page=1', 'score': 428}]</t>
+          <t>[{'title': '간판부터 바꾸면 안되나?', 'date': '2026.03.20 16:08', 'views': '103', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=002780&amp;nid=415512538&amp;page=1', 'score': 553}, {'title': '오늘 외국인 120만주 나감', 'date': '2026.03.20 14:46', 'views': '94', 'likes': '13', 'dislikes': '5', 'link': '/item/board_read.naver?code=002780&amp;nid=415500919&amp;page=2', 'score': 484}, {'title': '화가..많이 나시죠~[1]', 'date': '2026.03.20 15:10', 'views': '201', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=002780&amp;nid=415504779&amp;page=2', 'score': 501}, {'title': '난진흥이가 효성하고 잘하길 빌어', 'date': '2026.03.20 14:46', 'views': '57', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=002780&amp;nid=415500896&amp;page=2', 'score': 327}, {'title': '27프로[2]', 'date': '2026.03.20 14:36', 'views': '124', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=002780&amp;nid=415499375&amp;page=2', 'score': 394}, {'title': '날마다[5]', 'date': '2026.03.20 12:12', 'views': '71', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=002780&amp;nid=415477539&amp;page=6', 'score': 341}, {'title': '호재가 넘사라 내가봤을땐 삼표처럼 1만 찍는...[3]', 'date': '2026.03.20 13:36', 'views': '127', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=002780&amp;nid=415490049&amp;page=4', 'score': 367}, {'title': '3000 올까요 몇년전 오세훈 출마할때 물렸...', 'date': '2026.03.20 13:20', 'views': '47', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=002780&amp;nid=415487402&amp;page=4', 'score': 287}, {'title': '전력설비', 'date': '2026.03.20 08:03', 'views': '54', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=002780&amp;nid=415430271&amp;page=9', 'score': 294}, {'title': '이제1파 상승했다[2]', 'date': '2026.03.20 16:25', 'views': '221', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=002780&amp;nid=415513930&amp;page=1', 'score': 431}]</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>[{'title': '오늘 상한가한방~~~~![1]', 'date': '2026.03.20 10:04', 'views': '222', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=003530&amp;nid=415453916&amp;page=5', 'score': 612}, {'title': '다음주', 'date': '2026.03.20 15:07', 'views': '182', 'likes': '12', 'dislikes': '6', 'link': '/item/board_read.naver?code=003530&amp;nid=415504261&amp;page=1', 'score': 542}, {'title': '내 평단[1]', 'date': '2026.03.20 12:12', 'views': '145', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=003530&amp;nid=415477564&amp;page=4', 'score': 385}, {'title': '어이가없네 8000을넘겨버리네[1]', 'date': '2026.03.20 12:10', 'views': '70', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=003530&amp;nid=415477276&amp;page=4', 'score': 310}, {'title': '담주부터 오를거에용', 'date': '2026.03.20 16:55', 'views': '46', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=003530&amp;nid=415515972&amp;page=1', 'score': 256}, {'title': '쫄거있나? 담주 슈팅 나올듯[1]', 'date': '2026.03.20 17:18', 'views': '146', 'likes': '6', 'dislikes': '2', 'link': '/item/board_read.naver?code=003530&amp;nid=415517562&amp;page=1', 'score': 326}, {'title': '2018년 10월 부터 보유[3]', 'date': '2026.03.20 13:15', 'views': '138', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415486541&amp;page=3', 'score': 318}, {'title': '힘내라힘!!!', 'date': '2026.03.20 10:46', 'views': '26', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415462376&amp;page=5', 'score': 206}, {'title': '드디어 골든 크로스 !!!', 'date': '2026.03.20 10:17', 'views': '42', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415456712&amp;page=5', 'score': 222}, {'title': '중소형주로 매수 이동 ~~~', 'date': '2026.03.20 10:02', 'views': '43', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415453587&amp;page=5', 'score': 223}]</t>
+          <t>[{'title': '오늘 상한가한방~~~~![1]', 'date': '2026.03.20 10:04', 'views': '222', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=003530&amp;nid=415453916&amp;page=5', 'score': 612}, {'title': '다음주', 'date': '2026.03.20 15:07', 'views': '182', 'likes': '12', 'dislikes': '6', 'link': '/item/board_read.naver?code=003530&amp;nid=415504261&amp;page=1', 'score': 542}, {'title': '내 평단[1]', 'date': '2026.03.20 12:12', 'views': '145', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=003530&amp;nid=415477564&amp;page=4', 'score': 385}, {'title': '어이가없네 8000을넘겨버리네[1]', 'date': '2026.03.20 12:10', 'views': '70', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=003530&amp;nid=415477276&amp;page=4', 'score': 310}, {'title': '쫄거있나? 담주 슈팅 나올듯[1]', 'date': '2026.03.20 17:18', 'views': '148', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=003530&amp;nid=415517562&amp;page=1', 'score': 358}, {'title': '담주부터 오를거에용', 'date': '2026.03.20 16:55', 'views': '46', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=003530&amp;nid=415515972&amp;page=1', 'score': 256}, {'title': '2018년 10월 부터 보유[3]', 'date': '2026.03.20 13:15', 'views': '139', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415486541&amp;page=3', 'score': 319}, {'title': '힘내라힘!!!', 'date': '2026.03.20 10:46', 'views': '26', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415462376&amp;page=5', 'score': 206}, {'title': '드디어 골든 크로스 !!!', 'date': '2026.03.20 10:17', 'views': '42', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415456712&amp;page=5', 'score': 222}, {'title': '중소형주로 매수 이동 ~~~', 'date': '2026.03.20 10:02', 'views': '43', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415453587&amp;page=5', 'score': 223}]</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>[{'title': '3년 맘고생하고  쬐끔 수익 보고 갑니다[1]', 'date': '2026.03.20 13:52', 'views': '261', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415492503&amp;page=2', 'score': 711}, {'title': '차트 정배열 완성 됬네요[3]', 'date': '2026.03.20 15:55', 'views': '363', 'likes': '10', 'dislikes': '7', 'link': '/item/board_read.naver?code=417200&amp;nid=415511278&amp;page=1', 'score': 663}, {'title': '엘머', 'date': '2026.03.20 15:46', 'views': '123', 'likes': '10', 'dislikes': '5', 'link': '/item/board_read.naver?code=417200&amp;nid=415510182&amp;page=1', 'score': 423}, {'title': '오늘도', 'date': '2026.03.20 15:12', 'views': '74', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415504977&amp;page=1', 'score': 344}, {'title': '내년 연말까지 들고가렵니다. 목표가 15만원[2]', 'date': '2026.03.20 09:23', 'views': '275', 'likes': '9', 'dislikes': '7', 'link': '/item/board_read.naver?code=417200&amp;nid=415443758&amp;page=7', 'score': 545}, {'title': '뚫자 !! 30,000[1]', 'date': '2026.03.20 12:12', 'views': '88', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415477559&amp;page=3', 'score': 328}, {'title': '주가 오르니까 정신병원에서 대탈출했냐?[2]', 'date': '2026.03.20 16:59', 'views': '120', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415516220&amp;page=1', 'score': 330}, {'title': '3만원대만가면', 'date': '2026.03.20 16:40', 'views': '92', 'likes': '7', 'dislikes': '5', 'link': '/item/board_read.naver?code=417200&amp;nid=415514966&amp;page=1', 'score': 302}, {'title': '두시간 기어오르고 10분만에 내려오네 잡스...', 'date': '2026.03.20 13:09', 'views': '45', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=417200&amp;nid=415485662&amp;page=2', 'score': 255}, {'title': '이제[1]', 'date': '2026.03.20 12:08', 'views': '120', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=417200&amp;nid=415476899&amp;page=3', 'score': 330}]</t>
+          <t>[{'title': '3년 맘고생하고  쬐끔 수익 보고 갑니다[1]', 'date': '2026.03.20 13:52', 'views': '261', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415492503&amp;page=2', 'score': 711}, {'title': '차트 정배열 완성 됬네요[3]', 'date': '2026.03.20 15:55', 'views': '369', 'likes': '10', 'dislikes': '7', 'link': '/item/board_read.naver?code=417200&amp;nid=415511278&amp;page=1', 'score': 669}, {'title': '엘머', 'date': '2026.03.20 15:46', 'views': '125', 'likes': '10', 'dislikes': '5', 'link': '/item/board_read.naver?code=417200&amp;nid=415510182&amp;page=1', 'score': 425}, {'title': '오늘도', 'date': '2026.03.20 15:12', 'views': '74', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415504977&amp;page=1', 'score': 344}, {'title': '내년 연말까지 들고가렵니다. 목표가 15만원[2]', 'date': '2026.03.20 09:23', 'views': '275', 'likes': '9', 'dislikes': '7', 'link': '/item/board_read.naver?code=417200&amp;nid=415443758&amp;page=7', 'score': 545}, {'title': '뚫자 !! 30,000[1]', 'date': '2026.03.20 12:12', 'views': '89', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415477559&amp;page=3', 'score': 329}, {'title': '주가 오르니까 정신병원에서 대탈출했냐?[2]', 'date': '2026.03.20 16:59', 'views': '123', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415516220&amp;page=1', 'score': 333}, {'title': '3만원대만가면', 'date': '2026.03.20 16:40', 'views': '94', 'likes': '7', 'dislikes': '5', 'link': '/item/board_read.naver?code=417200&amp;nid=415514966&amp;page=1', 'score': 304}, {'title': '두시간 기어오르고 10분만에 내려오네 잡스...', 'date': '2026.03.20 13:09', 'views': '45', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=417200&amp;nid=415485662&amp;page=2', 'score': 255}, {'title': '이제[1]', 'date': '2026.03.20 12:08', 'views': '120', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=417200&amp;nid=415476899&amp;page=3', 'score': 330}]</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Positive (83%)</t>
+          <t>Positive (81%)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>[{'title': '배신자', 'date': '2026.03.20 15:35', 'views': '320', 'likes': '34', 'dislikes': '1', 'link': '/item/board_read.naver?code=088350&amp;nid=415508656&amp;page=2', 'score': 1340}, {'title': '대우건설보다는 높아야 하지않나???[1]', 'date': '2026.03.20 15:34', 'views': '127', 'likes': '26', 'dislikes': '2', 'link': '/item/board_read.naver?code=088350&amp;nid=415508561&amp;page=2', 'score': 907}, {'title': '예금보험공사  10퍼 지분[2]', 'date': '2026.03.20 08:20', 'views': '299', 'likes': '25', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415432488&amp;page=8', 'score': 1049}, {'title': '네이버에 저 pbr주 기사 떳으니[2]', 'date': '2026.03.20 16:08', 'views': '368', 'likes': '23', 'dislikes': '3', 'link': '/item/board_read.naver?code=088350&amp;nid=415512532&amp;page=1', 'score': 1058}, {'title': '잘 먹고 가거라[2]', 'date': '2026.03.20 15:33', 'views': '268', 'likes': '20', 'dislikes': '2', 'link': '/item/board_read.naver?code=088350&amp;nid=415508342&amp;page=2', 'score': 868}, {'title': '2남, 금융계열분리~', 'date': '2026.03.20 13:09', 'views': '225', 'likes': '19', 'dislikes': '3', 'link': '/item/board_read.naver?code=088350&amp;nid=415485697&amp;page=4', 'score': 795}, {'title': '뉴스에는 한생 pbr 0.18로 나오네요', 'date': '2026.03.20 10:55', 'views': '198', 'likes': '18', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415464145&amp;page=6', 'score': 738}, {'title': '다음주[1]', 'date': '2026.03.20 17:10', 'views': '76', 'likes': '17', 'dislikes': '1', 'link': '/item/board_read.naver?code=088350&amp;nid=415517019&amp;page=1', 'score': 586}, {'title': '진짜 사력을 다해 죽을힘을 다해 가용수단을 ...[1]', 'date': '2026.03.20 14:07', 'views': '144', 'likes': '17', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415494738&amp;page=3', 'score': 654}, {'title': '청와대 금감원 지역구 국회의원실에 자료 보내기', 'date': '2026.03.20 18:07', 'views': '66', 'likes': '15', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415520375&amp;page=1', 'score': 516}]</t>
+          <t>[{'title': '배신자', 'date': '2026.03.20 15:35', 'views': '323', 'likes': '34', 'dislikes': '1', 'link': '/item/board_read.naver?code=088350&amp;nid=415508656&amp;page=1', 'score': 1343}, {'title': '대우건설보다는 높아야 하지않나???[1]', 'date': '2026.03.20 15:34', 'views': '129', 'likes': '26', 'dislikes': '2', 'link': '/item/board_read.naver?code=088350&amp;nid=415508561&amp;page=2', 'score': 909}, {'title': '예금보험공사  10퍼 지분[2]', 'date': '2026.03.20 08:20', 'views': '299', 'likes': '25', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415432488&amp;page=8', 'score': 1049}, {'title': '네이버에 저 pbr주 기사 떳으니[2]', 'date': '2026.03.20 16:08', 'views': '373', 'likes': '23', 'dislikes': '3', 'link': '/item/board_read.naver?code=088350&amp;nid=415512532&amp;page=1', 'score': 1063}, {'title': '잘 먹고 가거라[2]', 'date': '2026.03.20 15:33', 'views': '270', 'likes': '20', 'dislikes': '2', 'link': '/item/board_read.naver?code=088350&amp;nid=415508342&amp;page=2', 'score': 870}, {'title': '2남, 금융계열분리~', 'date': '2026.03.20 13:09', 'views': '225', 'likes': '19', 'dislikes': '3', 'link': '/item/board_read.naver?code=088350&amp;nid=415485697&amp;page=4', 'score': 795}, {'title': '다음주[1]', 'date': '2026.03.20 17:10', 'views': '82', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=088350&amp;nid=415517019&amp;page=1', 'score': 622}, {'title': '뉴스에는 한생 pbr 0.18로 나오네요', 'date': '2026.03.20 10:55', 'views': '198', 'likes': '18', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415464145&amp;page=6', 'score': 738}, {'title': '청와대 금감원 지역구 국회의원실에 자료 보내기', 'date': '2026.03.20 18:07', 'views': '68', 'likes': '17', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415520375&amp;page=1', 'score': 578}, {'title': '진짜 사력을 다해 죽을힘을 다해 가용수단을 ...[1]', 'date': '2026.03.20 14:07', 'views': '144', 'likes': '17', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415494738&amp;page=3', 'score': 654}]</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Positive (70%)</t>
+          <t>Positive (68%)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>[{'title': '구멍가게 굴뚝주 잡고 시총 3조?[3]', 'date': '2026.03.20 17:23', 'views': '126', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415517895&amp;page=1', 'score': 486}, {'title': '외국인이 1백만주 팔든 사든', 'date': '2026.03.20 17:08', 'views': '63', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=006910&amp;nid=415516892&amp;page=1', 'score': 363}, {'title': '주린이인데 그래서 사야하는건가요 말아야하는건...[2]', 'date': '2026.03.20 10:59', 'views': '158', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=006910&amp;nid=415464951&amp;page=9', 'score': 458}, {'title': '정직한 주식은 실적으로 말한다.[1]', 'date': '2026.03.20 10:42', 'views': '63', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415461546&amp;page=9', 'score': 363}, {'title': '머머 한다. 카더라만 말고', 'date': '2026.03.20 17:47', 'views': '71', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415519288&amp;page=1', 'score': 341}, {'title': '한심한 사람들', 'date': '2026.03.20 17:43', 'views': '56', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=006910&amp;nid=415519033&amp;page=1', 'score': 326}, {'title': '주주분들 버티면 크게 갑니다', 'date': '2026.03.20 10:50', 'views': '62', 'likes': '9', 'dislikes': '3', 'link': '/item/board_read.naver?code=006910&amp;nid=415463282&amp;page=9', 'score': 332}, {'title': '어제 실적 발표한거 보니 전년대비 거의 10...', 'date': '2026.03.20 10:48', 'views': '110', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415462771&amp;page=9', 'score': 380}, {'title': '보성과 두산 신고가[2]', 'date': '2026.03.20 11:06', 'views': '101', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415466318&amp;page=9', 'score': 341}, {'title': '오늘은 상한가 가는날 맞죠ㅋ[3]', 'date': '2026.03.20 09:39', 'views': '95', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=006910&amp;nid=415448007&amp;page=11', 'score': 305}]</t>
+          <t>[{'title': '구멍가게 굴뚝주 잡고 시총 3조?[3]', 'date': '2026.03.20 17:23', 'views': '130', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415517895&amp;page=1', 'score': 490}, {'title': '외국인이 1백만주 팔든 사든', 'date': '2026.03.20 17:08', 'views': '64', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=006910&amp;nid=415516892&amp;page=1', 'score': 364}, {'title': '주린이인데 그래서 사야하는건가요 말아야하는건...[2]', 'date': '2026.03.20 10:59', 'views': '158', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=006910&amp;nid=415464951&amp;page=9', 'score': 458}, {'title': '정직한 주식은 실적으로 말한다.[1]', 'date': '2026.03.20 10:42', 'views': '63', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415461546&amp;page=9', 'score': 363}, {'title': '머머 한다. 카더라만 말고', 'date': '2026.03.20 17:47', 'views': '76', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415519288&amp;page=1', 'score': 346}, {'title': '한심한 사람들', 'date': '2026.03.20 17:43', 'views': '58', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=006910&amp;nid=415519033&amp;page=1', 'score': 328}, {'title': '주주분들 버티면 크게 갑니다', 'date': '2026.03.20 10:50', 'views': '62', 'likes': '9', 'dislikes': '3', 'link': '/item/board_read.naver?code=006910&amp;nid=415463282&amp;page=9', 'score': 332}, {'title': '어제 실적 발표한거 보니 전년대비 거의 10...', 'date': '2026.03.20 10:48', 'views': '110', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415462771&amp;page=9', 'score': 380}, {'title': '보성과 두산 신고가[2]', 'date': '2026.03.20 11:06', 'views': '101', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415466318&amp;page=9', 'score': 341}, {'title': '오늘은 상한가 가는날 맞죠ㅋ[3]', 'date': '2026.03.20 09:39', 'views': '95', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=006910&amp;nid=415448007&amp;page=11', 'score': 305}]</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>[{'title': 'SM상선.. 64억 sm자산개발로 대여함.[3]', 'date': '2026.03.20 08:48', 'views': '164', 'likes': '14', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415436015&amp;page=7', 'score': 584}, {'title': '건설자재 건설장비는 뭘로 옮길꺼요? 비행기로?...', 'date': '2026.03.20 15:51', 'views': '85', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415510767&amp;page=1', 'score': 415}, {'title': '정정당당하게 주식배당 줘라', 'date': '2026.03.20 11:25', 'views': '34', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415469747&amp;page=4', 'score': 334}, {'title': '뉴스에는 크게 이슈화되지 않았지만, 오늘 오른...', 'date': '2026.03.20 17:22', 'views': '115', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415517836&amp;page=1', 'score': 385}, {'title': '챗지피티[1]', 'date': '2026.03.20 08:14', 'views': '225', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415431613&amp;page=7', 'score': 495}, {'title': '탈 카타르 LNG선박 수혜주  (대한해운)[2]', 'date': '2026.03.20 08:48', 'views': '133', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415436009&amp;page=7', 'score': 373}, {'title': '와 부채 6천억 줄이고 당기순이익 100억 증...', 'date': '2026.03.20 16:47', 'views': '89', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415515380&amp;page=1', 'score': 299}, {'title': 'bts[2]', 'date': '2026.03.20 15:19', 'views': '141', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415506108&amp;page=1', 'score': 351}, {'title': '여기도', 'date': '2026.03.20 11:35', 'views': '31', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415471599&amp;page=4', 'score': 241}, {'title': '숏커버링 들어온다고 도대체 몇번을 말해도, ...', 'date': '2026.03.20 10:23', 'views': '53', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415457915&amp;page=5', 'score': 263}]</t>
+          <t>[{'title': 'SM상선.. 64억 sm자산개발로 대여함.[3]', 'date': '2026.03.20 08:48', 'views': '164', 'likes': '14', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415436015&amp;page=7', 'score': 584}, {'title': '건설자재 건설장비는 뭘로 옮길꺼요? 비행기로?...', 'date': '2026.03.20 15:51', 'views': '85', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415510767&amp;page=1', 'score': 415}, {'title': '정정당당하게 주식배당 줘라', 'date': '2026.03.20 11:25', 'views': '34', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415469747&amp;page=4', 'score': 334}, {'title': '뉴스에는 크게 이슈화되지 않았지만, 오늘 오른...', 'date': '2026.03.20 17:22', 'views': '116', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415517836&amp;page=1', 'score': 386}, {'title': '챗지피티[1]', 'date': '2026.03.20 08:14', 'views': '225', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415431613&amp;page=7', 'score': 495}, {'title': '탈 카타르 LNG선박 수혜주  (대한해운)[2]', 'date': '2026.03.20 08:48', 'views': '133', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415436009&amp;page=7', 'score': 373}, {'title': '와 부채 6천억 줄이고 당기순이익 100억 증...', 'date': '2026.03.20 16:47', 'views': '89', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415515380&amp;page=1', 'score': 299}, {'title': 'bts[2]', 'date': '2026.03.20 15:19', 'views': '141', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415506108&amp;page=1', 'score': 351}, {'title': '여기도', 'date': '2026.03.20 11:35', 'views': '31', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415471599&amp;page=4', 'score': 241}, {'title': '숏커버링 들어온다고 도대체 몇번을 말해도, ...', 'date': '2026.03.20 10:23', 'views': '53', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415457915&amp;page=5', 'score': 263}]</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Negative (51%)</t>
+          <t>Positive (51%)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>오늘, 진짜, 내가</t>
+          <t>오늘, 진짜, 태양광</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>[{'title': '오늘자 수급 동향[6]', 'date': '2026.03.20 16:24', 'views': '725', 'likes': '19', 'dislikes': '4', 'link': '/item/board_read.naver?code=009830&amp;nid=415513825&amp;page=4', 'score': 1295}, {'title': '머스크형 한마디만 해줘', 'date': '2026.03.20 18:14', 'views': '69', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=009830&amp;nid=415520777&amp;page=2', 'score': 609}, {'title': '거래  1조7천억터지고  공시호재가나왓는데도[1]', 'date': '2026.03.20 15:21', 'views': '260', 'likes': '17', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415506517&amp;page=8', 'score': 770}, {'title': '오늘 개미 다 털렸네', 'date': '2026.03.20 18:39', 'views': '47', 'likes': '15', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415522017&amp;page=2', 'score': 497}, {'title': '전에도 말했듯이 10만은 무조건 간다', 'date': '2026.03.20 18:12', 'views': '77', 'likes': '15', 'dislikes': '5', 'link': '/item/board_read.naver?code=009830&amp;nid=415520665&amp;page=2', 'score': 527}, {'title': '여수산단의 구조개편안', 'date': '2026.03.20 17:37', 'views': '182', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=009830&amp;nid=415518711&amp;page=3', 'score': 632}, {'title': '형들  나도 평탄 33000원 1억2...[5]', 'date': '2026.03.20 17:14', 'views': '914', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=009830&amp;nid=415517307&amp;page=3', 'score': 1364}, {'title': '3시  공시 설명 요청하신분', 'date': '2026.03.20 16:52', 'views': '468', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=009830&amp;nid=415515759&amp;page=3', 'score': 918}, {'title': '56800에 안판 내손이 웬수지', 'date': '2026.03.20 11:15', 'views': '38', 'likes': '15', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415467886&amp;page=28', 'score': 488}, {'title': '여수건 해결한다잖아.', 'date': '2026.03.20 18:12', 'views': '198', 'likes': '14', 'dislikes': '1', 'link': '/item/board_read.naver?code=009830&amp;nid=415520644&amp;page=2', 'score': 618}]</t>
+          <t>[{'title': '오늘자 수급 동향[6]', 'date': '2026.03.20 16:24', 'views': '725', 'likes': '19', 'dislikes': '4', 'link': '/item/board_read.naver?code=009830&amp;nid=415513825&amp;page=4', 'score': 1295}, {'title': '머스크형 한마디만 해줘', 'date': '2026.03.20 18:14', 'views': '71', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=009830&amp;nid=415520777&amp;page=2', 'score': 611}, {'title': '거래  1조7천억터지고  공시호재가나왓는데도[1]', 'date': '2026.03.20 15:21', 'views': '260', 'likes': '17', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415506517&amp;page=8', 'score': 770}, {'title': '오늘 개미 다 털렸네', 'date': '2026.03.20 18:39', 'views': '52', 'likes': '15', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415522017&amp;page=2', 'score': 502}, {'title': '전에도 말했듯이 10만은 무조건 간다', 'date': '2026.03.20 18:12', 'views': '78', 'likes': '15', 'dislikes': '5', 'link': '/item/board_read.naver?code=009830&amp;nid=415520665&amp;page=2', 'score': 528}, {'title': '여수산단의 구조개편안', 'date': '2026.03.20 17:37', 'views': '184', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=009830&amp;nid=415518711&amp;page=3', 'score': 634}, {'title': '형들  나도 평탄 33000원 1억2...[5]', 'date': '2026.03.20 17:14', 'views': '918', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=009830&amp;nid=415517307&amp;page=3', 'score': 1368}, {'title': '3시  공시 설명 요청하신분', 'date': '2026.03.20 16:52', 'views': '470', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=009830&amp;nid=415515759&amp;page=4', 'score': 920}, {'title': '56800에 안판 내손이 웬수지', 'date': '2026.03.20 11:15', 'views': '38', 'likes': '15', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415467886&amp;page=28', 'score': 488}, {'title': '여수건 해결한다잖아.', 'date': '2026.03.20 18:12', 'views': '201', 'likes': '14', 'dislikes': '1', 'link': '/item/board_read.naver?code=009830&amp;nid=415520644&amp;page=3', 'score': 621}]</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Positive (67%)</t>
+          <t>Positive (66%)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>[{'title': '주식이 가장 크게 상승하는 시점은', 'date': '2026.03.20 17:17', 'views': '412', 'likes': '32', 'dislikes': '2', 'link': '/item/board_read.naver?code=034020&amp;nid=415517501&amp;page=3', 'score': 1372}, {'title': '110,000다와간다[1]', 'date': '2026.03.20 16:17', 'views': '376', 'likes': '23', 'dislikes': '3', 'link': '/item/board_read.naver?code=034020&amp;nid=415513276&amp;page=4', 'score': 1066}, {'title': '주말에 발표나면  ~![1]', 'date': '2026.03.20 16:16', 'views': '621', 'likes': '23', 'dislikes': '8', 'link': '/item/board_read.naver?code=034020&amp;nid=415513252&amp;page=4', 'score': 1311}, {'title': '월욜 갭상승 120000원 시작', 'date': '2026.03.20 18:12', 'views': '79', 'likes': '21', 'dislikes': '4', 'link': '/item/board_read.naver?code=034020&amp;nid=415520661&amp;page=2', 'score': 709}, {'title': '우리 두빌이가 그렇게 애를 태우더니[3]', 'date': '2026.03.20 17:13', 'views': '405', 'likes': '20', 'dislikes': '0', 'link': '/item/board_read.naver?code=034020&amp;nid=415517193&amp;page=3', 'score': 1005}, {'title': '천정 열렸네...슈팅간다', 'date': '2026.03.20 10:39', 'views': '90', 'likes': '19', 'dislikes': '2', 'link': '/item/board_read.naver?code=034020&amp;nid=415460931&amp;page=29', 'score': 660}, {'title': '삼전보다 30만원대 먼저 가겠다 ~![1]', 'date': '2026.03.20 18:37', 'views': '247', 'likes': '18', 'dislikes': '2', 'link': '/item/board_read.naver?code=034020&amp;nid=415521912&amp;page=2', 'score': 787}, {'title': '두산에너빌리티를', 'date': '2026.03.20 16:48', 'views': '116', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=034020&amp;nid=415515435&amp;page=3', 'score': 656}, {'title': '오늘로 개미 매물 전멸[2]', 'date': '2026.03.20 15:17', 'views': '265', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=034020&amp;nid=415505727&amp;page=6', 'score': 805}, {'title': '긴급', 'date': '2026.03.20 17:13', 'views': '102', 'likes': '17', 'dislikes': '1', 'link': '/item/board_read.naver?code=034020&amp;nid=415517179&amp;page=3', 'score': 612}]</t>
+          <t>[{'title': '주식이 가장 크게 상승하는 시점은', 'date': '2026.03.20 17:17', 'views': '413', 'likes': '32', 'dislikes': '2', 'link': '/item/board_read.naver?code=034020&amp;nid=415517501&amp;page=3', 'score': 1373}, {'title': '110,000다와간다[1]', 'date': '2026.03.20 16:17', 'views': '376', 'likes': '23', 'dislikes': '3', 'link': '/item/board_read.naver?code=034020&amp;nid=415513276&amp;page=4', 'score': 1066}, {'title': '주말에 발표나면  ~![1]', 'date': '2026.03.20 16:16', 'views': '621', 'likes': '23', 'dislikes': '8', 'link': '/item/board_read.naver?code=034020&amp;nid=415513252&amp;page=4', 'score': 1311}, {'title': '월욜 갭상승 120000원 시작', 'date': '2026.03.20 18:12', 'views': '79', 'likes': '21', 'dislikes': '4', 'link': '/item/board_read.naver?code=034020&amp;nid=415520661&amp;page=2', 'score': 709}, {'title': '우리 두빌이가 그렇게 애를 태우더니[3]', 'date': '2026.03.20 17:13', 'views': '407', 'likes': '20', 'dislikes': '0', 'link': '/item/board_read.naver?code=034020&amp;nid=415517193&amp;page=3', 'score': 1007}, {'title': '삼전보다 30만원대 먼저 가겠다 ~![1]', 'date': '2026.03.20 18:37', 'views': '256', 'likes': '19', 'dislikes': '2', 'link': '/item/board_read.naver?code=034020&amp;nid=415521912&amp;page=2', 'score': 826}, {'title': '천정 열렸네...슈팅간다', 'date': '2026.03.20 10:39', 'views': '90', 'likes': '19', 'dislikes': '2', 'link': '/item/board_read.naver?code=034020&amp;nid=415460931&amp;page=29', 'score': 660}, {'title': '두산에너빌리티를', 'date': '2026.03.20 16:48', 'views': '116', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=034020&amp;nid=415515435&amp;page=4', 'score': 656}, {'title': '오늘로 개미 매물 전멸[2]', 'date': '2026.03.20 15:17', 'views': '265', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=034020&amp;nid=415505727&amp;page=6', 'score': 805}, {'title': '그동안 억눌렸던거 이제 미친듯이 날라간다[4]', 'date': '2026.03.20 18:22', 'views': '325', 'likes': '17', 'dislikes': '5', 'link': '/item/board_read.naver?code=034020&amp;nid=415521133&amp;page=2', 'score': 835}]</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>[{'title': '일단 2만은 무조건 찍을거 같은데[2]', 'date': '2026.03.20 16:49', 'views': '202', 'likes': '34', 'dislikes': '4', 'link': '/item/board_read.naver?code=187660&amp;nid=415515525&amp;page=3', 'score': 1222}, {'title': '증시 역사상 더큰 재료 없다[1]', 'date': '2026.03.20 17:29', 'views': '180', 'likes': '31', 'dislikes': '3', 'link': '/item/board_read.naver?code=187660&amp;nid=415518227&amp;page=2', 'score': 1110}, {'title': '주포형 욕해서 미안해[4]', 'date': '2026.03.20 15:45', 'views': '375', 'likes': '31', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415509975&amp;page=4', 'score': 1305}, {'title': '오늘 시외 거래가 마지막 최저 거래금액이다[2]', 'date': '2026.03.20 17:32', 'views': '295', 'likes': '30', 'dislikes': '6', 'link': '/item/board_read.naver?code=187660&amp;nid=415518422&amp;page=2', 'score': 1195}, {'title': 'ADM 3개월 후 가격을 AI에게물어보앗습니다...[4]', 'date': '2026.03.20 17:24', 'views': '532', 'likes': '30', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415517935&amp;page=2', 'score': 1432}, {'title': '진짜 사명변경!', 'date': '2026.03.20 16:54', 'views': '229', 'likes': '28', 'dislikes': '4', 'link': '/item/board_read.naver?code=187660&amp;nid=415515909&amp;page=2', 'score': 1069}, {'title': '털리고 털려서 배워라', 'date': '2026.03.20 17:37', 'views': '214', 'likes': '26', 'dislikes': '2', 'link': '/item/board_read.naver?code=187660&amp;nid=415518715&amp;page=1', 'score': 994}, {'title': '이런~~[1]', 'date': '2026.03.20 17:30', 'views': '166', 'likes': '25', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415518268&amp;page=2', 'score': 916}, {'title': '●●오늘부로 앱솔루리 페바사&amp;혐바사는 각...[1]', 'date': '2026.03.20 18:36', 'views': '296', 'likes': '24', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415521885&amp;page=1', 'score': 1016}, {'title': '아침글에 쓴 내용중 잘못된 부분을 바로잡습니다...[4]', 'date': '2026.03.20 16:30', 'views': '277', 'likes': '24', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415514319&amp;page=3', 'score': 997}]</t>
+          <t>[{'title': '일단 2만은 무조건 찍을거 같은데[2]', 'date': '2026.03.20 16:49', 'views': '203', 'likes': '34', 'dislikes': '4', 'link': '/item/board_read.naver?code=187660&amp;nid=415515525&amp;page=3', 'score': 1223}, {'title': '증시 역사상 더큰 재료 없다[1]', 'date': '2026.03.20 17:29', 'views': '182', 'likes': '31', 'dislikes': '3', 'link': '/item/board_read.naver?code=187660&amp;nid=415518227&amp;page=2', 'score': 1112}, {'title': '주포형 욕해서 미안해[4]', 'date': '2026.03.20 15:45', 'views': '375', 'likes': '31', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415509975&amp;page=4', 'score': 1305}, {'title': '오늘 시외 거래가 마지막 최저 거래금액이다[2]', 'date': '2026.03.20 17:32', 'views': '304', 'likes': '30', 'dislikes': '6', 'link': '/item/board_read.naver?code=187660&amp;nid=415518422&amp;page=2', 'score': 1204}, {'title': 'ADM 3개월 후 가격을 AI에게물어보앗습니다...[4]', 'date': '2026.03.20 17:24', 'views': '539', 'likes': '30', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415517935&amp;page=2', 'score': 1439}, {'title': '진짜 사명변경!', 'date': '2026.03.20 16:54', 'views': '229', 'likes': '28', 'dislikes': '4', 'link': '/item/board_read.naver?code=187660&amp;nid=415515909&amp;page=2', 'score': 1069}, {'title': '털리고 털려서 배워라', 'date': '2026.03.20 17:37', 'views': '221', 'likes': '26', 'dislikes': '2', 'link': '/item/board_read.naver?code=187660&amp;nid=415518715&amp;page=1', 'score': 1001}, {'title': '현재 홈피의 페니트리움 내용', 'date': '2026.03.20 18:53', 'views': '444', 'likes': '25', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415522712&amp;page=1', 'score': 1194}, {'title': '이런~~[1]', 'date': '2026.03.20 17:30', 'views': '171', 'likes': '25', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415518268&amp;page=2', 'score': 921}, {'title': '●●오늘부로 앱솔루리 페바사&amp;혐바사는 각...[1]', 'date': '2026.03.20 18:36', 'views': '313', 'likes': '24', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415521885&amp;page=1', 'score': 1033}]</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Positive (53%)</t>
+          <t>Positive (51%)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>[{'title': '카타르 파괴 &amp; 우크라-러시아종전[1]', 'date': '2026.03.20 17:03', 'views': '161', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=117580&amp;nid=415516500&amp;page=1', 'score': 461}, {'title': '브랜트유 급반등~107달러 돌파~107.39[1]', 'date': '2026.03.20 11:43', 'views': '81', 'likes': '10', 'dislikes': '4', 'link': '/item/board_read.naver?code=117580&amp;nid=415473003&amp;page=4', 'score': 381}, {'title': '[대성에너지 실적발표] 창사이래 최대실적 발표', 'date': '2026.03.20 10:52', 'views': '209', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415463626&amp;page=4', 'score': 509}, {'title': '오늘은 이놈이 가스 대장 잡을 것이다', 'date': '2026.03.20 08:20', 'views': '38', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415432432&amp;page=6', 'score': 308}, {'title': '유럽 천연가스 14% 급등 마감.', 'date': '2026.03.20 08:40', 'views': '49', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=117580&amp;nid=415435032&amp;page=6', 'score': 259}, {'title': '쩜상이겠지[1]', 'date': '2026.03.20 08:25', 'views': '34', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=117580&amp;nid=415433092&amp;page=6', 'score': 244}, {'title': 'Sk가스 10프로 상승중', 'date': '2026.03.20 08:02', 'views': '39', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415430159&amp;page=7', 'score': 249}, {'title': '3만까지 가는주식이다[1]', 'date': '2026.03.20 09:28', 'views': '128', 'likes': '6', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415444970&amp;page=5', 'score': 308}, {'title': '가스주대장 상한가간다.[2]', 'date': '2026.03.20 09:19', 'views': '119', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=117580&amp;nid=415442490&amp;page=5', 'score': 299}, {'title': 'ㅋㅋ 가스주떡락  장전에팔음 나이스', 'date': '2026.03.20 08:42', 'views': '38', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=117580&amp;nid=415435264&amp;page=6', 'score': 218}]</t>
+          <t>[{'title': '카타르 파괴 &amp; 우크라-러시아종전[1]', 'date': '2026.03.20 17:03', 'views': '162', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=117580&amp;nid=415516500&amp;page=1', 'score': 462}, {'title': '브랜트유 급반등~107달러 돌파~107.39[1]', 'date': '2026.03.20 11:43', 'views': '81', 'likes': '10', 'dislikes': '4', 'link': '/item/board_read.naver?code=117580&amp;nid=415473003&amp;page=4', 'score': 381}, {'title': '[대성에너지 실적발표] 창사이래 최대실적 발표', 'date': '2026.03.20 10:52', 'views': '209', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415463626&amp;page=4', 'score': 509}, {'title': '오늘은 이놈이 가스 대장 잡을 것이다', 'date': '2026.03.20 08:20', 'views': '38', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415432432&amp;page=6', 'score': 308}, {'title': '유럽 천연가스 14% 급등 마감.', 'date': '2026.03.20 08:40', 'views': '49', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=117580&amp;nid=415435032&amp;page=6', 'score': 259}, {'title': '쩜상이겠지[1]', 'date': '2026.03.20 08:25', 'views': '34', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=117580&amp;nid=415433092&amp;page=6', 'score': 244}, {'title': 'Sk가스 10프로 상승중', 'date': '2026.03.20 08:02', 'views': '39', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415430159&amp;page=7', 'score': 249}, {'title': '3만까지 가는주식이다[1]', 'date': '2026.03.20 09:28', 'views': '128', 'likes': '6', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415444970&amp;page=5', 'score': 308}, {'title': '가스주대장 상한가간다.[2]', 'date': '2026.03.20 09:19', 'views': '119', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=117580&amp;nid=415442490&amp;page=5', 'score': 299}, {'title': 'ㅋㅋ 가스주떡락  장전에팔음 나이스', 'date': '2026.03.20 08:42', 'views': '38', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=117580&amp;nid=415435264&amp;page=6', 'score': 218}]</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>이번주도 고생많으셨습니다 / 오늘자 뉴스다. Open ran 표준이 되는거...[5] / 12000원대 눌러주면 꾹꾹 담아라[2] / 다음주 매물다먹어버리고 상갈듯</t>
+          <t>이번주도 고생많으셨습니다 / 12000원대 눌러주면 꾹꾹 담아라[2] / 다음주 매물다먹어버리고 상갈듯 / 평단14350.[2]</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>[{'title': '이번주도 고생많으셨습니다', 'date': '2026.03.20 17:33', 'views': '139', 'likes': '16', 'dislikes': '2', 'link': '/item/board_read.naver?code=050890&amp;nid=415518484&amp;page=1', 'score': 619}, {'title': '다음주 매물다먹어버리고 상갈듯', 'date': '2026.03.20 17:59', 'views': '90', 'likes': '12', 'dislikes': '5', 'link': '/item/board_read.naver?code=050890&amp;nid=415519976&amp;page=1', 'score': 450}, {'title': '신고가를 기록해도 기분 드럽게 만드네....[1]', 'date': '2026.03.20 14:43', 'views': '115', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415500455&amp;page=4', 'score': 415}, {'title': '곧 큰형님들 몸푸십니다[1]', 'date': '2026.03.20 17:59', 'views': '140', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=050890&amp;nid=415519988&amp;page=1', 'score': 410}, {'title': '이런주식은 절대로[1]', 'date': '2026.03.20 15:44', 'views': '58', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=050890&amp;nid=415509871&amp;page=3', 'score': 328}, {'title': '평단14350.[2]', 'date': '2026.03.20 14:04', 'views': '157', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415494260&amp;page=5', 'score': 427}, {'title': '기가 막히게 털고 나가네~~[1]', 'date': '2026.03.20 14:05', 'views': '90', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415494364&amp;page=4', 'score': 330}, {'title': '뭐 겁나 오를것처럼 말하는대 그럼 로봇주나 반...', 'date': '2026.03.20 18:42', 'views': '113', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415522129&amp;page=1', 'score': 323}, {'title': '12000원대 눌러주면 꾹꾹 담아라[2]', 'date': '2026.03.20 17:23', 'views': '302', 'likes': '7', 'dislikes': '6', 'link': '/item/board_read.naver?code=050890&amp;nid=415517908&amp;page=1', 'score': 512}, {'title': '오늘자 뉴스다. Open ran 표준이 되는거...[5]', 'date': '2026.03.20 16:52', 'views': '308', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=050890&amp;nid=415515742&amp;page=2', 'score': 518}]</t>
+          <t>[{'title': '이번주도 고생많으셨습니다', 'date': '2026.03.20 17:33', 'views': '142', 'likes': '16', 'dislikes': '3', 'link': '/item/board_read.naver?code=050890&amp;nid=415518484&amp;page=1', 'score': 622}, {'title': '다음주 매물다먹어버리고 상갈듯', 'date': '2026.03.20 17:59', 'views': '95', 'likes': '12', 'dislikes': '6', 'link': '/item/board_read.naver?code=050890&amp;nid=415519976&amp;page=1', 'score': 455}, {'title': '신고가를 기록해도 기분 드럽게 만드네....[1]', 'date': '2026.03.20 14:43', 'views': '115', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415500455&amp;page=4', 'score': 415}, {'title': '곧 큰형님들 몸푸십니다[1]', 'date': '2026.03.20 17:59', 'views': '150', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=050890&amp;nid=415519988&amp;page=1', 'score': 420}, {'title': '이런주식은 절대로[1]', 'date': '2026.03.20 15:44', 'views': '58', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=050890&amp;nid=415509871&amp;page=3', 'score': 328}, {'title': '평단14350.[2]', 'date': '2026.03.20 14:04', 'views': '157', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415494260&amp;page=5', 'score': 427}, {'title': '뭐 겁나 오를것처럼 말하는대 그럼 로봇주나 반...', 'date': '2026.03.20 18:42', 'views': '124', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415522129&amp;page=1', 'score': 364}, {'title': '기가 막히게 털고 나가네~~[1]', 'date': '2026.03.20 14:05', 'views': '90', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415494364&amp;page=4', 'score': 330}, {'title': '12000원대 눌러주면 꾹꾹 담아라[2]', 'date': '2026.03.20 17:23', 'views': '309', 'likes': '7', 'dislikes': '7', 'link': '/item/board_read.naver?code=050890&amp;nid=415517908&amp;page=1', 'score': 519}, {'title': '참나!', 'date': '2026.03.20 17:08', 'views': '53', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415516847&amp;page=1', 'score': 263}]</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>마음편하게 주식합시다[1] / 골드만 삭스 280만주 매수 캬[2] / 공매 세력들 많이 쫄리나본데?? ㅋㅋㅋ[2] / 한온 1등 먹었네.[1]</t>
+          <t>마음편하게 주식합시다[1] / 골드만 삭스 280만주 매수 캬[2] / 형님들 제가 누누히 말하지만 이종목이[7] / 공매 세력들 많이 쫄리나본데?? ㅋㅋㅋ[2]</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Negative (52%)</t>
+          <t>Negative (54%)</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>[{'title': '마음편하게 주식합시다[1]', 'date': '2026.03.20 10:17', 'views': '172', 'likes': '18', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415456883&amp;page=7', 'score': 712}, {'title': '공매 세력들 많이 쫄리나본데?? ㅋㅋㅋ[2]', 'date': '2026.03.20 17:34', 'views': '201', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=018880&amp;nid=415518518&amp;page=1', 'score': 621}, {'title': '골드만 삭스 280만주 매수 캬[2]', 'date': '2026.03.20 16:29', 'views': '298', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=018880&amp;nid=415514180&amp;page=1', 'score': 688}, {'title': '월욜 시초가 갭상승[3]', 'date': '2026.03.20 17:59', 'views': '154', 'likes': '12', 'dislikes': '3', 'link': '/item/board_read.naver?code=018880&amp;nid=415520015&amp;page=1', 'score': 514}, {'title': '공매놈들 발등에 불남', 'date': '2026.03.20 15:53', 'views': '79', 'likes': '12', 'dislikes': '2', 'link': '/item/board_read.naver?code=018880&amp;nid=415510952&amp;page=2', 'score': 439}, {'title': '골드만삭스  매입만으로 신뢰도상승 그냥 뉴...', 'date': '2026.03.20 17:24', 'views': '112', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=018880&amp;nid=415517956&amp;page=1', 'score': 442}, {'title': '골드만이 본격적으로 사려고 맘 먹었나보네.', 'date': '2026.03.20 15:44', 'views': '121', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415509917&amp;page=2', 'score': 451}, {'title': '주식 모르는 작자들 글 쓰지맙시다~ 다른 종목 ...[4]', 'date': '2026.03.20 09:15', 'views': '117', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415441436&amp;page=10', 'score': 447}, {'title': '한온 1등 먹었네.[1]', 'date': '2026.03.20 08:16', 'views': '197', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415431925&amp;page=11', 'score': 527}, {'title': '내첫차는 아반떼[2]', 'date': '2026.03.20 17:55', 'views': '207', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=018880&amp;nid=415519711&amp;page=1', 'score': 507}]</t>
+          <t>[{'title': '마음편하게 주식합시다[1]', 'date': '2026.03.20 10:17', 'views': '172', 'likes': '18', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415456883&amp;page=7', 'score': 712}, {'title': '공매 세력들 많이 쫄리나본데?? ㅋㅋㅋ[2]', 'date': '2026.03.20 17:34', 'views': '203', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=018880&amp;nid=415518518&amp;page=1', 'score': 653}, {'title': '월욜 시초가 갭상승[3]', 'date': '2026.03.20 17:59', 'views': '164', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=018880&amp;nid=415520015&amp;page=1', 'score': 554}, {'title': '골드만 삭스 280만주 매수 캬[2]', 'date': '2026.03.20 16:29', 'views': '300', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=018880&amp;nid=415514180&amp;page=1', 'score': 690}, {'title': '공매놈들 발등에 불남', 'date': '2026.03.20 15:53', 'views': '79', 'likes': '12', 'dislikes': '2', 'link': '/item/board_read.naver?code=018880&amp;nid=415510952&amp;page=2', 'score': 439}, {'title': '형님들 제가 누누히 말하지만 이종목이[7]', 'date': '2026.03.20 18:23', 'views': '330', 'likes': '11', 'dislikes': '6', 'link': '/item/board_read.naver?code=018880&amp;nid=415521240&amp;page=1', 'score': 660}, {'title': '내첫차는 아반떼[3]', 'date': '2026.03.20 17:55', 'views': '213', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=018880&amp;nid=415519711&amp;page=1', 'score': 543}, {'title': '세계 경제지표 골드만삭스  매입만으로 신뢰...', 'date': '2026.03.20 17:24', 'views': '114', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=018880&amp;nid=415517956&amp;page=1', 'score': 444}, {'title': '골드만이 본격적으로 사려고 맘 먹었나보네.', 'date': '2026.03.20 15:44', 'views': '121', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415509917&amp;page=2', 'score': 451}, {'title': '주식 모르는 작자들 글 쓰지맙시다~ 다른 종목 ...[4]', 'date': '2026.03.20 09:15', 'views': '117', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415441436&amp;page=10', 'score': 447}]</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>[{'title': '애들아...[8]', 'date': '2026.03.20 15:35', 'views': '723', 'likes': '42', 'dislikes': '6', 'link': '/item/board_read.naver?code=010170&amp;nid=415508574&amp;page=1', 'score': 1983}, {'title': '제가 몇달 전에 빛과전자랑 대한광통신 반반씩 ...[2]', 'date': '2026.03.20 11:51', 'views': '417', 'likes': '16', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415474378&amp;page=6', 'score': 897}, {'title': '지금 통신관련주중에 투경은 이것만이다[1]', 'date': '2026.03.20 10:36', 'views': '154', 'likes': '16', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415460440&amp;page=7', 'score': 634}, {'title': '모든 파트의 대장주가 힘을 응축하면 그 폭발력...[1]', 'date': '2026.03.20 11:56', 'views': '238', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=010170&amp;nid=415475108&amp;page=6', 'score': 688}, {'title': '미국 광통신종목 루멘템 홀딩스', 'date': '2026.03.20 08:00', 'views': '108', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=010170&amp;nid=415429974&amp;page=12', 'score': 558}, {'title': "4월 24일 '15,000원' 고지 점령, 과...[2]", 'date': '2026.03.20 15:19', 'views': '412', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=010170&amp;nid=415506164&amp;page=2', 'score': 832}, {'title': '난 잘 가고있는거라 생각하는데..[3]', 'date': '2026.03.20 12:42', 'views': '350', 'likes': '14', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415481694&amp;page=5', 'score': 770}, {'title': '재미로 보는 프로그램 매동[2]', 'date': '2026.03.20 11:22', 'views': '295', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415469116&amp;page=7', 'score': 655}, {'title': '주식투자에 왕도는 신도 모릅니다..이리저리 불...[1]', 'date': '2026.03.20 12:43', 'views': '162', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415481823&amp;page=5', 'score': 492}, {'title': '저수지로 들어간 물량은 절대 안나온다 ㅎ[1]', 'date': '2026.03.20 12:02', 'views': '117', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=010170&amp;nid=415476057&amp;page=6', 'score': 447}]</t>
+          <t>[{'title': '애들아...[8]', 'date': '2026.03.20 15:35', 'views': '725', 'likes': '42', 'dislikes': '6', 'link': '/item/board_read.naver?code=010170&amp;nid=415508574&amp;page=1', 'score': 1985}, {'title': '제가 몇달 전에 빛과전자랑 대한광통신 반반씩 ...[2]', 'date': '2026.03.20 11:51', 'views': '417', 'likes': '16', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415474378&amp;page=6', 'score': 897}, {'title': '지금 통신관련주중에 투경은 이것만이다[1]', 'date': '2026.03.20 10:36', 'views': '154', 'likes': '16', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415460440&amp;page=7', 'score': 634}, {'title': '모든 파트의 대장주가 힘을 응축하면 그 폭발력...[1]', 'date': '2026.03.20 11:56', 'views': '238', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=010170&amp;nid=415475108&amp;page=6', 'score': 688}, {'title': '미국 광통신종목 루멘템 홀딩스', 'date': '2026.03.20 08:00', 'views': '108', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=010170&amp;nid=415429974&amp;page=12', 'score': 558}, {'title': "4월 24일 '15,000원' 고지 점령, 과...[2]", 'date': '2026.03.20 15:19', 'views': '413', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=010170&amp;nid=415506164&amp;page=2', 'score': 833}, {'title': '난 잘 가고있는거라 생각하는데..[3]', 'date': '2026.03.20 12:42', 'views': '350', 'likes': '14', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415481694&amp;page=5', 'score': 770}, {'title': '재미로 보는 프로그램 매동[2]', 'date': '2026.03.20 11:22', 'views': '295', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415469116&amp;page=7', 'score': 655}, {'title': '털리는 모지리들이 적당히 있는게 가볍게 수월하...[2]', 'date': '2026.03.20 17:03', 'views': '308', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=010170&amp;nid=415516549&amp;page=1', 'score': 638}, {'title': '주식투자에 왕도는 신도 모릅니다..이리저리 불...[1]', 'date': '2026.03.20 12:43', 'views': '162', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415481823&amp;page=5', 'score': 492}]</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>[{'title': '유증을[3]', 'date': '2026.03.20 17:29', 'views': '309', 'likes': '40', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415518245&amp;page=1', 'score': 1509}, {'title': '3779억원[1]', 'date': '2026.03.20 15:56', 'views': '97', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415511350&amp;page=2', 'score': 487}, {'title': '시세 조종으로 금감원 민원 접수함[1]', 'date': '2026.03.20 09:31', 'views': '82', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415445921&amp;page=13', 'score': 472}, {'title': '주총하면', 'date': '2026.03.20 16:31', 'views': '58', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=010140&amp;nid=415514368&amp;page=2', 'score': 418}, {'title': '놀랍다 수주 호재가 떴는데[1]', 'date': '2026.03.20 09:06', 'views': '108', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415439047&amp;page=15', 'score': 468}, {'title': '원래[1]', 'date': '2026.03.20 08:15', 'views': '103', 'likes': '12', 'dislikes': '2', 'link': '/item/board_read.naver?code=010140&amp;nid=415431782&amp;page=16', 'score': 463}, {'title': "[총공격] 삼성중공업 세력·연기금아, '슈퍼 사...[2]", 'date': '2026.03.20 18:25', 'views': '125', 'likes': '11', 'dislikes': '4', 'link': '/item/board_read.naver?code=010140&amp;nid=415521298&amp;page=1', 'score': 455}, {'title': '삼중 주포 짠지야. 너만. 배불리 먹으면 안되 ...', 'date': '2026.03.20 17:27', 'views': '70', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415518112&amp;page=1', 'score': 400}, {'title': '와 걍 손절치니까 스트레스 안받음', 'date': '2026.03.20 16:42', 'views': '42', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415515080&amp;page=2', 'score': 372}, {'title': '아이구 감사합니다.', 'date': '2026.03.20 16:07', 'views': '69', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=010140&amp;nid=415512387&amp;page=2', 'score': 399}]</t>
+          <t>[{'title': '유증을[3]', 'date': '2026.03.20 17:29', 'views': '316', 'likes': '41', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415518245&amp;page=1', 'score': 1546}, {'title': '3779억원[1]', 'date': '2026.03.20 15:56', 'views': '97', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415511350&amp;page=2', 'score': 487}, {'title': '시세 조종으로 금감원 민원 접수함[1]', 'date': '2026.03.20 09:31', 'views': '82', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415445921&amp;page=13', 'score': 472}, {'title': '주총하면', 'date': '2026.03.20 16:31', 'views': '58', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=010140&amp;nid=415514368&amp;page=2', 'score': 418}, {'title': '놀랍다 수주 호재가 떴는데[1]', 'date': '2026.03.20 09:06', 'views': '108', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415439047&amp;page=15', 'score': 468}, {'title': '원래[1]', 'date': '2026.03.20 08:15', 'views': '103', 'likes': '12', 'dislikes': '2', 'link': '/item/board_read.naver?code=010140&amp;nid=415431782&amp;page=16', 'score': 463}, {'title': '삼중 주포 짠지야. 너만. 배불리 먹으면 안되 ...', 'date': '2026.03.20 17:27', 'views': '71', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415518112&amp;page=1', 'score': 401}, {'title': '와 걍 손절치니까 스트레스 안받음', 'date': '2026.03.20 16:42', 'views': '42', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415515080&amp;page=2', 'score': 372}, {'title': '아이구 감사합니다.', 'date': '2026.03.20 16:07', 'views': '70', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=010140&amp;nid=415512387&amp;page=2', 'score': 400}, {'title': 'FLNG 수주좀 발표해라 지금 타이밍...', 'date': '2026.03.20 10:07', 'views': '56', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415454535&amp;page=12', 'score': 386}]</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>고생들했어요 월요일부터 10연상갈꺼같습니다.[6] / 대박뉴스[4] / --현재+30%상한가=매수9억원----꼭...꼭...[1] / 세력도 모질지만[2]</t>
+          <t>고생들했어요 월요일부터 10연상갈꺼같습니다.[6] / 대박뉴스[4] / 세력도 모질지만[2] / --현재+30%상한가=매수9억원----꼭...꼭...[1]</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>[{'title': '고생들했어요 월요일부터 10연상갈꺼같습니다.[6]', 'date': '2026.03.20 18:05', 'views': '442', 'likes': '28', 'dislikes': '11', 'link': '/item/board_read.naver?code=261780&amp;nid=415520275&amp;page=1', 'score': 1282}, {'title': '--현재+30%상한가=매수9억원----꼭...꼭...[1]', 'date': '2026.03.20 08:45', 'views': '72', 'likes': '21', 'dislikes': '1', 'link': '/item/board_read.naver?code=261780&amp;nid=415435652&amp;page=35', 'score': 702}, {'title': '대박뉴스[4]', 'date': '2026.03.20 17:07', 'views': '375', 'likes': '19', 'dislikes': '3', 'link': '/item/board_read.naver?code=261780&amp;nid=415516776&amp;page=3', 'score': 945}, {'title': '세력도 모질지만[2]', 'date': '2026.03.20 19:08', 'views': '197', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=261780&amp;nid=415523392&amp;page=1', 'score': 647}, {'title': '아리바이오, ADPD서 AR1001 ...[3]', 'date': '2026.03.20 16:27', 'views': '259', 'likes': '12', 'dislikes': '6', 'link': '/item/board_read.naver?code=261780&amp;nid=415514096&amp;page=4', 'score': 619}, {'title': '이러다', 'date': '2026.03.20 14:51', 'views': '28', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=261780&amp;nid=415501726&amp;page=14', 'score': 388}, {'title': '정상가격 1200~1300원대[1]', 'date': '2026.03.20 18:14', 'views': '276', 'likes': '11', 'dislikes': '11', 'link': '/item/board_read.naver?code=261780&amp;nid=415520771&amp;page=1', 'score': 606}, {'title': '현대도 상가구', 'date': '2026.03.20 17:20', 'views': '206', 'likes': '11', 'dislikes': '3', 'link': '/item/board_read.naver?code=261780&amp;nid=415517678&amp;page=2', 'score': 536}, {'title': '시외 물타다가 대주주되겠다', 'date': '2026.03.20 16:40', 'views': '36', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=261780&amp;nid=415514950&amp;page=4', 'score': 366}, {'title': '생각해 보니 딱딱 들어맞네[3]', 'date': '2026.03.20 18:52', 'views': '272', 'likes': '10', 'dislikes': '5', 'link': '/item/board_read.naver?code=261780&amp;nid=415522636&amp;page=1', 'score': 572}]</t>
+          <t>[{'title': '고생들했어요 월요일부터 10연상갈꺼같습니다.[6]', 'date': '2026.03.20 18:05', 'views': '452', 'likes': '28', 'dislikes': '11', 'link': '/item/board_read.naver?code=261780&amp;nid=415520275&amp;page=1', 'score': 1292}, {'title': '--현재+30%상한가=매수9억원----꼭...꼭...[1]', 'date': '2026.03.20 08:45', 'views': '72', 'likes': '21', 'dislikes': '1', 'link': '/item/board_read.naver?code=261780&amp;nid=415435652&amp;page=35', 'score': 702}, {'title': '대박뉴스[4]', 'date': '2026.03.20 17:07', 'views': '379', 'likes': '19', 'dislikes': '3', 'link': '/item/board_read.naver?code=261780&amp;nid=415516776&amp;page=3', 'score': 949}, {'title': '세력도 모질지만[2]', 'date': '2026.03.20 19:08', 'views': '232', 'likes': '17', 'dislikes': '3', 'link': '/item/board_read.naver?code=261780&amp;nid=415523392&amp;page=1', 'score': 742}, {'title': '아리바이오, ADPD서 AR1001 ...[3]', 'date': '2026.03.20 16:27', 'views': '263', 'likes': '12', 'dislikes': '6', 'link': '/item/board_read.naver?code=261780&amp;nid=415514096&amp;page=4', 'score': 623}, {'title': '이러다', 'date': '2026.03.20 14:51', 'views': '28', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=261780&amp;nid=415501726&amp;page=14', 'score': 388}, {'title': '생각해 보니 딱딱 들어맞네[3]', 'date': '2026.03.20 18:52', 'views': '294', 'likes': '11', 'dislikes': '5', 'link': '/item/board_read.naver?code=261780&amp;nid=415522636&amp;page=1', 'score': 624}, {'title': '정상가격 1200~1300원대[1]', 'date': '2026.03.20 18:14', 'views': '281', 'likes': '11', 'dislikes': '11', 'link': '/item/board_read.naver?code=261780&amp;nid=415520771&amp;page=1', 'score': 611}, {'title': '현대도 상가구', 'date': '2026.03.20 17:20', 'views': '208', 'likes': '11', 'dislikes': '3', 'link': '/item/board_read.naver?code=261780&amp;nid=415517678&amp;page=2', 'score': 538}, {'title': '시외 물타다가 대주주되겠다', 'date': '2026.03.20 16:40', 'views': '38', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=261780&amp;nid=415514950&amp;page=4', 'score': 368}]</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Negative (71%)</t>
+          <t>Negative (68%)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>오늘, 삼전, 외인</t>
+          <t>오늘, 월요일, 나스닥</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>[{'title': '이재명 지지율이 계속 오르는 이유.[1]', 'date': '2026.03.20 18:37', 'views': '66', 'likes': '14', 'dislikes': '8', 'link': '/item/board_read.naver?code=005930&amp;nid=415521895&amp;page=14', 'score': 486}, {'title': '▲금요일 밤 10시~ 일욜까지 뭔일이? ㅡ&gt;삼...[2]', 'date': '2026.03.20 17:02', 'views': '108', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415516432&amp;page=25', 'score': 498}, {'title': '반도체는 호황 불황사이클 반복 업종이다 ㅡ&gt;이...', 'date': '2026.03.20 16:54', 'views': '66', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=005930&amp;nid=415515896&amp;page=27', 'score': 456}, {'title': '어차피 여기서 백날 떠들어봤자 ㅋ[2]', 'date': '2026.03.20 16:46', 'views': '134', 'likes': '13', 'dislikes': '5', 'link': '/item/board_read.naver?code=005930&amp;nid=415515347&amp;page=27', 'score': 524}, {'title': '외인 10프로 나갔는데도 20만원[1]', 'date': '2026.03.20 16:00', 'views': '169', 'likes': '13', 'dislikes': '2', 'link': '/item/board_read.naver?code=005930&amp;nid=415511806&amp;page=33', 'score': 559}, {'title': '800만주는 삼성생명+삼성화재가 판것.[1]', 'date': '2026.03.20 15:45', 'views': '356', 'likes': '13', 'dislikes': '6', 'link': '/item/board_read.naver?code=005930&amp;nid=415510008&amp;page=36', 'score': 746}, {'title': '월요일 급등이네', 'date': '2026.03.20 17:38', 'views': '93', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=005930&amp;nid=415518754&amp;page=21', 'score': 453}, {'title': '전쟁 imf 유사한것 올때는 뭐가최고 예금자 ...', 'date': '2026.03.20 17:08', 'views': '60', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415516866&amp;page=25', 'score': 420}, {'title': '오늘 잘 버텼네요 .[1]', 'date': '2026.03.20 16:36', 'views': '337', 'likes': '12', 'dislikes': '3', 'link': '/item/board_read.naver?code=005930&amp;nid=415514717&amp;page=28', 'score': 697}, {'title': '현재 삼전은 졸라쎈거임', 'date': '2026.03.20 16:19', 'views': '135', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415513503&amp;page=30', 'score': 495}]</t>
+          <t>[{'title': '이재명 지지율이 계속 오르는 이유.[1]', 'date': '2026.03.20 18:37', 'views': '67', 'likes': '14', 'dislikes': '8', 'link': '/item/board_read.naver?code=005930&amp;nid=415521895&amp;page=16', 'score': 487}, {'title': '▲금요일 밤 10시~ 일욜까지 뭔일이? ㅡ&gt;...[2]', 'date': '2026.03.20 17:02', 'views': '108', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415516432&amp;page=28', 'score': 498}, {'title': '반도체는 호황 불황사이클 반복 업종이다 ㅡ&gt;이...', 'date': '2026.03.20 16:54', 'views': '66', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=005930&amp;nid=415515896&amp;page=29', 'score': 456}, {'title': '어차피 여기서 백날 떠들어봤자 ㅋ[2]', 'date': '2026.03.20 16:46', 'views': '134', 'likes': '13', 'dislikes': '5', 'link': '/item/board_read.naver?code=005930&amp;nid=415515347&amp;page=30', 'score': 524}, {'title': '외인 10프로 나갔는데도 20만원[1]', 'date': '2026.03.20 16:00', 'views': '169', 'likes': '13', 'dislikes': '2', 'link': '/item/board_read.naver?code=005930&amp;nid=415511806&amp;page=35', 'score': 559}, {'title': '800만주는 삼성생명+삼성화재가 판것.[1]', 'date': '2026.03.20 15:45', 'views': '356', 'likes': '13', 'dislikes': '6', 'link': '/item/board_read.naver?code=005930&amp;nid=415510008&amp;page=38', 'score': 746}, {'title': '월요일 급등이네', 'date': '2026.03.20 17:38', 'views': '93', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=005930&amp;nid=415518754&amp;page=23', 'score': 453}, {'title': '전쟁 imf 유사한것 올때는 뭐가최고 예금자 ...', 'date': '2026.03.20 17:08', 'views': '60', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415516866&amp;page=27', 'score': 420}, {'title': '오늘 잘 버텼네요 .[1]', 'date': '2026.03.20 16:36', 'views': '337', 'likes': '12', 'dislikes': '3', 'link': '/item/board_read.naver?code=005930&amp;nid=415514717&amp;page=31', 'score': 697}, {'title': '현재 삼전은 졸라쎈거임', 'date': '2026.03.20 16:19', 'views': '135', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415513503&amp;page=32', 'score': 495}]</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>오늘, 이제, ...</t>
+          <t>오늘, 이제, 단일가</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>[{'title': '장금상선·MSC 연합 ‘유조선 공룡’ 뜬다[1]', 'date': '2026.03.20 18:03', 'views': '248', 'likes': '19', 'dislikes': '5', 'link': '/item/board_read.naver?code=003280&amp;nid=415520181&amp;page=1', 'score': 818}, {'title': 'ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ전쟁 끝나봐라 운송전쟁이지', 'date': '2026.03.20 15:20', 'views': '94', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=003280&amp;nid=415506312&amp;page=4', 'score': 484}, {'title': '오늘은[1]', 'date': '2026.03.20 10:52', 'views': '66', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=003280&amp;nid=415463717&amp;page=15', 'score': 426}, {'title': '장금상선 지분 50% 매각이 호재인 이유 설...[2]', 'date': '2026.03.20 08:59', 'views': '320', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=003280&amp;nid=415437505&amp;page=20', 'score': 680}, {'title': '월요일부터[2]', 'date': '2026.03.20 18:03', 'views': '256', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=003280&amp;nid=415520188&amp;page=1', 'score': 586}, {'title': '다음주 바로 만원찍고 가시던가ㅋㅋ[1]', 'date': '2026.03.20 18:09', 'views': '140', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=003280&amp;nid=415520501&amp;page=1', 'score': 440}, {'title': '-4%시작 -6%찍고 +30%가능함?[2]', 'date': '2026.03.20 11:31', 'views': '138', 'likes': '10', 'dislikes': '5', 'link': '/item/board_read.naver?code=003280&amp;nid=415470964&amp;page=13', 'score': 438}, {'title': '오후장 빨간기둥 원하면 개추', 'date': '2026.03.20 10:46', 'views': '24', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=003280&amp;nid=415462474&amp;page=15', 'score': 324}, {'title': '외국인도 기관도 담았네~~~[2]', 'date': '2026.03.20 18:23', 'views': '221', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=003280&amp;nid=415521198&amp;page=1', 'score': 491}, {'title': '이곳이 싫으면 조용히 떠나라', 'date': '2026.03.20 12:40', 'views': '26', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=003280&amp;nid=415481462&amp;page=10', 'score': 296}]</t>
+          <t>[{'title': '장금상선·MSC 연합 ‘유조선 공룡’ 뜬다[1]', 'date': '2026.03.20 18:03', 'views': '250', 'likes': '19', 'dislikes': '5', 'link': '/item/board_read.naver?code=003280&amp;nid=415520181&amp;page=2', 'score': 820}, {'title': 'ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ전쟁 끝나봐라 운송전쟁이지', 'date': '2026.03.20 15:20', 'views': '94', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=003280&amp;nid=415506312&amp;page=4', 'score': 484}, {'title': '오늘은[1]', 'date': '2026.03.20 10:52', 'views': '66', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=003280&amp;nid=415463717&amp;page=15', 'score': 426}, {'title': '장금상선 지분 50% 매각이 호재인 이유 설...[2]', 'date': '2026.03.20 08:59', 'views': '320', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=003280&amp;nid=415437505&amp;page=20', 'score': 680}, {'title': '월요일부터[2]', 'date': '2026.03.20 18:03', 'views': '262', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=003280&amp;nid=415520188&amp;page=2', 'score': 592}, {'title': '다음주 바로 만원찍고 가시던가ㅋㅋ[1]', 'date': '2026.03.20 18:09', 'views': '142', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=003280&amp;nid=415520501&amp;page=1', 'score': 442}, {'title': '-4%시작 -6%찍고 +30%가능함?[2]', 'date': '2026.03.20 11:31', 'views': '138', 'likes': '10', 'dislikes': '5', 'link': '/item/board_read.naver?code=003280&amp;nid=415470964&amp;page=13', 'score': 438}, {'title': '오후장 빨간기둥 원하면 개추', 'date': '2026.03.20 10:46', 'views': '24', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=003280&amp;nid=415462474&amp;page=15', 'score': 324}, {'title': '외국인도 기관도 담았네~~~[2]', 'date': '2026.03.20 18:23', 'views': '226', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=003280&amp;nid=415521198&amp;page=1', 'score': 496}, {'title': '이곳이 싫으면 조용히 떠나라', 'date': '2026.03.20 12:40', 'views': '26', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=003280&amp;nid=415481462&amp;page=11', 'score': 296}]</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>어우 힘들다[3] / 대국민 공모 사기극 / 31일 주총입니다 다들 연장 챙기죠[1] / 하 벌써 20% 마이너스</t>
+          <t>어우 힘들다[3] / 31일 주총입니다 다들 연장 챙기죠[1] / 하 벌써 20% 마이너스 / 어디까지내려가려나?[1]</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>[{'title': '어우 힘들다[3]', 'date': '2026.03.20 13:41', 'views': '100', 'likes': '21', 'dislikes': '4', 'link': '/item/board_read.naver?code=279570&amp;nid=415490849&amp;page=6', 'score': 730}, {'title': '대국민 공모 사기극', 'date': '2026.03.20 11:51', 'views': '53', 'likes': '20', 'dislikes': '2', 'link': '/item/board_read.naver?code=279570&amp;nid=415474338&amp;page=11', 'score': 653}, {'title': '어디까지내려가려나?[1]', 'date': '2026.03.20 11:50', 'views': '54', 'likes': '10', 'dislikes': '4', 'link': '/item/board_read.naver?code=279570&amp;nid=415474183&amp;page=11', 'score': 354}, {'title': '하 벌써 20% 마이너스', 'date': '2026.03.20 11:29', 'views': '55', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415470622&amp;page=11', 'score': 355}, {'title': '31일 주총입니다 다들 연장 챙기죠[1]', 'date': '2026.03.20 11:21', 'views': '70', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415469038&amp;page=12', 'score': 370}, {'title': '개사기주 입니다', 'date': '2026.03.20 12:49', 'views': '34', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=279570&amp;nid=415482785&amp;page=9', 'score': 304}, {'title': '우리은행.NH투자증권 사외이사 물러나야', 'date': '2026.03.20 14:14', 'views': '38', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415495994&amp;page=5', 'score': 278}, {'title': '국민청원', 'date': '2026.03.20 12:17', 'views': '45', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415478260&amp;page=10', 'score': 285}, {'title': '패가망신.', 'date': '2026.03.20 14:10', 'views': '29', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415495372&amp;page=6', 'score': 239}, {'title': 'Per높다고?', 'date': '2026.03.20 12:34', 'views': '31', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415480533&amp;page=9', 'score': 241}]</t>
+          <t>[{'title': '어우 힘들다[3]', 'date': '2026.03.20 13:41', 'views': '100', 'likes': '21', 'dislikes': '4', 'link': '/item/board_read.naver?code=279570&amp;nid=415490849&amp;page=6', 'score': 730}, {'title': '어디까지내려가려나?[1]', 'date': '2026.03.20 11:50', 'views': '54', 'likes': '10', 'dislikes': '4', 'link': '/item/board_read.naver?code=279570&amp;nid=415474183&amp;page=11', 'score': 354}, {'title': '하 벌써 20% 마이너스', 'date': '2026.03.20 11:29', 'views': '55', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415470622&amp;page=11', 'score': 355}, {'title': '31일 주총입니다 다들 연장 챙기죠[1]', 'date': '2026.03.20 11:21', 'views': '70', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415469038&amp;page=12', 'score': 370}, {'title': '개사기주 입니다', 'date': '2026.03.20 12:49', 'views': '34', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=279570&amp;nid=415482785&amp;page=9', 'score': 304}, {'title': '우리은행.NH투자증권 사외이사 물러나야', 'date': '2026.03.20 14:14', 'views': '38', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415495994&amp;page=5', 'score': 278}, {'title': '국민청원', 'date': '2026.03.20 12:17', 'views': '45', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415478260&amp;page=10', 'score': 285}, {'title': '패가망신.', 'date': '2026.03.20 14:10', 'views': '29', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415495372&amp;page=6', 'score': 239}, {'title': 'Per높다고?', 'date': '2026.03.20 12:34', 'views': '31', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415480533&amp;page=9', 'score': 241}, {'title': '상장에 받은 10주[1]', 'date': '2026.03.20 12:21', 'views': '113', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=279570&amp;nid=415478760&amp;page=10', 'score': 323}]</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3489,7 +3489,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>■저 정도면-5일선 단거죠?[11] / ■주말애-사고 싶은거[16] / 오늘도 안타깝게 저의 예측이 맞았네요..ㅠ[17] / ■페이퍼-증권가[8]</t>
+          <t>■저 정도면-5일선 단거죠?[11] / ■주말애-사고 싶은거[17] / 오늘도 안타깝게 저의 예측이 맞았네요..ㅠ[17] / ■페이퍼-증권가[8]</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>[{'title': '■주말애-사고 싶은거[16]', 'date': '2026.03.20 15:36', 'views': '931', 'likes': '64', 'dislikes': '4', 'link': '/item/board_read.naver?code=032820&amp;nid=415508769&amp;page=4', 'score': 2851}, {'title': '■저 정도면-5일선 단거죠?[11]', 'date': '2026.03.20 15:38', 'views': '1306', 'likes': '57', 'dislikes': '6', 'link': '/item/board_read.naver?code=032820&amp;nid=415509037&amp;page=3', 'score': 3016}, {'title': '■인연-팔로잉[14]', 'date': '2026.03.20 10:22', 'views': '444', 'likes': '56', 'dislikes': '4', 'link': '/item/board_read.naver?code=032820&amp;nid=415457811&amp;page=22', 'score': 2124}, {'title': '■페이퍼-증권가[8]', 'date': '2026.03.20 08:09', 'views': '542', 'likes': '54', 'dislikes': '6', 'link': '/item/board_read.naver?code=032820&amp;nid=415430909&amp;page=29', 'score': 2162}, {'title': '■주식은-오르고..내리는건[7]', 'date': '2026.03.20 10:16', 'views': '468', 'likes': '51', 'dislikes': '5', 'link': '/item/board_read.naver?code=032820&amp;nid=415456653&amp;page=22', 'score': 1998}, {'title': '■두빌-14만[2]', 'date': '2026.03.20 11:00', 'views': '562', 'likes': '48', 'dislikes': '7', 'link': '/item/board_read.naver?code=032820&amp;nid=415465317&amp;page=20', 'score': 2002}, {'title': '■우기-매출에 대한 평가', 'date': '2026.03.20 10:44', 'views': '424', 'likes': '47', 'dislikes': '5', 'link': '/item/board_read.naver?code=032820&amp;nid=415461809&amp;page=21', 'score': 1834}, {'title': '■프매-2~3백만주 매수[2]', 'date': '2026.03.20 09:06', 'views': '438', 'likes': '47', 'dislikes': '7', 'link': '/item/board_read.naver?code=032820&amp;nid=415438984&amp;page=28', 'score': 1848}, {'title': '오늘도 안타깝게 저의 예측이 맞았네요..ㅠ[17]', 'date': '2026.03.20 15:37', 'views': '1443', 'likes': '44', 'dislikes': '1', 'link': '/item/board_read.naver?code=032820&amp;nid=415508951&amp;page=4', 'score': 2763}, {'title': '■쓰리바닥이며는[4]', 'date': '2026.03.20 12:55', 'views': '486', 'likes': '39', 'dislikes': '10', 'link': '/item/board_read.naver?code=032820&amp;nid=415483698&amp;page=16', 'score': 1656}]</t>
+          <t>[{'title': '■주말애-사고 싶은거[17]', 'date': '2026.03.20 15:36', 'views': '941', 'likes': '65', 'dislikes': '4', 'link': '/item/board_read.naver?code=032820&amp;nid=415508769&amp;page=4', 'score': 2891}, {'title': '■저 정도면-5일선 단거죠?[11]', 'date': '2026.03.20 15:38', 'views': '1316', 'likes': '57', 'dislikes': '6', 'link': '/item/board_read.naver?code=032820&amp;nid=415509037&amp;page=3', 'score': 3026}, {'title': '■인연-팔로잉[14]', 'date': '2026.03.20 10:22', 'views': '445', 'likes': '56', 'dislikes': '4', 'link': '/item/board_read.naver?code=032820&amp;nid=415457811&amp;page=22', 'score': 2125}, {'title': '■페이퍼-증권가[8]', 'date': '2026.03.20 08:09', 'views': '543', 'likes': '54', 'dislikes': '6', 'link': '/item/board_read.naver?code=032820&amp;nid=415430909&amp;page=29', 'score': 2163}, {'title': '■주식은-오르고..내리는건[7]', 'date': '2026.03.20 10:16', 'views': '468', 'likes': '51', 'dislikes': '5', 'link': '/item/board_read.naver?code=032820&amp;nid=415456653&amp;page=22', 'score': 1998}, {'title': '■두빌-14만[2]', 'date': '2026.03.20 11:00', 'views': '563', 'likes': '48', 'dislikes': '7', 'link': '/item/board_read.naver?code=032820&amp;nid=415465317&amp;page=20', 'score': 2003}, {'title': '■우기-매출에 대한 평가', 'date': '2026.03.20 10:44', 'views': '425', 'likes': '47', 'dislikes': '5', 'link': '/item/board_read.naver?code=032820&amp;nid=415461809&amp;page=21', 'score': 1835}, {'title': '■프매-2~3백만주 매수[2]', 'date': '2026.03.20 09:06', 'views': '438', 'likes': '47', 'dislikes': '7', 'link': '/item/board_read.naver?code=032820&amp;nid=415438984&amp;page=28', 'score': 1848}, {'title': '오늘도 안타깝게 저의 예측이 맞았네요..ㅠ[17]', 'date': '2026.03.20 15:37', 'views': '1450', 'likes': '44', 'dislikes': '1', 'link': '/item/board_read.naver?code=032820&amp;nid=415508951&amp;page=4', 'score': 2770}, {'title': '■쓰리바닥이며는[4]', 'date': '2026.03.20 12:55', 'views': '488', 'likes': '39', 'dislikes': '10', 'link': '/item/board_read.naver?code=032820&amp;nid=415483698&amp;page=16', 'score': 1658}]</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>휴림로봇, FTSE 스몰캡 지수 신규 편... / 모간이 눈치빨라서[4] / 오늘 15% 이상[1] / Ai가 분석한 오늘 모간이</t>
+          <t>휴림로봇, FTSE 스몰캡 지수 신규 편... / 모간이 눈치빨라서[4] / 오늘 15% 이상[1] / 우앙ㆍ290만주를 14020원에 외인...[2]</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>[{'title': '오늘 15% 이상[1]', 'date': '2026.03.20 08:23', 'views': '195', 'likes': '30', 'dislikes': '2', 'link': '/item/board_read.naver?code=090710&amp;nid=415432758&amp;page=10', 'score': 1095}, {'title': '휴림로봇, FTSE 스몰캡 지수 신규 편...', 'date': '2026.03.20 15:56', 'views': '850', 'likes': '21', 'dislikes': '3', 'link': '/item/board_read.naver?code=090710&amp;nid=415511389&amp;page=2', 'score': 1480}, {'title': '모간이 눈치빨라서[4]', 'date': '2026.03.20 15:51', 'views': '685', 'likes': '20', 'dislikes': '2', 'link': '/item/board_read.naver?code=090710&amp;nid=415510748&amp;page=2', 'score': 1285}, {'title': '다음주 기대 되는구만~~~~~', 'date': '2026.03.20 15:58', 'views': '192', 'likes': '18', 'dislikes': '3', 'link': '/item/board_read.naver?code=090710&amp;nid=415511546&amp;page=2', 'score': 732}, {'title': '로보스타  장전거래 급등', 'date': '2026.03.20 08:22', 'views': '115', 'likes': '18', 'dislikes': '2', 'link': '/item/board_read.naver?code=090710&amp;nid=415432731&amp;page=10', 'score': 655}, {'title': '안티들아 미안하지만[1]', 'date': '2026.03.20 08:06', 'views': '141', 'likes': '14', 'dislikes': '5', 'link': '/item/board_read.naver?code=090710&amp;nid=415430565&amp;page=10', 'score': 561}, {'title': '우앙ㆍ290만주를 14020원에 외인...[2]', 'date': '2026.03.20 17:14', 'views': '593', 'likes': '13', 'dislikes': '4', 'link': '/item/board_read.naver?code=090710&amp;nid=415517298&amp;page=1', 'score': 983}, {'title': '어제 시외털린 개미들[2]', 'date': '2026.03.20 08:12', 'views': '184', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=090710&amp;nid=415431415&amp;page=10', 'score': 574}, {'title': 'Ai가 분석한 오늘 모간이', 'date': '2026.03.20 16:10', 'views': '681', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=090710&amp;nid=415512751&amp;page=2', 'score': 1041}, {'title': '감보만', 'date': '2026.03.20 15:57', 'views': '149', 'likes': '11', 'dislikes': '3', 'link': '/item/board_read.naver?code=090710&amp;nid=415511420&amp;page=2', 'score': 479}]</t>
+          <t>[{'title': '오늘 15% 이상[1]', 'date': '2026.03.20 08:23', 'views': '196', 'likes': '30', 'dislikes': '2', 'link': '/item/board_read.naver?code=090710&amp;nid=415432758&amp;page=10', 'score': 1096}, {'title': '휴림로봇, FTSE 스몰캡 지수 신규 편...', 'date': '2026.03.20 15:56', 'views': '859', 'likes': '21', 'dislikes': '3', 'link': '/item/board_read.naver?code=090710&amp;nid=415511389&amp;page=2', 'score': 1489}, {'title': '모간이 눈치빨라서[4]', 'date': '2026.03.20 15:51', 'views': '689', 'likes': '20', 'dislikes': '2', 'link': '/item/board_read.naver?code=090710&amp;nid=415510748&amp;page=2', 'score': 1289}, {'title': '다음주 기대 되는구만~~~~~', 'date': '2026.03.20 15:58', 'views': '192', 'likes': '18', 'dislikes': '3', 'link': '/item/board_read.naver?code=090710&amp;nid=415511546&amp;page=2', 'score': 732}, {'title': '로보스타  장전거래 급등', 'date': '2026.03.20 08:22', 'views': '115', 'likes': '18', 'dislikes': '2', 'link': '/item/board_read.naver?code=090710&amp;nid=415432731&amp;page=10', 'score': 655}, {'title': '우앙ㆍ290만주를 14020원에 외인...[2]', 'date': '2026.03.20 17:14', 'views': '610', 'likes': '15', 'dislikes': '4', 'link': '/item/board_read.naver?code=090710&amp;nid=415517298&amp;page=1', 'score': 1060}, {'title': '안티들아 미안하지만[1]', 'date': '2026.03.20 08:06', 'views': '141', 'likes': '14', 'dislikes': '5', 'link': '/item/board_read.naver?code=090710&amp;nid=415430565&amp;page=10', 'score': 561}, {'title': '어제 시외털린 개미들[2]', 'date': '2026.03.20 08:12', 'views': '184', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=090710&amp;nid=415431415&amp;page=10', 'score': 574}, {'title': 'Ai가 분석한 오늘 모간이', 'date': '2026.03.20 16:10', 'views': '685', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=090710&amp;nid=415512751&amp;page=2', 'score': 1045}, {'title': '감보만', 'date': '2026.03.20 15:57', 'views': '150', 'likes': '11', 'dislikes': '3', 'link': '/item/board_read.naver?code=090710&amp;nid=415511420&amp;page=2', 'score': 480}]</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>[{'title': '5년만에 조금 손해보고 나왔다', 'date': '2026.03.20 11:31', 'views': '85', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=011930&amp;nid=415470896&amp;page=4', 'score': 385}, {'title': '에헤라디여[1]', 'date': '2026.03.20 15:26', 'views': '258', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415507334&amp;page=1', 'score': 528}, {'title': '기관,외인 몰빵이네~)와!!시간외 급등~', 'date': '2026.03.20 17:14', 'views': '121', 'likes': '8', 'dislikes': '3', 'link': '/item/board_read.naver?code=011930&amp;nid=415517289&amp;page=1', 'score': 361}, {'title': '저점높이고있죠잉', 'date': '2026.03.20 11:10', 'views': '60', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415466941&amp;page=5', 'score': 300}, {'title': '이 작은 주식에 외인 빠졌어도 아직 8%넘고', 'date': '2026.03.20 17:54', 'views': '125', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=011930&amp;nid=415519674&amp;page=1', 'score': 335}, {'title': '월요일최소20프로는갈듯', 'date': '2026.03.20 14:17', 'views': '114', 'likes': '7', 'dislikes': '6', 'link': '/item/board_read.naver?code=011930&amp;nid=415496446&amp;page=2', 'score': 324}, {'title': '5년동안', 'date': '2026.03.20 12:36', 'views': '77', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415480849&amp;page=4', 'score': 287}, {'title': '금감원[2]', 'date': '2026.03.20 10:47', 'views': '144', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=011930&amp;nid=415462666&amp;page=5', 'score': 354}, {'title': '프로그램 매수 금액이  양선으로 돌아섯다.', 'date': '2026.03.20 11:18', 'views': '70', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=011930&amp;nid=415468523&amp;page=5', 'score': 250}, {'title': '퇴계이황이', 'date': '2026.03.20 11:10', 'views': '36', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415466907&amp;page=5', 'score': 216}]</t>
+          <t>[{'title': '5년만에 조금 손해보고 나왔다', 'date': '2026.03.20 11:31', 'views': '86', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=011930&amp;nid=415470896&amp;page=4', 'score': 386}, {'title': '에헤라디여[1]', 'date': '2026.03.20 15:26', 'views': '260', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415507334&amp;page=1', 'score': 530}, {'title': '기관,외인 몰빵이네~)와!!시간외 급등~', 'date': '2026.03.20 17:14', 'views': '124', 'likes': '8', 'dislikes': '3', 'link': '/item/board_read.naver?code=011930&amp;nid=415517289&amp;page=1', 'score': 364}, {'title': '저점높이고있죠잉', 'date': '2026.03.20 11:10', 'views': '61', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415466941&amp;page=5', 'score': 301}, {'title': '이 작은 주식에 외인 빠졌어도 아직 8%넘고', 'date': '2026.03.20 17:54', 'views': '129', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=011930&amp;nid=415519674&amp;page=1', 'score': 339}, {'title': '월요일최소20프로는갈듯', 'date': '2026.03.20 14:17', 'views': '115', 'likes': '7', 'dislikes': '6', 'link': '/item/board_read.naver?code=011930&amp;nid=415496446&amp;page=2', 'score': 325}, {'title': '5년동안', 'date': '2026.03.20 12:36', 'views': '78', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415480849&amp;page=4', 'score': 288}, {'title': '금감원[2]', 'date': '2026.03.20 10:47', 'views': '145', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=011930&amp;nid=415462666&amp;page=5', 'score': 355}, {'title': '프로그램 매수 금액이  양선으로 돌아섯다.', 'date': '2026.03.20 11:18', 'views': '71', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=011930&amp;nid=415468523&amp;page=5', 'score': 251}, {'title': '퇴계이황이', 'date': '2026.03.20 11:10', 'views': '37', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415466907&amp;page=5', 'score': 217}]</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>[{'title': '삼전본주  25만가면[3]', 'date': '2026.03.20 11:56', 'views': '643', 'likes': '19', 'dislikes': '12', 'link': '/item/board_read.naver?code=005935&amp;nid=415475248&amp;page=4', 'score': 1213}, {'title': '네마녀관련 리벨런싱된겁니다.[1]', 'date': '2026.03.20 15:41', 'views': '581', 'likes': '18', 'dislikes': '5', 'link': '/item/board_read.naver?code=005935&amp;nid=415509542&amp;page=1', 'score': 1121}, {'title': '우선주 괜히삿다[4]', 'date': '2026.03.20 14:39', 'views': '451', 'likes': '15', 'dislikes': '5', 'link': '/item/board_read.naver?code=005935&amp;nid=415499789&amp;page=2', 'score': 901}, {'title': '이거는 얼마에 주워야됌?[3]', 'date': '2026.03.20 12:21', 'views': '924', 'likes': '14', 'dislikes': '0', 'link': '/item/board_read.naver?code=005935&amp;nid=415478727&amp;page=4', 'score': 1344}, {'title': '진짜 우선주는 상폐시켜야', 'date': '2026.03.20 13:27', 'views': '110', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=005935&amp;nid=415488525&amp;page=3', 'score': 500}, {'title': '초보들은 우선주가 뭔지도 모른다', 'date': '2026.03.20 14:49', 'views': '349', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=005935&amp;nid=415501372&amp;page=2', 'score': 679}, {'title': '우선주 없애야 할듯', 'date': '2026.03.20 13:30', 'views': '232', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=005935&amp;nid=415489108&amp;page=3', 'score': 562}, {'title': '삼전우만 어디 전쟁났음?', 'date': '2026.03.20 16:04', 'views': '173', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=005935&amp;nid=415512166&amp;page=1', 'score': 473}, {'title': '우선주가[2]', 'date': '2026.03.20 14:30', 'views': '266', 'likes': '10', 'dislikes': '4', 'link': '/item/board_read.naver?code=005935&amp;nid=415498427&amp;page=2', 'score': 566}, {'title': '속보) 삼성전자: 7.2조(3700...[4]', 'date': '2026.03.20 11:56', 'views': '502', 'likes': '10', 'dislikes': '4', 'link': '/item/board_read.naver?code=005935&amp;nid=415475154&amp;page=4', 'score': 802}]</t>
+          <t>[{'title': '삼전본주  25만가면[3]', 'date': '2026.03.20 11:56', 'views': '646', 'likes': '21', 'dislikes': '12', 'link': '/item/board_read.naver?code=005935&amp;nid=415475248&amp;page=4', 'score': 1276}, {'title': '네마녀관련 리벨런싱된겁니다.[1]', 'date': '2026.03.20 15:41', 'views': '591', 'likes': '19', 'dislikes': '5', 'link': '/item/board_read.naver?code=005935&amp;nid=415509542&amp;page=1', 'score': 1161}, {'title': '우선주 괜히삿다[4]', 'date': '2026.03.20 14:39', 'views': '453', 'likes': '15', 'dislikes': '5', 'link': '/item/board_read.naver?code=005935&amp;nid=415499789&amp;page=2', 'score': 903}, {'title': '이거는 얼마에 주워야됌?[3]', 'date': '2026.03.20 12:21', 'views': '924', 'likes': '14', 'dislikes': '0', 'link': '/item/board_read.naver?code=005935&amp;nid=415478727&amp;page=4', 'score': 1344}, {'title': '진짜 우선주는 상폐시켜야', 'date': '2026.03.20 13:27', 'views': '110', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=005935&amp;nid=415488525&amp;page=3', 'score': 500}, {'title': '초보들은 우선주가 뭔지도 모른다', 'date': '2026.03.20 14:49', 'views': '352', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=005935&amp;nid=415501372&amp;page=2', 'score': 682}, {'title': '우선주가[2]', 'date': '2026.03.20 14:30', 'views': '267', 'likes': '11', 'dislikes': '4', 'link': '/item/board_read.naver?code=005935&amp;nid=415498427&amp;page=2', 'score': 597}, {'title': '우선주 없애야 할듯', 'date': '2026.03.20 13:30', 'views': '233', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=005935&amp;nid=415489108&amp;page=3', 'score': 563}, {'title': '삼전우만 어디 전쟁났음?', 'date': '2026.03.20 16:04', 'views': '175', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=005935&amp;nid=415512166&amp;page=1', 'score': 475}, {'title': '외국인들 패대기에', 'date': '2026.03.20 15:39', 'views': '174', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=005935&amp;nid=415509179&amp;page=1', 'score': 474}]</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>현재 붉은사막 상황[6] / 안티할 생각 없습니다. 다만 현실을 직시하세요...[3] / 어제 지켜보자고 글썼는데[2] / 스팀평가 심각성을 못 느끼시네요[3]</t>
+          <t>안티할 생각 없습니다. 다만 현실을 직시하...[3] / 저는 걍 들고 갑니다 ㅋㅋ[10] / 스팀 매출 순위, 게임에 대한 평가[4] / 처음부터 공매도세력이 작전한거다.[8]</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Negative (67%)</t>
+          <t>Negative (66%)</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>[{'title': '안티할 생각 없습니다. 다만 현실을 직시하세요...[3]', 'date': '2026.03.20 19:01', 'views': '265', 'likes': '20', 'dislikes': '3', 'link': '/item/board_read.naver?code=263750&amp;nid=415523055&amp;page=10', 'score': 865}, {'title': '풍월량) 조작감 진짜 최악이다[1]', 'date': '2026.03.20 19:08', 'views': '180', 'likes': '17', 'dislikes': '1', 'link': '/item/board_read.naver?code=263750&amp;nid=415523388&amp;page=8', 'score': 690}, {'title': '성질 급한 나라에선 낮은평점[3]', 'date': '2026.03.20 17:53', 'views': '145', 'likes': '17', 'dislikes': '2', 'link': '/item/board_read.naver?code=263750&amp;nid=415519627&amp;page=25', 'score': 655}, {'title': '어제 지켜보자고 글썼는데[2]', 'date': '2026.03.20 18:06', 'views': '298', 'likes': '16', 'dislikes': '4', 'link': '/item/board_read.naver?code=263750&amp;nid=415520353&amp;page=22', 'score': 778}, {'title': '스팀평가 심각성을 못 느끼시네요[3]', 'date': '2026.03.20 18:05', 'views': '288', 'likes': '16', 'dislikes': '4', 'link': '/item/board_read.naver?code=263750&amp;nid=415520296&amp;page=22', 'score': 768}, {'title': '업데이트만 잘 되면 싸펑급이 될거다[1]', 'date': '2026.03.20 17:42', 'views': '160', 'likes': '16', 'dislikes': '2', 'link': '/item/board_read.naver?code=263750&amp;nid=415518970&amp;page=28', 'score': 640}, {'title': '스팀 일본 1위로 상승[2]', 'date': '2026.03.20 18:02', 'views': '231', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=263750&amp;nid=415520132&amp;page=23', 'score': 681}, {'title': '난  물린 사람들. 유튜버들이 한몫했다 봄[2]', 'date': '2026.03.20 18:09', 'views': '142', 'likes': '14', 'dislikes': '0', 'link': '/item/board_read.naver?code=263750&amp;nid=415520486&amp;page=21', 'score': 562}, {'title': '안티들은 붉은사막이 오늘 하루 팔고 끝나는 건줄...[11]', 'date': '2026.03.20 17:12', 'views': '309', 'likes': '14', 'dislikes': '9', 'link': '/item/board_read.naver?code=263750&amp;nid=415517146&amp;page=36', 'score': 729}, {'title': '현재 붉은사막 상황[6]', 'date': '2026.03.20 17:07', 'views': '552', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=263750&amp;nid=415516781&amp;page=36', 'score': 942}]</t>
+          <t>[{'title': '처음부터 공매도세력이 작전한거다.[8]', 'date': '2026.03.20 19:41', 'views': '197', 'likes': '20', 'dislikes': '8', 'link': '/item/board_read.naver?code=263750&amp;nid=415525033&amp;page=2', 'score': 797}, {'title': '안티할 생각 없습니다. 다만 현실을 직시하...[3]', 'date': '2026.03.20 19:01', 'views': '265', 'likes': '20', 'dislikes': '3', 'link': '/item/board_read.naver?code=263750&amp;nid=415523055&amp;page=12', 'score': 865}, {'title': '저는 걍 들고 갑니다 ㅋㅋ[10]', 'date': '2026.03.20 19:41', 'views': '292', 'likes': '19', 'dislikes': '6', 'link': '/item/board_read.naver?code=263750&amp;nid=415525032&amp;page=2', 'score': 862}, {'title': '풍월량) 조작감 진짜 최악이다[1]', 'date': '2026.03.20 19:08', 'views': '183', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=263750&amp;nid=415523388&amp;page=10', 'score': 723}, {'title': '성질 급한 나라에선 낮은평점[3]', 'date': '2026.03.20 17:53', 'views': '145', 'likes': '17', 'dislikes': '2', 'link': '/item/board_read.naver?code=263750&amp;nid=415519627&amp;page=27', 'score': 655}, {'title': '어제 지켜보자고 글썼는데[2]', 'date': '2026.03.20 18:06', 'views': '298', 'likes': '16', 'dislikes': '4', 'link': '/item/board_read.naver?code=263750&amp;nid=415520353&amp;page=23', 'score': 778}, {'title': '스팀평가 심각성을 못 느끼시네요[3]', 'date': '2026.03.20 18:05', 'views': '289', 'likes': '16', 'dislikes': '4', 'link': '/item/board_read.naver?code=263750&amp;nid=415520296&amp;page=24', 'score': 769}, {'title': '업데이트만 잘 되면 싸펑급이 될거다[1]', 'date': '2026.03.20 17:42', 'views': '160', 'likes': '16', 'dislikes': '2', 'link': '/item/board_read.naver?code=263750&amp;nid=415518970&amp;page=29', 'score': 640}, {'title': '스팀 매출 순위, 게임에 대한 평가[4]', 'date': '2026.03.20 19:39', 'views': '368', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=263750&amp;nid=415524942&amp;page=3', 'score': 818}, {'title': '스팀 일본 1위로 상승[2]', 'date': '2026.03.20 18:02', 'views': '233', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=263750&amp;nid=415520132&amp;page=25', 'score': 683}]</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>소룩스랑 차백신[3] / 소룩스가 주인인데 소룩스가 소외된다는 것...[3] / 사채회사여?[2] / 뉴스도 안보시나요 ..아리랑 차백신 합병 방향...[1]</t>
+          <t>소룩스랑 차백신[4] / 소룩스가 주인인데 소룩스가 소외된다는 것...[3] / 사채회사여?[2] / 뉴스도 안보시나요 ..아리랑 차백신 합병 방향...[1]</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>[{'title': '소룩스랑 차백신[3]', 'date': '2026.03.20 17:29', 'views': '452', 'likes': '12', 'dislikes': '17', 'link': '/item/board_read.naver?code=290690&amp;nid=415518240&amp;page=1', 'score': 812}, {'title': '@@이런 대단 한 스래기 첨본다~상폐가답이다', 'date': '2026.03.20 15:01', 'views': '44', 'likes': '12', 'dislikes': '3', 'link': '/item/board_read.naver?code=290690&amp;nid=415503277&amp;page=2', 'score': 404}, {'title': '소룩스 떨어지는 이유', 'date': '2026.03.20 09:45', 'views': '90', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=290690&amp;nid=415449513&amp;page=6', 'score': 450}, {'title': '소룩스가 주인인데 소룩스가 소외된다는 것...[3]', 'date': '2026.03.20 08:22', 'views': '242', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=290690&amp;nid=415432717&amp;page=8', 'score': 602}, {'title': '누가봐도 소룩스인데?', 'date': '2026.03.20 09:43', 'views': '78', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=290690&amp;nid=415448877&amp;page=7', 'score': 378}, {'title': '뉴스도 안보시나요 ..아리랑 차백신 합병 방향...[1]', 'date': '2026.03.20 18:39', 'views': '220', 'likes': '9', 'dislikes': '8', 'link': '/item/board_read.naver?code=290690&amp;nid=415521986&amp;page=1', 'score': 490}, {'title': '기대한 내가 ㄷㅅ이지..[1]', 'date': '2026.03.20 16:05', 'views': '135', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=290690&amp;nid=415512228&amp;page=1', 'score': 405}, {'title': '사채회사여?[2]', 'date': '2026.03.20 15:37', 'views': '273', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=290690&amp;nid=415508956&amp;page=1', 'score': 543}, {'title': '신입 많이 받으셨네', 'date': '2026.03.20 15:21', 'views': '59', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=290690&amp;nid=415506515&amp;page=2', 'score': 329}, {'title': '주가조작으로 망할듯', 'date': '2026.03.20 13:27', 'views': '42', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=290690&amp;nid=415488509&amp;page=3', 'score': 312}]</t>
+          <t>[{'title': '소룩스랑 차백신[4]', 'date': '2026.03.20 17:29', 'views': '465', 'likes': '12', 'dislikes': '17', 'link': '/item/board_read.naver?code=290690&amp;nid=415518240&amp;page=1', 'score': 825}, {'title': '@@이런 대단 한 스래기 첨본다~상폐가답이다', 'date': '2026.03.20 15:01', 'views': '44', 'likes': '12', 'dislikes': '3', 'link': '/item/board_read.naver?code=290690&amp;nid=415503277&amp;page=2', 'score': 404}, {'title': '소룩스 떨어지는 이유', 'date': '2026.03.20 09:45', 'views': '90', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=290690&amp;nid=415449513&amp;page=6', 'score': 450}, {'title': '소룩스가 주인인데 소룩스가 소외된다는 것...[3]', 'date': '2026.03.20 08:22', 'views': '242', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=290690&amp;nid=415432717&amp;page=8', 'score': 602}, {'title': '누가봐도 소룩스인데?', 'date': '2026.03.20 09:43', 'views': '78', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=290690&amp;nid=415448877&amp;page=7', 'score': 378}, {'title': '뉴스도 안보시나요 ..아리랑 차백신 합병 방향...[1]', 'date': '2026.03.20 18:39', 'views': '237', 'likes': '9', 'dislikes': '8', 'link': '/item/board_read.naver?code=290690&amp;nid=415521986&amp;page=1', 'score': 507}, {'title': '기대한 내가 ㄷㅅ이지..[1]', 'date': '2026.03.20 16:05', 'views': '137', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=290690&amp;nid=415512228&amp;page=1', 'score': 407}, {'title': '사채회사여?[2]', 'date': '2026.03.20 15:37', 'views': '274', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=290690&amp;nid=415508956&amp;page=1', 'score': 544}, {'title': '신입 많이 받으셨네', 'date': '2026.03.20 15:21', 'views': '59', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=290690&amp;nid=415506515&amp;page=2', 'score': 329}, {'title': '주가조작으로 망할듯', 'date': '2026.03.20 13:27', 'views': '42', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=290690&amp;nid=415488509&amp;page=3', 'score': 312}]</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">

--- a/data/monthly_report_2026-03.xlsx
+++ b/data/monthly_report_2026-03.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,55 +456,65 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>외인변화</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>당일_게시글수</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>현재_외국인비중</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>시장구분</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>어제_종가</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>어제_외국인비중</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>게시물_요약</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>감정분석</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Top_Keyword</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>연속_등록</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>latest_posts</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>scraper_version</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
@@ -518,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -535,44 +545,48 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>314</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1.04%</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>279</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2개 받았는데 300% 개꿀딱[7] / 미친 한국주식시장..이런거나 고쳐라 / 알지노믹 공모가 22,500원.최고가23만.....[1] / 조단위 기술수출+96.5%보호예수.품절주됨...[1]</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
+          <t>2개 받았는데 300% 개꿀딱[4] / 돈 될만한 종목은 개미한테 매수 기회조차 ...[2] / 미친 한국주식시장..이런거나 고쳐라 / 미국1조3천억+중국5천억. 총 1조8천억 기술...</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>Positive (57%)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>상한가, ..., 유통물량</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>미친, 한국주식시장, 이런거나, 고쳐라, 2개</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>[{'title': '미친 한국주식시장..이런거나 고쳐라', 'date': '2026.03.20 11:46', 'views': '143', 'likes': '20', 'dislikes': '2', 'link': '/item/board_read.naver?code=493280&amp;nid=415473520&amp;page=5', 'score': 743}, {'title': '2개 받았는데 300% 개꿀딱[7]', 'date': '2026.03.20 09:22', 'views': '1208', 'likes': '18', 'dislikes': '5', 'link': '/item/board_read.naver?code=493280&amp;nid=415443396&amp;page=9', 'score': 1748}, {'title': '월욜 상한가 135200원이 종가', 'date': '2026.03.20 15:15', 'views': '128', 'likes': '15', 'dislikes': '4', 'link': '/item/board_read.naver?code=493280&amp;nid=415505509&amp;page=3', 'score': 578}, {'title': '조단위 기술수출+96.5%보호예수.품절주됨...[1]', 'date': '2026.03.20 12:22', 'views': '228', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=493280&amp;nid=415478934&amp;page=5', 'score': 618}, {'title': '■■■따따블매수■■■[1]', 'date': '2026.03.20 09:28', 'views': '153', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=493280&amp;nid=415445066&amp;page=8', 'score': 513}, {'title': '알지노믹 공모가 22,500원.최고가23만.....[1]', 'date': '2026.03.20 17:02', 'views': '290', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=493280&amp;nid=415516486&amp;page=1', 'score': 620}, {'title': '조단위 기술수출+96.5%보호예수.품절주됨.....', 'date': '2026.03.20 17:00', 'views': '139', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=493280&amp;nid=415516332&amp;page=1', 'score': 469}, {'title': '연기금 보험이', 'date': '2026.03.20 16:13', 'views': '133', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=493280&amp;nid=415512981&amp;page=2', 'score': 463}, {'title': '유통물량 14% 기관 확약률 96.5% 점상 몇방이...[1]', 'date': '2026.03.20 15:39', 'views': '231', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=493280&amp;nid=415509202&amp;page=2', 'score': 561}, {'title': '매년적자 펩트론은 수출도없이 40만원 갔다....[2]', 'date': '2026.03.20 13:18', 'views': '226', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=493280&amp;nid=415487110&amp;page=4', 'score': 556}]</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
+        <is>
+          <t>[{'title': '미친 한국주식시장..이런거나 고쳐라', 'date': '2026.03.20 11:46', 'views': '135', 'likes': '19', 'dislikes': '2', 'link': '/item/board_read.naver?code=493280&amp;nid=415473520&amp;page=3', 'body': '', 'score': 705}, {'title': '2개 받았는데 300% 개꿀딱[4]', 'date': '2026.03.20 09:22', 'views': '983', 'likes': '15', 'dislikes': '5', 'link': '/item/board_read.naver?code=493280&amp;nid=415443396&amp;page=7', 'body': '', 'score': 1433}, {'title': '조단위 기술수출+96.5%보호예수.품절주됨...[1]', 'date': '2026.03.20 12:22', 'views': '216', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=493280&amp;nid=415478934&amp;page=3', 'body': '', 'score': 576}, {'title': '미국1조3천억+중국5천억. 총 1조8천억 기술...', 'date': '2026.03.20 10:16', 'views': '292', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=493280&amp;nid=415456611&amp;page=5', 'body': '', 'score': 622}, {'title': '■■■따따블매수■■■[1]', 'date': '2026.03.20 09:28', 'views': '147', 'likes': '11', 'dislikes': '3', 'link': '/item/board_read.naver?code=493280&amp;nid=415445066&amp;page=6', 'body': '', 'score': 477}, {'title': '매년적자 펩트론은 수출도없이 40만원 갔다....[2]', 'date': '2026.03.20 13:18', 'views': '200', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=493280&amp;nid=415487110&amp;page=2', 'body': '', 'score': 500}, {'title': '2024년 1.8조원 기술이전 성과 기반....', 'date': '2026.03.20 12:28', 'views': '132', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=493280&amp;nid=415479764&amp;page=3', 'body': '', 'score': 402}, {'title': '돈 될만한 종목은 개미한테 매수 기회조차 ...[2]', 'date': '2026.03.20 11:47', 'views': '555', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=493280&amp;nid=415473753&amp;page=3', 'body': '', 'score': 825}, {'title': '내가 알지노믹스 상따했었다.', 'date': '2026.03.20 09:33', 'views': '132', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=493280&amp;nid=415446443&amp;page=6', 'body': '', 'score': 402}, {'title': '300% 오른거 사면 진짜 바보다[1]', 'date': '2026.03.20 11:33', 'views': '138', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=493280&amp;nid=415471232&amp;page=3', 'body': '', 'score': 378}]</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>493280</t>
         </is>
@@ -586,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -603,50 +617,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>129</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>4.63%</t>
-        </is>
+        <v>-0.39</v>
+      </c>
+      <c r="G3" t="n">
+        <v>118</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>7.03%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>2085</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>7.03%</t>
-        </is>
+      <c r="J3" t="n">
+        <v>1605</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>국내외 광트랜시버 제조사에 채택 가능성- 제미나...[2] / 대한광통신VS우리로광통신~~~[3] / 우리로광통신! / 털렸네 ㅋㅋ</t>
+          <t>7.42%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>대한광통신VS우리로광통신~~~[3] / 털렸네 ㅋㅋ / 개인의 그릇이 정확히 드러나는 시점이내[2] / 지금 없어서 못판다고 합니다!!</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>Positive (70%)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>상한가, 지금, 시총</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>없어서, 못판다고, 일단, 1조, 가자</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>[{'title': '일단 1조 가자', 'date': '2026.03.20 14:05', 'views': '95', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=046970&amp;nid=415494439&amp;page=1', 'score': 485}, {'title': '쩜상10방200Gbps광검출기없어서못판다...', 'date': '2026.03.20 11:12', 'views': '159', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415467252&amp;page=2', 'score': 549}, {'title': '우리로광통신!', 'date': '2026.03.20 13:18', 'views': '230', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415487096&amp;page=2', 'score': 590}, {'title': '응아가 10연발 간다고 어제 분명히 말했...', 'date': '2026.03.20 11:12', 'views': '78', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415467305&amp;page=2', 'score': 438}, {'title': '지금 없어서 못판다고 합니다!!', 'date': '2026.03.20 10:57', 'views': '192', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415464594&amp;page=3', 'score': 552}, {'title': '대한광통신VS우리로광통신~~~[3]', 'date': '2026.03.20 10:22', 'views': '264', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415457884&amp;page=3', 'score': 624}, {'title': '국내외 광트랜시버 제조사에 채택 가능성- 제미나...[2]', 'date': '2026.03.20 16:12', 'views': '531', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415512943&amp;page=1', 'score': 861}, {'title': '털렸네 ㅋㅋ', 'date': '2026.03.20 11:05', 'views': '237', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415466133&amp;page=2', 'score': 567}, {'title': '개인의 그릇이 정확히 드러나는 시점이내[2]', 'date': '2026.03.20 10:16', 'views': '227', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415456527&amp;page=3', 'score': 557}, {'title': '오늘 감사보고서 받아 적정판결', 'date': '2026.03.20 14:16', 'views': '166', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415496290&amp;page=1', 'score': 466}]</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
+        <is>
+          <t>[{'title': '지금 없어서 못판다고 합니다!!', 'date': '2026.03.20 10:57', 'views': '168', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415464594&amp;page=2', 'body': '', 'score': 528}, {'title': '일단 1조 가자', 'date': '2026.03.20 14:05', 'views': '53', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415494439&amp;page=1', 'body': '', 'score': 383}, {'title': '우리로광통신!', 'date': '2026.03.20 13:18', 'views': '171', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415487096&amp;page=1', 'body': '', 'score': 501}, {'title': '응아가 10연발 간다고 어제 분명히 말했...', 'date': '2026.03.20 11:12', 'views': '69', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415467305&amp;page=2', 'body': '', 'score': 399}, {'title': '쩜상10방200Gbps광검출기없어서못판다...', 'date': '2026.03.20 11:12', 'views': '133', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415467252&amp;page=2', 'body': '', 'score': 463}, {'title': '털렸네 ㅋㅋ', 'date': '2026.03.20 11:05', 'views': '208', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415466133&amp;page=2', 'body': '', 'score': 538}, {'title': '대한광통신VS우리로광통신~~~[3]', 'date': '2026.03.20 10:22', 'views': '237', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415457884&amp;page=2', 'body': '', 'score': 567}, {'title': '개인의 그릇이 정확히 드러나는 시점이내[2]', 'date': '2026.03.20 10:16', 'views': '204', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415456527&amp;page=2', 'body': '', 'score': 534}, {'title': '쩜상10방뉴스200Gbps광검출기국산화성공', 'date': '2026.03.20 10:05', 'views': '104', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=046970&amp;nid=415454212&amp;page=3', 'body': '', 'score': 404}, {'title': '오늘 감사보고서 받아 적정판결', 'date': '2026.03.20 14:16', 'views': '110', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=046970&amp;nid=415496290&amp;page=1', 'body': '', 'score': 380}]</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>046970</t>
         </is>
@@ -660,7 +682,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -677,50 +699,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>241</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>29.72%</t>
-        </is>
+        <v>-0.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>172</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>29.24%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>51900</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>29.24%</t>
-        </is>
+      <c r="J4" t="n">
+        <v>51600</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>진짜 설마 설마 했는데[5] / 미국 원전주..이란 전쟁 재건주[4] / 이란 전쟁재건 대장주는 DL이앤씨다. 왜냐하 / 5년을 기다렸다[2]</t>
+          <t>29.28%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Positive (90%)</t>
+          <t>너희들 월봉 매물대 봤냐?[2] / 이란 전쟁재건 대장주는 DL이앤씨다. 왜냐하 / 5년을 기다렸다[2] / 소형모듈원전 SMR 건설 분야 국내  1...</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>상한가, 오늘, 대장주</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
+          <t>Positive (82%)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>너희들, 월봉, 매물대, 봤냐, 이란</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>[{'title': '진짜 설마 설마 했는데[5]', 'date': '2026.03.20 15:23', 'views': '589', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=375500&amp;nid=415506745&amp;page=4', 'score': 979}, {'title': '미국 원전주..이란 전쟁 재건주[4]', 'date': '2026.03.20 18:08', 'views': '366', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=375500&amp;nid=415520425&amp;page=1', 'score': 666}, {'title': '축하드립니다.[2]', 'date': '2026.03.20 15:09', 'views': '152', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415504578&amp;page=5', 'score': 422}, {'title': '이란 전쟁재건 대장주는 DL이앤씨다. 왜냐하', 'date': '2026.03.20 14:22', 'views': '293', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=375500&amp;nid=415497229&amp;page=6', 'score': 563}, {'title': '5년을 기다렸다[2]', 'date': '2026.03.20 10:21', 'views': '241', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415457629&amp;page=10', 'score': 511}, {'title': '소형모듈원전 SMR 건설 분야 국내  1...', 'date': '2026.03.20 10:02', 'views': '186', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415453423&amp;page=10', 'score': 456}, {'title': '미-이란 전쟁이 끝나면 대박', 'date': '2026.03.20 16:46', 'views': '119', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415515306&amp;page=2', 'score': 359}, {'title': 'Gs건설 더 간다', 'date': '2026.03.20 09:25', 'views': '55', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415444110&amp;page=11', 'score': 295}, {'title': '앞으로 5년', 'date': '2026.03.20 18:29', 'views': '54', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=375500&amp;nid=415521565&amp;page=1', 'score': 264}, {'title': '월요일 10퍼이상 상승출발예측[1]', 'date': '2026.03.20 16:50', 'views': '218', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=375500&amp;nid=415515620&amp;page=2', 'score': 428}]</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
+        <is>
+          <t>[{'title': '너희들 월봉 매물대 봤냐?[2]', 'date': '2026.03.20 10:21', 'views': '1152', 'likes': '17', 'dislikes': '5', 'link': '/item/board_read.naver?code=375500&amp;nid=415457604&amp;page=6', 'body': '', 'score': 1662}, {'title': '이란 전쟁재건 대장주는 DL이앤씨다. 왜냐하', 'date': '2026.03.20 14:22', 'views': '234', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=375500&amp;nid=415497229&amp;page=2', 'body': '', 'score': 504}, {'title': '소형모듈원전 SMR 건설 분야 국내  1...', 'date': '2026.03.20 10:02', 'views': '181', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415453423&amp;page=7', 'body': '', 'score': 451}, {'title': '5년을 기다렸다[2]', 'date': '2026.03.20 10:21', 'views': '230', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415457629&amp;page=6', 'body': '', 'score': 470}, {'title': 'Gs건설 더 간다', 'date': '2026.03.20 09:25', 'views': '53', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415444110&amp;page=8', 'body': '', 'score': 293}, {'title': '염승환이 추천한주', 'date': '2026.03.20 12:57', 'views': '135', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415483870&amp;page=4', 'body': '', 'score': 315}, {'title': 'DL이엔씨 ㅡ원전 대장주 X에너지 지분 투...', 'date': '2026.03.20 11:19', 'views': '241', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415468705&amp;page=6', 'body': '', 'score': 421}, {'title': '축하드립니다.[2]', 'date': '2026.03.20 15:09', 'views': '110', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415504578&amp;page=1', 'body': '', 'score': 260}, {'title': '헐~~', 'date': '2026.03.20 14:24', 'views': '58', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=375500&amp;nid=415497467&amp;page=2', 'body': '', 'score': 208}, {'title': '속이 후련하네요[2]', 'date': '2026.03.20 10:32', 'views': '141', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=375500&amp;nid=415459688&amp;page=6', 'body': '', 'score': 291}]</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>375500</t>
         </is>
@@ -734,7 +764,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -751,50 +781,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>602</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>6.07%</t>
-        </is>
+        <v>0.22</v>
+      </c>
+      <c r="G5" t="n">
+        <v>489</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>6.23%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>19680</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>6.23%</t>
-        </is>
+      <c r="J5" t="n">
+        <v>18940</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>6.01%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>오션플랜트가 오늘 해상풍력 대장주가 된 이유는[5] / IPO 막히면 SK가 매각할 이유가 없음 / 개인적으로 생각하는 갑자기 오르는 이유 / 여기 돈 못버는 애들 특징 다 나오네[4]</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Positive (56%)</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>상한가, 오늘, 이제</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
+          <t>Positive (59%)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>해상풍력, 대장주가, 이유는, 디오션, 매각</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>[{'title': '오션플랜트가 오늘 해상풍력 대장주가 된 이유는[5]', 'date': '2026.03.20 14:07', 'views': '283', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=100090&amp;nid=415494734&amp;page=11', 'score': 733}, {'title': '월요일', 'date': '2026.03.20 16:16', 'views': '123', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=100090&amp;nid=415513208&amp;page=6', 'score': 423}, {'title': '디오션 sk오션플랜트 매각 확실히 물건너감..[1]', 'date': '2026.03.20 14:21', 'views': '173', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=100090&amp;nid=415497052&amp;page=11', 'score': 473}, {'title': '아까 누가 상 못간다고 한놈 있었는데?[4]', 'date': '2026.03.20 15:03', 'views': '189', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=100090&amp;nid=415503619&amp;page=8', 'score': 459}, {'title': '25-29층에 물린 사람이 제일 많음[1]', 'date': '2026.03.20 14:36', 'views': '154', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=100090&amp;nid=415499281&amp;page=9', 'score': 424}, {'title': '여기 돈 못버는 애들 특징 다 나오네[4]', 'date': '2026.03.20 10:26', 'views': '211', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=100090&amp;nid=415458579&amp;page=22', 'score': 481}, {'title': '개인적으로 생각하는 갑자기 오르는 이유', 'date': '2026.03.20 09:16', 'views': '229', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=100090&amp;nid=415441684&amp;page=27', 'score': 499}, {'title': 'IPO 막히면 SK가 매각할 이유가 없음', 'date': '2026.03.20 08:22', 'views': '249', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=100090&amp;nid=415432658&amp;page=30', 'score': 519}, {'title': '잘 알아보니[1]', 'date': '2026.03.20 15:38', 'views': '123', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=100090&amp;nid=415509071&amp;page=7', 'score': 363}, {'title': '상에서1000만주를 흡수했으면 뭐다', 'date': '2026.03.20 15:03', 'views': '86', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=100090&amp;nid=415503522&amp;page=8', 'score': 326}]</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
+        <is>
+          <t>[{'title': '오션플랜트가 오늘 해상풍력 대장주가 된 이유는[5]', 'date': '2026.03.20 14:07', 'views': '263', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=100090&amp;nid=415494734&amp;page=5', 'body': '', 'score': 713}, {'title': '디오션 sk오션플랜트 매각 확실히 물건너감..[1]', 'date': '2026.03.20 14:21', 'views': '157', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=100090&amp;nid=415497052&amp;page=4', 'body': '', 'score': 457}, {'title': '25-29층에 물린 사람이 제일 많음[1]', 'date': '2026.03.20 14:36', 'views': '131', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=100090&amp;nid=415499281&amp;page=3', 'body': '', 'score': 401}, {'title': '여기 돈 못버는 애들 특징 다 나오네[4]', 'date': '2026.03.20 10:26', 'views': '208', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=100090&amp;nid=415458579&amp;page=16', 'body': '', 'score': 478}, {'title': '개인적으로 생각하는 갑자기 오르는 이유', 'date': '2026.03.20 09:16', 'views': '225', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=100090&amp;nid=415441684&amp;page=21', 'body': '', 'score': 495}, {'title': 'IPO 막히면 SK가 매각할 이유가 없음', 'date': '2026.03.20 08:22', 'views': '245', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=100090&amp;nid=415432658&amp;page=24', 'body': '', 'score': 515}, {'title': '아까 누가 상 못간다고 한놈 있었는데?[4]', 'date': '2026.03.20 15:03', 'views': '160', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=100090&amp;nid=415503619&amp;page=1', 'body': '', 'score': 400}, {'title': '상에서1000만주를 흡수했으면 뭐다', 'date': '2026.03.20 15:03', 'views': '71', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100090&amp;nid=415503522&amp;page=2', 'body': '', 'score': 281}, {'title': 'SK 그룹이', 'date': '2026.03.20 12:13', 'views': '193', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100090&amp;nid=415477606&amp;page=11', 'body': '', 'score': 403}, {'title': '설거지다', 'date': '2026.03.20 11:38', 'views': '42', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100090&amp;nid=415472071&amp;page=12', 'body': '', 'score': 252}]</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>100090</t>
         </is>
@@ -808,7 +846,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -817,58 +855,66 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>53300</v>
+        <v>53400</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+28.28%</t>
+          <t>+28.52%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>171</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>6.53%</t>
-        </is>
+        <v>-0.02</v>
+      </c>
+      <c r="G6" t="n">
+        <v>131</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>5.22%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>41550</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>5.22%</t>
-        </is>
+      <c r="J6" t="n">
+        <v>42050</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>석유·가스 플랜트에 들어가는 공랭식 열교환기(A...[1] / EB로 풀린 45만주 오늘 정리?[5] / 목표가 10만 기도 54일차[3] / 이놈이 대장이었네..</t>
+          <t>5.24%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Positive (59%)</t>
+          <t>석유·가스 플랜트에 들어가는 공랭식 열교환기(A... / 목표가 10만 기도 54일차[3] / 이놈이 대장이었네.. / 사우디 아람코와 아랍에미레이트 석유국은 완전 ...[1]</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>상한가, 이상, 상승했어요</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
+          <t>Positive (57%)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>석유, 가스, 플랜트에, 들어가는, 공랭식</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>[{'title': '석유·가스 플랜트에 들어가는 공랭식 열교환기(A...[1]', 'date': '2026.03.20 12:10', 'views': '441', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415477187&amp;page=5', 'score': 981}, {'title': 'EB로 풀린 45만주 오늘 정리?[5]', 'date': '2026.03.20 15:36', 'views': '157', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415508766&amp;page=2', 'score': 457}, {'title': '목표가 10만 기도 54일차[3]', 'date': '2026.03.20 12:46', 'views': '118', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415482256&amp;page=5', 'score': 388}, {'title': '이놈이 대장이었네..', 'date': '2026.03.20 09:56', 'views': '73', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415451935&amp;page=8', 'score': 343}, {'title': '지주사가 50%이상 가지고 있는데', 'date': '2026.03.20 18:04', 'views': '62', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415520229&amp;page=1', 'score': 272}, {'title': '운전실력.예술![2]', 'date': '2026.03.20 15:21', 'views': '116', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=100840&amp;nid=415506519&amp;page=3', 'score': 326}, {'title': 'IMM 제발 오늘 다 털고 꺼지시길[1]', 'date': '2026.03.20 15:07', 'views': '63', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=100840&amp;nid=415504219&amp;page=3', 'score': 273}, {'title': '차트', 'date': '2026.03.20 14:33', 'views': '33', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415498879&amp;page=4', 'score': 243}, {'title': '사우디 아람코와 아랍에미레이트 석유국은 완전 ...[1]', 'date': '2026.03.20 10:04', 'views': '131', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415454003&amp;page=8', 'score': 341}, {'title': '주식이 이런거지...[1]', 'date': '2026.03.20 09:43', 'views': '73', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415449004&amp;page=8', 'score': 283}]</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
+        <is>
+          <t>[{'title': '석유·가스 플랜트에 들어가는 공랭식 열교환기(A...', 'date': '2026.03.20 12:10', 'views': '277', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415477187&amp;page=3', 'body': '', 'score': 667}, {'title': '목표가 10만 기도 54일차[3]', 'date': '2026.03.20 12:46', 'views': '111', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415482256&amp;page=3', 'body': '', 'score': 381}, {'title': '이놈이 대장이었네..', 'date': '2026.03.20 09:56', 'views': '69', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415451935&amp;page=6', 'body': '', 'score': 339}, {'title': '차트', 'date': '2026.03.20 14:33', 'views': '27', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415498879&amp;page=2', 'body': '', 'score': 237}, {'title': '사우디 아람코와 아랍에미레이트 석유국은 완전 ...[1]', 'date': '2026.03.20 10:04', 'views': '127', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415454003&amp;page=6', 'body': '', 'score': 337}, {'title': '주식이 이런거지...[1]', 'date': '2026.03.20 09:43', 'views': '71', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415449004&amp;page=6', 'body': '', 'score': 281}, {'title': '어후[1]', 'date': '2026.03.20 09:33', 'views': '36', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415446336&amp;page=6', 'body': '', 'score': 246}, {'title': 'IMM 제발 오늘 다 털고 꺼지시길[1]', 'date': '2026.03.20 15:07', 'views': '37', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415504219&amp;page=1', 'body': '', 'score': 217}, {'title': '이정도면 이미 미국 수주 받았나보다[1]', 'date': '2026.03.20 13:40', 'views': '120', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=100840&amp;nid=415490711&amp;page=2', 'body': '', 'score': 300}, {'title': '좋은주식이란?[1]', 'date': '2026.03.20 10:31', 'views': '43', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=100840&amp;nid=415459456&amp;page=5', 'body': '', 'score': 223}]</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>100840</t>
         </is>
@@ -882,7 +928,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -899,50 +945,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>129</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>5.04%</t>
-        </is>
+        <v>-0.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>104</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>3.67%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>45300</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>3.67%</t>
-        </is>
+      <c r="J7" t="n">
+        <v>44100</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>이런 월요일[1] / 테마 엮기 좋고 가벼워서 세력붙으면 정신없이 ... / 상한가에 전량 매도~ 감사감사[2] / 이제 매물이 없어요..🤗</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Positive (73%)</t>
+          <t>자꾸 상한가 풀리는것이 불안하네[1] / 테마 엮기 좋고 가벼워서 세력붙으면 정신없이 쏠... / 상한가에 전량 매도~ 감사감사[2] / 태웅</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>태웅, 상한가, 이상</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
+          <t>Positive (71%)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>테마, 엮기, 좋고, 가벼워서, 세력붙으면</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>[{'title': '테마 엮기 좋고 가벼워서 세력붙으면 정신없이 ...', 'date': '2026.03.20 08:25', 'views': '59', 'likes': '8', 'dislikes': '4', 'link': '/item/board_read.naver?code=044490&amp;nid=415433094&amp;page=7', 'score': 299}, {'title': '이런 월요일[1]', 'date': '2026.03.20 17:08', 'views': '192', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=044490&amp;nid=415516846&amp;page=1', 'score': 402}, {'title': '아 짜증나서 던졌음..', 'date': '2026.03.20 17:00', 'views': '43', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415516322&amp;page=1', 'score': 223}, {'title': '이제 매물이 없어요..🤗', 'date': '2026.03.20 16:07', 'views': '57', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=044490&amp;nid=415512465&amp;page=2', 'score': 237}, {'title': '문어발', 'date': '2026.03.20 12:29', 'views': '51', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=044490&amp;nid=415479929&amp;page=3', 'score': 231}, {'title': '상한가에 전량 매도~ 감사감사[2]', 'date': '2026.03.20 12:03', 'views': '90', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415476158&amp;page=3', 'score': 270}, {'title': '오늘 상이네 ㅎㅎ', 'date': '2026.03.20 09:34', 'views': '27', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415446673&amp;page=6', 'score': 207}, {'title': '태웅', 'date': '2026.03.20 08:44', 'views': '32', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415435563&amp;page=7', 'score': 212}, {'title': '요상하다[1]', 'date': '2026.03.20 18:16', 'views': '87', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=044490&amp;nid=415520871&amp;page=1', 'score': 237}, {'title': '축하 축하 드립니다  상입니다!', 'date': '2026.03.20 18:28', 'views': '21', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=044490&amp;nid=415521465&amp;page=1', 'score': 141}]</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
+        <is>
+          <t>[{'title': '테마 엮기 좋고 가벼워서 세력붙으면 정신없이 쏠...', 'date': '2026.03.20 08:25', 'views': '57', 'likes': '8', 'dislikes': '4', 'link': '/item/board_read.naver?code=044490&amp;nid=415433094&amp;page=5', 'body': '', 'score': 297}, {'title': '상한가에 전량 매도~ 감사감사[2]', 'date': '2026.03.20 12:03', 'views': '72', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415476158&amp;page=2', 'body': '', 'score': 252}, {'title': '자꾸 상한가 풀리는것이 불안하네[1]', 'date': '2026.03.20 10:43', 'views': '121', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=044490&amp;nid=415461740&amp;page=3', 'body': '', 'score': 301}, {'title': '오늘 상이네 ㅎㅎ', 'date': '2026.03.20 09:34', 'views': '24', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415446673&amp;page=5', 'body': '', 'score': 204}, {'title': '태웅', 'date': '2026.03.20 08:44', 'views': '29', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415435563&amp;page=5', 'body': '', 'score': 209}, {'title': '문어발', 'date': '2026.03.20 12:29', 'views': '43', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=044490&amp;nid=415479929&amp;page=1', 'body': '', 'score': 193}, {'title': '57,400원 매도후 관망중이다', 'date': '2026.03.20 12:04', 'views': '27', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=044490&amp;nid=415476415&amp;page=2', 'body': '', 'score': 147}, {'title': '상한가를 못가는 애구만;;', 'date': '2026.03.20 11:43', 'views': '25', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415472853&amp;page=2', 'body': '', 'score': 145}, {'title': '상 풀리면 좋지 않은데....', 'date': '2026.03.20 10:53', 'views': '31', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415463795&amp;page=3', 'body': '', 'score': 151}, {'title': '내가', 'date': '2026.03.20 09:46', 'views': '25', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=044490&amp;nid=415449785&amp;page=5', 'body': '', 'score': 145}]</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>044490</t>
         </is>
@@ -956,7 +1010,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -965,58 +1019,66 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13700</v>
+        <v>13580</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>+24.77%</t>
+          <t>+23.68%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>164</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>4.76%</t>
-        </is>
+        <v>-1.07</v>
+      </c>
+      <c r="G8" t="n">
+        <v>142</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>4.33%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>10980</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>4.33%</t>
-        </is>
+      <c r="J8" t="n">
+        <v>9920</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>답답하다 투경이고뭐고[2] / 눈물 나네요.[2] / 오늘 13568 밑에서 끝나면[3] / 원전 해체 세계 최초 상용화 뭐가 두렵노[1]</t>
+          <t>5.40%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Positive (70%)</t>
+          <t>눈물 나네요.[2] / 오늘 13568 밑에서 끝나면[3] / 3만원은 넘길듯...[2] / 오르비텍</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>투경, 상한가, 오르비텍</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
+          <t>Positive (84%)</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>눈물, 3만원은, 넘길듯, 밑에서, 끝나면</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>[{'title': '원전 해체 세계 최초 상용화 뭐가 두렵노[1]', 'date': '2026.03.20 15:43', 'views': '245', 'likes': '20', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415509812&amp;page=2', 'score': 845}, {'title': '눈물 나네요.[2]', 'date': '2026.03.20 13:54', 'views': '299', 'likes': '19', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415492815&amp;page=4', 'score': 869}, {'title': '오르비텍', 'date': '2026.03.20 13:16', 'views': '189', 'likes': '18', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415486662&amp;page=4', 'score': 729}, {'title': '답답하다 투경이고뭐고[2]', 'date': '2026.03.20 16:42', 'views': '581', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=046120&amp;nid=415515087&amp;page=1', 'score': 1001}, {'title': '100주 샀음요', 'date': '2026.03.20 16:10', 'views': '101', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=046120&amp;nid=415512779&amp;page=1', 'score': 521}, {'title': '3만원은 넘길듯...[2]', 'date': '2026.03.20 13:09', 'views': '345', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=046120&amp;nid=415485691&amp;page=4', 'score': 765}, {'title': '여기 주포는', 'date': '2026.03.20 16:40', 'views': '418', 'likes': '13', 'dislikes': '2', 'link': '/item/board_read.naver?code=046120&amp;nid=415514954&amp;page=1', 'score': 808}, {'title': '시간 외 상 박아 주고 담주 20% 갭으로 가자...', 'date': '2026.03.20 15:28', 'views': '131', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415507583&amp;page=2', 'score': 521}, {'title': '오늘 13568 밑에서 끝나면[3]', 'date': '2026.03.20 14:46', 'views': '497', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=046120&amp;nid=415500943&amp;page=3', 'score': 857}, {'title': '신고가 축하드립니다.', 'date': '2026.03.20 14:26', 'views': '149', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=046120&amp;nid=415497809&amp;page=3', 'score': 509}]</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
+        <is>
+          <t>[{'title': '눈물 나네요.[2]', 'date': '2026.03.20 13:54', 'views': '273', 'likes': '19', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415492815&amp;page=3', 'body': '', 'score': 843}, {'title': '오르비텍', 'date': '2026.03.20 13:16', 'views': '178', 'likes': '18', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415486662&amp;page=3', 'body': '', 'score': 718}, {'title': '3만원은 넘길듯...[2]', 'date': '2026.03.20 13:09', 'views': '329', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=046120&amp;nid=415485691&amp;page=3', 'body': '', 'score': 749}, {'title': '오늘 13568 밑에서 끝나면[3]', 'date': '2026.03.20 14:46', 'views': '406', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=046120&amp;nid=415500943&amp;page=2', 'body': '', 'score': 766}, {'title': '일주일 만에 다시 상한가 가 보자', 'date': '2026.03.20 11:53', 'views': '27', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=046120&amp;nid=415474612&amp;page=5', 'body': '', 'score': 387}, {'title': '오늘 상한가치고 일찍문닫자', 'date': '2026.03.20 11:29', 'views': '33', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415470529&amp;page=5', 'body': '', 'score': 393}, {'title': '형이5만간다하면', 'date': '2026.03.20 09:44', 'views': '119', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=046120&amp;nid=415449240&amp;page=6', 'body': '', 'score': 479}, {'title': '2만[1]', 'date': '2026.03.20 14:40', 'views': '135', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415499916&amp;page=2', 'body': '', 'score': 465}, {'title': '오늘도', 'date': '2026.03.20 10:37', 'views': '63', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=046120&amp;nid=415460541&amp;page=5', 'body': '', 'score': 393}, {'title': '다들 성투하세요![1]', 'date': '2026.03.20 09:27', 'views': '198', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=046120&amp;nid=415444739&amp;page=6', 'body': '', 'score': 528}]</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>046120</t>
         </is>
@@ -1030,7 +1092,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1039,58 +1101,66 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31800</v>
+        <v>31700</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+22.54%</t>
+          <t>+22.16%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>369</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>23.05%</t>
-        </is>
+        <v>-0.79</v>
+      </c>
+      <c r="G9" t="n">
+        <v>259</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>23.16%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>25950</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>23.16%</t>
-        </is>
+      <c r="J9" t="n">
+        <v>25650</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Gs건설이 원전으로만 올라가는걸로 보... / 매물소화중이라니까 계속들 파시네 / 미국에서 SMR건설 누가하겠냐 GS건설[1] / 건설 우량주 Gs건설 상한가 한방 묵자</t>
+          <t>23.95%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Positive (81%)</t>
+          <t>Gs건설이 원전으로만 올라가는걸로 보이나??? / 건설 우량주 Gs건설 상한가 한방 묵... / 상한가 가도 / 월봉[1]</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>상한가, 이제, 원전</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
+          <t>Positive (90%)</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>거래량, 우량주, 한방, 원전으로만, 올라가는걸로</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>[{'title': '매물소화중이라니까 계속들 파시네', 'date': '2026.03.20 15:27', 'views': '196', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415507418&amp;page=7', 'score': 646}, {'title': '건설 우량주 Gs건설 상한가 한방 묵자', 'date': '2026.03.20 12:50', 'views': '105', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415482959&amp;page=11', 'score': 465}, {'title': '뉴스케일파워 믿고 투자하세요.', 'date': '2026.03.20 18:25', 'views': '69', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=006360&amp;nid=415521311&amp;page=4', 'score': 369}, {'title': 's넥장[1]', 'date': '2026.03.20 15:47', 'views': '155', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415510318&amp;page=6', 'score': 455}, {'title': 'Gs건설이 원전으로만 올라가는걸로 보...', 'date': '2026.03.20 11:30', 'views': '523', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=006360&amp;nid=415470730&amp;page=12', 'score': 823}, {'title': '누가 원전주  아니라더니', 'date': '2026.03.20 16:06', 'views': '102', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=006360&amp;nid=415512357&amp;page=6', 'score': 372}, {'title': '상한가 가도', 'date': '2026.03.20 13:06', 'views': '74', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=006360&amp;nid=415485164&amp;page=11', 'score': 344}, {'title': '미국에서 SMR건설 누가하겠냐 GS건설[1]', 'date': '2026.03.20 17:27', 'views': '295', 'likes': '8', 'dislikes': '3', 'link': '/item/board_read.naver?code=006360&amp;nid=415518090&amp;page=5', 'score': 535}, {'title': '상 안쳐도 되는이유[3]', 'date': '2026.03.20 16:05', 'views': '175', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=006360&amp;nid=415512280&amp;page=6', 'score': 415}, {'title': '지건인 에너지 회사임[1]', 'date': '2026.03.20 15:57', 'views': '104', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=006360&amp;nid=415511460&amp;page=6', 'score': 344}]</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
+        <is>
+          <t>[{'title': '건설 우량주 Gs건설 상한가 한방 묵...', 'date': '2026.03.20 12:50', 'views': '100', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415482959&amp;page=6', 'body': '', 'score': 460}, {'title': 'Gs건설이 원전으로만 올라가는걸로 보이나???', 'date': '2026.03.20 11:30', 'views': '512', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=006360&amp;nid=415470730&amp;page=7', 'body': '', 'score': 812}, {'title': '상한가 가도', 'date': '2026.03.20 13:06', 'views': '71', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=006360&amp;nid=415485164&amp;page=5', 'body': '', 'score': 341}, {'title': '월봉[1]', 'date': '2026.03.20 14:36', 'views': '126', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=006360&amp;nid=415499293&amp;page=2', 'body': '', 'score': 336}, {'title': '몇년내 최다 거래량', 'date': '2026.03.20 13:56', 'views': '25', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415493022&amp;page=4', 'body': '', 'score': 235}, {'title': '10여년만에', 'date': '2026.03.20 12:36', 'views': '70', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415480873&amp;page=6', 'body': '', 'score': 280}, {'title': '키 맞추기 하려면 한참 더 가야한다', 'date': '2026.03.20 09:21', 'views': '33', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415443209&amp;page=11', 'body': '', 'score': 243}, {'title': '4년 물타니까 오는구나', 'date': '2026.03.20 09:18', 'views': '36', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415442358&amp;page=11', 'body': '', 'score': 246}, {'title': '사상 최대 거래량', 'date': '2026.03.20 12:56', 'views': '76', 'likes': '6', 'dislikes': '2', 'link': '/item/board_read.naver?code=006360&amp;nid=415483753&amp;page=5', 'body': '', 'score': 256}, {'title': '딱보니 상한가네', 'date': '2026.03.20 13:30', 'views': '39', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=006360&amp;nid=415489056&amp;page=4', 'body': '', 'score': 189}]</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>006360</t>
         </is>
@@ -1104,69 +1174,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>유니슨</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1682</v>
+        <v>73000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>+20.75%</t>
+          <t>+19.67%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>131</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>5.25%</t>
-        </is>
+        <v>0.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>228</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>9.63%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>1393</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.08%</t>
-        </is>
+      <c r="J10" t="n">
+        <v>62900</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>답지 준다. 이거만 외워라.[4] / 총 칠천만주에 거래량 3800만주  터... / 3,000원대 까지는 ~~~[5] / 1차 목표가 만원 2차 목표가 5만원[2]</t>
+          <t>9.59%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Positive (76%)</t>
+          <t>이 정도면 쩜상 가야지[1] / 세력이 핸들링 잘한다고 본다[2] / 한미반도체가 본딩장비로 재평가 받았듯이[2] / 세계 최초 주성만이 할 수 있는 기술입니다...[1]</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>오늘, 이상, 상승했어요</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
+          <t>Positive (62%)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>한미반도체가, 본딩장비로, 재평가, 받았듯이, 정도면</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>[{'title': '총 칠천만주에 거래량 3800만주  터...', 'date': '2026.03.20 15:38', 'views': '278', 'likes': '21', 'dislikes': '1', 'link': '/item/board_read.naver?code=018000&amp;nid=415509095&amp;page=2', 'score': 908}, {'title': '1차 목표가 만원 2차 목표가 5만원[2]', 'date': '2026.03.20 11:35', 'views': '292', 'likes': '20', 'dislikes': '2', 'link': '/item/board_read.naver?code=018000&amp;nid=415471508&amp;page=4', 'score': 892}, {'title': '신재생에너지 기업 주가가', 'date': '2026.03.20 15:49', 'views': '250', 'likes': '19', 'dislikes': '1', 'link': '/item/board_read.naver?code=018000&amp;nid=415510489&amp;page=2', 'score': 820}, {'title': '유니슨 오늘 외인 매수  및 프로그램 대량 매수중[1]', 'date': '2026.03.20 11:51', 'views': '179', 'likes': '19', 'dislikes': '0', 'link': '/item/board_read.naver?code=018000&amp;nid=415474322&amp;page=4', 'score': 749}, {'title': '3,000원대 까지는 ~~~[5]', 'date': '2026.03.20 16:19', 'views': '367', 'likes': '18', 'dislikes': '2', 'link': '/item/board_read.naver?code=018000&amp;nid=415513488&amp;page=1', 'score': 907}, {'title': '답지 준다. 이거만 외워라.[4]', 'date': '2026.03.20 10:24', 'views': '644', 'likes': '17', 'dislikes': '5', 'link': '/item/board_read.naver?code=018000&amp;nid=415458177&amp;page=4', 'score': 1154}, {'title': '오후에 .. 일단 상[1]', 'date': '2026.03.20 12:26', 'views': '258', 'likes': '16', 'dislikes': '5', 'link': '/item/board_read.naver?code=018000&amp;nid=415479527&amp;page=3', 'score': 738}, {'title': '지금까지[1]', 'date': '2026.03.20 11:01', 'views': '204', 'likes': '16', 'dislikes': '1', 'link': '/item/board_read.naver?code=018000&amp;nid=415465465&amp;page=4', 'score': 684}, {'title': '십수년동안 요즘이 거의 저점이다...', 'date': '2026.03.20 16:42', 'views': '134', 'likes': '14', 'dislikes': '0', 'link': '/item/board_read.naver?code=018000&amp;nid=415515055&amp;page=1', 'score': 554}, {'title': '소머리국밥 먹으러 갑니다.[1]', 'date': '2026.03.20 17:48', 'views': '170', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=018000&amp;nid=415519355&amp;page=1', 'score': 560}]</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>018000</t>
+          <t>[{'title': '한미반도체가 본딩장비로 재평가 받았듯이[2]', 'date': '2026.03.20 14:31', 'views': '185', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=036930&amp;nid=415498603&amp;page=2', 'body': '', 'score': 425}, {'title': '이 정도면 쩜상 가야지[1]', 'date': '2026.03.20 12:09', 'views': '216', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=036930&amp;nid=415477137&amp;page=4', 'body': '', 'score': 456}, {'title': '본드로 시가 총액 30조---- 신노광장비...', 'date': '2026.03.20 10:21', 'views': '139', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=036930&amp;nid=415457543&amp;page=7', 'body': '', 'score': 349}, {'title': '사람든 웃긴게', 'date': '2026.03.20 09:28', 'views': '60', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=036930&amp;nid=415445041&amp;page=10', 'body': '', 'score': 270}, {'title': '우리 주성이는요[1]', 'date': '2026.03.20 09:24', 'views': '165', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=036930&amp;nid=415443933&amp;page=11', 'body': '', 'score': 375}, {'title': '이건 대형호재가 아니라[3]', 'date': '2026.03.20 14:35', 'views': '201', 'likes': '6', 'dislikes': '2', 'link': '/item/board_read.naver?code=036930&amp;nid=415499249&amp;page=2', 'body': '', 'score': 381}, {'title': '서서히 폭락 준비하네요. 2시 쯤 이면 ...[2]', 'date': '2026.03.20 13:24', 'views': '130', 'likes': '6', 'dislikes': '5', 'link': '/item/board_read.naver?code=036930&amp;nid=415488103&amp;page=3', 'body': '', 'score': 310}, {'title': '세력이 핸들링 잘한다고 본다[2]', 'date': '2026.03.20 11:34', 'views': '256', 'likes': '6', 'dislikes': '2', 'link': '/item/board_read.naver?code=036930&amp;nid=415471426&amp;page=5', 'body': '', 'score': 436}, {'title': '물적분할이니 뻘소리만 또 안하면 쭉간다', 'date': '2026.03.20 11:05', 'views': '58', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=036930&amp;nid=415466071&amp;page=5', 'body': '', 'score': 238}, {'title': '세계 최초 주성만이 할 수 있는 기술입니다...[1]', 'date': '2026.03.20 11:03', 'views': '232', 'likes': '6', 'dislikes': '4', 'link': '/item/board_read.naver?code=036930&amp;nid=415465731&amp;page=5', 'body': '', 'score': 412}]</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>036930</t>
         </is>
       </c>
     </row>
@@ -1178,69 +1256,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>티엠씨</t>
+          <t>유니슨</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23600</v>
+        <v>1666</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+20.53%</t>
+          <t>+19.60%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>182</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2.43%</t>
-        </is>
+        <v>0.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>106</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>19580</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.28%</t>
-        </is>
+          <t>4.08%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1427</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>주린인데..투경예고? 아닌가요?[3] / TMC 선박케이블 세계1위, 원전케이블도 장... / 22층에 3개월 물려잇었는데[5] / 22200원 입성</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Positive (54%)</t>
+          <t>답지 준다. 이거만 외워라.[4] / 1차 목표가 만원 2차 목표가 5만원[2] / 지금부터 시작인가요?[3] / 오후에 .. 일단 상[1]</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>오늘, 티엠씨, 어제</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
+          <t>Positive (81%)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>외인, 프로그램, 대량, 매수중, 1차</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>[{'title': '22200원 입성', 'date': '2026.03.20 13:16', 'views': '35', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=217590&amp;nid=415486668&amp;page=5', 'score': 215}, {'title': '24050 추매', 'date': '2026.03.20 17:00', 'views': '21', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415516296&amp;page=3', 'score': 171}, {'title': 'TMC 선박케이블 세계1위, 원전케이블도 장...', 'date': '2026.03.20 12:16', 'views': '250', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415478084&amp;page=6', 'score': 400}, {'title': '25050 전량매도[1]', 'date': '2026.03.20 18:15', 'views': '84', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=217590&amp;nid=415520806&amp;page=2', 'score': 204}, {'title': '22층에 3개월 물려잇었는데[5]', 'date': '2026.03.20 18:02', 'views': '146', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=217590&amp;nid=415520147&amp;page=2', 'score': 266}, {'title': '성호전자 엔비디아 뉴스로 시총 3조 됐다', 'date': '2026.03.20 17:19', 'views': '50', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=217590&amp;nid=415517635&amp;page=3', 'score': 170}, {'title': '주린인데..투경예고? 아닌가요?[3]', 'date': '2026.03.20 16:26', 'views': '697', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=217590&amp;nid=415513982&amp;page=3', 'score': 817}, {'title': '오늘 연기금 81779주 떡 매수로', 'date': '2026.03.20 16:07', 'views': '63', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415512408&amp;page=4', 'score': 183}, {'title': '상이가', 'date': '2026.03.20 16:02', 'views': '36', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415511962&amp;page=4', 'score': 156}, {'title': '신고가에 수급좋고 상 가나요?', 'date': '2026.03.20 15:58', 'views': '33', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=217590&amp;nid=415511584&amp;page=4', 'score': 153}]</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>217590</t>
+          <t>[{'title': '유니슨 오늘 외인 매수  및 프로그램 대량 매수중[1]', 'date': '2026.03.20 11:51', 'views': '164', 'likes': '17', 'dislikes': '0', 'link': '/item/board_read.naver?code=018000&amp;nid=415474322&amp;page=2', 'body': '', 'score': 674}, {'title': '1차 목표가 만원 2차 목표가 5만원[2]', 'date': '2026.03.20 11:35', 'views': '264', 'likes': '17', 'dislikes': '2', 'link': '/item/board_read.naver?code=018000&amp;nid=415471508&amp;page=2', 'body': '', 'score': 774}, {'title': '답지 준다. 이거만 외워라.[4]', 'date': '2026.03.20 10:24', 'views': '621', 'likes': '16', 'dislikes': '4', 'link': '/item/board_read.naver?code=018000&amp;nid=415458177&amp;page=3', 'body': '', 'score': 1101}, {'title': '오후에 .. 일단 상[1]', 'date': '2026.03.20 12:26', 'views': '244', 'likes': '15', 'dislikes': '5', 'link': '/item/board_read.naver?code=018000&amp;nid=415479527&amp;page=2', 'body': '', 'score': 694}, {'title': '지금까지[1]', 'date': '2026.03.20 11:01', 'views': '192', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=018000&amp;nid=415465465&amp;page=3', 'body': '', 'score': 642}, {'title': '26년상반기해풍입찰에서 유니슨이', 'date': '2026.03.20 09:53', 'views': '158', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=018000&amp;nid=415451246&amp;page=4', 'body': '', 'score': 518}, {'title': '정부에서 풍력 연구 개발비 지원해주고[2]', 'date': '2026.03.20 11:40', 'views': '311', 'likes': '11', 'dislikes': '3', 'link': '/item/board_read.naver?code=018000&amp;nid=415472460&amp;page=2', 'body': '', 'score': 641}, {'title': '유니슨 시총1조9782억원 기원 13일차', 'date': '2026.03.20 12:18', 'views': '77', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=018000&amp;nid=415478278&amp;page=2', 'body': '', 'score': 377}, {'title': '지금부터 시작인가요?[3]', 'date': '2026.03.20 09:59', 'views': '414', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=018000&amp;nid=415452671&amp;page=3', 'body': '', 'score': 714}, {'title': '대박~~~ 텐버거 가즈아~~~~~~~~', 'date': '2026.03.20 09:37', 'views': '48', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=018000&amp;nid=415447447&amp;page=4', 'body': '', 'score': 348}]</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>018000</t>
         </is>
       </c>
     </row>
@@ -1252,69 +1338,77 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>SK증권</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>72800</v>
+        <v>2605</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+19.34%</t>
+          <t>+19.50%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>252</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>11.35%</t>
-        </is>
+        <v>1.33</v>
+      </c>
+      <c r="G12" t="n">
+        <v>684</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>61000</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>9.63%</t>
-        </is>
+          <t>6.40%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1880</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>불안하신 분은 필독) / 뉴스 보셨죠? -  삼전의 M&amp;A 가능성 대두....[9] / 월요일도...15~20% 내외 상승 예상[4] / +소부장 Top Pickup 1으로 찜~1년 가...[3]</t>
+          <t>5.07%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Positive (60%)</t>
+          <t>1100원대에 산거[2] / ■ [필독] 'SK이터닉스' 와의 관계[2] / 기관이 매집만 하는 이유가 있을텐데[1] / 이런 사람들은 뭐하는 사람들일까요?[3]</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>오늘, ..., 상한가</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
+          <t>Positive (61%)</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>안가도, 되니께, 기관이, 매집만, 이유가</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>[{'title': '불안하신 분은 필독)', 'date': '2026.03.20 16:17', 'views': '320', 'likes': '13', 'dislikes': '5', 'link': '/item/board_read.naver?code=036930&amp;nid=415513340&amp;page=2', 'score': 710}, {'title': '+소부장 Top Pickup 1으로 찜~1년 가...[3]', 'date': '2026.03.20 16:49', 'views': '183', 'likes': '11', 'dislikes': '4', 'link': '/item/board_read.naver?code=036930&amp;nid=415515572&amp;page=1', 'score': 513}, {'title': '월요일도...15~20% 내외 상승 예상[4]', 'date': '2026.03.20 15:20', 'views': '249', 'likes': '10', 'dislikes': '7', 'link': '/item/board_read.naver?code=036930&amp;nid=415506370&amp;page=3', 'score': 549}, {'title': '외국인 역대급 매수', 'date': '2026.03.20 16:13', 'views': '221', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=036930&amp;nid=415512980&amp;page=2', 'score': 491}, {'title': '한미반도체가 본딩장비로 재평가 받았듯이[2]', 'date': '2026.03.20 14:31', 'views': '205', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=036930&amp;nid=415498603&amp;page=4', 'score': 475}, {'title': '이 정도면 쩜상 가야지[1]', 'date': '2026.03.20 12:09', 'views': '221', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=036930&amp;nid=415477137&amp;page=6', 'score': 491}, {'title': '뉴스 보셨죠? -  삼전의 M&amp;A 가능성 대두....[9]', 'date': '2026.03.20 18:43', 'views': '322', 'likes': '8', 'dislikes': '6', 'link': '/item/board_read.naver?code=036930&amp;nid=415522176&amp;page=1', 'score': 562}, {'title': '고맙다 시외에서 싸게 던져줘서[1]', 'date': '2026.03.20 18:07', 'views': '93', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=036930&amp;nid=415520385&amp;page=1', 'score': 303}, {'title': '공매도는 숏커버 안할까?[2]', 'date': '2026.03.20 16:04', 'views': '193', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=036930&amp;nid=415512174&amp;page=2', 'score': 403}, {'title': '본드로 시가 총액 30조---- 신노광장비...', 'date': '2026.03.20 10:21', 'views': '143', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=036930&amp;nid=415457543&amp;page=8', 'score': 353}]</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>[{'title': '상 안가도 되니께', 'date': '2026.03.20 14:07', 'views': '68', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=001510&amp;nid=415494827&amp;page=6', 'body': '', 'score': 338}, {'title': '상 안가도 되니께', 'date': '2026.03.20 14:07', 'views': '68', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=001510&amp;nid=415494827&amp;page=7', 'body': '', 'score': 338}, {'title': '기관이 매집만 하는 이유가 있을텐데[1]', 'date': '2026.03.20 14:54', 'views': '189', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=001510&amp;nid=415502197&amp;page=2', 'body': '', 'score': 429}, {'title': '1100원대에 산거[2]', 'date': '2026.03.20 12:17', 'views': '288', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=001510&amp;nid=415478132&amp;page=19', 'body': '', 'score': 528}, {'title': "■ [필독] 'SK이터닉스' 와의 관계[2]", 'date': '2026.03.20 08:16', 'views': '277', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=001510&amp;nid=415431951&amp;page=35', 'body': '', 'score': 517}, {'title': '프매 뮈췬런', 'date': '2026.03.20 15:12', 'views': '41', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=001510&amp;nid=415505028&amp;page=1', 'body': '', 'score': 251}, {'title': '2치파동 시작인듯 한데[1]', 'date': '2026.03.20 13:32', 'views': '111', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=001510&amp;nid=415489484&amp;page=10', 'body': '', 'score': 321}, {'title': 'SK증권 어떻게 할지 고민중이시라면…??...', 'date': '2026.03.20 11:46', 'views': '67', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=001510&amp;nid=415473420&amp;page=23', 'body': '', 'score': 277}, {'title': '이런 사람들은 뭐하는 사람들일까요?[3]', 'date': '2026.03.20 09:14', 'views': '151', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=001510&amp;nid=415441137&amp;page=33', 'body': '', 'score': 361}, {'title': '프로그램', 'date': '2026.03.20 15:12', 'views': '35', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=001510&amp;nid=415505038&amp;page=1', 'body': '', 'score': 215}]</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>001510</t>
         </is>
       </c>
     </row>
@@ -1326,69 +1420,77 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>우진</t>
+          <t>티엠씨</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>31200</v>
+        <v>23300</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+19.31%</t>
+          <t>+19.00%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>123</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>11.47%</t>
-        </is>
+        <v>0.41</v>
+      </c>
+      <c r="G13" t="n">
+        <v>116</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>2.28%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>26150</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>9.43%</t>
-        </is>
+      <c r="J13" t="n">
+        <v>19060</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>원전해체1위[1] / [AI 요약] 우진의 단일판매ㆍ공급계약 ...[1] / 시간외 5시 30분후에 만주 몰빵[1] / ■우리기술 &gt; 우진으로 순환매 첫 도입이네요!...</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Positive (87%)</t>
+          <t>TMC 선박케이블 세계1위, 원전케이블도 장... / 와우[2] / 오늘끝[2] / 22000원 깨지면 들어갈게요</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>오늘, 우진, 이상</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
+          <t>Positive (70%)</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>22000원, 깨지면, TMC, 선박케이블, 세계1위</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>[{'title': '원전해체1위[1]', 'date': '2026.03.20 10:17', 'views': '330', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415456769&amp;page=6', 'score': 660}, {'title': '■우리기술 &gt; 우진으로 순환매 첫 도입이네요!...', 'date': '2026.03.20 15:33', 'views': '64', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415508292&amp;page=2', 'score': 334}, {'title': '님들 시총 2조 가능하다고 보심????', 'date': '2026.03.20 15:23', 'views': '46', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=105840&amp;nid=415506832&amp;page=2', 'score': 226}, {'title': '종가 풀매수[1]', 'date': '2026.03.20 15:55', 'views': '104', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=105840&amp;nid=415511288&amp;page=1', 'score': 254}, {'title': '어디가 찐일까?', 'date': '2026.03.20 15:15', 'views': '48', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415505510&amp;page=2', 'score': 198}, {'title': '상가자[1]', 'date': '2026.03.20 14:37', 'views': '89', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415499569&amp;page=3', 'score': 239}, {'title': '[AI 요약] 우진의 단일판매ㆍ공급계약 ...[1]', 'date': '2026.03.20 13:55', 'views': '244', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=105840&amp;nid=415492926&amp;page=4', 'score': 394}, {'title': '시간외 5시 30분후에 만주 몰빵[1]', 'date': '2026.03.20 15:44', 'views': '215', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=105840&amp;nid=415509911&amp;page=1', 'score': 335}, {'title': '물린 주주들도 없고[1]', 'date': '2026.03.20 15:42', 'views': '109', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=105840&amp;nid=415509703&amp;page=1', 'score': 229}, {'title': '개미 50만주 매도 외인기관50만주 매수[1]', 'date': '2026.03.20 15:39', 'views': '93', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=105840&amp;nid=415509272&amp;page=1', 'score': 213}]</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>105840</t>
+          <t>[{'title': '22000원 깨지면 들어갈게요', 'date': '2026.03.20 13:16', 'views': '28', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=217590&amp;nid=415486668&amp;page=2', 'body': '', 'score': 208}, {'title': 'TMC 선박케이블 세계1위, 원전케이블도 장...', 'date': '2026.03.20 12:16', 'views': '226', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415478084&amp;page=2', 'body': '', 'score': 376}, {'title': '와우[2]', 'date': '2026.03.20 14:14', 'views': '165', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=217590&amp;nid=415495975&amp;page=1', 'body': '', 'score': 285}, {'title': '월봉', 'date': '2026.03.20 13:14', 'views': '48', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415486479&amp;page=2', 'body': '', 'score': 168}, {'title': '오늘끝[2]', 'date': '2026.03.20 12:45', 'views': '96', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=217590&amp;nid=415482197&amp;page=2', 'body': '', 'score': 216}, {'title': '넥스트에서 상한가 한번가주라', 'date': '2026.03.20 15:23', 'views': '13', 'likes': '3', 'dislikes': '1', 'link': '/item/board_read.naver?code=217590&amp;nid=415506736&amp;page=1', 'body': '', 'score': 103}, {'title': '신고가 가겠네', 'date': '2026.03.20 14:34', 'views': '34', 'likes': '3', 'dislikes': '2', 'link': '/item/board_read.naver?code=217590&amp;nid=415499047&amp;page=1', 'body': '', 'score': 124}, {'title': '오전에 대광 넘어간 사람 없지?', 'date': '2026.03.20 14:28', 'views': '31', 'likes': '3', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415498176&amp;page=1', 'body': '', 'score': 121}, {'title': '오늘[1]', 'date': '2026.03.20 13:12', 'views': '33', 'likes': '3', 'dislikes': '3', 'link': '/item/board_read.naver?code=217590&amp;nid=415486169&amp;page=2', 'body': '', 'score': 123}, {'title': '4개월물린거', 'date': '2026.03.20 10:33', 'views': '96', 'likes': '3', 'dislikes': '0', 'link': '/item/board_read.naver?code=217590&amp;nid=415459970&amp;page=3', 'body': '', 'score': 186}]</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>217590</t>
         </is>
       </c>
     </row>
@@ -1400,69 +1502,77 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2585</v>
+        <v>19080</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>+18.58%</t>
+          <t>+18.00%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>756</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>7.03%</t>
-        </is>
+        <v>-0.67</v>
+      </c>
+      <c r="G14" t="n">
+        <v>800</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>11.28%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>2180</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>6.40%</t>
-        </is>
+      <c r="J14" t="n">
+        <v>14870</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>봐라 또 개미들만 팔았제 ?[2] / ㅎ ㅎ ㅎ / 오늘의 시황//그리고 액면병합 모멘텀은 계속 유...[1] / 개인만 열라게[2]</t>
+          <t>11.95%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Positive (62%)</t>
+          <t>금일 상한가 21,000원[1] / 평단 8400ㅋㅋㅋㅋ[2] / 프로그램  매도매수  반복중...[1] / 난 안팔았어~~[2]</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>오늘, 프로그램, 상한가</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>[{'title': '개인만 열라게[2]', 'date': '2026.03.20 15:42', 'views': '216', 'likes': '16', 'dislikes': '2', 'link': '/item/board_read.naver?code=001510&amp;nid=415509682&amp;page=4', 'score': 696}, {'title': '봐라 또 개미들만 팔았제 ?[2]', 'date': '2026.03.20 15:36', 'views': '491', 'likes': '16', 'dislikes': '1', 'link': '/item/board_read.naver?code=001510&amp;nid=415508782&amp;page=4', 'score': 971}, {'title': '오늘의 시황//그리고 액면병합 모멘텀은 계속 유...[1]', 'date': '2026.03.20 18:59', 'views': '352', 'likes': '14', 'dislikes': '3', 'link': '/item/board_read.naver?code=001510&amp;nid=415522976&amp;page=1', 'score': 772}, {'title': '솔직히 형들', 'date': '2026.03.20 17:50', 'views': '293', 'likes': '13', 'dislikes': '4', 'link': '/item/board_read.naver?code=001510&amp;nid=415519424&amp;page=2', 'score': 683}, {'title': '증권주 비교하면 적정가 5~6천이상은 가야...[2]', 'date': '2026.03.20 15:59', 'views': '290', 'likes': '13', 'dislikes': '2', 'link': '/item/board_read.naver?code=001510&amp;nid=415511679&amp;page=4', 'score': 680}, {'title': 'ㅎ ㅎ ㅎ', 'date': '2026.03.20 18:09', 'views': '541', 'likes': '12', 'dislikes': '3', 'link': '/item/board_read.naver?code=001510&amp;nid=415520530&amp;page=1', 'score': 901}, {'title': '아직 저평가 야', 'date': '2026.03.20 18:41', 'views': '166', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=001510&amp;nid=415522092&amp;page=1', 'score': 496}, {'title': '개미 짜였네 짜였어ㅋㅋㅋ[1]', 'date': '2026.03.20 15:38', 'views': '200', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=001510&amp;nid=415509133&amp;page=4', 'score': 530}, {'title': '또 개미만 털림', 'date': '2026.03.20 15:36', 'views': '274', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=001510&amp;nid=415508740&amp;page=4', 'score': 604}, {'title': '길게 보세요 거래량은 못 속입니다 1차 300...', 'date': '2026.03.20 15:32', 'views': '238', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=001510&amp;nid=415508198&amp;page=5', 'score': 568}]</t>
-        </is>
+          <t>Positive (57%)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>금일, 000원, 프로그램, 매도매수, 반복중</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>001510</t>
+          <t>[{'title': '금일 상한가 21,000원[1]', 'date': '2026.03.20 11:13', 'views': '144', 'likes': '33', 'dislikes': '5', 'link': '/item/board_read.naver?code=047040&amp;nid=415467547&amp;page=26', 'body': '', 'score': 1134}, {'title': '프로그램  매도매수  반복중...[1]', 'date': '2026.03.20 10:26', 'views': '250', 'likes': '17', 'dislikes': '1', 'link': '/item/board_read.naver?code=047040&amp;nid=415458667&amp;page=30', 'body': '', 'score': 760}, {'title': '오늘', 'date': '2026.03.20 14:17', 'views': '45', 'likes': '16', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415496414&amp;page=8', 'body': '', 'score': 525}, {'title': '평단 8400ㅋㅋㅋㅋ[2]', 'date': '2026.03.20 14:15', 'views': '313', 'likes': '16', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415496107&amp;page=8', 'body': '', 'score': 793}, {'title': '털린사람', 'date': '2026.03.20 14:46', 'views': '48', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=047040&amp;nid=415500894&amp;page=5', 'body': '', 'score': 498}, {'title': '난 안팔았어~~[2]', 'date': '2026.03.20 14:20', 'views': '242', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=047040&amp;nid=415496929&amp;page=7', 'body': '', 'score': 692}, {'title': '추매 완료', 'date': '2026.03.20 10:31', 'views': '56', 'likes': '15', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415459527&amp;page=30', 'body': '', 'score': 506}, {'title': '믿음.', 'date': '2026.03.20 14:17', 'views': '46', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415496462&amp;page=8', 'body': '', 'score': 436}, {'title': '드뎌 18층[1]', 'date': '2026.03.20 09:19', 'views': '171', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415442520&amp;page=40', 'body': '', 'score': 561}, {'title': '무빙 미첫다', 'date': '2026.03.20 14:17', 'views': '76', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415496520&amp;page=7', 'body': '', 'score': 406}]</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1474,69 +1584,77 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>하림지주</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>19110</v>
+        <v>17740</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+18.18%</t>
+          <t>+17.48%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>800</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>11.54%</t>
-        </is>
+        <v>-0.03</v>
+      </c>
+      <c r="G15" t="n">
+        <v>192</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>16170</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>11.28%</t>
-        </is>
+          <t>7.67%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>15760</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>시간외  단가~~~~[4] / 투자 경보는 시총 100위내에는 해당안됨 '중복...[1] / 월요일엄청쏠듯[2] / 상한가  한방없이 여지껏  이리 말아올린  주...[2]</t>
+          <t>7.70%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Positive (61%)</t>
+          <t>매집중[3] / 팩트 공유~ 3/17일 2시 양재동 부지 건...[1] / [하림지주 공유][3] / 양재동 상법</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>오늘, 대우건설, 이거</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
+          <t>Positive (58%)</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>양재동, 공유, 상법, 매집중, 팩트</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>[{'title': '시간외  단가~~~~[4]', 'date': '2026.03.20 18:01', 'views': '991', 'likes': '39', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415520059&amp;page=1', 'score': 2161}, {'title': "투자 경보는 시총 100위내에는 해당안됨 '중복...[1]", 'date': '2026.03.20 18:31', 'views': '614', 'likes': '38', 'dislikes': '1', 'link': '/item/board_read.naver?code=047040&amp;nid=415521635&amp;page=1', 'score': 1754}, {'title': '대우야 니가 삼전 하닉 현기차보다 효자다......', 'date': '2026.03.20 15:55', 'views': '194', 'likes': '35', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415511194&amp;page=4', 'score': 1244}, {'title': '월요일엄청쏠듯[2]', 'date': '2026.03.20 17:15', 'views': '601', 'likes': '33', 'dislikes': '3', 'link': '/item/board_read.naver?code=047040&amp;nid=415517331&amp;page=2', 'score': 1591}, {'title': '금일 상한가 21,000원[1]', 'date': '2026.03.20 11:13', 'views': '146', 'likes': '33', 'dislikes': '5', 'link': '/item/board_read.naver?code=047040&amp;nid=415467547&amp;page=30', 'score': 1136}, {'title': '상한가  한방없이 여지껏  이리 말아올린  주...[2]', 'date': '2026.03.20 15:51', 'views': '468', 'likes': '32', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415510710&amp;page=4', 'score': 1428}, {'title': '2만원 가면 호가 50원씩~~', 'date': '2026.03.20 15:52', 'views': '185', 'likes': '27', 'dislikes': '1', 'link': '/item/board_read.naver?code=047040&amp;nid=415510815&amp;page=4', 'score': 995}, {'title': '5년 기다린 보람있네요.[3]', 'date': '2026.03.20 16:04', 'views': '547', 'likes': '26', 'dislikes': '0', 'link': '/item/board_read.naver?code=047040&amp;nid=415512192&amp;page=4', 'score': 1327}, {'title': '월요일에 갭 뜰 것 같은데', 'date': '2026.03.20 17:53', 'views': '110', 'likes': '23', 'dislikes': '1', 'link': '/item/board_read.naver?code=047040&amp;nid=415519631&amp;page=1', 'score': 800}, {'title': '10만원  직행......[1]', 'date': '2026.03.20 16:24', 'views': '287', 'likes': '23', 'dislikes': '2', 'link': '/item/board_read.naver?code=047040&amp;nid=415513878&amp;page=3', 'score': 977}]</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>[{'title': '양재동 상법', 'date': '2026.03.20 14:59', 'views': '160', 'likes': '19', 'dislikes': '2', 'link': '/item/board_read.naver?code=003380&amp;nid=415502969&amp;page=1', 'body': '', 'score': 730}, {'title': '매집중[3]', 'date': '2026.03.20 11:18', 'views': '343', 'likes': '19', 'dislikes': '3', 'link': '/item/board_read.naver?code=003380&amp;nid=415468347&amp;page=5', 'body': '', 'score': 913}, {'title': '[하림지주 공유][3]', 'date': '2026.03.20 10:37', 'views': '218', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=003380&amp;nid=415460583&amp;page=7', 'body': '', 'score': 758}, {'title': '팩트 공유~ 3/17일 2시 양재동 부지 건...[1]', 'date': '2026.03.20 12:08', 'views': '356', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=003380&amp;nid=415476901&amp;page=5', 'body': '', 'score': 806}, {'title': '갈 수 밖에 없는 이유', 'date': '2026.03.20 14:41', 'views': '113', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=003380&amp;nid=415500156&amp;page=1', 'body': '', 'score': 503}, {'title': '19000원대면 공매도 반대매매 나오는 단가...', 'date': '2026.03.20 14:32', 'views': '112', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=003380&amp;nid=415498781&amp;page=2', 'body': '', 'score': 502}, {'title': '월요일 20000원 찍고 화요일 발표하자[1]', 'date': '2026.03.20 13:41', 'views': '185', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=003380&amp;nid=415490894&amp;page=3', 'body': '', 'score': 575}, {'title': '오늘은 지주사들 날이구만', 'date': '2026.03.20 11:35', 'views': '106', 'likes': '13', 'dislikes': '2', 'link': '/item/board_read.naver?code=003380&amp;nid=415471552&amp;page=5', 'body': '', 'score': 496}, {'title': '자사주[3]', 'date': '2026.03.20 11:12', 'views': '237', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=003380&amp;nid=415467206&amp;page=5', 'body': '', 'score': 627}, {'title': '어차피 올라갑니다,,,,[1]', 'date': '2026.03.20 08:41', 'views': '150', 'likes': '13', 'dislikes': '4', 'link': '/item/board_read.naver?code=003380&amp;nid=415435176&amp;page=10', 'body': '', 'score': 540}]</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>003380</t>
         </is>
       </c>
     </row>
@@ -1548,69 +1666,77 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>하림지주</t>
+          <t>에이프로젠</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17700</v>
+        <v>347</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+17.22%</t>
+          <t>+15.67%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>212</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>8.95%</t>
-        </is>
+        <v>-0.11</v>
+      </c>
+      <c r="G16" t="n">
+        <v>104</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>15100</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>7.67%</t>
-        </is>
+          <t>7.76%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>306</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>묻어 두면  몇배 ![1] / 매집중[3] / 차트충은 아니지만...[4] / 안녕하세요 차티스트입니다.</t>
+          <t>7.87%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Positive (64%)</t>
+          <t>이회사는 진짜[1] / 20연상 가야지[1] / 느낌에...[1] / 감사보고서 장종료 하고 나올거임.담주450원 넘으...[1]</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>형이, 오늘, 양재동</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
+          <t>Positive (69%)</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>이회사는, 20연상, 가야지, 오늘360원, 안착</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>[{'title': '양재동 상법', 'date': '2026.03.20 14:59', 'views': '244', 'likes': '21', 'dislikes': '2', 'link': '/item/board_read.naver?code=003380&amp;nid=415502969&amp;page=2', 'score': 874}, {'title': '매집중[3]', 'date': '2026.03.20 11:18', 'views': '385', 'likes': '21', 'dislikes': '4', 'link': '/item/board_read.naver?code=003380&amp;nid=415468347&amp;page=6', 'score': 1015}, {'title': '[하림지주 공유][3]', 'date': '2026.03.20 10:37', 'views': '227', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=003380&amp;nid=415460583&amp;page=8', 'score': 767}, {'title': '안녕하세요 차티스트입니다.', 'date': '2026.03.20 16:20', 'views': '394', 'likes': '17', 'dislikes': '3', 'link': '/item/board_read.naver?code=003380&amp;nid=415513578&amp;page=1', 'score': 904}, {'title': '묻어 두면  몇배 ![1]', 'date': '2026.03.20 15:44', 'views': '549', 'likes': '16', 'dislikes': '2', 'link': '/item/board_read.naver?code=003380&amp;nid=415509939&amp;page=2', 'score': 1029}, {'title': '차트충은 아니지만...[4]', 'date': '2026.03.20 15:32', 'views': '461', 'likes': '16', 'dislikes': '0', 'link': '/item/board_read.naver?code=003380&amp;nid=415508104&amp;page=2', 'score': 941}, {'title': '갈 수 밖에 없는 이유', 'date': '2026.03.20 14:41', 'views': '167', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=003380&amp;nid=415500156&amp;page=3', 'score': 617}, {'title': '월요일 20000원 찍고 화요일 발표하자[1]', 'date': '2026.03.20 13:41', 'views': '201', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=003380&amp;nid=415490894&amp;page=4', 'score': 651}, {'title': '팩트 공유~ 3/17일 2시 양재동 부지 건...[1]', 'date': '2026.03.20 12:08', 'views': '362', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=003380&amp;nid=415476901&amp;page=6', 'score': 812}, {'title': '오늘은 지주사들 날이구만', 'date': '2026.03.20 11:35', 'views': '110', 'likes': '13', 'dislikes': '2', 'link': '/item/board_read.naver?code=003380&amp;nid=415471552&amp;page=6', 'score': 500}]</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>003380</t>
+          <t>[{'title': '이회사는 진짜[1]', 'date': '2026.03.20 10:56', 'views': '65', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=007460&amp;nid=415464456&amp;page=3', 'body': '', 'score': 275}, {'title': '20연상 가야지[1]', 'date': '2026.03.20 09:30', 'views': '75', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=007460&amp;nid=415445608&amp;page=4', 'body': '', 'score': 255}, {'title': '오늘360원 안착', 'date': '2026.03.20 14:58', 'views': '17', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=007460&amp;nid=415502818&amp;page=1', 'body': '', 'score': 167}, {'title': '또 이러네... 재섭고 정줄논 넘드라[1]', 'date': '2026.03.20 11:45', 'views': '43', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415473398&amp;page=2', 'body': '', 'score': 193}, {'title': '감사보고서 장종료 하고 나올거임.담주450원 넘으...[1]', 'date': '2026.03.20 14:42', 'views': '102', 'likes': '4', 'dislikes': '7', 'link': '/item/board_read.naver?code=007460&amp;nid=415500219&amp;page=1', 'body': '', 'score': 222}, {'title': '느낌에...[1]', 'date': '2026.03.20 13:26', 'views': '133', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415488389&amp;page=1', 'body': '', 'score': 253}, {'title': '원전주', 'date': '2026.03.20 11:44', 'views': '68', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=007460&amp;nid=415473151&amp;page=3', 'body': '', 'score': 188}, {'title': '380원에 2만주 털고 간다,,ㅎㅎ[2]', 'date': '2026.03.20 09:54', 'views': '95', 'likes': '4', 'dislikes': '3', 'link': '/item/board_read.naver?code=007460&amp;nid=415451527&amp;page=4', 'body': '', 'score': 215}, {'title': '1000원 까지...', 'date': '2026.03.20 09:44', 'views': '60', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=007460&amp;nid=415449091&amp;page=4', 'body': '', 'score': 180}, {'title': '이것도 주식. 왜 상폐 안시킬까..[1]', 'date': '2026.03.20 13:31', 'views': '76', 'likes': '3', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415489273&amp;page=1', 'body': '', 'score': 166}]</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>007460</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1748,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1639,50 +1765,58 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>116</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>8.40%</t>
-        </is>
+        <v>-0.29</v>
+      </c>
+      <c r="G17" t="n">
+        <v>101</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>4.86%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>11710</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>4.86%</t>
-        </is>
+      <c r="J17" t="n">
+        <v>11720</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>오랜만에 글써봅니다.[3] / 3년의 저항 뚫음 / 신고가 영역이라 / ▣ 1.4만 터치하는 순간...</t>
+          <t>5.15%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Positive (57%)</t>
+          <t>오랜만에 글써봅니다.[3] / 신고가 영역이라 / ▣ 1.4만 터치하는 순간... / &lt;진짜 한결같다 너도.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>윗꼬리, 내가, 이상</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
+          <t>Positive (53%)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>윗꼬리, 오랜만에, 신고가, 영역이라, 너도</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
         <v>1</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>[{'title': '오랜만에 글써봅니다.[3]', 'date': '2026.03.20 13:40', 'views': '291', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=388050&amp;nid=415490676&amp;page=3', 'score': 471}, {'title': '3년의 저항 뚫음', 'date': '2026.03.20 16:28', 'views': '90', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=388050&amp;nid=415514142&amp;page=1', 'score': 210}, {'title': '다음주 대장 이겠네', 'date': '2026.03.20 15:21', 'views': '43', 'likes': '3', 'dislikes': '1', 'link': '/item/board_read.naver?code=388050&amp;nid=415506512&amp;page=1', 'score': 133}, {'title': '신고가 영역이라', 'date': '2026.03.20 13:36', 'views': '72', 'likes': '3', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415490070&amp;page=3', 'score': 162}, {'title': '&lt;진짜 한결같다 너도.', 'date': '2026.03.20 11:01', 'views': '36', 'likes': '3', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415465467&amp;page=4', 'score': 126}, {'title': '여기 주포 개양이라 윗꼬리 조심하소', 'date': '2026.03.20 11:01', 'views': '26', 'likes': '3', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415465361&amp;page=4', 'score': 116}, {'title': '4만 이상은 가이지♡', 'date': '2026.03.20 19:03', 'views': '16', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415523174&amp;page=1', 'score': 76}, {'title': '▣ 1.4만 터치하는 순간...', 'date': '2026.03.20 11:32', 'views': '74', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415471054&amp;page=3', 'score': 134}, {'title': '윗꼬리 전문 상한가 없는 종목임[1]', 'date': '2026.03.20 10:49', 'views': '31', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415462920&amp;page=4', 'score': 91}, {'title': '이게', 'date': '2026.03.20 10:35', 'views': '22', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415460191&amp;page=4', 'score': 82}]</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
+        <is>
+          <t>[{'title': '오랜만에 글써봅니다.[3]', 'date': '2026.03.20 13:40', 'views': '165', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=388050&amp;nid=415490676&amp;page=2', 'body': '', 'score': 315}, {'title': '신고가 영역이라', 'date': '2026.03.20 13:36', 'views': '66', 'likes': '3', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415490070&amp;page=2', 'body': '', 'score': 156}, {'title': '&lt;진짜 한결같다 너도.', 'date': '2026.03.20 11:01', 'views': '33', 'likes': '3', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415465467&amp;page=3', 'body': '', 'score': 123}, {'title': '여기 주포 개양이라 윗꼬리 조심하소', 'date': '2026.03.20 11:01', 'views': '24', 'likes': '3', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415465361&amp;page=3', 'body': '', 'score': 114}, {'title': '▣ 1.4만 터치하는 순간...', 'date': '2026.03.20 11:32', 'views': '71', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415471054&amp;page=3', 'body': '', 'score': 131}, {'title': '윗꼬리 전문 상한가 없는 종목임[1]', 'date': '2026.03.20 10:49', 'views': '29', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415462920&amp;page=3', 'body': '', 'score': 89}, {'title': '이게', 'date': '2026.03.20 10:35', 'views': '20', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415460191&amp;page=4', 'body': '', 'score': 80}, {'title': '장중조정시 쓸어 담으시길~~~~[2]', 'date': '2026.03.20 09:46', 'views': '59', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415449742&amp;page=4', 'body': '', 'score': 119}, {'title': '거래량을 봐라~~전이 들어오고 있다', 'date': '2026.03.20 09:29', 'views': '28', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415445162&amp;page=5', 'body': '', 'score': 88}, {'title': '태양광 관련주 올 폭등중..', 'date': '2026.03.20 08:36', 'views': '32', 'likes': '2', 'dislikes': '0', 'link': '/item/board_read.naver?code=388050&amp;nid=415434539&amp;page=6', 'body': '', 'score': 92}]</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>388050</t>
         </is>
@@ -1696,69 +1830,77 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>카나프테라퓨틱스</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>52200</v>
+        <v>911000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>+14.98%</t>
+          <t>+14.59%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>297</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1.47%</t>
-        </is>
+        <v>-0.03</v>
+      </c>
+      <c r="G18" t="n">
+        <v>555</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>5.89%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>45400</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0.51%</t>
-        </is>
+      <c r="J18" t="n">
+        <v>784000</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>목표가 10만원 갑시다.[2] / 시외상이가?[2] / 참 이상해.. 3분기 기준 아이엠바이오로직스 ... / 단일가로 상승할 확률이 높아보이네요[1]</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Positive (58%)</t>
+          <t>[[[삼천당꿈(시즌2)]]] - 삼천당의 자신...[18] / [[[삼천당꿈(시즌2)]]]  -경구인슐린 10...[24] / 제 자신을 반성합니다.[7] / ▒▒  삼천당제약 기업설명회 개최 의미[3]</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>오늘은, 오늘, 아이엠</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
+          <t>Positive (59%)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>시즌2, 자신, 경구인슐린, 공매야, 이제</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>[{'title': '목표가 10만원 갑시다.[2]', 'date': '2026.03.20 15:55', 'views': '249', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415511206&amp;page=3', 'score': 549}, {'title': '시외상이가?[2]', 'date': '2026.03.20 15:46', 'views': '134', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415510141&amp;page=3', 'score': 374}, {'title': '면역항암제[1]', 'date': '2026.03.20 14:48', 'views': '55', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415501211&amp;page=7', 'score': 265}, {'title': '참 이상해.. 3분기 기준 아이엠바이오로직스 ...', 'date': '2026.03.20 09:16', 'views': '116', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415441602&amp;page=14', 'score': 326}, {'title': '매동! 외인/기관 양끌이 매수~[1]', 'date': '2026.03.20 15:36', 'views': '80', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415508796&amp;page=3', 'score': 260}, {'title': '또 속았수다', 'date': '2026.03.20 12:36', 'views': '25', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415480879&amp;page=9', 'score': 205}, {'title': '단일가로 상승할 확률이 높아보이네요[1]', 'date': '2026.03.20 15:42', 'views': '168', 'likes': '5', 'dislikes': '3', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415509687&amp;page=3', 'score': 318}, {'title': '어짜피[1]', 'date': '2026.03.20 14:09', 'views': '51', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415495129&amp;page=8', 'score': 201}, {'title': '재미없네', 'date': '2026.03.20 12:57', 'views': '16', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415483933&amp;page=9', 'score': 166}, {'title': '어제 기도가 통했네[2]', 'date': '2026.03.20 11:58', 'views': '39', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=0082N0&amp;nid=415475444&amp;page=10', 'score': 189}]</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0082N0</t>
+          <t>[{'title': '[[[삼천당꿈(시즌2)]]] - 삼천당의 자신...[18]', 'date': '2026.03.20 09:05', 'views': '1144', 'likes': '131', 'dislikes': '1', 'link': '/item/board_read.naver?code=000250&amp;nid=415438916&amp;page=28', 'body': '', 'score': 5074}, {'title': '[[[삼천당꿈(시즌2)]]]  -경구인슐린 10...[24]', 'date': '2026.03.20 12:05', 'views': '534', 'likes': '129', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415476519&amp;page=11', 'body': '', 'score': 4404}, {'title': '공매야! 이제 슬슬 반격한다.[2]', 'date': '2026.03.20 13:06', 'views': '293', 'likes': '58', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415485204&amp;page=7', 'body': '', 'score': 2033}, {'title': '제 자신을 반성합니다.[7]', 'date': '2026.03.20 10:49', 'views': '439', 'likes': '58', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415462962&amp;page=21', 'body': '', 'score': 2179}, {'title': '미국 세마 15조 계약도 임박 ^^', 'date': '2026.03.20 12:32', 'views': '247', 'likes': '56', 'dislikes': '1', 'link': '/item/board_read.naver?code=000250&amp;nid=415480305&amp;page=9', 'body': '', 'score': 1927}, {'title': '▒▒  삼천당제약 기업설명회 개최 의미[3]', 'date': '2026.03.20 09:41', 'views': '470', 'likes': '56', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415448353&amp;page=26', 'body': '', 'score': 2150}, {'title': '아일리아BS 8월 미국판매, 인슐린 공시', 'date': '2026.03.20 08:47', 'views': '237', 'likes': '54', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415435832&amp;page=28', 'body': '', 'score': 1857}, {'title': '키트루다 글로벌 매출  약40조[1]', 'date': '2026.03.20 13:12', 'views': '357', 'likes': '51', 'dislikes': '1', 'link': '/item/board_read.naver?code=000250&amp;nid=415486130&amp;page=7', 'body': '', 'score': 1887}, {'title': '경구용 키트루다?[1]', 'date': '2026.03.20 10:17', 'views': '288', 'likes': '49', 'dislikes': '2', 'link': '/item/board_read.naver?code=000250&amp;nid=415456711&amp;page=23', 'body': '', 'score': 1758}, {'title': '줍줍! 홀딩![2]', 'date': '2026.03.20 12:30', 'views': '278', 'likes': '48', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415480017&amp;page=9', 'body': '', 'score': 1718}]</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1770,69 +1912,77 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>에이프로젠</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>343</v>
+        <v>60000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>+14.33%</t>
+          <t>+11.73%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>116</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>6.75%</t>
-        </is>
+        <v>-0.37</v>
+      </c>
+      <c r="G19" t="n">
+        <v>800</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>300</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>7.76%</t>
-        </is>
+      <c r="J19" t="n">
+        <v>42600</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>감사보고서 장종료 하고 나올거임.담주450원 넘으...[2] / 이회사는 진짜[1] / 느낌에...[1] / 20연상 가야지[1]</t>
+          <t>3.37%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Positive (69%)</t>
+          <t>다음주엔 앞자리7?[1] / [매동] 실시간 매매추이 5차 / 66500에 풀신용 지른 1인입니다[3] / 오전에 심약개미들 다 털렸겠네 ㅋ[2]</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-오빠들, 이상, 상승했어요</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
+          <t>Negative (61%)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>다음주엔, 앞자리7, 매동, 매매추이, 5차</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
         <v>1</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>[{'title': '이회사는 진짜[1]', 'date': '2026.03.20 10:56', 'views': '72', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415464456&amp;page=3', 'score': 282}, {'title': '20연상 가야지[1]', 'date': '2026.03.20 09:30', 'views': '80', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=007460&amp;nid=415445608&amp;page=5', 'score': 260}, {'title': '기술적 반등일 뿐,,,ㅎㅎ[2]', 'date': '2026.03.20 16:55', 'views': '76', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415515936&amp;page=1', 'score': 226}, {'title': '오늘360원 안착[1]', 'date': '2026.03.20 14:58', 'views': '90', 'likes': '5', 'dislikes': '3', 'link': '/item/board_read.naver?code=007460&amp;nid=415502818&amp;page=1', 'score': 240}, {'title': '장 끝나고', 'date': '2026.03.20 14:57', 'views': '52', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415502648&amp;page=1', 'score': 202}, {'title': '감사보고서 장종료 하고 나올거임.담주450원 넘으...[2]', 'date': '2026.03.20 14:42', 'views': '243', 'likes': '5', 'dislikes': '10', 'link': '/item/board_read.naver?code=007460&amp;nid=415500219&amp;page=1', 'score': 393}, {'title': '또 이러네... 재섭고 정줄논 넘드라[1]', 'date': '2026.03.20 11:45', 'views': '48', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415473398&amp;page=3', 'score': 198}, {'title': '불쌍한 개미들....[1]', 'date': '2026.03.20 16:04', 'views': '130', 'likes': '4', 'dislikes': '4', 'link': '/item/board_read.naver?code=007460&amp;nid=415512154&amp;page=1', 'score': 250}, {'title': '느낌에...[1]', 'date': '2026.03.20 13:26', 'views': '160', 'likes': '4', 'dislikes': '2', 'link': '/item/board_read.naver?code=007460&amp;nid=415488389&amp;page=2', 'score': 280}, {'title': '원전주', 'date': '2026.03.20 11:44', 'views': '74', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=007460&amp;nid=415473151&amp;page=3', 'score': 194}]</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>007460</t>
+          <t>[{'title': '다음주엔 앞자리7?[1]', 'date': '2026.03.20 14:30', 'views': '320', 'likes': '15', 'dislikes': '4', 'link': '/item/board_read.naver?code=475150&amp;nid=415498430&amp;page=5', 'body': '', 'score': 770}, {'title': '[매동] 실시간 매매추이 5차', 'date': '2026.03.20 14:25', 'views': '218', 'likes': '14', 'dislikes': '3', 'link': '/item/board_read.naver?code=475150&amp;nid=415497771&amp;page=5', 'body': '', 'score': 638}, {'title': '66500에 풀신용 지른 1인입니다[3]', 'date': '2026.03.20 15:01', 'views': '202', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=475150&amp;nid=415503210&amp;page=3', 'body': '', 'score': 562}, {'title': '오전에 심약개미들 다 털렸겠네 ㅋ[2]', 'date': '2026.03.20 12:31', 'views': '87', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=475150&amp;nid=415480115&amp;page=15', 'body': '', 'score': 417}, {'title': '이왕 이렇게 된거 쭉빼고', 'date': '2026.03.20 14:36', 'views': '55', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=475150&amp;nid=415499429&amp;page=5', 'body': '', 'score': 355}, {'title': '담주 내내 SK주식만 오릅니다', 'date': '2026.03.20 13:26', 'views': '87', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=475150&amp;nid=415488465&amp;page=9', 'body': '', 'score': 357}, {'title': '떨어져도 편안~허다^^', 'date': '2026.03.20 10:23', 'views': '52', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=475150&amp;nid=415458055&amp;page=39', 'body': '', 'score': 322}, {'title': '나도 좀 사자~ 6만이라니~~[1]', 'date': '2026.03.20 15:21', 'views': '93', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=475150&amp;nid=415506534&amp;page=1', 'body': '', 'score': 333}, {'title': '똥글들 그만싸시고', 'date': '2026.03.20 15:04', 'views': '41', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=475150&amp;nid=415503681&amp;page=2', 'body': '', 'score': 281}, {'title': '투경 먹을꺼면', 'date': '2026.03.20 14:39', 'views': '67', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=475150&amp;nid=415499766&amp;page=5', 'body': '', 'score': 307}]</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>475150</t>
         </is>
       </c>
     </row>
@@ -1844,69 +1994,77 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>휴림에이텍</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>907000</v>
+        <v>1017</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>+14.09%</t>
+          <t>+11.51%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>630</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>6.20%</t>
-        </is>
+        <v>-1.1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>130</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>795000</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>5.89%</t>
-        </is>
+      <c r="J20" t="n">
+        <v>912</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>[[[삼천당꿈(시즌2)]]] - 삼천당의 자신...[18] / [[[삼천당꿈(시즌2)]]]  -경구인슐린 100...[26] / 공매와 안티야, 형이야[11] / 3월 주총과 4월 20일 IR에서 듣고 싶...[5]</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Positive (61%)</t>
+          <t>■제2의 우리기술주다[1] / 상철아 ㅡ / 천원 뚫기[1] / 공포에사라</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>코스닥, 삼천당, 오늘</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
+          <t>Positive (64%)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>상철아, 공포에사라, 신바거, 대차게, 들어올려라</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>[{'title': '[[[삼천당꿈(시즌2)]]] - 삼천당의 자신...[18]', 'date': '2026.03.20 09:05', 'views': '1321', 'likes': '145', 'dislikes': '2', 'link': '/item/board_read.naver?code=000250&amp;nid=415438916&amp;page=31', 'score': 5671}, {'title': '[[[삼천당꿈(시즌2)]]]  -경구인슐린 100...[26]', 'date': '2026.03.20 12:05', 'views': '615', 'likes': '141', 'dislikes': '1', 'link': '/item/board_read.naver?code=000250&amp;nid=415476519&amp;page=15', 'score': 4845}, {'title': '공매와 안티야, 형이야[11]', 'date': '2026.03.20 16:41', 'views': '454', 'likes': '92', 'dislikes': '1', 'link': '/item/board_read.naver?code=000250&amp;nid=415515012&amp;page=4', 'score': 3214}, {'title': '나의 10대 소원[8]', 'date': '2026.03.20 15:53', 'views': '420', 'likes': '90', 'dislikes': '1', 'link': '/item/board_read.naver?code=000250&amp;nid=415510993&amp;page=5', 'score': 3120}, {'title': '터제파타이드 경구용 daily &amp; weekly...[9]', 'date': '2026.03.20 15:40', 'views': '554', 'likes': '88', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415509385&amp;page=6', 'score': 3194}, {'title': '가슴이 또[5]', 'date': '2026.03.20 16:10', 'views': '566', 'likes': '84', 'dislikes': '2', 'link': '/item/board_read.naver?code=000250&amp;nid=415512731&amp;page=4', 'score': 3086}, {'title': '3월 주총과 4월 20일 IR에서 듣고 싶...[5]', 'date': '2026.03.20 16:56', 'views': '751', 'likes': '82', 'dislikes': '5', 'link': '/item/board_read.naver?code=000250&amp;nid=415515999&amp;page=4', 'score': 3211}, {'title': 'PeternAnne님 감사합니다^^[7]', 'date': '2026.03.20 15:57', 'views': '377', 'likes': '79', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415511422&amp;page=5', 'score': 2747}, {'title': '주주분들, 코스닥 1위 달성을 축하드립니다[5]', 'date': '2026.03.20 18:01', 'views': '422', 'likes': '78', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415520063&amp;page=2', 'score': 2762}, {'title': '대한민국에 위해주 애널리스트 말고 전부 외...[3]', 'date': '2026.03.20 18:31', 'views': '464', 'likes': '73', 'dislikes': '0', 'link': '/item/board_read.naver?code=000250&amp;nid=415521650&amp;page=2', 'score': 2654}]</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>[{'title': '상철아 ㅡ', 'date': '2026.03.20 13:55', 'views': '23', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=078590&amp;nid=415492834&amp;page=3', 'body': '', 'score': 263}, {'title': '공포에사라', 'date': '2026.03.20 14:38', 'views': '21', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415499587&amp;page=2', 'body': '', 'score': 231}, {'title': '신바거!', 'date': '2026.03.20 14:37', 'views': '16', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415499557&amp;page=2', 'body': '', 'score': 196}, {'title': '대차게 들어올려라~~~~~', 'date': '2026.03.20 14:24', 'views': '22', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415497582&amp;page=2', 'body': '', 'score': 202}, {'title': '상 상 상', 'date': '2026.03.20 13:51', 'views': '24', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415492355&amp;page=3', 'body': '', 'score': 204}, {'title': '천원 뚫기[1]', 'date': '2026.03.20 13:26', 'views': '75', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415488372&amp;page=4', 'body': '', 'score': 255}, {'title': '■제2의 우리기술주다[1]', 'date': '2026.03.20 12:39', 'views': '186', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=078590&amp;nid=415481237&amp;page=4', 'body': '', 'score': 366}, {'title': '세력아[1]', 'date': '2026.03.20 14:46', 'views': '50', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415500881&amp;page=2', 'body': '', 'score': 200}, {'title': '휴리에이텍', 'date': '2026.03.20 08:25', 'views': '40', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415433048&amp;page=7', 'body': '', 'score': 190}, {'title': '상가보자', 'date': '2026.03.20 14:44', 'views': '20', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415500551&amp;page=2', 'body': '', 'score': 140}]</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>078590</t>
         </is>
       </c>
     </row>
@@ -1918,69 +2076,77 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>아남전자</t>
+          <t>진흥기업</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1774</v>
+        <v>1146</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>+12.71%</t>
+          <t>+9.67%</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>105</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2.10%</t>
-        </is>
+        <v>0.22</v>
+      </c>
+      <c r="G21" t="n">
+        <v>157</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>1574</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>1.99%</t>
-        </is>
+      <c r="J21" t="n">
+        <v>804</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>9년 만에 주총참여[1] / 전체주식 33%나 매수+소각은.증시역사 최초.....[1] / 3연상간다[2] / 욕심없이 잘 먹고갑니다</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Positive (64%)</t>
+          <t>호재가 넘사라 내가봤을땐 삼표처럼 1만 찍는다[3] / 27프로[2] / 날마다[5] / 화가..많이 나시죠~[1]</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>공개매수, 이상, 상승했어요</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
+          <t>Positive (71%)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>27프로, 외국인, 120만주, 나감, 호재가</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
         <v>1</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>[{'title': '9년 만에 주총참여[1]', 'date': '2026.03.20 11:40', 'views': '421', 'likes': '25', 'dislikes': '0', 'link': '/item/board_read.naver?code=008700&amp;nid=415472484&amp;page=3', 'score': 1171}, {'title': '3연상간다[2]', 'date': '2026.03.20 09:11', 'views': '175', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=008700&amp;nid=415440381&amp;page=5', 'score': 385}, {'title': '전체주식 33%나 매수+소각은.증시역사 최초.....[1]', 'date': '2026.03.20 16:36', 'views': '241', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=008700&amp;nid=415514670&amp;page=1', 'score': 421}, {'title': '욕심없이 잘 먹고갑니다', 'date': '2026.03.20 09:06', 'views': '176', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=008700&amp;nid=415439116&amp;page=5', 'score': 356}, {'title': '매수가 1560원보다 올라가면', 'date': '2026.03.20 08:21', 'views': '85', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=008700&amp;nid=415432634&amp;page=6', 'score': 265}, {'title': '유통주식 반을. 소각 5연상', 'date': '2026.03.20 11:27', 'views': '104', 'likes': '5', 'dislikes': '4', 'link': '/item/board_read.naver?code=008700&amp;nid=415470137&amp;page=3', 'score': 254}, {'title': '매각 포지션 보다 엠엔에이 인것같다[3]', 'date': '2026.03.20 10:43', 'views': '168', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=008700&amp;nid=415461642&amp;page=3', 'score': 318}, {'title': '공개매수 소각 한다는건', 'date': '2026.03.20 09:01', 'views': '66', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=008700&amp;nid=415437807&amp;page=5', 'score': 216}, {'title': '36층 주민입니다.', 'date': '2026.03.20 15:56', 'views': '92', 'likes': '4', 'dislikes': '1', 'link': '/item/board_read.naver?code=008700&amp;nid=415511332&amp;page=1', 'score': 212}, {'title': '시작 동시호가 끝나는 동시호가[1]', 'date': '2026.03.20 15:31', 'views': '111', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=008700&amp;nid=415507932&amp;page=1', 'score': 231}]</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>008700</t>
+          <t>[{'title': '27프로[2]', 'date': '2026.03.20 14:36', 'views': '74', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=002780&amp;nid=415499375&amp;page=1', 'body': '', 'score': 344}, {'title': '날마다[5]', 'date': '2026.03.20 12:12', 'views': '66', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=002780&amp;nid=415477539&amp;page=5', 'body': '', 'score': 336}, {'title': '오늘 외국인 120만주 나감', 'date': '2026.03.20 14:46', 'views': '49', 'likes': '8', 'dislikes': '4', 'link': '/item/board_read.naver?code=002780&amp;nid=415500919&amp;page=1', 'body': '', 'score': 289}, {'title': '호재가 넘사라 내가봤을땐 삼표처럼 1만 찍는다[3]', 'date': '2026.03.20 13:36', 'views': '109', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=002780&amp;nid=415490049&amp;page=2', 'body': '', 'score': 349}, {'title': '3000 올까요 몇년전 오세훈 출마할때 물렸...', 'date': '2026.03.20 13:20', 'views': '39', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=002780&amp;nid=415487402&amp;page=3', 'body': '', 'score': 279}, {'title': '전력설비', 'date': '2026.03.20 08:03', 'views': '51', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=002780&amp;nid=415430271&amp;page=8', 'body': '', 'score': 291}, {'title': '화가..많이 나시죠~[1]', 'date': '2026.03.20 15:10', 'views': '88', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=002780&amp;nid=415504779&amp;page=1', 'body': '', 'score': 298}, {'title': '이주식 올해 안에 10배는간다', 'date': '2026.03.20 14:09', 'views': '51', 'likes': '7', 'dislikes': '6', 'link': '/item/board_read.naver?code=002780&amp;nid=415495090&amp;page=1', 'body': '', 'score': 261}, {'title': '이거래량으로', 'date': '2026.03.20 14:53', 'views': '80', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=002780&amp;nid=415502094&amp;page=1', 'body': '', 'score': 260}, {'title': 'AI데이터센터 + 오세훈까지 묶인 미친 재료', 'date': '2026.03.20 13:26', 'views': '56', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=002780&amp;nid=415488376&amp;page=3', 'body': '', 'score': 236}]</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>002780</t>
         </is>
       </c>
     </row>
@@ -1992,69 +2158,77 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>휴림에이텍</t>
+          <t>한화투자증권</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1020</v>
+        <v>7960</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>+11.84%</t>
+          <t>+7.86%</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>140</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2.63%</t>
-        </is>
+        <v>0.04</v>
+      </c>
+      <c r="G22" t="n">
+        <v>100</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>912</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>1.31%</t>
-        </is>
+          <t>6.45%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>7540</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>휴림로봇과 키맞춤 할거야[3] / ■제2의 우리기술주다[1] / 텐버거 종목 같다[1] / 헤헤헤헤[1]</t>
+          <t>6.41%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Positive (64%)</t>
+          <t>오늘 상한가한방~~~~![1] / 내 평단[1] / 어이가없네 8000을넘겨버리네[1] / 2018년 10월 부터 보유[3]</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>..., 이상, 3시</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
+          <t>Positive (87%)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>상한가한방, 평단, 어이가없네, 8000을넘겨버리네, 힘내라힘</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>[{'title': '상철아 ㅡ', 'date': '2026.03.20 13:55', 'views': '27', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=078590&amp;nid=415492834&amp;page=4', 'score': 267}, {'title': '헤헤헤헤[1]', 'date': '2026.03.20 16:50', 'views': '63', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415515630&amp;page=1', 'score': 273}, {'title': '공포에사라', 'date': '2026.03.20 14:38', 'views': '28', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415499587&amp;page=2', 'score': 238}, {'title': '텐버거 종목 같다[1]', 'date': '2026.03.20 15:33', 'views': '138', 'likes': '6', 'dislikes': '2', 'link': '/item/board_read.naver?code=078590&amp;nid=415508262&amp;page=1', 'score': 318}, {'title': '신바거!', 'date': '2026.03.20 14:37', 'views': '22', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415499557&amp;page=2', 'score': 202}, {'title': '대차게 들어올려라~~~~~', 'date': '2026.03.20 14:24', 'views': '26', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415497582&amp;page=3', 'score': 206}, {'title': '상 상 상', 'date': '2026.03.20 13:51', 'views': '29', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415492355&amp;page=4', 'score': 209}, {'title': '천원 뚫기[1]', 'date': '2026.03.20 13:26', 'views': '81', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=078590&amp;nid=415488372&amp;page=5', 'score': 261}, {'title': '■제2의 우리기술주다[1]', 'date': '2026.03.20 12:39', 'views': '192', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=078590&amp;nid=415481237&amp;page=5', 'score': 372}, {'title': '휴림로봇과 키맞춤 할거야[3]', 'date': '2026.03.20 12:07', 'views': '559', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=078590&amp;nid=415476887&amp;page=5', 'score': 739}]</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>078590</t>
+          <t>[{'title': '오늘 상한가한방~~~~![1]', 'date': '2026.03.20 10:04', 'views': '163', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415453916&amp;page=5', 'body': '', 'score': 463}, {'title': '내 평단[1]', 'date': '2026.03.20 12:12', 'views': '140', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=003530&amp;nid=415477564&amp;page=4', 'body': '', 'score': 380}, {'title': '어이가없네 8000을넘겨버리네[1]', 'date': '2026.03.20 12:10', 'views': '64', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=003530&amp;nid=415477276&amp;page=4', 'body': '', 'score': 304}, {'title': '힘내라힘!!!', 'date': '2026.03.20 10:46', 'views': '22', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415462376&amp;page=4', 'body': '', 'score': 202}, {'title': '2018년 10월 부터 보유[3]', 'date': '2026.03.20 13:15', 'views': '126', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415486541&amp;page=2', 'body': '', 'score': 276}, {'title': '상한가 가도 - 임[1]', 'date': '2026.03.20 12:47', 'views': '48', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415482475&amp;page=3', 'body': '', 'score': 198}, {'title': '드디어 골든 크로스 !!!', 'date': '2026.03.20 10:17', 'views': '35', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415456712&amp;page=5', 'body': '', 'score': 185}, {'title': '중소형주로 매수 이동 ~~~', 'date': '2026.03.20 10:02', 'views': '38', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415453587&amp;page=5', 'body': '', 'score': 188}, {'title': 'sk증권보다 못한 이유가 모냐', 'date': '2026.03.20 12:55', 'views': '38', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415483640&amp;page=3', 'body': '', 'score': 158}, {'title': '갑자기 왜 이러는거래요?[1]', 'date': '2026.03.20 12:46', 'views': '128', 'likes': '4', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415482330&amp;page=3', 'body': '', 'score': 248}]</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>003530</t>
         </is>
       </c>
     </row>
@@ -2066,69 +2240,77 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>LS머트리얼즈</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>59900</v>
+        <v>25300</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>+11.55%</t>
+          <t>+6.53%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>800</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2.67%</t>
-        </is>
+        <v>-0.78</v>
+      </c>
+      <c r="G23" t="n">
+        <v>174</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>53700</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>3.00%</t>
-        </is>
+          <t>4.80%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>22950</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>60층 이상에서 마음고생 중인 주주분들을 위해[4] / 66500원에 신용으로 산거 손절하고 간다[5] / 다음주엔 앞자리7?[1] / 66500에 풀신용 지른 1인입니다[3]</t>
+          <t>5.58%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Negative (66%)</t>
+          <t>3년 맘고생하고  쬐끔 수익 보고 갑니다[1] / 내년 연말까지 들고가렵니다. 목표가 15만원[2] / 다른 주식들 싹다 정리하고[2] / 이제[1]</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>오늘, 투경, ...</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
+          <t>Negative (52%)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>3년, 맘고생하고, 쬐끔, 수익, 보고</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
         <v>1</v>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>[{'title': '60층 이상에서 마음고생 중인 주주분들을 위해[4]', 'date': '2026.03.20 18:03', 'views': '489', 'likes': '21', 'dislikes': '2', 'link': '/item/board_read.naver?code=475150&amp;nid=415520191&amp;page=3', 'score': 1119}, {'title': 'SK다[1]', 'date': '2026.03.20 18:56', 'views': '144', 'likes': '15', 'dislikes': '6', 'link': '/item/board_read.naver?code=475150&amp;nid=415522858&amp;page=2', 'score': 594}, {'title': '다음주엔 앞자리7?[1]', 'date': '2026.03.20 14:30', 'views': '332', 'likes': '15', 'dislikes': '4', 'link': '/item/board_read.naver?code=475150&amp;nid=415498430&amp;page=14', 'score': 782}, {'title': '[매동] 실시간 매매추이 5차', 'date': '2026.03.20 14:25', 'views': '227', 'likes': '14', 'dislikes': '3', 'link': '/item/board_read.naver?code=475150&amp;nid=415497771&amp;page=14', 'score': 647}, {'title': '물렸으면 지금 넥장에서 판매할거 아니면 그냥...[1]', 'date': '2026.03.20 17:30', 'views': '185', 'likes': '13', 'dislikes': '5', 'link': '/item/board_read.naver?code=475150&amp;nid=415518308&amp;page=5', 'score': 575}, {'title': '상한가ㄱㄱ', 'date': '2026.03.20 16:10', 'views': '64', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=475150&amp;nid=415512777&amp;page=7', 'score': 454}, {'title': '66500에 풀신용 지른 1인입니다[3]', 'date': '2026.03.20 15:01', 'views': '262', 'likes': '13', 'dislikes': '5', 'link': '/item/board_read.naver?code=475150&amp;nid=415503210&amp;page=12', 'score': 652}, {'title': '간단히 얘기한다 시총 20조 넘는다', 'date': '2026.03.20 19:18', 'views': '229', 'likes': '12', 'dislikes': '2', 'link': '/item/board_read.naver?code=475150&amp;nid=415523855&amp;page=2', 'score': 589}, {'title': '차라리', 'date': '2026.03.20 16:10', 'views': '109', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=475150&amp;nid=415512730&amp;page=7', 'score': 469}, {'title': '66500원에 신용으로 산거 손절하고 간다[5]', 'date': '2026.03.20 16:18', 'views': '530', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=475150&amp;nid=415513374&amp;page=7', 'score': 860}]</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>[{'title': '3년 맘고생하고  쬐끔 수익 보고 갑니다[1]', 'date': '2026.03.20 13:52', 'views': '217', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=417200&amp;nid=415492503&amp;page=1', 'body': '', 'score': 547}, {'title': '내년 연말까지 들고가렵니다. 목표가 15만원[2]', 'date': '2026.03.20 09:23', 'views': '272', 'likes': '9', 'dislikes': '7', 'link': '/item/board_read.naver?code=417200&amp;nid=415443758&amp;page=7', 'body': '', 'score': 542}, {'title': '두시간 기어오르고 10분만에 내려오네 잡스...', 'date': '2026.03.20 13:09', 'views': '43', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=417200&amp;nid=415485662&amp;page=2', 'body': '', 'score': 253}, {'title': '뚫자 !! 30,000[1]', 'date': '2026.03.20 12:12', 'views': '82', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415477559&amp;page=2', 'body': '', 'score': 292}, {'title': '전고점들 중에 19000원은 돌파했네', 'date': '2026.03.20 10:41', 'views': '61', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=417200&amp;nid=415461391&amp;page=4', 'body': '', 'score': 271}, {'title': '이제[1]', 'date': '2026.03.20 12:08', 'views': '113', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=417200&amp;nid=415476899&amp;page=3', 'body': '', 'score': 293}, {'title': '다른 주식들 싹다 정리하고[2]', 'date': '2026.03.20 12:06', 'views': '175', 'likes': '6', 'dislikes': '4', 'link': '/item/board_read.naver?code=417200&amp;nid=415476714&amp;page=3', 'body': '', 'score': 355}, {'title': '에너지', 'date': '2026.03.20 09:24', 'views': '38', 'likes': '6', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415444088&amp;page=7', 'body': '', 'score': 218}, {'title': '2년만에 빨간불 ㅎㅎㅎㅎㅎㅎ', 'date': '2026.03.20 09:20', 'views': '53', 'likes': '6', 'dislikes': '4', 'link': '/item/board_read.naver?code=417200&amp;nid=415442951&amp;page=7', 'body': '', 'score': 233}, {'title': '얼.죽.상[1]', 'date': '2026.03.20 09:19', 'views': '51', 'likes': '6', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415442607&amp;page=7', 'body': '', 'score': 231}]</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>417200</t>
         </is>
       </c>
     </row>
@@ -2140,69 +2322,77 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>진흥기업</t>
+          <t>보성파워텍</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1150</v>
+        <v>12840</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>+10.05%</t>
+          <t>+5.94%</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>177</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0.76%</t>
-        </is>
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>213</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>1045</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>1.61%</t>
-        </is>
+          <t>8.06%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>12760</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>간판부터 바꾸면 안되나? / 화가..많이 나시죠~[1] / 오늘 외국인 120만주 나감 / 이제1파 상승했다[2]</t>
+          <t>8.13%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>주린이인데 그래서 사야하는건가요 말아야하는건...[2] / 어제 실적 발표한거 보니 전년대비 거의 10... / 정직한 주식은 실적으로 말한다.[1] / 보성과 두산 신고가[2]</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
           <t>Positive (68%)</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>오늘, 상한가, 진흥</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>가자, 주린이인데, 그래서, 말아야하는건, 정직한</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>[{'title': '간판부터 바꾸면 안되나?', 'date': '2026.03.20 16:08', 'views': '103', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=002780&amp;nid=415512538&amp;page=1', 'score': 553}, {'title': '오늘 외국인 120만주 나감', 'date': '2026.03.20 14:46', 'views': '94', 'likes': '13', 'dislikes': '5', 'link': '/item/board_read.naver?code=002780&amp;nid=415500919&amp;page=2', 'score': 484}, {'title': '화가..많이 나시죠~[1]', 'date': '2026.03.20 15:10', 'views': '201', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=002780&amp;nid=415504779&amp;page=2', 'score': 501}, {'title': '난진흥이가 효성하고 잘하길 빌어', 'date': '2026.03.20 14:46', 'views': '57', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=002780&amp;nid=415500896&amp;page=2', 'score': 327}, {'title': '27프로[2]', 'date': '2026.03.20 14:36', 'views': '124', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=002780&amp;nid=415499375&amp;page=2', 'score': 394}, {'title': '날마다[5]', 'date': '2026.03.20 12:12', 'views': '71', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=002780&amp;nid=415477539&amp;page=6', 'score': 341}, {'title': '호재가 넘사라 내가봤을땐 삼표처럼 1만 찍는...[3]', 'date': '2026.03.20 13:36', 'views': '127', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=002780&amp;nid=415490049&amp;page=4', 'score': 367}, {'title': '3000 올까요 몇년전 오세훈 출마할때 물렸...', 'date': '2026.03.20 13:20', 'views': '47', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=002780&amp;nid=415487402&amp;page=4', 'score': 287}, {'title': '전력설비', 'date': '2026.03.20 08:03', 'views': '54', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=002780&amp;nid=415430271&amp;page=9', 'score': 294}, {'title': '이제1파 상승했다[2]', 'date': '2026.03.20 16:25', 'views': '221', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=002780&amp;nid=415513930&amp;page=1', 'score': 431}]</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>002780</t>
+          <t>[{'title': '주린이인데 그래서 사야하는건가요 말아야하는건...[2]', 'date': '2026.03.20 10:59', 'views': '155', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=006910&amp;nid=415464951&amp;page=8', 'body': '', 'score': 455}, {'title': '정직한 주식은 실적으로 말한다.[1]', 'date': '2026.03.20 10:42', 'views': '59', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415461546&amp;page=8', 'body': '', 'score': 359}, {'title': '주주분들 버티면 크게 갑니다', 'date': '2026.03.20 10:50', 'views': '58', 'likes': '9', 'dislikes': '3', 'link': '/item/board_read.naver?code=006910&amp;nid=415463282&amp;page=8', 'body': '', 'score': 328}, {'title': '어제 실적 발표한거 보니 전년대비 거의 10...', 'date': '2026.03.20 10:48', 'views': '108', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415462771&amp;page=8', 'body': '', 'score': 378}, {'title': '보성과 두산 신고가[2]', 'date': '2026.03.20 11:06', 'views': '97', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415466318&amp;page=8', 'body': '', 'score': 337}, {'title': '오늘은 상한가 가는날 맞죠ㅋ[3]', 'date': '2026.03.20 09:39', 'views': '92', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=006910&amp;nid=415448007&amp;page=10', 'body': '', 'score': 302}, {'title': '또이런다~~~~', 'date': '2026.03.20 12:40', 'views': '22', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415481457&amp;page=5', 'body': '', 'score': 202}, {'title': '1분뒤에 상항가 가자 안그럼 신고한다ㅡ[2]', 'date': '2026.03.20 12:17', 'views': '57', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=006910&amp;nid=415478177&amp;page=6', 'body': '', 'score': 207}, {'title': '자... 14천원 가자', 'date': '2026.03.20 11:55', 'views': '16', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=006910&amp;nid=415475026&amp;page=6', 'body': '', 'score': 166}, {'title': '이러다 보합갈수도있는놈', 'date': '2026.03.20 11:41', 'views': '17', 'likes': '5', 'dislikes': '2', 'link': '/item/board_read.naver?code=006910&amp;nid=415472575&amp;page=7', 'body': '', 'score': 167}]</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>006910</t>
         </is>
       </c>
     </row>
@@ -2214,69 +2404,77 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한화투자증권</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7920</v>
+        <v>5220</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>+7.32%</t>
+          <t>+5.88%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>106</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>6.42%</t>
-        </is>
+        <v>-0.18</v>
+      </c>
+      <c r="G25" t="n">
+        <v>123</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t>6.12%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>7380</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>6.45%</t>
-        </is>
+      <c r="J25" t="n">
+        <v>5250</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>오늘 상한가한방~~~~![1] / 다음주 / 내 평단[1] / 쫄거있나? 담주 슈팅 나올듯[1]</t>
+          <t>6.30%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Positive (87%)</t>
+          <t>예금보험공사  10퍼 지분[2] / 2남, 금융계열분리~ / 뉴스에는 한생 pbr 0.18로 나오네요 / 진짜 사력을 다해 죽을힘을 다해 가용수단을 총...[1]</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>오늘, SK, 종가</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
+          <t>Positive (90%)</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>pbr, 다해, 예금보험공사, 10퍼, 지분</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
         <v>1</v>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>[{'title': '오늘 상한가한방~~~~![1]', 'date': '2026.03.20 10:04', 'views': '222', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=003530&amp;nid=415453916&amp;page=5', 'score': 612}, {'title': '다음주', 'date': '2026.03.20 15:07', 'views': '182', 'likes': '12', 'dislikes': '6', 'link': '/item/board_read.naver?code=003530&amp;nid=415504261&amp;page=1', 'score': 542}, {'title': '내 평단[1]', 'date': '2026.03.20 12:12', 'views': '145', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=003530&amp;nid=415477564&amp;page=4', 'score': 385}, {'title': '어이가없네 8000을넘겨버리네[1]', 'date': '2026.03.20 12:10', 'views': '70', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=003530&amp;nid=415477276&amp;page=4', 'score': 310}, {'title': '쫄거있나? 담주 슈팅 나올듯[1]', 'date': '2026.03.20 17:18', 'views': '148', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=003530&amp;nid=415517562&amp;page=1', 'score': 358}, {'title': '담주부터 오를거에용', 'date': '2026.03.20 16:55', 'views': '46', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=003530&amp;nid=415515972&amp;page=1', 'score': 256}, {'title': '2018년 10월 부터 보유[3]', 'date': '2026.03.20 13:15', 'views': '139', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415486541&amp;page=3', 'score': 319}, {'title': '힘내라힘!!!', 'date': '2026.03.20 10:46', 'views': '26', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415462376&amp;page=5', 'score': 206}, {'title': '드디어 골든 크로스 !!!', 'date': '2026.03.20 10:17', 'views': '42', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415456712&amp;page=5', 'score': 222}, {'title': '중소형주로 매수 이동 ~~~', 'date': '2026.03.20 10:02', 'views': '43', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=003530&amp;nid=415453587&amp;page=5', 'score': 223}]</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>003530</t>
+          <t>[{'title': '예금보험공사  10퍼 지분[2]', 'date': '2026.03.20 08:20', 'views': '294', 'likes': '25', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415432488&amp;page=7', 'body': '', 'score': 1044}, {'title': '2남, 금융계열분리~', 'date': '2026.03.20 13:09', 'views': '211', 'likes': '19', 'dislikes': '3', 'link': '/item/board_read.naver?code=088350&amp;nid=415485697&amp;page=3', 'body': '', 'score': 781}, {'title': '뉴스에는 한생 pbr 0.18로 나오네요', 'date': '2026.03.20 10:55', 'views': '190', 'likes': '18', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415464145&amp;page=4', 'body': '', 'score': 730}, {'title': '진짜 사력을 다해 죽을힘을 다해 가용수단을 총...[1]', 'date': '2026.03.20 14:07', 'views': '119', 'likes': '15', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415494738&amp;page=2', 'body': '', 'score': 569}, {'title': '대한민국 4번째 대기업에서~', 'date': '2026.03.20 09:32', 'views': '55', 'likes': '15', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415446002&amp;page=6', 'body': '', 'score': 505}, {'title': '대한민국의 본보기로~[1]', 'date': '2026.03.20 10:42', 'views': '57', 'likes': '14', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415461578&amp;page=5', 'body': '', 'score': 477}, {'title': '한씨화발 생명은 오늘도 액면가에서 노는중이에요[1]', 'date': '2026.03.20 11:20', 'views': '64', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415468722&amp;page=4', 'body': '', 'score': 454}, {'title': '생보사들 중 pbr 저평가 기업은 얘뿐임[1]', 'date': '2026.03.20 11:09', 'views': '96', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415466841&amp;page=4', 'body': '', 'score': 486}, {'title': '한화생명, 자사주 소각·배당 강화 기대감 본...[1]', 'date': '2026.03.20 10:09', 'views': '128', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=088350&amp;nid=415455082&amp;page=5', 'body': '', 'score': 488}, {'title': '한화생명은 너무 눌렀지뭐', 'date': '2026.03.20 14:31', 'views': '73', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415498649&amp;page=2', 'body': '', 'score': 403}]</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>088350</t>
         </is>
       </c>
     </row>
@@ -2288,69 +2486,77 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LS머트리얼즈</t>
+          <t>대한해운</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>25300</v>
+        <v>2350</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>+6.53%</t>
+          <t>+5.15%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>185</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>5.40%</t>
-        </is>
+        <v>-0.35</v>
+      </c>
+      <c r="G26" t="n">
+        <v>125</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>23750</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>4.80%</t>
-        </is>
+          <t>7.65%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>2270</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>3년 맘고생하고  쬐끔 수익 보고 갑니다[1] / 차트 정배열 완성 됬네요[3] / 내년 연말까지 들고가렵니다. 목표가 15만원[2] / 엘머</t>
+          <t>8.00%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>SM상선.. 64억 sm자산개발로 대여함.[3] / 챗지피티[1] / 탈 카타르 LNG선박 수혜주  (대한해운)[2] / 에너지 수급 불균형[1]</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>오늘, 시외, 상한가</t>
-        </is>
-      </c>
-      <c r="N26" t="n">
+          <t>Positive (70%)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>SM상선, 64억, sm자산개발로, 정정당당하게, 주식배당</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>[{'title': '3년 맘고생하고  쬐끔 수익 보고 갑니다[1]', 'date': '2026.03.20 13:52', 'views': '261', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415492503&amp;page=2', 'score': 711}, {'title': '차트 정배열 완성 됬네요[3]', 'date': '2026.03.20 15:55', 'views': '369', 'likes': '10', 'dislikes': '7', 'link': '/item/board_read.naver?code=417200&amp;nid=415511278&amp;page=1', 'score': 669}, {'title': '엘머', 'date': '2026.03.20 15:46', 'views': '125', 'likes': '10', 'dislikes': '5', 'link': '/item/board_read.naver?code=417200&amp;nid=415510182&amp;page=1', 'score': 425}, {'title': '오늘도', 'date': '2026.03.20 15:12', 'views': '74', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415504977&amp;page=1', 'score': 344}, {'title': '내년 연말까지 들고가렵니다. 목표가 15만원[2]', 'date': '2026.03.20 09:23', 'views': '275', 'likes': '9', 'dislikes': '7', 'link': '/item/board_read.naver?code=417200&amp;nid=415443758&amp;page=7', 'score': 545}, {'title': '뚫자 !! 30,000[1]', 'date': '2026.03.20 12:12', 'views': '89', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415477559&amp;page=3', 'score': 329}, {'title': '주가 오르니까 정신병원에서 대탈출했냐?[2]', 'date': '2026.03.20 16:59', 'views': '123', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=417200&amp;nid=415516220&amp;page=1', 'score': 333}, {'title': '3만원대만가면', 'date': '2026.03.20 16:40', 'views': '94', 'likes': '7', 'dislikes': '5', 'link': '/item/board_read.naver?code=417200&amp;nid=415514966&amp;page=1', 'score': 304}, {'title': '두시간 기어오르고 10분만에 내려오네 잡스...', 'date': '2026.03.20 13:09', 'views': '45', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=417200&amp;nid=415485662&amp;page=2', 'score': 255}, {'title': '이제[1]', 'date': '2026.03.20 12:08', 'views': '120', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=417200&amp;nid=415476899&amp;page=3', 'score': 330}]</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>417200</t>
+          <t>[{'title': 'SM상선.. 64억 sm자산개발로 대여함.[3]', 'date': '2026.03.20 08:48', 'views': '156', 'likes': '14', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415436015&amp;page=6', 'body': '', 'score': 576}, {'title': '정정당당하게 주식배당 줘라', 'date': '2026.03.20 11:25', 'views': '29', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415469747&amp;page=4', 'body': '', 'score': 329}, {'title': '챗지피티[1]', 'date': '2026.03.20 08:14', 'views': '222', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415431613&amp;page=7', 'body': '', 'score': 492}, {'title': '에너지 수급 불균형[1]', 'date': '2026.03.20 13:28', 'views': '127', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415488678&amp;page=2', 'body': '', 'score': 367}, {'title': '벌크선/LNG선 수요 폭발[1]', 'date': '2026.03.20 12:39', 'views': '111', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415481226&amp;page=3', 'body': '', 'score': 351}, {'title': '탈 카타르 LNG선박 수혜주  (대한해운)[2]', 'date': '2026.03.20 08:48', 'views': '129', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415436009&amp;page=6', 'body': '', 'score': 369}, {'title': '여기도', 'date': '2026.03.20 11:35', 'views': '28', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415471599&amp;page=4', 'body': '', 'score': 238}, {'title': '숏커버링 들어온다고 도대체 몇번을 말해도, ...', 'date': '2026.03.20 10:23', 'views': '49', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415457915&amp;page=5', 'body': '', 'score': 259}, {'title': '공매견들 아침부터 바쁘네', 'date': '2026.03.20 08:56', 'views': '21', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415437131&amp;page=6', 'body': '', 'score': 231}, {'title': '망했네. 더 싸게 매수할수있었는데', 'date': '2026.03.20 08:03', 'views': '105', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415430205&amp;page=7', 'body': '', 'score': 315}]</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>005880</t>
         </is>
       </c>
     </row>
@@ -2362,69 +2568,77 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한화생명</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5230</v>
+        <v>51700</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>+6.09%</t>
+          <t>+3.92%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>146</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>6.23%</t>
-        </is>
+        <v>-0.3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>800</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
+          <t>14.46%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>4930</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>6.12%</t>
-        </is>
+      <c r="J27" t="n">
+        <v>50800</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>배신자 / 네이버에 저 pbr주 기사 떳으니[2] / 예금보험공사  10퍼 지분[2] / 대우건설보다는 높아야 하지않나???[1]</t>
+          <t>14.76%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Positive (81%)</t>
+          <t>외인 기관 연기금은 싹쓸이중인데[3] / 56800에 안판 내손이 웬수지 / 거래  1조7천억터지고  공시호재가나왓는데도[1] / 버핏: 주식시장은</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>오늘, 먹고, 이제</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>[{'title': '배신자', 'date': '2026.03.20 15:35', 'views': '323', 'likes': '34', 'dislikes': '1', 'link': '/item/board_read.naver?code=088350&amp;nid=415508656&amp;page=1', 'score': 1343}, {'title': '대우건설보다는 높아야 하지않나???[1]', 'date': '2026.03.20 15:34', 'views': '129', 'likes': '26', 'dislikes': '2', 'link': '/item/board_read.naver?code=088350&amp;nid=415508561&amp;page=2', 'score': 909}, {'title': '예금보험공사  10퍼 지분[2]', 'date': '2026.03.20 08:20', 'views': '299', 'likes': '25', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415432488&amp;page=8', 'score': 1049}, {'title': '네이버에 저 pbr주 기사 떳으니[2]', 'date': '2026.03.20 16:08', 'views': '373', 'likes': '23', 'dislikes': '3', 'link': '/item/board_read.naver?code=088350&amp;nid=415512532&amp;page=1', 'score': 1063}, {'title': '잘 먹고 가거라[2]', 'date': '2026.03.20 15:33', 'views': '270', 'likes': '20', 'dislikes': '2', 'link': '/item/board_read.naver?code=088350&amp;nid=415508342&amp;page=2', 'score': 870}, {'title': '2남, 금융계열분리~', 'date': '2026.03.20 13:09', 'views': '225', 'likes': '19', 'dislikes': '3', 'link': '/item/board_read.naver?code=088350&amp;nid=415485697&amp;page=4', 'score': 795}, {'title': '다음주[1]', 'date': '2026.03.20 17:10', 'views': '82', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=088350&amp;nid=415517019&amp;page=1', 'score': 622}, {'title': '뉴스에는 한생 pbr 0.18로 나오네요', 'date': '2026.03.20 10:55', 'views': '198', 'likes': '18', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415464145&amp;page=6', 'score': 738}, {'title': '청와대 금감원 지역구 국회의원실에 자료 보내기', 'date': '2026.03.20 18:07', 'views': '68', 'likes': '17', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415520375&amp;page=1', 'score': 578}, {'title': '진짜 사력을 다해 죽을힘을 다해 가용수단을 ...[1]', 'date': '2026.03.20 14:07', 'views': '144', 'likes': '17', 'dislikes': '0', 'link': '/item/board_read.naver?code=088350&amp;nid=415494738&amp;page=3', 'score': 654}]</t>
-        </is>
+          <t>Negative (59%)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>56800에, 안판, 내손이, 웬수지, 거래</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>2</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>088350</t>
+          <t>[{'title': '56800에 안판 내손이 웬수지', 'date': '2026.03.20 11:15', 'views': '35', 'likes': '15', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415467886&amp;page=22', 'body': '', 'score': 485}, {'title': '거래  1조7천억터지고  공시호재가나왓는데도[1]', 'date': '2026.03.20 15:21', 'views': '133', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415506517&amp;page=1', 'body': '', 'score': 463}, {'title': '버핏: 주식시장은', 'date': '2026.03.20 14:22', 'views': '76', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=009830&amp;nid=415497291&amp;page=7', 'body': '', 'score': 406}, {'title': '그냥 확 상찍어버려', 'date': '2026.03.20 12:27', 'views': '36', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415479697&amp;page=15', 'body': '', 'score': 366}, {'title': '그럼 그렇지', 'date': '2026.03.20 11:08', 'views': '25', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415466612&amp;page=24', 'body': '', 'score': 355}, {'title': '뭐이런 개잡주가 다있노?[1]', 'date': '2026.03.20 15:22', 'views': '49', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=009830&amp;nid=415506693&amp;page=1', 'body': '', 'score': 349}, {'title': '또속으신분?', 'date': '2026.03.20 12:32', 'views': '39', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415480270&amp;page=15', 'body': '', 'score': 339}, {'title': '외인 기관 연기금은 싹쓸이중인데[3]', 'date': '2026.03.20 12:21', 'views': '200', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=009830&amp;nid=415478716&amp;page=16', 'body': '', 'score': 500}, {'title': '거래대금이..', 'date': '2026.03.20 11:50', 'views': '40', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415474234&amp;page=18', 'body': '', 'score': 340}, {'title': '계속 답없이구네~', 'date': '2026.03.20 10:58', 'views': '66', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415464913&amp;page=26', 'body': '', 'score': 366}]</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>009830</t>
         </is>
       </c>
     </row>
@@ -2436,69 +2650,77 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>보성파워텍</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12850</v>
+        <v>109400</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>+6.02%</t>
+          <t>+2.92%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>230</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>10.16%</t>
-        </is>
+        <v>0.05</v>
+      </c>
+      <c r="G28" t="n">
+        <v>645</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>12120</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>8.06%</t>
-        </is>
+          <t>24.24%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>107300</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>구멍가게 굴뚝주 잡고 시총 3조?[3] / 주린이인데 그래서 사야하는건가요 말아야하는건...[2] / 어제 실적 발표한거 보니 전년대비 거의 10... / 외국인이 1백만주 팔든 사든</t>
+          <t>24.19%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Positive (68%)</t>
+          <t>천정 열렸네...슈팅간다 / 오늘부터 11만원대에[2] / 회장 매수가 10,7만 / 15는 금방 가겠는데</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>오르비텍, 보성, 시총</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>[{'title': '구멍가게 굴뚝주 잡고 시총 3조?[3]', 'date': '2026.03.20 17:23', 'views': '130', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415517895&amp;page=1', 'score': 490}, {'title': '외국인이 1백만주 팔든 사든', 'date': '2026.03.20 17:08', 'views': '64', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=006910&amp;nid=415516892&amp;page=1', 'score': 364}, {'title': '주린이인데 그래서 사야하는건가요 말아야하는건...[2]', 'date': '2026.03.20 10:59', 'views': '158', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=006910&amp;nid=415464951&amp;page=9', 'score': 458}, {'title': '정직한 주식은 실적으로 말한다.[1]', 'date': '2026.03.20 10:42', 'views': '63', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415461546&amp;page=9', 'score': 363}, {'title': '머머 한다. 카더라만 말고', 'date': '2026.03.20 17:47', 'views': '76', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415519288&amp;page=1', 'score': 346}, {'title': '한심한 사람들', 'date': '2026.03.20 17:43', 'views': '58', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=006910&amp;nid=415519033&amp;page=1', 'score': 328}, {'title': '주주분들 버티면 크게 갑니다', 'date': '2026.03.20 10:50', 'views': '62', 'likes': '9', 'dislikes': '3', 'link': '/item/board_read.naver?code=006910&amp;nid=415463282&amp;page=9', 'score': 332}, {'title': '어제 실적 발표한거 보니 전년대비 거의 10...', 'date': '2026.03.20 10:48', 'views': '110', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415462771&amp;page=9', 'score': 380}, {'title': '보성과 두산 신고가[2]', 'date': '2026.03.20 11:06', 'views': '101', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=006910&amp;nid=415466318&amp;page=9', 'score': 341}, {'title': '오늘은 상한가 가는날 맞죠ㅋ[3]', 'date': '2026.03.20 09:39', 'views': '95', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=006910&amp;nid=415448007&amp;page=11', 'score': 305}]</t>
-        </is>
+          <t>Positive (65%)</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>천정, 열렸네, 15는, 금방, 가겠는데</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>2</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>006910</t>
+          <t>[{'title': '천정 열렸네...슈팅간다', 'date': '2026.03.20 10:39', 'views': '88', 'likes': '19', 'dislikes': '2', 'link': '/item/board_read.naver?code=034020&amp;nid=415460931&amp;page=24', 'body': '', 'score': 658}, {'title': '15는 금방 가겠는데', 'date': '2026.03.20 12:08', 'views': '57', 'likes': '15', 'dislikes': '1', 'link': '/item/board_read.naver?code=034020&amp;nid=415476964&amp;page=13', 'body': '', 'score': 507}, {'title': '시원하게 12만원대로 넘어가자![1]', 'date': '2026.03.20 08:39', 'views': '78', 'likes': '14', 'dislikes': '0', 'link': '/item/board_read.naver?code=034020&amp;nid=415434916&amp;page=30', 'body': '', 'score': 498}, {'title': '회장 매수가 10,7만', 'date': '2026.03.20 13:59', 'views': '124', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=034020&amp;nid=415493548&amp;page=6', 'body': '', 'score': 514}, {'title': '자 두빌아 오늘 110,700 뚫었으니', 'date': '2026.03.20 12:45', 'views': '70', 'likes': '13', 'dislikes': '2', 'link': '/item/board_read.naver?code=034020&amp;nid=415482071&amp;page=10', 'body': '', 'score': 460}, {'title': '전고도 뚫었는데 오늘 상 쳐야지', 'date': '2026.03.20 12:08', 'views': '49', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=034020&amp;nid=415477031&amp;page=13', 'body': '', 'score': 439}, {'title': '미쳤다 오늘 왠일이래', 'date': '2026.03.20 11:50', 'views': '82', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=034020&amp;nid=415474118&amp;page=16', 'body': '', 'score': 472}, {'title': '오늘부터 11만원대에[2]', 'date': '2026.03.20 12:22', 'views': '228', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=034020&amp;nid=415478875&amp;page=12', 'body': '', 'score': 588}, {'title': '오늘로 개미 매물 전멸[1]', 'date': '2026.03.20 15:17', 'views': '122', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=034020&amp;nid=415505727&amp;page=1', 'body': '', 'score': 452}, {'title': '오늘도 위에 있는 매물들 많이 소화 했습...[3]', 'date': '2026.03.20 13:44', 'views': '117', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=034020&amp;nid=415491370&amp;page=7', 'body': '', 'score': 447}]</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2510,69 +2732,77 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>대한해운</t>
+          <t>현대ADM</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2350</v>
+        <v>14790</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>+5.15%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>134</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>8.76%</t>
-        </is>
+        <v>0.23</v>
+      </c>
+      <c r="G29" t="n">
+        <v>764</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>2235</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>7.65%</t>
-        </is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>16200</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SM상선.. 64억 sm자산개발로 대여함.[3] / 챗지피티[1] / 건설자재 건설장비는 뭘로 옮길꺼요? 비행기로?... / 뉴스에는 크게 이슈화되지 않았지만, 오늘 오른...</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Positive (70%)</t>
+          <t>AACR 2026 참가여부 2[16] / AACR26 참석 부스 위치입니다.[5] / 오후2시전 발표있습니다.[1] / 큰 제약사 왔다고 합니다[1]</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>오늘, ..., 대한해운</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
+          <t>Negative (56%)</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>AACR26, AACR, 참가여부, 오후2시전, 불금</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
         <v>1</v>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>[{'title': 'SM상선.. 64억 sm자산개발로 대여함.[3]', 'date': '2026.03.20 08:48', 'views': '164', 'likes': '14', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415436015&amp;page=7', 'score': 584}, {'title': '건설자재 건설장비는 뭘로 옮길꺼요? 비행기로?...', 'date': '2026.03.20 15:51', 'views': '85', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415510767&amp;page=1', 'score': 415}, {'title': '정정당당하게 주식배당 줘라', 'date': '2026.03.20 11:25', 'views': '34', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415469747&amp;page=4', 'score': 334}, {'title': '뉴스에는 크게 이슈화되지 않았지만, 오늘 오른...', 'date': '2026.03.20 17:22', 'views': '116', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415517836&amp;page=1', 'score': 386}, {'title': '챗지피티[1]', 'date': '2026.03.20 08:14', 'views': '225', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415431613&amp;page=7', 'score': 495}, {'title': '탈 카타르 LNG선박 수혜주  (대한해운)[2]', 'date': '2026.03.20 08:48', 'views': '133', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415436009&amp;page=7', 'score': 373}, {'title': '와 부채 6천억 줄이고 당기순이익 100억 증...', 'date': '2026.03.20 16:47', 'views': '89', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415515380&amp;page=1', 'score': 299}, {'title': 'bts[2]', 'date': '2026.03.20 15:19', 'views': '141', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415506108&amp;page=1', 'score': 351}, {'title': '여기도', 'date': '2026.03.20 11:35', 'views': '31', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=005880&amp;nid=415471599&amp;page=4', 'score': 241}, {'title': '숏커버링 들어온다고 도대체 몇번을 말해도, ...', 'date': '2026.03.20 10:23', 'views': '53', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=005880&amp;nid=415457915&amp;page=5', 'score': 263}]</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>005880</t>
+          <t>[{'title': 'AACR 2026 참가여부 2[16]', 'date': '2026.03.20 08:11', 'views': '477', 'likes': '42', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415431173&amp;page=38', 'body': '', 'score': 1737}, {'title': '오후2시전 발표있습니다.[1]', 'date': '2026.03.20 11:08', 'views': '291', 'likes': '19', 'dislikes': '2', 'link': '/item/board_read.naver?code=187660&amp;nid=415466624&amp;page=25', 'body': '', 'score': 861}, {'title': '불금~[1]', 'date': '2026.03.20 08:01', 'views': '74', 'likes': '19', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415430011&amp;page=39', 'body': '', 'score': 644}, {'title': '오늘은', 'date': '2026.03.20 08:16', 'views': '57', 'likes': '18', 'dislikes': '0', 'link': '/item/board_read.naver?code=187660&amp;nid=415431938&amp;page=38', 'body': '', 'score': 597}, {'title': '●오늘●[1]', 'date': '2026.03.20 08:12', 'views': '106', 'likes': '18', 'dislikes': '9', 'link': '/item/board_read.naver?code=187660&amp;nid=415431412&amp;page=38', 'body': '', 'score': 646}, {'title': '페니야', 'date': '2026.03.20 08:05', 'views': '41', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415430506&amp;page=39', 'body': '', 'score': 581}, {'title': 'AACR26 참석 부스 위치입니다.[5]', 'date': '2026.03.20 13:39', 'views': '453', 'likes': '17', 'dislikes': '2', 'link': '/item/board_read.naver?code=187660&amp;nid=415490582&amp;page=9', 'body': '', 'score': 963}, {'title': '천지 개벽 할 기술이전 비밀로 초록 미공개!![2]', 'date': '2026.03.20 13:49', 'views': '240', 'likes': '16', 'dislikes': '4', 'link': '/item/board_read.naver?code=187660&amp;nid=415492042&amp;page=8', 'body': '', 'score': 720}, {'title': '큰 제약사 왔다고 합니다[1]', 'date': '2026.03.20 11:19', 'views': '277', 'likes': '16', 'dislikes': '4', 'link': '/item/board_read.naver?code=187660&amp;nid=415468547&amp;page=22', 'body': '', 'score': 757}, {'title': '회사측이 AACR26 준비하느라 정신없이 바쁜...', 'date': '2026.03.20 10:36', 'views': '246', 'likes': '16', 'dislikes': '2', 'link': '/item/board_read.naver?code=187660&amp;nid=415460465&amp;page=27', 'body': '', 'score': 726}]</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>187660</t>
         </is>
       </c>
     </row>
@@ -2584,69 +2814,77 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>쏠리드</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>51700</v>
+        <v>13200</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>+3.92%</t>
+          <t>+2.33%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>800</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>14.66%</t>
-        </is>
+        <v>-1.38</v>
+      </c>
+      <c r="G30" t="n">
+        <v>402</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>49750</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>14.46%</t>
-        </is>
+          <t>14.13%</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>13220</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>형들  나도 평탄 33000원 1억2...[5] / 오늘자 수급 동향[6] / 3시  공시 설명 요청하신분 / 거래  1조7천억터지고  공시호재가나왓는데도[1]</t>
+          <t>15.51%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Positive (51%)</t>
+          <t>평단14350.[2] / 신고가를 기록해도 기분 드럽게 만드네....[1] / 어이가 없노 ㅋ[3] / 쏠리드 공략비법을 공개한다[2]</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>오늘, 진짜, 태양광</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
+          <t>Negative (67%)</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>신고가를, 기록해도, 기분, 드럽게, 만드네</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>[{'title': '오늘자 수급 동향[6]', 'date': '2026.03.20 16:24', 'views': '725', 'likes': '19', 'dislikes': '4', 'link': '/item/board_read.naver?code=009830&amp;nid=415513825&amp;page=4', 'score': 1295}, {'title': '머스크형 한마디만 해줘', 'date': '2026.03.20 18:14', 'views': '71', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=009830&amp;nid=415520777&amp;page=2', 'score': 611}, {'title': '거래  1조7천억터지고  공시호재가나왓는데도[1]', 'date': '2026.03.20 15:21', 'views': '260', 'likes': '17', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415506517&amp;page=8', 'score': 770}, {'title': '오늘 개미 다 털렸네', 'date': '2026.03.20 18:39', 'views': '52', 'likes': '15', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415522017&amp;page=2', 'score': 502}, {'title': '전에도 말했듯이 10만은 무조건 간다', 'date': '2026.03.20 18:12', 'views': '78', 'likes': '15', 'dislikes': '5', 'link': '/item/board_read.naver?code=009830&amp;nid=415520665&amp;page=2', 'score': 528}, {'title': '여수산단의 구조개편안', 'date': '2026.03.20 17:37', 'views': '184', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=009830&amp;nid=415518711&amp;page=3', 'score': 634}, {'title': '형들  나도 평탄 33000원 1억2...[5]', 'date': '2026.03.20 17:14', 'views': '918', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=009830&amp;nid=415517307&amp;page=3', 'score': 1368}, {'title': '3시  공시 설명 요청하신분', 'date': '2026.03.20 16:52', 'views': '470', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=009830&amp;nid=415515759&amp;page=4', 'score': 920}, {'title': '56800에 안판 내손이 웬수지', 'date': '2026.03.20 11:15', 'views': '38', 'likes': '15', 'dislikes': '0', 'link': '/item/board_read.naver?code=009830&amp;nid=415467886&amp;page=28', 'score': 488}, {'title': '여수건 해결한다잖아.', 'date': '2026.03.20 18:12', 'views': '201', 'likes': '14', 'dislikes': '1', 'link': '/item/board_read.naver?code=009830&amp;nid=415520644&amp;page=3', 'score': 621}]</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>[{'title': '신고가를 기록해도 기분 드럽게 만드네....[1]', 'date': '2026.03.20 14:43', 'views': '95', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415500455&amp;page=1', 'body': '', 'score': 395}, {'title': '평단14350.[2]', 'date': '2026.03.20 14:04', 'views': '146', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415494260&amp;page=3', 'body': '', 'score': 416}, {'title': '기가 막히게 털고 나가네~~[1]', 'date': '2026.03.20 14:05', 'views': '86', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415494364&amp;page=2', 'body': '', 'score': 326}, {'title': '주가조작 아님?[1]', 'date': '2026.03.20 12:08', 'views': '51', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415476934&amp;page=11', 'body': '', 'score': 261}, {'title': '내가 잘못했다[2]', 'date': '2026.03.20 14:03', 'views': '77', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415494065&amp;page=3', 'body': '', 'score': 257}, {'title': '13시 10분 현재 상황.', 'date': '2026.03.20 13:13', 'views': '121', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415486290&amp;page=5', 'body': '', 'score': 301}, {'title': '적당히 해야지', 'date': '2026.03.20 12:07', 'views': '37', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=050890&amp;nid=415476873&amp;page=11', 'body': '', 'score': 217}, {'title': '어제 올린글 다시 한번', 'date': '2026.03.20 09:55', 'views': '145', 'likes': '6', 'dislikes': '4', 'link': '/item/board_read.naver?code=050890&amp;nid=415451724&amp;page=19', 'body': '', 'score': 325}, {'title': '어이가 없노 ㅋ[3]', 'date': '2026.03.20 09:24', 'views': '196', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415443936&amp;page=20', 'body': '', 'score': 376}, {'title': '쏠리드 공략비법을 공개한다[2]', 'date': '2026.03.20 14:58', 'views': '179', 'likes': '5', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415502847&amp;page=1', 'body': '', 'score': 329}]</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>050890</t>
         </is>
       </c>
     </row>
@@ -2658,69 +2896,77 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대성에너지</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>109600</v>
+        <v>11120</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>+3.10%</t>
+          <t>+2.11%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>730</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>24.46%</t>
-        </is>
+        <v>-0.99</v>
+      </c>
+      <c r="G31" t="n">
+        <v>111</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>106300</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>24.24%</t>
-        </is>
+      <c r="J31" t="n">
+        <v>9770</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>주식이 가장 크게 상승하는 시점은 / 주말에 발표나면  ~![1] / 110,000다와간다[1] / 우리 두빌이가 그렇게 애를 태우더니[3]</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Positive (66%)</t>
+          <t>[대성에너지 실적발표] 창사이래 최대실적 발표 / 브랜트유 급반등~107달러 돌파~107.39[1] / 오늘은 이놈이 가스 대장 잡을 것이다 / 3만까지 가는주식이다[1]</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>오늘, 두빌, ㅋㅋ</t>
-        </is>
-      </c>
-      <c r="N31" t="n">
+          <t>Positive (60%)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>브랜트유, 급반등, 107달러, 돌파, 실적발표</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>[{'title': '주식이 가장 크게 상승하는 시점은', 'date': '2026.03.20 17:17', 'views': '413', 'likes': '32', 'dislikes': '2', 'link': '/item/board_read.naver?code=034020&amp;nid=415517501&amp;page=3', 'score': 1373}, {'title': '110,000다와간다[1]', 'date': '2026.03.20 16:17', 'views': '376', 'likes': '23', 'dislikes': '3', 'link': '/item/board_read.naver?code=034020&amp;nid=415513276&amp;page=4', 'score': 1066}, {'title': '주말에 발표나면  ~![1]', 'date': '2026.03.20 16:16', 'views': '621', 'likes': '23', 'dislikes': '8', 'link': '/item/board_read.naver?code=034020&amp;nid=415513252&amp;page=4', 'score': 1311}, {'title': '월욜 갭상승 120000원 시작', 'date': '2026.03.20 18:12', 'views': '79', 'likes': '21', 'dislikes': '4', 'link': '/item/board_read.naver?code=034020&amp;nid=415520661&amp;page=2', 'score': 709}, {'title': '우리 두빌이가 그렇게 애를 태우더니[3]', 'date': '2026.03.20 17:13', 'views': '407', 'likes': '20', 'dislikes': '0', 'link': '/item/board_read.naver?code=034020&amp;nid=415517193&amp;page=3', 'score': 1007}, {'title': '삼전보다 30만원대 먼저 가겠다 ~![1]', 'date': '2026.03.20 18:37', 'views': '256', 'likes': '19', 'dislikes': '2', 'link': '/item/board_read.naver?code=034020&amp;nid=415521912&amp;page=2', 'score': 826}, {'title': '천정 열렸네...슈팅간다', 'date': '2026.03.20 10:39', 'views': '90', 'likes': '19', 'dislikes': '2', 'link': '/item/board_read.naver?code=034020&amp;nid=415460931&amp;page=29', 'score': 660}, {'title': '두산에너빌리티를', 'date': '2026.03.20 16:48', 'views': '116', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=034020&amp;nid=415515435&amp;page=4', 'score': 656}, {'title': '오늘로 개미 매물 전멸[2]', 'date': '2026.03.20 15:17', 'views': '265', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=034020&amp;nid=415505727&amp;page=6', 'score': 805}, {'title': '그동안 억눌렸던거 이제 미친듯이 날라간다[4]', 'date': '2026.03.20 18:22', 'views': '325', 'likes': '17', 'dislikes': '5', 'link': '/item/board_read.naver?code=034020&amp;nid=415521133&amp;page=2', 'score': 835}]</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>[{'title': '브랜트유 급반등~107달러 돌파~107.39[1]', 'date': '2026.03.20 11:43', 'views': '78', 'likes': '10', 'dislikes': '4', 'link': '/item/board_read.naver?code=117580&amp;nid=415473003&amp;page=3', 'body': '', 'score': 378}, {'title': '[대성에너지 실적발표] 창사이래 최대실적 발표', 'date': '2026.03.20 10:52', 'views': '206', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415463626&amp;page=3', 'body': '', 'score': 506}, {'title': '오늘은 이놈이 가스 대장 잡을 것이다', 'date': '2026.03.20 08:20', 'views': '36', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415432432&amp;page=6', 'body': '', 'score': 306}, {'title': '유럽 천연가스 14% 급등 마감.', 'date': '2026.03.20 08:40', 'views': '47', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=117580&amp;nid=415435032&amp;page=5', 'body': '', 'score': 257}, {'title': '쩜상이겠지[1]', 'date': '2026.03.20 08:25', 'views': '32', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=117580&amp;nid=415433092&amp;page=6', 'body': '', 'score': 242}, {'title': 'Sk가스 10프로 상승중', 'date': '2026.03.20 08:02', 'views': '37', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415430159&amp;page=6', 'body': '', 'score': 247}, {'title': '3만까지 가는주식이다[1]', 'date': '2026.03.20 09:28', 'views': '126', 'likes': '6', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415444970&amp;page=4', 'body': '', 'score': 306}, {'title': '가스주대장 상한가간다.[2]', 'date': '2026.03.20 09:19', 'views': '117', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=117580&amp;nid=415442490&amp;page=5', 'body': '', 'score': 297}, {'title': 'ㅋㅋ 가스주떡락  장전에팔음 나이스', 'date': '2026.03.20 08:42', 'views': '36', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=117580&amp;nid=415435264&amp;page=5', 'body': '', 'score': 216}, {'title': '오빠 벌써끝났어..?[2]', 'date': '2026.03.20 10:07', 'views': '95', 'likes': '5', 'dislikes': '1', 'link': '/item/board_read.naver?code=117580&amp;nid=415454663&amp;page=4', 'body': '', 'score': 245}]</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>117580</t>
         </is>
       </c>
     </row>
@@ -2732,69 +2978,77 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>현대ADM</t>
+          <t>차백신연구소</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14790</v>
+        <v>4130</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>+2.78%</t>
+          <t>+1.10%</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>800</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>1.32%</t>
-        </is>
+        <v>-0.52</v>
+      </c>
+      <c r="G32" t="n">
+        <v>604</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>14390</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>1.21%</t>
-        </is>
+      <c r="J32" t="n">
+        <v>3145</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>ADM 3개월 후 가격을 AI에게물어보앗습니다...[4] / 주포형 욕해서 미안해[4] / 일단 2만은 무조건 찍을거 같은데[2] / 오늘 시외 거래가 마지막 최저 거래금액이다[2]</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Negative (56%)</t>
+          <t>--현재+30%상한가=매수9억원----꼭...꼭...[1] / 소룩스랑 아리바이오 합병 거절당해서 여기...[1] / 계약금지급완료-소룩스합병때1조넘김[2] / 이러다</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>오늘, 진짜, 시외</t>
-        </is>
-      </c>
-      <c r="N32" t="n">
+          <t>Negative (55%)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>합병, 나는, 주포, 좋아보이는데, 매수9억원</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>[{'title': '일단 2만은 무조건 찍을거 같은데[2]', 'date': '2026.03.20 16:49', 'views': '203', 'likes': '34', 'dislikes': '4', 'link': '/item/board_read.naver?code=187660&amp;nid=415515525&amp;page=3', 'score': 1223}, {'title': '증시 역사상 더큰 재료 없다[1]', 'date': '2026.03.20 17:29', 'views': '182', 'likes': '31', 'dislikes': '3', 'link': '/item/board_read.naver?code=187660&amp;nid=415518227&amp;page=2', 'score': 1112}, {'title': '주포형 욕해서 미안해[4]', 'date': '2026.03.20 15:45', 'views': '375', 'likes': '31', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415509975&amp;page=4', 'score': 1305}, {'title': '오늘 시외 거래가 마지막 최저 거래금액이다[2]', 'date': '2026.03.20 17:32', 'views': '304', 'likes': '30', 'dislikes': '6', 'link': '/item/board_read.naver?code=187660&amp;nid=415518422&amp;page=2', 'score': 1204}, {'title': 'ADM 3개월 후 가격을 AI에게물어보앗습니다...[4]', 'date': '2026.03.20 17:24', 'views': '539', 'likes': '30', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415517935&amp;page=2', 'score': 1439}, {'title': '진짜 사명변경!', 'date': '2026.03.20 16:54', 'views': '229', 'likes': '28', 'dislikes': '4', 'link': '/item/board_read.naver?code=187660&amp;nid=415515909&amp;page=2', 'score': 1069}, {'title': '털리고 털려서 배워라', 'date': '2026.03.20 17:37', 'views': '221', 'likes': '26', 'dislikes': '2', 'link': '/item/board_read.naver?code=187660&amp;nid=415518715&amp;page=1', 'score': 1001}, {'title': '현재 홈피의 페니트리움 내용', 'date': '2026.03.20 18:53', 'views': '444', 'likes': '25', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415522712&amp;page=1', 'score': 1194}, {'title': '이런~~[1]', 'date': '2026.03.20 17:30', 'views': '171', 'likes': '25', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415518268&amp;page=2', 'score': 921}, {'title': '●●오늘부로 앱솔루리 페바사&amp;혐바사는 각...[1]', 'date': '2026.03.20 18:36', 'views': '313', 'likes': '24', 'dislikes': '1', 'link': '/item/board_read.naver?code=187660&amp;nid=415521885&amp;page=1', 'score': 1033}]</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>[{'title': '--현재+30%상한가=매수9억원----꼭...꼭...[1]', 'date': '2026.03.20 08:45', 'views': '69', 'likes': '21', 'dislikes': '1', 'link': '/item/board_read.naver?code=261780&amp;nid=415435652&amp;page=30', 'body': '', 'score': 699}, {'title': '이러다', 'date': '2026.03.20 14:51', 'views': '26', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=261780&amp;nid=415501726&amp;page=7', 'body': '', 'score': 386}, {'title': '소룩스랑 아리바이오 합병 거절당해서 여기...[1]', 'date': '2026.03.20 09:49', 'views': '132', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=261780&amp;nid=415450437&amp;page=25', 'body': '', 'score': 432}, {'title': '나는 주포 좋아보이는데..', 'date': '2026.03.20 14:25', 'views': '109', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=261780&amp;nid=415497682&amp;page=9', 'body': '', 'score': 349}, {'title': '나는 주포 좋아보이는데..', 'date': '2026.03.20 14:25', 'views': '109', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=261780&amp;nid=415497682&amp;page=10', 'body': '', 'score': 349}, {'title': '피곤하다', 'date': '2026.03.20 13:23', 'views': '22', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=261780&amp;nid=415487938&amp;page=14', 'body': '', 'score': 262}, {'title': '형이 딱 말해준다[1]', 'date': '2026.03.20 10:55', 'views': '97', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=261780&amp;nid=415464175&amp;page=21', 'body': '', 'score': 337}, {'title': '계약금지급완료-소룩스합병때1조넘김[2]', 'date': '2026.03.20 08:34', 'views': '160', 'likes': '8', 'dislikes': '3', 'link': '/item/board_read.naver?code=261780&amp;nid=415434243&amp;page=30', 'body': '', 'score': 400}, {'title': '세계최초 먹는 치매약 아리바이오와 합병', 'date': '2026.03.20 08:25', 'views': '80', 'likes': '8', 'dislikes': '3', 'link': '/item/board_read.naver?code=261780&amp;nid=415433058&amp;page=30', 'body': '', 'score': 320}, {'title': '형이알려줄께! 오늘이 젤저점이다 가만히 있어라[1]', 'date': '2026.03.20 12:10', 'views': '64', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=261780&amp;nid=415477284&amp;page=18', 'body': '', 'score': 274}]</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>261780</t>
         </is>
       </c>
     </row>
@@ -2806,69 +3060,77 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>대성에너지</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11140</v>
+        <v>28625</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>126</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0.62%</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>284</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
+          <t>34.05%</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>10890</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+      <c r="J33" t="n">
+        <v>29100</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>[대성에너지 실적발표] 창사이래 최대실적 발표 / 카타르 파괴 &amp; 우크라-러시아종전[1] / 브랜트유 급반등~107달러 돌파~107.39[1] / 오늘은 이놈이 가스 대장 잡을 것이다</t>
+          <t>34.05%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Positive (51%)</t>
+          <t>시세 조종으로 금감원 민원 접수함[1] / 놀랍다 수주 호재가 떴는데[1] / 원래[1] / 3800억 계약공시에도[1]</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>가스, 카타르, 오늘</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
+          <t>Negative (51%)</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>시세, 조종으로, 금감원, 민원, 수주</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>[{'title': '카타르 파괴 &amp; 우크라-러시아종전[1]', 'date': '2026.03.20 17:03', 'views': '162', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=117580&amp;nid=415516500&amp;page=1', 'score': 462}, {'title': '브랜트유 급반등~107달러 돌파~107.39[1]', 'date': '2026.03.20 11:43', 'views': '81', 'likes': '10', 'dislikes': '4', 'link': '/item/board_read.naver?code=117580&amp;nid=415473003&amp;page=4', 'score': 381}, {'title': '[대성에너지 실적발표] 창사이래 최대실적 발표', 'date': '2026.03.20 10:52', 'views': '209', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415463626&amp;page=4', 'score': 509}, {'title': '오늘은 이놈이 가스 대장 잡을 것이다', 'date': '2026.03.20 08:20', 'views': '38', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415432432&amp;page=6', 'score': 308}, {'title': '유럽 천연가스 14% 급등 마감.', 'date': '2026.03.20 08:40', 'views': '49', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=117580&amp;nid=415435032&amp;page=6', 'score': 259}, {'title': '쩜상이겠지[1]', 'date': '2026.03.20 08:25', 'views': '34', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=117580&amp;nid=415433092&amp;page=6', 'score': 244}, {'title': 'Sk가스 10프로 상승중', 'date': '2026.03.20 08:02', 'views': '39', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415430159&amp;page=7', 'score': 249}, {'title': '3만까지 가는주식이다[1]', 'date': '2026.03.20 09:28', 'views': '128', 'likes': '6', 'dislikes': '2', 'link': '/item/board_read.naver?code=117580&amp;nid=415444970&amp;page=5', 'score': 308}, {'title': '가스주대장 상한가간다.[2]', 'date': '2026.03.20 09:19', 'views': '119', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=117580&amp;nid=415442490&amp;page=5', 'score': 299}, {'title': 'ㅋㅋ 가스주떡락  장전에팔음 나이스', 'date': '2026.03.20 08:42', 'views': '38', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=117580&amp;nid=415435264&amp;page=6', 'score': 218}]</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>117580</t>
+          <t>[{'title': '시세 조종으로 금감원 민원 접수함[1]', 'date': '2026.03.20 09:31', 'views': '79', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415445921&amp;page=11', 'body': '', 'score': 469}, {'title': '놀랍다 수주 호재가 떴는데[1]', 'date': '2026.03.20 09:06', 'views': '105', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415439047&amp;page=13', 'body': '', 'score': 465}, {'title': '원래[1]', 'date': '2026.03.20 08:15', 'views': '100', 'likes': '12', 'dislikes': '2', 'link': '/item/board_read.naver?code=010140&amp;nid=415431782&amp;page=14', 'body': '', 'score': 460}, {'title': 'FLNG 수주좀 발표해라 지금 타이밍 기가막히...', 'date': '2026.03.20 10:07', 'views': '53', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415454535&amp;page=10', 'body': '', 'score': 383}, {'title': '정말로', 'date': '2026.03.20 11:05', 'views': '33', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415466073&amp;page=6', 'body': '', 'score': 333}, {'title': '너도 10%이상 급등하는 것 좀 보여...', 'date': '2026.03.20 10:25', 'views': '22', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=010140&amp;nid=415458420&amp;page=8', 'body': '', 'score': 322}, {'title': '얼마나', 'date': '2026.03.20 10:23', 'views': '24', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415458118&amp;page=8', 'body': '', 'score': 324}, {'title': '3800억 계약공시에도[1]', 'date': '2026.03.20 09:32', 'views': '110', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=010140&amp;nid=415446064&amp;page=11', 'body': '', 'score': 410}, {'title': '주총날인데[1]', 'date': '2026.03.20 14:38', 'views': '98', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415499656&amp;page=1', 'body': '', 'score': 368}, {'title': '뭐가 문젤까?', 'date': '2026.03.20 11:07', 'views': '46', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415466392&amp;page=5', 'body': '', 'score': 316}]</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -2880,69 +3142,77 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>쏠리드</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13120</v>
+        <v>7410</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>+1.71%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>422</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>12.90%</t>
-        </is>
+        <v>-0.02</v>
+      </c>
+      <c r="G34" t="n">
+        <v>211</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
+          <t>5.73%</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>12900</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>14.13%</t>
-        </is>
+      <c r="J34" t="n">
+        <v>7030</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>이번주도 고생많으셨습니다 / 12000원대 눌러주면 꾹꾹 담아라[2] / 다음주 매물다먹어버리고 상갈듯 / 평단14350.[2]</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Negative (67%)</t>
+          <t>제가 몇달 전에 빛과전자랑 대한광통신 반반씩...[2] / 난 잘 가고있는거라 생각하는데..[3] / 모든 파트의 대장주가 힘을 응축하면 그 폭발...[1] / 재미로 보는 프로그램 매동[2]</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>오늘, 쏠리드, 프로그램</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
+          <t>Positive (60%)</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>몇달, 전에, 빛과전자랑, 반반씩, 통신관련주중에</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>[{'title': '이번주도 고생많으셨습니다', 'date': '2026.03.20 17:33', 'views': '142', 'likes': '16', 'dislikes': '3', 'link': '/item/board_read.naver?code=050890&amp;nid=415518484&amp;page=1', 'score': 622}, {'title': '다음주 매물다먹어버리고 상갈듯', 'date': '2026.03.20 17:59', 'views': '95', 'likes': '12', 'dislikes': '6', 'link': '/item/board_read.naver?code=050890&amp;nid=415519976&amp;page=1', 'score': 455}, {'title': '신고가를 기록해도 기분 드럽게 만드네....[1]', 'date': '2026.03.20 14:43', 'views': '115', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415500455&amp;page=4', 'score': 415}, {'title': '곧 큰형님들 몸푸십니다[1]', 'date': '2026.03.20 17:59', 'views': '150', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=050890&amp;nid=415519988&amp;page=1', 'score': 420}, {'title': '이런주식은 절대로[1]', 'date': '2026.03.20 15:44', 'views': '58', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=050890&amp;nid=415509871&amp;page=3', 'score': 328}, {'title': '평단14350.[2]', 'date': '2026.03.20 14:04', 'views': '157', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415494260&amp;page=5', 'score': 427}, {'title': '뭐 겁나 오를것처럼 말하는대 그럼 로봇주나 반...', 'date': '2026.03.20 18:42', 'views': '124', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415522129&amp;page=1', 'score': 364}, {'title': '기가 막히게 털고 나가네~~[1]', 'date': '2026.03.20 14:05', 'views': '90', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415494364&amp;page=4', 'score': 330}, {'title': '12000원대 눌러주면 꾹꾹 담아라[2]', 'date': '2026.03.20 17:23', 'views': '309', 'likes': '7', 'dislikes': '7', 'link': '/item/board_read.naver?code=050890&amp;nid=415517908&amp;page=1', 'score': 519}, {'title': '참나!', 'date': '2026.03.20 17:08', 'views': '53', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=050890&amp;nid=415516847&amp;page=1', 'score': 263}]</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>050890</t>
+          <t>[{'title': '제가 몇달 전에 빛과전자랑 대한광통신 반반씩...[2]', 'date': '2026.03.20 11:51', 'views': '409', 'likes': '16', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415474378&amp;page=5', 'body': '', 'score': 889}, {'title': '지금 통신관련주중에 투경은 이것만이다[1]', 'date': '2026.03.20 10:36', 'views': '148', 'likes': '16', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415460440&amp;page=7', 'body': '', 'score': 628}, {'title': '모든 파트의 대장주가 힘을 응축하면 그 폭발...[1]', 'date': '2026.03.20 11:56', 'views': '231', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=010170&amp;nid=415475108&amp;page=5', 'body': '', 'score': 681}, {'title': '미국 광통신종목 루멘템 홀딩스', 'date': '2026.03.20 08:00', 'views': '102', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=010170&amp;nid=415429974&amp;page=11', 'body': '', 'score': 552}, {'title': '난 잘 가고있는거라 생각하는데..[3]', 'date': '2026.03.20 12:42', 'views': '337', 'likes': '14', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415481694&amp;page=5', 'body': '', 'score': 757}, {'title': '재미로 보는 프로그램 매동[2]', 'date': '2026.03.20 11:22', 'views': '289', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415469116&amp;page=6', 'body': '', 'score': 649}, {'title': '주식투자에 왕도는 신도 모릅니다..이리저리 ...[1]', 'date': '2026.03.20 12:43', 'views': '158', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415481823&amp;page=5', 'body': '', 'score': 488}, {'title': '저수지로 들어간 물량은 절대 안나온다 ㅎ[1]', 'date': '2026.03.20 12:02', 'views': '112', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=010170&amp;nid=415476057&amp;page=5', 'body': '', 'score': 442}, {'title': '매수후 푸근하게 기다리시길', 'date': '2026.03.20 11:42', 'views': '116', 'likes': '11', 'dislikes': '3', 'link': '/item/board_read.naver?code=010170&amp;nid=415472718&amp;page=5', 'body': '', 'score': 446}, {'title': '효자종목 대광이는 걱정1도 없습니다~^^[1]', 'date': '2026.03.20 11:23', 'views': '138', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=010170&amp;nid=415469378&amp;page=6', 'body': '', 'score': 468}]</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2954,69 +3224,77 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한온시스템</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4140</v>
+        <v>3050</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>214</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>6.92%</t>
-        </is>
+        <v>-0.05</v>
+      </c>
+      <c r="G35" t="n">
+        <v>396</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
+          <t>2.39%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>4110</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>6.87%</t>
-        </is>
+      <c r="J35" t="n">
+        <v>2915</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>마음편하게 주식합시다[1] / 골드만 삭스 280만주 매수 캬[2] / 형님들 제가 누누히 말하지만 이종목이[7] / 공매 세력들 많이 쫄리나본데?? ㅋㅋㅋ[2]</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Negative (54%)</t>
+          <t>장금상선 지분 50% 매각이 호재인 이유 설...[2] / 형들 잘봐바 이게 왜 안가는지 / 장금마리타임 지분 MSC 매각 이슈는.... / -4%시작 -6%찍고 +30%가능함?[2]</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>어제, 오늘, 한온</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
+          <t>Positive (53%)</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>지분, 장금상선, 매각이, 호재인, 이유</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>[{'title': '마음편하게 주식합시다[1]', 'date': '2026.03.20 10:17', 'views': '172', 'likes': '18', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415456883&amp;page=7', 'score': 712}, {'title': '공매 세력들 많이 쫄리나본데?? ㅋㅋㅋ[2]', 'date': '2026.03.20 17:34', 'views': '203', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=018880&amp;nid=415518518&amp;page=1', 'score': 653}, {'title': '월욜 시초가 갭상승[3]', 'date': '2026.03.20 17:59', 'views': '164', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=018880&amp;nid=415520015&amp;page=1', 'score': 554}, {'title': '골드만 삭스 280만주 매수 캬[2]', 'date': '2026.03.20 16:29', 'views': '300', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=018880&amp;nid=415514180&amp;page=1', 'score': 690}, {'title': '공매놈들 발등에 불남', 'date': '2026.03.20 15:53', 'views': '79', 'likes': '12', 'dislikes': '2', 'link': '/item/board_read.naver?code=018880&amp;nid=415510952&amp;page=2', 'score': 439}, {'title': '형님들 제가 누누히 말하지만 이종목이[7]', 'date': '2026.03.20 18:23', 'views': '330', 'likes': '11', 'dislikes': '6', 'link': '/item/board_read.naver?code=018880&amp;nid=415521240&amp;page=1', 'score': 660}, {'title': '내첫차는 아반떼[3]', 'date': '2026.03.20 17:55', 'views': '213', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=018880&amp;nid=415519711&amp;page=1', 'score': 543}, {'title': '세계 경제지표 골드만삭스  매입만으로 신뢰...', 'date': '2026.03.20 17:24', 'views': '114', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=018880&amp;nid=415517956&amp;page=1', 'score': 444}, {'title': '골드만이 본격적으로 사려고 맘 먹었나보네.', 'date': '2026.03.20 15:44', 'views': '121', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415509917&amp;page=2', 'score': 451}, {'title': '주식 모르는 작자들 글 쓰지맙시다~ 다른 종목 ...[4]', 'date': '2026.03.20 09:15', 'views': '117', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415441436&amp;page=10', 'score': 447}]</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>018880</t>
+          <t>[{'title': '오늘은[1]', 'date': '2026.03.20 10:52', 'views': '63', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=003280&amp;nid=415463717&amp;page=12', 'body': '', 'score': 423}, {'title': '장금상선 지분 50% 매각이 호재인 이유 설...[2]', 'date': '2026.03.20 08:59', 'views': '318', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=003280&amp;nid=415437505&amp;page=17', 'body': '', 'score': 678}, {'title': '-4%시작 -6%찍고 +30%가능함?[2]', 'date': '2026.03.20 11:31', 'views': '135', 'likes': '10', 'dislikes': '5', 'link': '/item/board_read.naver?code=003280&amp;nid=415470964&amp;page=10', 'body': '', 'score': 435}, {'title': '오후장 빨간기둥 원하면 개추', 'date': '2026.03.20 10:46', 'views': '21', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=003280&amp;nid=415462474&amp;page=12', 'body': '', 'score': 321}, {'title': '이곳이 싫으면 조용히 떠나라', 'date': '2026.03.20 12:40', 'views': '24', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=003280&amp;nid=415481462&amp;page=8', 'body': '', 'score': 294}, {'title': '교보, ls 창구[1]', 'date': '2026.03.20 11:42', 'views': '93', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=003280&amp;nid=415472781&amp;page=10', 'body': '', 'score': 363}, {'title': '형들 잘봐바 이게 왜 안가는지', 'date': '2026.03.20 10:14', 'views': '302', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=003280&amp;nid=415456141&amp;page=13', 'body': '', 'score': 572}, {'title': '단일가매매끝나가네', 'date': '2026.03.20 14:06', 'views': '73', 'likes': '8', 'dislikes': '3', 'link': '/item/board_read.naver?code=003280&amp;nid=415494506&amp;page=4', 'body': '', 'score': 313}, {'title': '지금 상승은 뻥카다 속지 마라~~~~', 'date': '2026.03.20 13:55', 'views': '40', 'likes': '8', 'dislikes': '6', 'link': '/item/board_read.naver?code=003280&amp;nid=415492837&amp;page=4', 'body': '', 'score': 280}, {'title': '장금마리타임 지분 MSC 매각 이슈는....', 'date': '2026.03.20 13:51', 'views': '202', 'likes': '8', 'dislikes': '3', 'link': '/item/board_read.naver?code=003280&amp;nid=415492375&amp;page=4', 'body': '', 'score': 442}]</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>003280</t>
         </is>
       </c>
     </row>
@@ -3028,69 +3306,77 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>7440</v>
+        <v>200250</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>224</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>4.88%</t>
-        </is>
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G36" t="n">
+        <v>800</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>7390</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>5.73%</t>
-        </is>
+          <t>49.53%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>208500</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>애들아...[8] / 제가 몇달 전에 빛과전자랑 대한광통신 반반씩 ...[2] / 4월 24일 '15,000원' 고지 점령, 과...[2] / 난 잘 가고있는거라 생각하는데..[3]</t>
+          <t>49.60%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Positive (61%)</t>
+          <t>201000원. 15억 쓸어담았다 **[13] / 아니 진짜 이해가 안되는게[1] / 투매가 없는게 바닥징후다.. 외인이 숏을 몰빵...[1] / 바닥 같은데  ㅋㅋ[2]</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>오늘, 대한광통신, 투경</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>[{'title': '애들아...[8]', 'date': '2026.03.20 15:35', 'views': '725', 'likes': '42', 'dislikes': '6', 'link': '/item/board_read.naver?code=010170&amp;nid=415508574&amp;page=1', 'score': 1985}, {'title': '제가 몇달 전에 빛과전자랑 대한광통신 반반씩 ...[2]', 'date': '2026.03.20 11:51', 'views': '417', 'likes': '16', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415474378&amp;page=6', 'score': 897}, {'title': '지금 통신관련주중에 투경은 이것만이다[1]', 'date': '2026.03.20 10:36', 'views': '154', 'likes': '16', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415460440&amp;page=7', 'score': 634}, {'title': '모든 파트의 대장주가 힘을 응축하면 그 폭발력...[1]', 'date': '2026.03.20 11:56', 'views': '238', 'likes': '15', 'dislikes': '2', 'link': '/item/board_read.naver?code=010170&amp;nid=415475108&amp;page=6', 'score': 688}, {'title': '미국 광통신종목 루멘템 홀딩스', 'date': '2026.03.20 08:00', 'views': '108', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=010170&amp;nid=415429974&amp;page=12', 'score': 558}, {'title': "4월 24일 '15,000원' 고지 점령, 과...[2]", 'date': '2026.03.20 15:19', 'views': '413', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=010170&amp;nid=415506164&amp;page=2', 'score': 833}, {'title': '난 잘 가고있는거라 생각하는데..[3]', 'date': '2026.03.20 12:42', 'views': '350', 'likes': '14', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415481694&amp;page=5', 'score': 770}, {'title': '재미로 보는 프로그램 매동[2]', 'date': '2026.03.20 11:22', 'views': '295', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415469116&amp;page=7', 'score': 655}, {'title': '털리는 모지리들이 적당히 있는게 가볍게 수월하...[2]', 'date': '2026.03.20 17:03', 'views': '308', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=010170&amp;nid=415516549&amp;page=1', 'score': 638}, {'title': '주식투자에 왕도는 신도 모릅니다..이리저리 불...[1]', 'date': '2026.03.20 12:43', 'views': '162', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=010170&amp;nid=415481823&amp;page=5', 'score': 492}]</t>
-        </is>
+          <t>Negative (57%)</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>201000원, 15억, 투매가, 없는게, 외인이</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>12</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>[{'title': '201000원. 15억 쓸어담았다 **[13]', 'date': '2026.03.20 14:59', 'views': '140', 'likes': '12', 'dislikes': '5', 'link': '/item/board_read.naver?code=005930&amp;nid=415502975&amp;page=8', 'body': '', 'score': 500}, {'title': '투매가 없는게 바닥징후다.. 외인이 숏을 몰빵...[1]', 'date': '2026.03.20 15:00', 'views': '148', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415503095&amp;page=8', 'body': '', 'score': 478}, {'title': '바닥 같은데  ㅋㅋ[2]', 'date': '2026.03.20 14:56', 'views': '129', 'likes': '10', 'dislikes': '5', 'link': '/item/board_read.naver?code=005930&amp;nid=415502413&amp;page=9', 'body': '', 'score': 429}, {'title': '종가 205000원[2]', 'date': '2026.03.20 14:54', 'views': '97', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=005930&amp;nid=415502188&amp;page=9', 'body': '', 'score': 397}, {'title': '다음주 전고점 돌파 후 25만원[2]', 'date': '2026.03.20 14:45', 'views': '113', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415500770&amp;page=11', 'body': '', 'score': 413}, {'title': '아니 진짜 이해가 안되는게[1]', 'date': '2026.03.20 14:34', 'views': '191', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415499053&amp;page=14', 'body': '', 'score': 491}, {'title': '패배를 인정해라 JP모건[1]', 'date': '2026.03.20 15:02', 'views': '118', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415503416&amp;page=8', 'body': '', 'score': 388}, {'title': '★ 반도체) 샌디스크 신고가 27배 폭등: 삼...[1]', 'date': '2026.03.20 14:00', 'views': '96', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415493650&amp;page=25', 'body': '', 'score': 366}, {'title': "'李 비자금’ 방송한 전한길…강경 대응 예고에...", 'date': '2026.03.20 15:08', 'views': '35', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=005930&amp;nid=415504443&amp;page=6', 'body': '', 'score': 275}, {'title': '정신차려보니 어느새 바닥이 20만원.[1]', 'date': '2026.03.20 14:38', 'views': '101', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415499674&amp;page=13', 'body': '', 'score': 341}]</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -3102,69 +3388,69 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>한온시스템</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>28550</v>
+        <v>4100</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>320</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>33.97%</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>162</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
         <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>28500</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>34.05%</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>유증을[3] / 3779억원[1] / 시세 조종으로 금감원 민원 접수함[1] / 놀랍다 수주 호재가 떴는데[1]</t>
-        </is>
-      </c>
+      <c r="J37" t="n">
+        <v>4109</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Negative (56%)</t>
+          <t>마음편하게 주식합시다[1] / 한온 1등 먹었네.[1] / 주식 모르는 작자들 글 쓰지맙시다~ 다른 종목...[4] / 어제 시간외[3]</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>오늘, 삼중, ...</t>
-        </is>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>[{'title': '유증을[3]', 'date': '2026.03.20 17:29', 'views': '316', 'likes': '41', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415518245&amp;page=1', 'score': 1546}, {'title': '3779억원[1]', 'date': '2026.03.20 15:56', 'views': '97', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415511350&amp;page=2', 'score': 487}, {'title': '시세 조종으로 금감원 민원 접수함[1]', 'date': '2026.03.20 09:31', 'views': '82', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415445921&amp;page=13', 'score': 472}, {'title': '주총하면', 'date': '2026.03.20 16:31', 'views': '58', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=010140&amp;nid=415514368&amp;page=2', 'score': 418}, {'title': '놀랍다 수주 호재가 떴는데[1]', 'date': '2026.03.20 09:06', 'views': '108', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415439047&amp;page=15', 'score': 468}, {'title': '원래[1]', 'date': '2026.03.20 08:15', 'views': '103', 'likes': '12', 'dislikes': '2', 'link': '/item/board_read.naver?code=010140&amp;nid=415431782&amp;page=16', 'score': 463}, {'title': '삼중 주포 짠지야. 너만. 배불리 먹으면 안되 ...', 'date': '2026.03.20 17:27', 'views': '71', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415518112&amp;page=1', 'score': 401}, {'title': '와 걍 손절치니까 스트레스 안받음', 'date': '2026.03.20 16:42', 'views': '42', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415515080&amp;page=2', 'score': 372}, {'title': '아이구 감사합니다.', 'date': '2026.03.20 16:07', 'views': '70', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=010140&amp;nid=415512387&amp;page=2', 'score': 400}, {'title': 'FLNG 수주좀 발표해라 지금 타이밍...', 'date': '2026.03.20 10:07', 'views': '56', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=010140&amp;nid=415454535&amp;page=12', 'score': 386}]</t>
-        </is>
+          <t>Negative (64%)</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>마음편하게, 모르는, 작자들, 다른, 1등</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>5</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>[{'title': '마음편하게 주식합시다[1]', 'date': '2026.03.20 10:17', 'views': '167', 'likes': '18', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415456883&amp;page=4', 'body': '', 'score': 707}, {'title': '주식 모르는 작자들 글 쓰지맙시다~ 다른 종목...[4]', 'date': '2026.03.20 09:15', 'views': '113', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415441436&amp;page=7', 'body': '', 'score': 443}, {'title': '한온 1등 먹었네.[1]', 'date': '2026.03.20 08:16', 'views': '194', 'likes': '11', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415431925&amp;page=8', 'body': '', 'score': 524}, {'title': '데이터센터 냉각기술 전문기업되길', 'date': '2026.03.20 12:00', 'views': '46', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415475721&amp;page=3', 'body': '', 'score': 346}, {'title': '어제 시간외[3]', 'date': '2026.03.20 08:28', 'views': '122', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=018880&amp;nid=415433465&amp;page=8', 'body': '', 'score': 422}, {'title': '악재도 아닌 이미 선반영된 공시로…', 'date': '2026.03.20 11:53', 'views': '99', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=018880&amp;nid=415474648&amp;page=3', 'body': '', 'score': 369}, {'title': '갑자기[2]', 'date': '2026.03.20 10:16', 'views': '131', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=018880&amp;nid=415456515&amp;page=4', 'body': '', 'score': 371}, {'title': '돈이 돈을 번다고.....', 'date': '2026.03.20 09:26', 'views': '59', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415444423&amp;page=6', 'body': '', 'score': 299}, {'title': '1분기 실적 향상', 'date': '2026.03.20 10:38', 'views': '57', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415460808&amp;page=4', 'body': '', 'score': 237}, {'title': '도망치라는애들[1]', 'date': '2026.03.20 10:13', 'views': '57', 'likes': '6', 'dislikes': '0', 'link': '/item/board_read.naver?code=018880&amp;nid=415456020&amp;page=5', 'body': '', 'score': 237}]</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>018880</t>
         </is>
       </c>
     </row>
@@ -3176,69 +3462,77 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>차백신연구소</t>
+          <t>케이뱅크</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4080</v>
+        <v>6600</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>702</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>-0.05</v>
+      </c>
+      <c r="G38" t="n">
+        <v>406</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>4085</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>6950</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>고생들했어요 월요일부터 10연상갈꺼같습니다.[6] / 대박뉴스[4] / 세력도 모질지만[2] / --현재+30%상한가=매수9억원----꼭...꼭...[1]</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Negative (57%)</t>
+          <t>어우 힘들다[3] / 대국민 공모 사기극 / 31일 주총입니다 다들 연장 챙기죠[1] / 하 벌써 20% 마이너스</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>오늘, 아리바이오, ㅋㅋ</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
+          <t>Positive (55%)</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>어우, 대국민, 공모, 사기극, 어디까지내려가려나</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
         <v>1</v>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>[{'title': '고생들했어요 월요일부터 10연상갈꺼같습니다.[6]', 'date': '2026.03.20 18:05', 'views': '452', 'likes': '28', 'dislikes': '11', 'link': '/item/board_read.naver?code=261780&amp;nid=415520275&amp;page=1', 'score': 1292}, {'title': '--현재+30%상한가=매수9억원----꼭...꼭...[1]', 'date': '2026.03.20 08:45', 'views': '72', 'likes': '21', 'dislikes': '1', 'link': '/item/board_read.naver?code=261780&amp;nid=415435652&amp;page=35', 'score': 702}, {'title': '대박뉴스[4]', 'date': '2026.03.20 17:07', 'views': '379', 'likes': '19', 'dislikes': '3', 'link': '/item/board_read.naver?code=261780&amp;nid=415516776&amp;page=3', 'score': 949}, {'title': '세력도 모질지만[2]', 'date': '2026.03.20 19:08', 'views': '232', 'likes': '17', 'dislikes': '3', 'link': '/item/board_read.naver?code=261780&amp;nid=415523392&amp;page=1', 'score': 742}, {'title': '아리바이오, ADPD서 AR1001 ...[3]', 'date': '2026.03.20 16:27', 'views': '263', 'likes': '12', 'dislikes': '6', 'link': '/item/board_read.naver?code=261780&amp;nid=415514096&amp;page=4', 'score': 623}, {'title': '이러다', 'date': '2026.03.20 14:51', 'views': '28', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=261780&amp;nid=415501726&amp;page=14', 'score': 388}, {'title': '생각해 보니 딱딱 들어맞네[3]', 'date': '2026.03.20 18:52', 'views': '294', 'likes': '11', 'dislikes': '5', 'link': '/item/board_read.naver?code=261780&amp;nid=415522636&amp;page=1', 'score': 624}, {'title': '정상가격 1200~1300원대[1]', 'date': '2026.03.20 18:14', 'views': '281', 'likes': '11', 'dislikes': '11', 'link': '/item/board_read.naver?code=261780&amp;nid=415520771&amp;page=1', 'score': 611}, {'title': '현대도 상가구', 'date': '2026.03.20 17:20', 'views': '208', 'likes': '11', 'dislikes': '3', 'link': '/item/board_read.naver?code=261780&amp;nid=415517678&amp;page=2', 'score': 538}, {'title': '시외 물타다가 대주주되겠다', 'date': '2026.03.20 16:40', 'views': '38', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=261780&amp;nid=415514950&amp;page=4', 'score': 368}]</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>261780</t>
+          <t>[{'title': '어우 힘들다[3]', 'date': '2026.03.20 13:41', 'views': '93', 'likes': '20', 'dislikes': '4', 'link': '/item/board_read.naver?code=279570&amp;nid=415490849&amp;page=4', 'body': '', 'score': 693}, {'title': '대국민 공모 사기극', 'date': '2026.03.20 11:51', 'views': '48', 'likes': '20', 'dislikes': '2', 'link': '/item/board_read.naver?code=279570&amp;nid=415474338&amp;page=8', 'body': '', 'score': 648}, {'title': '어디까지내려가려나?[1]', 'date': '2026.03.20 11:50', 'views': '49', 'likes': '10', 'dislikes': '4', 'link': '/item/board_read.naver?code=279570&amp;nid=415474183&amp;page=8', 'body': '', 'score': 349}, {'title': '하 벌써 20% 마이너스', 'date': '2026.03.20 11:29', 'views': '53', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415470622&amp;page=9', 'body': '', 'score': 353}, {'title': '31일 주총입니다 다들 연장 챙기죠[1]', 'date': '2026.03.20 11:21', 'views': '65', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415469038&amp;page=9', 'body': '', 'score': 365}, {'title': '개사기주 입니다', 'date': '2026.03.20 12:49', 'views': '32', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=279570&amp;nid=415482785&amp;page=6', 'body': '', 'score': 302}, {'title': '우리은행.NH투자증권 사외이사 물러나야', 'date': '2026.03.20 14:14', 'views': '34', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415495994&amp;page=3', 'body': '', 'score': 274}, {'title': '국민청원', 'date': '2026.03.20 12:17', 'views': '41', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415478260&amp;page=7', 'body': '', 'score': 281}, {'title': '패가망신.', 'date': '2026.03.20 14:10', 'views': '26', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415495372&amp;page=3', 'body': '', 'score': 236}, {'title': 'Per높다고?', 'date': '2026.03.20 12:34', 'views': '29', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415480533&amp;page=7', 'body': '', 'score': 239}]</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>279570</t>
         </is>
       </c>
     </row>
@@ -3250,69 +3544,77 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>신성이엔지</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>199400</v>
+        <v>3025</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>800</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>49.52%</t>
-        </is>
+        <v>-2.23</v>
+      </c>
+      <c r="G39" t="n">
+        <v>149</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
+          <t>8.85%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>KOSPI</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>200500</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>49.53%</t>
-        </is>
+      <c r="J39" t="n">
+        <v>2990</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>800만주는 삼성생명+삼성화재가 판것.[1] / 오늘 잘 버텼네요 .[1] / 외인 10프로 나갔는데도 20만원[1] / 어차피 여기서 백날 떠들어봤자 ㅋ[2]</t>
+          <t>11.08%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Negative (68%)</t>
+          <t>5년만에 조금 손해보고 나왔다 / 금감원[2] / 팁 준다 / 저점높이고있죠잉</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>오늘, 월요일, 나스닥</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>[{'title': '이재명 지지율이 계속 오르는 이유.[1]', 'date': '2026.03.20 18:37', 'views': '67', 'likes': '14', 'dislikes': '8', 'link': '/item/board_read.naver?code=005930&amp;nid=415521895&amp;page=16', 'score': 487}, {'title': '▲금요일 밤 10시~ 일욜까지 뭔일이? ㅡ&gt;...[2]', 'date': '2026.03.20 17:02', 'views': '108', 'likes': '13', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415516432&amp;page=28', 'score': 498}, {'title': '반도체는 호황 불황사이클 반복 업종이다 ㅡ&gt;이...', 'date': '2026.03.20 16:54', 'views': '66', 'likes': '13', 'dislikes': '0', 'link': '/item/board_read.naver?code=005930&amp;nid=415515896&amp;page=29', 'score': 456}, {'title': '어차피 여기서 백날 떠들어봤자 ㅋ[2]', 'date': '2026.03.20 16:46', 'views': '134', 'likes': '13', 'dislikes': '5', 'link': '/item/board_read.naver?code=005930&amp;nid=415515347&amp;page=30', 'score': 524}, {'title': '외인 10프로 나갔는데도 20만원[1]', 'date': '2026.03.20 16:00', 'views': '169', 'likes': '13', 'dislikes': '2', 'link': '/item/board_read.naver?code=005930&amp;nid=415511806&amp;page=35', 'score': 559}, {'title': '800만주는 삼성생명+삼성화재가 판것.[1]', 'date': '2026.03.20 15:45', 'views': '356', 'likes': '13', 'dislikes': '6', 'link': '/item/board_read.naver?code=005930&amp;nid=415510008&amp;page=38', 'score': 746}, {'title': '월요일 급등이네', 'date': '2026.03.20 17:38', 'views': '93', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=005930&amp;nid=415518754&amp;page=23', 'score': 453}, {'title': '전쟁 imf 유사한것 올때는 뭐가최고 예금자 ...', 'date': '2026.03.20 17:08', 'views': '60', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415516866&amp;page=27', 'score': 420}, {'title': '오늘 잘 버텼네요 .[1]', 'date': '2026.03.20 16:36', 'views': '337', 'likes': '12', 'dislikes': '3', 'link': '/item/board_read.naver?code=005930&amp;nid=415514717&amp;page=31', 'score': 697}, {'title': '현재 삼전은 졸라쎈거임', 'date': '2026.03.20 16:19', 'views': '135', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=005930&amp;nid=415513503&amp;page=32', 'score': 495}]</t>
-        </is>
+          <t>Positive (72%)</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5년만에, 조금, 손해보고, 저점높이고있죠잉, 5년동안</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>2</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>[{'title': '5년만에 조금 손해보고 나왔다', 'date': '2026.03.20 11:31', 'views': '80', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=011930&amp;nid=415470896&amp;page=4', 'body': '', 'score': 380}, {'title': '저점높이고있죠잉', 'date': '2026.03.20 11:10', 'views': '57', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415466941&amp;page=4', 'body': '', 'score': 297}, {'title': '5년동안', 'date': '2026.03.20 12:36', 'views': '72', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415480849&amp;page=3', 'body': '', 'score': 282}, {'title': '금감원[2]', 'date': '2026.03.20 10:47', 'views': '140', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=011930&amp;nid=415462666&amp;page=4', 'body': '', 'score': 350}, {'title': '월요일최소20프로는갈듯', 'date': '2026.03.20 14:17', 'views': '88', 'likes': '6', 'dislikes': '4', 'link': '/item/board_read.naver?code=011930&amp;nid=415496446&amp;page=1', 'body': '', 'score': 268}, {'title': '프로그램 매수 금액이  양선으로 돌아섯다.', 'date': '2026.03.20 11:18', 'views': '66', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=011930&amp;nid=415468523&amp;page=4', 'body': '', 'score': 246}, {'title': '퇴계이황이', 'date': '2026.03.20 11:10', 'views': '33', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415466907&amp;page=4', 'body': '', 'score': 213}, {'title': '태양광 날아가는데 이놈만 빌빌대네', 'date': '2026.03.20 10:48', 'views': '71', 'likes': '6', 'dislikes': '2', 'link': '/item/board_read.naver?code=011930&amp;nid=415462725&amp;page=4', 'body': '', 'score': 251}, {'title': '오후장이 기대되는걸?', 'date': '2026.03.20 10:33', 'views': '61', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415459898&amp;page=4', 'body': '', 'score': 241}, {'title': '팁 준다', 'date': '2026.03.20 09:54', 'views': '168', 'likes': '6', 'dislikes': '5', 'link': '/item/board_read.naver?code=011930&amp;nid=415451641&amp;page=5', 'body': '', 'score': 348}]</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>011930</t>
         </is>
       </c>
     </row>
@@ -3324,69 +3626,77 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3030</v>
+        <v>28400</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-1.90%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>454</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2.40%</t>
-        </is>
+        <v>-2.95</v>
+      </c>
+      <c r="G40" t="n">
+        <v>526</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>3050</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2.39%</t>
-        </is>
+          <t>10.44%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>29300</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>장금상선·MSC 연합 ‘유조선 공룡’ 뜬다[1] / 장금상선 지분 50% 매각이 호재인 이유 설...[2] / 월요일부터[2] / 외국인도 기관도 담았네~~~[2]</t>
+          <t>13.39%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Positive (54%)</t>
+          <t>■페이퍼-증권가[8] / ■인연-팔로잉[14] / ■주식은-오르고..내리는건[7] / ■두빌-14만[2]</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>오늘, 이제, 단일가</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>[{'title': '장금상선·MSC 연합 ‘유조선 공룡’ 뜬다[1]', 'date': '2026.03.20 18:03', 'views': '250', 'likes': '19', 'dislikes': '5', 'link': '/item/board_read.naver?code=003280&amp;nid=415520181&amp;page=2', 'score': 820}, {'title': 'ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ전쟁 끝나봐라 운송전쟁이지', 'date': '2026.03.20 15:20', 'views': '94', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=003280&amp;nid=415506312&amp;page=4', 'score': 484}, {'title': '오늘은[1]', 'date': '2026.03.20 10:52', 'views': '66', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=003280&amp;nid=415463717&amp;page=15', 'score': 426}, {'title': '장금상선 지분 50% 매각이 호재인 이유 설...[2]', 'date': '2026.03.20 08:59', 'views': '320', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=003280&amp;nid=415437505&amp;page=20', 'score': 680}, {'title': '월요일부터[2]', 'date': '2026.03.20 18:03', 'views': '262', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=003280&amp;nid=415520188&amp;page=2', 'score': 592}, {'title': '다음주 바로 만원찍고 가시던가ㅋㅋ[1]', 'date': '2026.03.20 18:09', 'views': '142', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=003280&amp;nid=415520501&amp;page=1', 'score': 442}, {'title': '-4%시작 -6%찍고 +30%가능함?[2]', 'date': '2026.03.20 11:31', 'views': '138', 'likes': '10', 'dislikes': '5', 'link': '/item/board_read.naver?code=003280&amp;nid=415470964&amp;page=13', 'score': 438}, {'title': '오후장 빨간기둥 원하면 개추', 'date': '2026.03.20 10:46', 'views': '24', 'likes': '10', 'dislikes': '1', 'link': '/item/board_read.naver?code=003280&amp;nid=415462474&amp;page=15', 'score': 324}, {'title': '외국인도 기관도 담았네~~~[2]', 'date': '2026.03.20 18:23', 'views': '226', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=003280&amp;nid=415521198&amp;page=1', 'score': 496}, {'title': '이곳이 싫으면 조용히 떠나라', 'date': '2026.03.20 12:40', 'views': '26', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=003280&amp;nid=415481462&amp;page=11', 'score': 296}]</t>
-        </is>
+          <t>Negative (59%)</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>인연, 팔로잉, 페이퍼, 증권가, 주식은</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>2</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>[{'title': '■인연-팔로잉[14]', 'date': '2026.03.20 10:22', 'views': '403', 'likes': '56', 'dislikes': '4', 'link': '/item/board_read.naver?code=032820&amp;nid=415457811&amp;page=19', 'body': '', 'score': 2083}, {'title': '■페이퍼-증권가[8]', 'date': '2026.03.20 08:09', 'views': '531', 'likes': '54', 'dislikes': '6', 'link': '/item/board_read.naver?code=032820&amp;nid=415430909&amp;page=27', 'body': '', 'score': 2151}, {'title': '■주식은-오르고..내리는건[7]', 'date': '2026.03.20 10:16', 'views': '439', 'likes': '51', 'dislikes': '5', 'link': '/item/board_read.naver?code=032820&amp;nid=415456653&amp;page=19', 'body': '', 'score': 1969}, {'title': '■프매-2~3백만주 매수[2]', 'date': '2026.03.20 09:06', 'views': '426', 'likes': '47', 'dislikes': '7', 'link': '/item/board_read.naver?code=032820&amp;nid=415438984&amp;page=25', 'body': '', 'score': 1836}, {'title': '■우기-매출에 대한 평가', 'date': '2026.03.20 10:44', 'views': '399', 'likes': '46', 'dislikes': '5', 'link': '/item/board_read.naver?code=032820&amp;nid=415461809&amp;page=18', 'body': '', 'score': 1779}, {'title': '■두빌-14만[2]', 'date': '2026.03.20 11:00', 'views': '518', 'likes': '45', 'dislikes': '7', 'link': '/item/board_read.naver?code=032820&amp;nid=415465317&amp;page=17', 'body': '', 'score': 1868}, {'title': '■선빵-2인3각', 'date': '2026.03.20 10:56', 'views': '291', 'likes': '36', 'dislikes': '4', 'link': '/item/board_read.naver?code=032820&amp;nid=415464545&amp;page=17', 'body': '', 'score': 1371}, {'title': '■5일선-터치 시킬려고[1]', 'date': '2026.03.20 09:45', 'views': '335', 'likes': '36', 'dislikes': '2', 'link': '/item/board_read.naver?code=032820&amp;nid=415449390&amp;page=23', 'body': '', 'score': 1415}, {'title': '■쓰리바닥이며는[5]', 'date': '2026.03.20 12:55', 'views': '435', 'likes': '35', 'dislikes': '10', 'link': '/item/board_read.naver?code=032820&amp;nid=415483698&amp;page=13', 'body': '', 'score': 1485}, {'title': '우리기술 오늘은 어찌 될 것 같나요?[4]', 'date': '2026.03.20 08:35', 'views': '583', 'likes': '34', 'dislikes': '4', 'link': '/item/board_read.naver?code=032820&amp;nid=415434436&amp;page=26', 'body': '', 'score': 1603}]</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -3398,69 +3708,77 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>케이뱅크</t>
+          <t>휴림로봇</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6600</v>
+        <v>13890</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>448</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>0.08%</t>
-        </is>
+        <v>-1.46</v>
+      </c>
+      <c r="G41" t="n">
+        <v>162</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>6710</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0.01%</t>
-        </is>
+          <t>7.42%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>14890</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>어우 힘들다[3] / 31일 주총입니다 다들 연장 챙기죠[1] / 하 벌써 20% 마이너스 / 어디까지내려가려나?[1]</t>
+          <t>8.88%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>오늘 15% 이상[1] / 로보스타  장전거래 급등 / 어제 시외털린 개미들[2] / 쳇 지피티 물어보니 결론만 얘기하면[3]</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
           <t>Positive (58%)</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>케이뱅크, 이거, 오늘</t>
-        </is>
-      </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>[{'title': '어우 힘들다[3]', 'date': '2026.03.20 13:41', 'views': '100', 'likes': '21', 'dislikes': '4', 'link': '/item/board_read.naver?code=279570&amp;nid=415490849&amp;page=6', 'score': 730}, {'title': '어디까지내려가려나?[1]', 'date': '2026.03.20 11:50', 'views': '54', 'likes': '10', 'dislikes': '4', 'link': '/item/board_read.naver?code=279570&amp;nid=415474183&amp;page=11', 'score': 354}, {'title': '하 벌써 20% 마이너스', 'date': '2026.03.20 11:29', 'views': '55', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415470622&amp;page=11', 'score': 355}, {'title': '31일 주총입니다 다들 연장 챙기죠[1]', 'date': '2026.03.20 11:21', 'views': '70', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415469038&amp;page=12', 'score': 370}, {'title': '개사기주 입니다', 'date': '2026.03.20 12:49', 'views': '34', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=279570&amp;nid=415482785&amp;page=9', 'score': 304}, {'title': '우리은행.NH투자증권 사외이사 물러나야', 'date': '2026.03.20 14:14', 'views': '38', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415495994&amp;page=5', 'score': 278}, {'title': '국민청원', 'date': '2026.03.20 12:17', 'views': '45', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415478260&amp;page=10', 'score': 285}, {'title': '패가망신.', 'date': '2026.03.20 14:10', 'views': '29', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415495372&amp;page=6', 'score': 239}, {'title': 'Per높다고?', 'date': '2026.03.20 12:34', 'views': '31', 'likes': '7', 'dislikes': '0', 'link': '/item/board_read.naver?code=279570&amp;nid=415480533&amp;page=9', 'score': 241}, {'title': '상장에 받은 10주[1]', 'date': '2026.03.20 12:21', 'views': '113', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=279570&amp;nid=415478760&amp;page=10', 'score': 323}]</t>
-        </is>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>이상, 로보스타, 장전거래, 안티들아, 미안하지만</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>5</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>279570</t>
+          <t>[{'title': '오늘 15% 이상[1]', 'date': '2026.03.20 08:23', 'views': '191', 'likes': '30', 'dislikes': '2', 'link': '/item/board_read.naver?code=090710&amp;nid=415432758&amp;page=8', 'body': '', 'score': 1091}, {'title': '로보스타  장전거래 급등', 'date': '2026.03.20 08:22', 'views': '111', 'likes': '18', 'dislikes': '2', 'link': '/item/board_read.naver?code=090710&amp;nid=415432731&amp;page=8', 'body': '', 'score': 651}, {'title': '안티들아 미안하지만[1]', 'date': '2026.03.20 08:06', 'views': '136', 'likes': '14', 'dislikes': '2', 'link': '/item/board_read.naver?code=090710&amp;nid=415430565&amp;page=9', 'body': '', 'score': 556}, {'title': '어제 시외털린 개미들[2]', 'date': '2026.03.20 08:12', 'views': '181', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=090710&amp;nid=415431415&amp;page=8', 'body': '', 'score': 571}, {'title': '오르는 신호가 아니라', 'date': '2026.03.20 09:16', 'views': '112', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=090710&amp;nid=415441767&amp;page=8', 'body': '', 'score': 442}, {'title': '돈 못버는 사람들의 특징[1]', 'date': '2026.03.20 08:00', 'views': '70', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=090710&amp;nid=415429970&amp;page=9', 'body': '', 'score': 400}, {'title': '개잡주', 'date': '2026.03.20 09:23', 'views': '42', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=090710&amp;nid=415443771&amp;page=7', 'body': '', 'score': 342}, {'title': '단 한주만 사면  바로 물림니다[2]', 'date': '2026.03.20 13:54', 'views': '262', 'likes': '8', 'dislikes': '3', 'link': '/item/board_read.naver?code=090710&amp;nid=415492688&amp;page=2', 'body': '', 'score': 502}, {'title': '쳇 지피티 물어보니 결론만 얘기하면[3]', 'date': '2026.03.20 13:00', 'views': '325', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=090710&amp;nid=415484414&amp;page=2', 'body': '', 'score': 565}, {'title': '지수보지말고  신한증권만', 'date': '2026.03.20 12:08', 'views': '49', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=090710&amp;nid=415476911&amp;page=4', 'body': '', 'score': 289}]</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>090710</t>
         </is>
       </c>
     </row>
@@ -3472,69 +3790,77 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>소룩스</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>28400</v>
+        <v>3760</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-1.90%</t>
+          <t>-9.29%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>582</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>8.20%</t>
-        </is>
+        <v>-0.6</v>
+      </c>
+      <c r="G42" t="n">
+        <v>138</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>28950</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>10.44%</t>
-        </is>
+      <c r="J42" t="n">
+        <v>3810</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>■저 정도면-5일선 단거죠?[11] / ■주말애-사고 싶은거[17] / 오늘도 안타깝게 저의 예측이 맞았네요..ㅠ[17] / ■페이퍼-증권가[8]</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Negative (61%)</t>
+          <t>소룩스가 주인인데 소룩스가 소외된다는 것...[3] / 소룩스 떨어지는 이유 / 차바이오텍 합병 듣고 소룩스 CB받음[1] / 소룩스는 버려지지 않습니다. 이번 딜에서...</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>우리기술, 오늘, ...</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
+          <t>Negative (77%)</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>떨어지는, 이유, 주인인데, 소외된다는, 이런</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>[{'title': '■주말애-사고 싶은거[17]', 'date': '2026.03.20 15:36', 'views': '941', 'likes': '65', 'dislikes': '4', 'link': '/item/board_read.naver?code=032820&amp;nid=415508769&amp;page=4', 'score': 2891}, {'title': '■저 정도면-5일선 단거죠?[11]', 'date': '2026.03.20 15:38', 'views': '1316', 'likes': '57', 'dislikes': '6', 'link': '/item/board_read.naver?code=032820&amp;nid=415509037&amp;page=3', 'score': 3026}, {'title': '■인연-팔로잉[14]', 'date': '2026.03.20 10:22', 'views': '445', 'likes': '56', 'dislikes': '4', 'link': '/item/board_read.naver?code=032820&amp;nid=415457811&amp;page=22', 'score': 2125}, {'title': '■페이퍼-증권가[8]', 'date': '2026.03.20 08:09', 'views': '543', 'likes': '54', 'dislikes': '6', 'link': '/item/board_read.naver?code=032820&amp;nid=415430909&amp;page=29', 'score': 2163}, {'title': '■주식은-오르고..내리는건[7]', 'date': '2026.03.20 10:16', 'views': '468', 'likes': '51', 'dislikes': '5', 'link': '/item/board_read.naver?code=032820&amp;nid=415456653&amp;page=22', 'score': 1998}, {'title': '■두빌-14만[2]', 'date': '2026.03.20 11:00', 'views': '563', 'likes': '48', 'dislikes': '7', 'link': '/item/board_read.naver?code=032820&amp;nid=415465317&amp;page=20', 'score': 2003}, {'title': '■우기-매출에 대한 평가', 'date': '2026.03.20 10:44', 'views': '425', 'likes': '47', 'dislikes': '5', 'link': '/item/board_read.naver?code=032820&amp;nid=415461809&amp;page=21', 'score': 1835}, {'title': '■프매-2~3백만주 매수[2]', 'date': '2026.03.20 09:06', 'views': '438', 'likes': '47', 'dislikes': '7', 'link': '/item/board_read.naver?code=032820&amp;nid=415438984&amp;page=28', 'score': 1848}, {'title': '오늘도 안타깝게 저의 예측이 맞았네요..ㅠ[17]', 'date': '2026.03.20 15:37', 'views': '1450', 'likes': '44', 'dislikes': '1', 'link': '/item/board_read.naver?code=032820&amp;nid=415508951&amp;page=4', 'score': 2770}, {'title': '■쓰리바닥이며는[4]', 'date': '2026.03.20 12:55', 'views': '488', 'likes': '39', 'dislikes': '10', 'link': '/item/board_read.naver?code=032820&amp;nid=415483698&amp;page=16', 'score': 1658}]</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>[{'title': '소룩스 떨어지는 이유', 'date': '2026.03.20 09:45', 'views': '86', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=290690&amp;nid=415449513&amp;page=6', 'body': '', 'score': 446}, {'title': '소룩스가 주인인데 소룩스가 소외된다는 것...[3]', 'date': '2026.03.20 08:22', 'views': '238', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=290690&amp;nid=415432717&amp;page=7', 'body': '', 'score': 598}, {'title': '@@이런 대단 한 스래기 첨본다~상폐가답이다', 'date': '2026.03.20 15:01', 'views': '18', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=290690&amp;nid=415503277&amp;page=1', 'body': '', 'score': 318}, {'title': '누가봐도 소룩스인데?', 'date': '2026.03.20 09:43', 'views': '73', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=290690&amp;nid=415448877&amp;page=6', 'body': '', 'score': 343}, {'title': '2년을 기다린주주만[1]', 'date': '2026.03.20 13:04', 'views': '87', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=290690&amp;nid=415485001&amp;page=3', 'body': '', 'score': 327}, {'title': '월요일 cb납입되면 쏠껴[1]', 'date': '2026.03.20 12:53', 'views': '122', 'likes': '8', 'dislikes': '3', 'link': '/item/board_read.naver?code=290690&amp;nid=415483371&amp;page=3', 'body': '', 'score': 362}, {'title': '소룩스는 버려지지 않습니다. 이번 딜에서...', 'date': '2026.03.20 11:12', 'views': '144', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=290690&amp;nid=415467264&amp;page=4', 'body': '', 'score': 384}, {'title': '차바이오텍 합병 듣고 소룩스 CB받음[1]', 'date': '2026.03.20 09:23', 'views': '152', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=290690&amp;nid=415443699&amp;page=6', 'body': '', 'score': 392}, {'title': '주가조작으로 망할듯', 'date': '2026.03.20 13:27', 'views': '38', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=290690&amp;nid=415488509&amp;page=3', 'body': '', 'score': 248}, {'title': '조막손이든 세력이든 뭔가가 들어오긴 한 ...[1]', 'date': '2026.03.20 10:35', 'views': '174', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=290690&amp;nid=415460266&amp;page=5', 'body': '', 'score': 384}]</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>290690</t>
         </is>
       </c>
     </row>
@@ -3546,365 +3872,77 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>휴림로봇</t>
+          <t>펄어비스</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14020</v>
+        <v>41200</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-10.43%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>200</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>6.97%</t>
-        </is>
+        <v>-0.34</v>
+      </c>
+      <c r="G43" t="n">
+        <v>800</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
+          <t>2.33%</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
           <t>KOSDAQ</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>14330</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>7.42%</t>
-        </is>
+      <c r="J43" t="n">
+        <v>65600</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>휴림로봇, FTSE 스몰캡 지수 신규 편... / 모간이 눈치빨라서[4] / 오늘 15% 이상[1] / 우앙ㆍ290만주를 14020원에 외인...[2]</t>
+          <t>2.67%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Positive (62%)</t>
+          <t>희망찬 소식 알려줄께...플레이스테이션 소식 ...[2] / 대체로 부정적 평가가 나온건 / 유명 게임지에 뉴스 떴다.[1] / 게임 4시간 해본 소감[1]</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>휴림로봇, 어제, 휴림</t>
-        </is>
-      </c>
-      <c r="N43" t="n">
+          <t>Positive (52%)</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>소식, 대체로, 부정적, 희망찬, 알려줄께</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>[{'title': '오늘 15% 이상[1]', 'date': '2026.03.20 08:23', 'views': '196', 'likes': '30', 'dislikes': '2', 'link': '/item/board_read.naver?code=090710&amp;nid=415432758&amp;page=10', 'score': 1096}, {'title': '휴림로봇, FTSE 스몰캡 지수 신규 편...', 'date': '2026.03.20 15:56', 'views': '859', 'likes': '21', 'dislikes': '3', 'link': '/item/board_read.naver?code=090710&amp;nid=415511389&amp;page=2', 'score': 1489}, {'title': '모간이 눈치빨라서[4]', 'date': '2026.03.20 15:51', 'views': '689', 'likes': '20', 'dislikes': '2', 'link': '/item/board_read.naver?code=090710&amp;nid=415510748&amp;page=2', 'score': 1289}, {'title': '다음주 기대 되는구만~~~~~', 'date': '2026.03.20 15:58', 'views': '192', 'likes': '18', 'dislikes': '3', 'link': '/item/board_read.naver?code=090710&amp;nid=415511546&amp;page=2', 'score': 732}, {'title': '로보스타  장전거래 급등', 'date': '2026.03.20 08:22', 'views': '115', 'likes': '18', 'dislikes': '2', 'link': '/item/board_read.naver?code=090710&amp;nid=415432731&amp;page=10', 'score': 655}, {'title': '우앙ㆍ290만주를 14020원에 외인...[2]', 'date': '2026.03.20 17:14', 'views': '610', 'likes': '15', 'dislikes': '4', 'link': '/item/board_read.naver?code=090710&amp;nid=415517298&amp;page=1', 'score': 1060}, {'title': '안티들아 미안하지만[1]', 'date': '2026.03.20 08:06', 'views': '141', 'likes': '14', 'dislikes': '5', 'link': '/item/board_read.naver?code=090710&amp;nid=415430565&amp;page=10', 'score': 561}, {'title': '어제 시외털린 개미들[2]', 'date': '2026.03.20 08:12', 'views': '184', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=090710&amp;nid=415431415&amp;page=10', 'score': 574}, {'title': 'Ai가 분석한 오늘 모간이', 'date': '2026.03.20 16:10', 'views': '685', 'likes': '12', 'dislikes': '0', 'link': '/item/board_read.naver?code=090710&amp;nid=415512751&amp;page=2', 'score': 1045}, {'title': '감보만', 'date': '2026.03.20 15:57', 'views': '150', 'likes': '11', 'dislikes': '3', 'link': '/item/board_read.naver?code=090710&amp;nid=415511420&amp;page=2', 'score': 480}]</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>090710</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>신성이엔지</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>3010</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-2.27%</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>158</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>8.88%</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>3080</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>8.85%</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>에헤라디여[1] / 5년만에 조금 손해보고 나왔다 / 기관,외인 몰빵이네~)와!!시간외 급등~ / 금감원[2]</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Positive (76%)</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>태양광, 오늘, 외인</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>[{'title': '5년만에 조금 손해보고 나왔다', 'date': '2026.03.20 11:31', 'views': '86', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=011930&amp;nid=415470896&amp;page=4', 'score': 386}, {'title': '에헤라디여[1]', 'date': '2026.03.20 15:26', 'views': '260', 'likes': '9', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415507334&amp;page=1', 'score': 530}, {'title': '기관,외인 몰빵이네~)와!!시간외 급등~', 'date': '2026.03.20 17:14', 'views': '124', 'likes': '8', 'dislikes': '3', 'link': '/item/board_read.naver?code=011930&amp;nid=415517289&amp;page=1', 'score': 364}, {'title': '저점높이고있죠잉', 'date': '2026.03.20 11:10', 'views': '61', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415466941&amp;page=5', 'score': 301}, {'title': '이 작은 주식에 외인 빠졌어도 아직 8%넘고', 'date': '2026.03.20 17:54', 'views': '129', 'likes': '7', 'dislikes': '2', 'link': '/item/board_read.naver?code=011930&amp;nid=415519674&amp;page=1', 'score': 339}, {'title': '월요일최소20프로는갈듯', 'date': '2026.03.20 14:17', 'views': '115', 'likes': '7', 'dislikes': '6', 'link': '/item/board_read.naver?code=011930&amp;nid=415496446&amp;page=2', 'score': 325}, {'title': '5년동안', 'date': '2026.03.20 12:36', 'views': '78', 'likes': '7', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415480849&amp;page=4', 'score': 288}, {'title': '금감원[2]', 'date': '2026.03.20 10:47', 'views': '145', 'likes': '7', 'dislikes': '3', 'link': '/item/board_read.naver?code=011930&amp;nid=415462666&amp;page=5', 'score': 355}, {'title': '프로그램 매수 금액이  양선으로 돌아섯다.', 'date': '2026.03.20 11:18', 'views': '71', 'likes': '6', 'dislikes': '3', 'link': '/item/board_read.naver?code=011930&amp;nid=415468523&amp;page=5', 'score': 251}, {'title': '퇴계이황이', 'date': '2026.03.20 11:10', 'views': '37', 'likes': '6', 'dislikes': '1', 'link': '/item/board_read.naver?code=011930&amp;nid=415466907&amp;page=5', 'score': 217}]</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>011930</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>삼성전자우</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>139200</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-3.47%</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>104</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>76.49%</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>144200</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>76.79%</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>이거는 얼마에 주워야됌?[3] / 삼전본주  25만가면[3] / 네마녀관련 리벨런싱된겁니다.[1] / 우선주 괜히삿다[4]</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Positive (60%)</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>우선주, 우선주가, 진짜</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>[{'title': '삼전본주  25만가면[3]', 'date': '2026.03.20 11:56', 'views': '646', 'likes': '21', 'dislikes': '12', 'link': '/item/board_read.naver?code=005935&amp;nid=415475248&amp;page=4', 'score': 1276}, {'title': '네마녀관련 리벨런싱된겁니다.[1]', 'date': '2026.03.20 15:41', 'views': '591', 'likes': '19', 'dislikes': '5', 'link': '/item/board_read.naver?code=005935&amp;nid=415509542&amp;page=1', 'score': 1161}, {'title': '우선주 괜히삿다[4]', 'date': '2026.03.20 14:39', 'views': '453', 'likes': '15', 'dislikes': '5', 'link': '/item/board_read.naver?code=005935&amp;nid=415499789&amp;page=2', 'score': 903}, {'title': '이거는 얼마에 주워야됌?[3]', 'date': '2026.03.20 12:21', 'views': '924', 'likes': '14', 'dislikes': '0', 'link': '/item/board_read.naver?code=005935&amp;nid=415478727&amp;page=4', 'score': 1344}, {'title': '진짜 우선주는 상폐시켜야', 'date': '2026.03.20 13:27', 'views': '110', 'likes': '13', 'dislikes': '3', 'link': '/item/board_read.naver?code=005935&amp;nid=415488525&amp;page=3', 'score': 500}, {'title': '초보들은 우선주가 뭔지도 모른다', 'date': '2026.03.20 14:49', 'views': '352', 'likes': '11', 'dislikes': '2', 'link': '/item/board_read.naver?code=005935&amp;nid=415501372&amp;page=2', 'score': 682}, {'title': '우선주가[2]', 'date': '2026.03.20 14:30', 'views': '267', 'likes': '11', 'dislikes': '4', 'link': '/item/board_read.naver?code=005935&amp;nid=415498427&amp;page=2', 'score': 597}, {'title': '우선주 없애야 할듯', 'date': '2026.03.20 13:30', 'views': '233', 'likes': '11', 'dislikes': '1', 'link': '/item/board_read.naver?code=005935&amp;nid=415489108&amp;page=3', 'score': 563}, {'title': '삼전우만 어디 전쟁났음?', 'date': '2026.03.20 16:04', 'views': '175', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=005935&amp;nid=415512166&amp;page=1', 'score': 475}, {'title': '외국인들 패대기에', 'date': '2026.03.20 15:39', 'views': '174', 'likes': '10', 'dislikes': '2', 'link': '/item/board_read.naver?code=005935&amp;nid=415509179&amp;page=1', 'score': 474}]</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>005935</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>펄어비스</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>41500</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-9.78%</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>800</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>3.09%</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>46000</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2.33%</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>안티할 생각 없습니다. 다만 현실을 직시하...[3] / 저는 걍 들고 갑니다 ㅋㅋ[10] / 스팀 매출 순위, 게임에 대한 평가[4] / 처음부터 공매도세력이 작전한거다.[8]</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Negative (66%)</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>펄어비스, 스팀, 붉은사막</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>[{'title': '처음부터 공매도세력이 작전한거다.[8]', 'date': '2026.03.20 19:41', 'views': '197', 'likes': '20', 'dislikes': '8', 'link': '/item/board_read.naver?code=263750&amp;nid=415525033&amp;page=2', 'score': 797}, {'title': '안티할 생각 없습니다. 다만 현실을 직시하...[3]', 'date': '2026.03.20 19:01', 'views': '265', 'likes': '20', 'dislikes': '3', 'link': '/item/board_read.naver?code=263750&amp;nid=415523055&amp;page=12', 'score': 865}, {'title': '저는 걍 들고 갑니다 ㅋㅋ[10]', 'date': '2026.03.20 19:41', 'views': '292', 'likes': '19', 'dislikes': '6', 'link': '/item/board_read.naver?code=263750&amp;nid=415525032&amp;page=2', 'score': 862}, {'title': '풍월량) 조작감 진짜 최악이다[1]', 'date': '2026.03.20 19:08', 'views': '183', 'likes': '18', 'dislikes': '1', 'link': '/item/board_read.naver?code=263750&amp;nid=415523388&amp;page=10', 'score': 723}, {'title': '성질 급한 나라에선 낮은평점[3]', 'date': '2026.03.20 17:53', 'views': '145', 'likes': '17', 'dislikes': '2', 'link': '/item/board_read.naver?code=263750&amp;nid=415519627&amp;page=27', 'score': 655}, {'title': '어제 지켜보자고 글썼는데[2]', 'date': '2026.03.20 18:06', 'views': '298', 'likes': '16', 'dislikes': '4', 'link': '/item/board_read.naver?code=263750&amp;nid=415520353&amp;page=23', 'score': 778}, {'title': '스팀평가 심각성을 못 느끼시네요[3]', 'date': '2026.03.20 18:05', 'views': '289', 'likes': '16', 'dislikes': '4', 'link': '/item/board_read.naver?code=263750&amp;nid=415520296&amp;page=24', 'score': 769}, {'title': '업데이트만 잘 되면 싸펑급이 될거다[1]', 'date': '2026.03.20 17:42', 'views': '160', 'likes': '16', 'dislikes': '2', 'link': '/item/board_read.naver?code=263750&amp;nid=415518970&amp;page=29', 'score': 640}, {'title': '스팀 매출 순위, 게임에 대한 평가[4]', 'date': '2026.03.20 19:39', 'views': '368', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=263750&amp;nid=415524942&amp;page=3', 'score': 818}, {'title': '스팀 일본 1위로 상승[2]', 'date': '2026.03.20 18:02', 'views': '233', 'likes': '15', 'dislikes': '3', 'link': '/item/board_read.naver?code=263750&amp;nid=415520132&amp;page=25', 'score': 683}]</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
+          <t>[{'title': '희망찬 소식 알려줄께...플레이스테이션 소식 ...[2]', 'date': '2026.03.20 15:20', 'views': '183', 'likes': '12', 'dislikes': '2', 'link': '/item/board_read.naver?code=263750&amp;nid=415506359&amp;page=6', 'body': '', 'score': 543}, {'title': '스팀평가 대체로 부정적[1]', 'date': '2026.03.20 14:49', 'views': '94', 'likes': '10', 'dislikes': '3', 'link': '/item/board_read.naver?code=263750&amp;nid=415501338&amp;page=24', 'body': '', 'score': 394}, {'title': '대체로 부정적 평가가 나온건', 'date': '2026.03.20 14:48', 'views': '263', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=263750&amp;nid=415501241&amp;page=24', 'body': '', 'score': 533}, {'title': '조직이 얼마나 융통성이 없는 회사인지.. 참', 'date': '2026.03.20 14:43', 'views': '95', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=263750&amp;nid=415500374&amp;page=28', 'body': '', 'score': 365}, {'title': '절대 꼬시기에 넘어가지마...호구개미 지킴이', 'date': '2026.03.20 14:31', 'views': '41', 'likes': '9', 'dislikes': '3', 'link': '/item/board_read.naver?code=263750&amp;nid=415498591&amp;page=35', 'body': '', 'score': 311}, {'title': '지극히 개인적인 붉은사막 리뷰[2]', 'date': '2026.03.20 15:18', 'views': '149', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=263750&amp;nid=415505939&amp;page=8', 'body': '', 'score': 389}, {'title': '유명 게임지에 뉴스 떴다.[1]', 'date': '2026.03.20 14:58', 'views': '180', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=263750&amp;nid=415502731&amp;page=19', 'body': '', 'score': 420}, {'title': '김대일씨.. 이게 최선입니까..[2]', 'date': '2026.03.20 14:42', 'views': '100', 'likes': '8', 'dislikes': '0', 'link': '/item/board_read.naver?code=263750&amp;nid=415500251&amp;page=29', 'body': '', 'score': 340}, {'title': '게임 4시간 해본 소감[1]', 'date': '2026.03.20 14:33', 'views': '163', 'likes': '8', 'dislikes': '2', 'link': '/item/board_read.naver?code=263750&amp;nid=415498874&amp;page=34', 'body': '', 'score': 403}, {'title': '이거 싸게 사서 뭐해요...?', 'date': '2026.03.20 14:29', 'views': '46', 'likes': '8', 'dislikes': '1', 'link': '/item/board_read.naver?code=263750&amp;nid=415498275&amp;page=37', 'body': '', 'score': 286}]</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>9.5 (Trigger-Ready &amp; Unified Auth)</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
         <is>
           <t>263750</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>소룩스</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>3700</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>-10.74%</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>148</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>4145</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>0.34%</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>소룩스랑 차백신[4] / 소룩스가 주인인데 소룩스가 소외된다는 것...[3] / 사채회사여?[2] / 뉴스도 안보시나요 ..아리랑 차백신 합병 방향...[1]</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Negative (66%)</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>소룩스, 차백신, 내가</t>
-        </is>
-      </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>[{'title': '소룩스랑 차백신[4]', 'date': '2026.03.20 17:29', 'views': '465', 'likes': '12', 'dislikes': '17', 'link': '/item/board_read.naver?code=290690&amp;nid=415518240&amp;page=1', 'score': 825}, {'title': '@@이런 대단 한 스래기 첨본다~상폐가답이다', 'date': '2026.03.20 15:01', 'views': '44', 'likes': '12', 'dislikes': '3', 'link': '/item/board_read.naver?code=290690&amp;nid=415503277&amp;page=2', 'score': 404}, {'title': '소룩스 떨어지는 이유', 'date': '2026.03.20 09:45', 'views': '90', 'likes': '12', 'dislikes': '1', 'link': '/item/board_read.naver?code=290690&amp;nid=415449513&amp;page=6', 'score': 450}, {'title': '소룩스가 주인인데 소룩스가 소외된다는 것...[3]', 'date': '2026.03.20 08:22', 'views': '242', 'likes': '12', 'dislikes': '4', 'link': '/item/board_read.naver?code=290690&amp;nid=415432717&amp;page=8', 'score': 602}, {'title': '누가봐도 소룩스인데?', 'date': '2026.03.20 09:43', 'views': '78', 'likes': '10', 'dislikes': '0', 'link': '/item/board_read.naver?code=290690&amp;nid=415448877&amp;page=7', 'score': 378}, {'title': '뉴스도 안보시나요 ..아리랑 차백신 합병 방향...[1]', 'date': '2026.03.20 18:39', 'views': '237', 'likes': '9', 'dislikes': '8', 'link': '/item/board_read.naver?code=290690&amp;nid=415521986&amp;page=1', 'score': 507}, {'title': '기대한 내가 ㄷㅅ이지..[1]', 'date': '2026.03.20 16:05', 'views': '137', 'likes': '9', 'dislikes': '0', 'link': '/item/board_read.naver?code=290690&amp;nid=415512228&amp;page=1', 'score': 407}, {'title': '사채회사여?[2]', 'date': '2026.03.20 15:37', 'views': '274', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=290690&amp;nid=415508956&amp;page=1', 'score': 544}, {'title': '신입 많이 받으셨네', 'date': '2026.03.20 15:21', 'views': '59', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=290690&amp;nid=415506515&amp;page=2', 'score': 329}, {'title': '주가조작으로 망할듯', 'date': '2026.03.20 13:27', 'views': '42', 'likes': '9', 'dislikes': '2', 'link': '/item/board_read.naver?code=290690&amp;nid=415488509&amp;page=3', 'score': 312}]</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>290690</t>
         </is>
       </c>
     </row>
